--- a/BaoCao-KiemThu-CareerCompass.xlsx
+++ b/BaoCao-KiemThu-CareerCompass.xlsx
@@ -1643,8 +1643,8 @@
     <mergeCell ref="F8:H8"/>
     <mergeCell ref="F17:H17"/>
     <mergeCell ref="F23:H23"/>
+    <mergeCell ref="F28:H28"/>
     <mergeCell ref="F22:H22"/>
-    <mergeCell ref="F28:H28"/>
     <mergeCell ref="F13:H13"/>
     <mergeCell ref="F30:H30"/>
     <mergeCell ref="F9:H9"/>
@@ -1710,6 +1710,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="30" t="inlineStr">
         <is>
@@ -1838,6 +1839,7 @@
         <v>7</v>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="30" t="inlineStr">
         <is>
@@ -1928,7 +1930,7 @@
       </c>
       <c r="F11" s="33" t="inlineStr">
         <is>
-          <t>calculatePercent_totalZero</t>
+          <t>calculatePercent_whenTotalZero_returnsZero</t>
         </is>
       </c>
       <c r="G11" s="33" t="inlineStr">
@@ -1975,7 +1977,7 @@
       </c>
       <c r="F12" s="36" t="inlineStr">
         <is>
-          <t>calculatePercent_normalCase</t>
+          <t>calculatePercent_roundsToTwoDecimals</t>
         </is>
       </c>
       <c r="G12" s="36" t="inlineStr">
@@ -2022,7 +2024,7 @@
       </c>
       <c r="F13" s="33" t="inlineStr">
         <is>
-          <t>isNodeLocked_tier1Null</t>
+          <t>isNodeLocked_whenTierIsNull_treatsNodeAsTierOne</t>
         </is>
       </c>
       <c r="G13" s="33" t="inlineStr">
@@ -2069,7 +2071,7 @@
       </c>
       <c r="F14" s="36" t="inlineStr">
         <is>
-          <t>isNodeLocked_explicitTier1</t>
+          <t>isNodeLocked_whenTierOne_alwaysUnlocked</t>
         </is>
       </c>
       <c r="G14" s="36" t="inlineStr">
@@ -2116,7 +2118,7 @@
       </c>
       <c r="F15" s="33" t="inlineStr">
         <is>
-          <t>isNodeLocked_tier2AllDone</t>
+          <t>isNodeLocked_whenAllLowerTiersDone_returnsUnlocked</t>
         </is>
       </c>
       <c r="G15" s="33" t="inlineStr">
@@ -2163,7 +2165,7 @@
       </c>
       <c r="F16" s="36" t="inlineStr">
         <is>
-          <t>isNodeLocked_tier2NotDone</t>
+          <t>isNodeLocked_whenLowerTierNotAllDone_returnsLocked</t>
         </is>
       </c>
       <c r="G16" s="36" t="inlineStr">
@@ -2182,7 +2184,7 @@
         </is>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="30" customHeight="1">
       <c r="A17" s="32" t="inlineStr">
         <is>
           <t>isNodeLocked()</t>
@@ -2210,7 +2212,8 @@
       </c>
       <c r="F17" s="33" t="inlineStr">
         <is>
-          <t>isNodeLocked_tier3Tier1NotDone</t>
+          <t>lockExpression_coversConditionCombinations
+[tier 3 bị khóa khi tier 1 chưa xong]</t>
         </is>
       </c>
       <c r="G17" s="33" t="inlineStr">
@@ -2229,7 +2232,7 @@
         </is>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="30" customHeight="1">
       <c r="A18" s="35" t="inlineStr">
         <is>
           <t>isNodeLocked()</t>
@@ -2257,7 +2260,8 @@
       </c>
       <c r="F18" s="36" t="inlineStr">
         <is>
-          <t>isNodeLocked_tier3Tier2NotDone</t>
+          <t>lockExpression_coversConditionCombinations
+[tier 3 bị khóa khi tier 2 chưa xong]</t>
         </is>
       </c>
       <c r="G18" s="36" t="inlineStr">
@@ -2276,7 +2280,7 @@
         </is>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="30" customHeight="1">
       <c r="A19" s="32" t="inlineStr">
         <is>
           <t>isNodeLocked()</t>
@@ -2304,7 +2308,8 @@
       </c>
       <c r="F19" s="33" t="inlineStr">
         <is>
-          <t>isNodeLocked_tier3AllDone</t>
+          <t>lockExpression_coversConditionCombinations
+[tier 3 mở khi tier 1 và tier 2 đã xong]</t>
         </is>
       </c>
       <c r="G19" s="33" t="inlineStr">
@@ -9312,6 +9317,7 @@
           <t>Kiểm thử đơn vị tầng dịch vụ · Kiểm thử hộp đen chương IV · Xây dựng bộ kiểm thử API và giao diện · Khắc phục khiếm khuyết</t>
         </is>
       </c>
+      <c r="C8" s="9" t="n"/>
       <c r="D8" s="6" t="n">
         <v>53</v>
       </c>
@@ -9331,6 +9337,7 @@
           <t>Kiểm thử hộp trắng · Kiểm thử tầng điều khiển · Kiểm thử giá trị biên · Sửa lỗi giao diện · Các báo cáo dạng bảng</t>
         </is>
       </c>
+      <c r="C9" s="9" t="n"/>
       <c r="D9" s="6" t="n">
         <v>19</v>
       </c>
@@ -9350,6 +9357,7 @@
           <t>Thực hiện kiểm thử API và kiểm thử giao diện đầu-cuối, lập báo cáo kết quả · Bản thuyết minh kiểm chứng phần mềm bằng văn bản</t>
         </is>
       </c>
+      <c r="C10" s="9" t="n"/>
       <c r="D10" s="6" t="n">
         <v>2</v>
       </c>
@@ -9405,11 +9413,13 @@
           <t>Tổng hợp bốn tầng kiểm thử, độ bao phủ, số phép kiểm</t>
         </is>
       </c>
+      <c r="C15" s="9" t="n"/>
       <c r="D15" s="5" t="inlineStr">
         <is>
           <t>Nguyễn Thành Phát</t>
         </is>
       </c>
+      <c r="E15" s="9" t="n"/>
       <c r="F15" s="5" t="inlineStr"/>
       <c r="G15" s="5" t="inlineStr"/>
       <c r="H15" s="5" t="inlineStr"/>
@@ -9425,11 +9435,13 @@
           <t>Giá trị biên và phân hoạch lớp tương đương cho biểu mẫu đăng ký; giá trị biên cho dung lượng tệp</t>
         </is>
       </c>
+      <c r="C16" s="9" t="n"/>
       <c r="D16" s="5" t="inlineStr">
         <is>
           <t>Nguyễn Thành Phát · Vòng Minh Quân</t>
         </is>
       </c>
+      <c r="E16" s="9" t="n"/>
       <c r="F16" s="5" t="inlineStr"/>
       <c r="G16" s="5" t="inlineStr"/>
       <c r="H16" s="5" t="inlineStr"/>
@@ -9445,11 +9457,13 @@
           <t>Bảng quyết định — luật chặn cập nhật tiến độ học</t>
         </is>
       </c>
+      <c r="C17" s="9" t="n"/>
       <c r="D17" s="5" t="inlineStr">
         <is>
           <t>Nguyễn Thành Phát</t>
         </is>
       </c>
+      <c r="E17" s="9" t="n"/>
       <c r="F17" s="5" t="inlineStr"/>
       <c r="G17" s="5" t="inlineStr"/>
       <c r="H17" s="5" t="inlineStr"/>
@@ -9465,11 +9479,13 @@
           <t>Bảng quyết định — hiệu lực mã đặt lại mật khẩu</t>
         </is>
       </c>
+      <c r="C18" s="9" t="n"/>
       <c r="D18" s="5" t="inlineStr">
         <is>
           <t>Nguyễn Thành Phát</t>
         </is>
       </c>
+      <c r="E18" s="9" t="n"/>
       <c r="F18" s="5" t="inlineStr"/>
       <c r="G18" s="5" t="inlineStr"/>
       <c r="H18" s="5" t="inlineStr"/>
@@ -9485,11 +9501,13 @@
           <t>Bảng quyết định — định dạng và dung lượng tệp bảng điểm</t>
         </is>
       </c>
+      <c r="C19" s="9" t="n"/>
       <c r="D19" s="5" t="inlineStr">
         <is>
           <t>Nguyễn Thành Phát</t>
         </is>
       </c>
+      <c r="E19" s="9" t="n"/>
       <c r="F19" s="5" t="inlineStr"/>
       <c r="G19" s="5" t="inlineStr"/>
       <c r="H19" s="5" t="inlineStr"/>
@@ -9505,11 +9523,13 @@
           <t>Chuyển đổi trạng thái — tiến độ node kỹ năng</t>
         </is>
       </c>
+      <c r="C20" s="9" t="n"/>
       <c r="D20" s="5" t="inlineStr">
         <is>
           <t>Nguyễn Thành Phát</t>
         </is>
       </c>
+      <c r="E20" s="9" t="n"/>
       <c r="F20" s="5" t="inlineStr"/>
       <c r="G20" s="5" t="inlineStr"/>
       <c r="H20" s="5" t="inlineStr"/>
@@ -9525,11 +9545,13 @@
           <t>Chuyển đổi trạng thái — vòng đời mã đặt lại mật khẩu</t>
         </is>
       </c>
+      <c r="C21" s="9" t="n"/>
       <c r="D21" s="5" t="inlineStr">
         <is>
           <t>Nguyễn Thành Phát</t>
         </is>
       </c>
+      <c r="E21" s="9" t="n"/>
       <c r="F21" s="5" t="inlineStr"/>
       <c r="G21" s="5" t="inlineStr"/>
       <c r="H21" s="5" t="inlineStr"/>
@@ -9545,11 +9567,13 @@
           <t>Chuyển đổi trạng thái — quy trình khai báo hồ sơ</t>
         </is>
       </c>
+      <c r="C22" s="9" t="n"/>
       <c r="D22" s="5" t="inlineStr">
         <is>
           <t>Nguyễn Thành Phát</t>
         </is>
       </c>
+      <c r="E22" s="9" t="n"/>
       <c r="F22" s="5" t="inlineStr"/>
       <c r="G22" s="5" t="inlineStr"/>
       <c r="H22" s="5" t="inlineStr"/>
@@ -9565,11 +9589,13 @@
           <t>Đồ thị dòng điều khiển, độ phức tạp Cyclomatic, 9 đường cơ sở</t>
         </is>
       </c>
+      <c r="C23" s="9" t="n"/>
       <c r="D23" s="5" t="inlineStr">
         <is>
           <t>Vòng Minh Quân</t>
         </is>
       </c>
+      <c r="E23" s="9" t="n"/>
       <c r="F23" s="5" t="inlineStr"/>
       <c r="G23" s="5" t="inlineStr"/>
       <c r="H23" s="5" t="inlineStr"/>
@@ -9585,11 +9611,13 @@
           <t>So sánh bốn mức bao phủ và ma trận tổ hợp điều kiện MC/DC</t>
         </is>
       </c>
+      <c r="C24" s="9" t="n"/>
       <c r="D24" s="5" t="inlineStr">
         <is>
           <t>Vòng Minh Quân</t>
         </is>
       </c>
+      <c r="E24" s="9" t="n"/>
       <c r="F24" s="5" t="inlineStr"/>
       <c r="G24" s="5" t="inlineStr"/>
       <c r="H24" s="5" t="inlineStr"/>
@@ -9605,11 +9633,13 @@
           <t>Độ bao phủ trước và sau khi bổ sung kiểm thử, kèm nhận xét</t>
         </is>
       </c>
+      <c r="C25" s="9" t="n"/>
       <c r="D25" s="5" t="inlineStr">
         <is>
           <t>Vòng Minh Quân</t>
         </is>
       </c>
+      <c r="E25" s="9" t="n"/>
       <c r="F25" s="5" t="inlineStr"/>
       <c r="G25" s="5" t="inlineStr"/>
       <c r="H25" s="5" t="inlineStr"/>
@@ -9625,11 +9655,13 @@
           <t>Độ bao phủ chi tiết theo từng lớp</t>
         </is>
       </c>
+      <c r="C26" s="9" t="n"/>
       <c r="D26" s="5" t="inlineStr">
         <is>
           <t>Vòng Minh Quân</t>
         </is>
       </c>
+      <c r="E26" s="9" t="n"/>
       <c r="F26" s="5" t="inlineStr"/>
       <c r="G26" s="5" t="inlineStr"/>
       <c r="H26" s="5" t="inlineStr"/>
@@ -9645,11 +9677,13 @@
           <t>Danh mục tệp kiểm thử thuộc phạm vi hộp trắng</t>
         </is>
       </c>
+      <c r="C27" s="9" t="n"/>
       <c r="D27" s="5" t="inlineStr">
         <is>
           <t>Vòng Minh Quân</t>
         </is>
       </c>
+      <c r="E27" s="9" t="n"/>
       <c r="F27" s="5" t="inlineStr"/>
       <c r="G27" s="5" t="inlineStr"/>
       <c r="H27" s="5" t="inlineStr"/>
@@ -9665,11 +9699,13 @@
           <t>Kiểm thử API: phân bổ theo nhóm chức năng, phép kiểm, lỗi. Bộ kiểm thử do Nguyễn Thành Phát và Vòng Minh Quân xây dựng</t>
         </is>
       </c>
+      <c r="C28" s="9" t="n"/>
       <c r="D28" s="5" t="inlineStr">
         <is>
           <t>Trần Tô Như Ngọc</t>
         </is>
       </c>
+      <c r="E28" s="9" t="n"/>
       <c r="F28" s="5" t="inlineStr"/>
       <c r="G28" s="5" t="inlineStr"/>
       <c r="H28" s="5" t="inlineStr"/>
@@ -9685,11 +9721,13 @@
           <t>Kiểm thử giao diện đầu-cuối: 17 kịch bản, ma trận truy vết. Bộ kiểm thử do Nguyễn Thành Phát xây dựng</t>
         </is>
       </c>
+      <c r="C29" s="9" t="n"/>
       <c r="D29" s="5" t="inlineStr">
         <is>
           <t>Trần Tô Như Ngọc</t>
         </is>
       </c>
+      <c r="E29" s="9" t="n"/>
       <c r="F29" s="5" t="inlineStr"/>
       <c r="G29" s="5" t="inlineStr"/>
       <c r="H29" s="5" t="inlineStr"/>
@@ -9705,11 +9743,13 @@
           <t>11 khiếm khuyết: mô tả, kỹ thuật phát hiện, cách khắc phục</t>
         </is>
       </c>
+      <c r="C30" s="9" t="n"/>
       <c r="D30" s="5" t="inlineStr">
         <is>
           <t>Nguyễn Thành Phát</t>
         </is>
       </c>
+      <c r="E30" s="9" t="n"/>
       <c r="F30" s="5" t="inlineStr"/>
       <c r="G30" s="5" t="inlineStr"/>
       <c r="H30" s="5" t="inlineStr"/>
@@ -9768,11 +9808,13 @@
           <t>24 lớp kiểm thử, phủ 9 phân hệ nghiệp vụ</t>
         </is>
       </c>
+      <c r="C36" s="9" t="n"/>
       <c r="D36" s="5" t="inlineStr">
         <is>
           <t>Nguyễn Thành Phát</t>
         </is>
       </c>
+      <c r="E36" s="9" t="n"/>
       <c r="F36" s="5" t="inlineStr"/>
       <c r="G36" s="5" t="inlineStr"/>
       <c r="H36" s="5" t="inlineStr"/>
@@ -9788,11 +9830,13 @@
           <t>8 lớp kiểm thử, kèm 2 lớp hỗ trợ CSRF và bảo mật</t>
         </is>
       </c>
+      <c r="C37" s="9" t="n"/>
       <c r="D37" s="5" t="inlineStr">
         <is>
           <t>Vòng Minh Quân</t>
         </is>
       </c>
+      <c r="E37" s="9" t="n"/>
       <c r="F37" s="5" t="inlineStr"/>
       <c r="G37" s="5" t="inlineStr"/>
       <c r="H37" s="5" t="inlineStr"/>
@@ -9808,11 +9852,13 @@
           <t>Đối chiếu loại ngoại lệ với mã trạng thái HTTP</t>
         </is>
       </c>
+      <c r="C38" s="9" t="n"/>
       <c r="D38" s="5" t="inlineStr">
         <is>
           <t>Vòng Minh Quân</t>
         </is>
       </c>
+      <c r="E38" s="9" t="n"/>
       <c r="F38" s="5" t="inlineStr"/>
       <c r="G38" s="5" t="inlineStr"/>
       <c r="H38" s="5" t="inlineStr"/>
@@ -9828,11 +9874,13 @@
           <t>Bốn phần: đơn vị, API, giao diện, kỹ thuật dựa trên kinh nghiệm</t>
         </is>
       </c>
+      <c r="C39" s="9" t="n"/>
       <c r="D39" s="5" t="inlineStr">
         <is>
           <t>Trần Tô Như Ngọc</t>
         </is>
       </c>
+      <c r="E39" s="9" t="n"/>
       <c r="F39" s="5" t="inlineStr"/>
       <c r="G39" s="5" t="inlineStr"/>
       <c r="H39" s="5" t="inlineStr"/>
@@ -9848,11 +9896,13 @@
           <t>Tập lệnh Postman, biến môi trường, bảo đảm chạy lại được nhiều lần</t>
         </is>
       </c>
+      <c r="C40" s="9" t="n"/>
       <c r="D40" s="5" t="inlineStr">
         <is>
           <t>Nguyễn Thành Phát · Vòng Minh Quân</t>
         </is>
       </c>
+      <c r="E40" s="9" t="n"/>
       <c r="F40" s="5" t="inlineStr"/>
       <c r="G40" s="5" t="inlineStr"/>
       <c r="H40" s="5" t="inlineStr"/>
@@ -9868,11 +9918,13 @@
           <t>CodeceptJS và Playwright, mô hình Page Object</t>
         </is>
       </c>
+      <c r="C41" s="9" t="n"/>
       <c r="D41" s="5" t="inlineStr">
         <is>
           <t>Nguyễn Thành Phát</t>
         </is>
       </c>
+      <c r="E41" s="9" t="n"/>
       <c r="F41" s="5" t="inlineStr"/>
       <c r="G41" s="5" t="inlineStr"/>
       <c r="H41" s="5" t="inlineStr"/>
@@ -9888,11 +9940,13 @@
           <t>Lỗi rời trang KCPMS-22, trang cố vấn AI</t>
         </is>
       </c>
+      <c r="C42" s="9" t="n"/>
       <c r="D42" s="5" t="inlineStr">
         <is>
           <t>Vòng Minh Quân</t>
         </is>
       </c>
+      <c r="E42" s="9" t="n"/>
       <c r="F42" s="5" t="inlineStr"/>
       <c r="G42" s="5" t="inlineStr"/>
       <c r="H42" s="5" t="inlineStr"/>
@@ -9908,11 +9962,13 @@
           <t>GitHub Actions, Docker, VPS, chặn deploy khi đỏ</t>
         </is>
       </c>
+      <c r="C43" s="9" t="n"/>
       <c r="D43" s="5" t="inlineStr">
         <is>
           <t>Vòng Minh Quân · Nguyễn Thành Phát</t>
         </is>
       </c>
+      <c r="E43" s="9" t="n"/>
       <c r="F43" s="5" t="inlineStr"/>
       <c r="G43" s="5" t="inlineStr"/>
       <c r="H43" s="5" t="inlineStr"/>
@@ -9928,11 +9984,13 @@
           <t>SonarCloud, JaCoCo, ngưỡng chặn 65% nhánh</t>
         </is>
       </c>
+      <c r="C44" s="9" t="n"/>
       <c r="D44" s="5" t="inlineStr">
         <is>
           <t>Nguyễn Thành Phát</t>
         </is>
       </c>
+      <c r="E44" s="9" t="n"/>
       <c r="F44" s="5" t="inlineStr"/>
       <c r="G44" s="5" t="inlineStr"/>
       <c r="H44" s="5" t="inlineStr"/>
@@ -9948,11 +10006,13 @@
           <t>11 khiếm khuyết, kèm kiểm thử hồi quy</t>
         </is>
       </c>
+      <c r="C45" s="9" t="n"/>
       <c r="D45" s="5" t="inlineStr">
         <is>
           <t>Nguyễn Thành Phát</t>
         </is>
       </c>
+      <c r="E45" s="9" t="n"/>
       <c r="F45" s="5" t="inlineStr"/>
       <c r="G45" s="5" t="inlineStr"/>
       <c r="H45" s="5" t="inlineStr"/>
@@ -9974,9 +10034,9 @@
     <mergeCell ref="A11:H11"/>
     <mergeCell ref="D22:E22"/>
     <mergeCell ref="D40:E40"/>
-    <mergeCell ref="B18:C18"/>
     <mergeCell ref="B27:C27"/>
     <mergeCell ref="D36:E36"/>
+    <mergeCell ref="B18:C18"/>
     <mergeCell ref="D45:E45"/>
     <mergeCell ref="A6:H6"/>
     <mergeCell ref="B43:C43"/>

--- a/BaoCao-KiemThu-CareerCompass.xlsx
+++ b/BaoCao-KiemThu-CareerCompass.xlsx
@@ -33,7 +33,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="26">
+  <fonts count="29">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -159,6 +159,19 @@
       <b val="1"/>
       <color rgb="007F6000"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <color rgb="00808080"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="16">
@@ -367,7 +380,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -544,6 +557,45 @@
     </xf>
     <xf numFmtId="0" fontId="25" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1643,8 +1695,8 @@
     <mergeCell ref="F8:H8"/>
     <mergeCell ref="F17:H17"/>
     <mergeCell ref="F23:H23"/>
+    <mergeCell ref="F22:H22"/>
     <mergeCell ref="F28:H28"/>
-    <mergeCell ref="F22:H22"/>
     <mergeCell ref="F13:H13"/>
     <mergeCell ref="F30:H30"/>
     <mergeCell ref="F9:H9"/>
@@ -1710,7 +1762,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="30" t="inlineStr">
         <is>
@@ -1839,7 +1890,6 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" s="30" t="inlineStr">
         <is>
@@ -13428,17 +13478,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:N47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13451,894 +13507,1746 @@
     <row r="2">
       <c r="A2" s="53" t="inlineStr">
         <is>
-          <t>OnboardingService.saveTranscript(). Bảng thiết kế theo mẫu slide 44, có bước rút gọn rule.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
+          <t>OnboardingService.saveTranscript(). Bảng thiết kế theo mẫu slide 44: bảng đầy đủ trước, bảng rút gọn sau.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
       <c r="A4" s="54" t="inlineStr">
         <is>
-          <t>TỔNG KẾT THI HÀNH — 9 test đã chạy, 9 PASS, 0 fail. 8 test ứng với 8 rule của bảng, 1 test kiểm tra bổ sung ngoài bảng.</t>
+          <t>TỔNG KẾT THI HÀNH — 9 test đã chạy, 9 PASS, 0 fail.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="65" t="inlineStr">
         <is>
           <t>Lớp test trong source</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="65" t="inlineStr">
         <is>
           <t>Số test</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="65" t="inlineStr">
         <is>
           <t>Kỹ thuật áp dụng</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr"/>
-      <c r="E5" s="4" t="inlineStr"/>
-      <c r="F5" s="4" t="inlineStr"/>
-      <c r="G5" s="4" t="inlineStr"/>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="D5" s="65" t="inlineStr"/>
+      <c r="E5" s="65" t="inlineStr"/>
+      <c r="F5" s="65" t="inlineStr"/>
+      <c r="G5" s="65" t="inlineStr"/>
+      <c r="H5" s="65" t="inlineStr"/>
+      <c r="I5" s="65" t="inlineStr"/>
+      <c r="J5" s="65" t="inlineStr"/>
+      <c r="K5" s="65" t="inlineStr"/>
+      <c r="L5" s="65" t="inlineStr"/>
+      <c r="M5" s="65" t="inlineStr"/>
+      <c r="N5" s="65" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="66" t="inlineStr">
         <is>
           <t>TranscriptFileDecisionTableTest</t>
         </is>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B6" s="67" t="n">
         <v>9</v>
       </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>Bảng quyết định · 8 rule</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="13" t="inlineStr">
+      <c r="C6" s="66" t="inlineStr">
+        <is>
+          <t>Bảng quyết định · 24 rule → 8 rule</t>
+        </is>
+      </c>
+      <c r="D6" s="66" t="inlineStr"/>
+      <c r="E6" s="66" t="inlineStr"/>
+      <c r="F6" s="66" t="inlineStr"/>
+      <c r="G6" s="66" t="inlineStr"/>
+      <c r="H6" s="66" t="inlineStr"/>
+      <c r="I6" s="66" t="inlineStr"/>
+      <c r="J6" s="66" t="inlineStr"/>
+      <c r="K6" s="66" t="inlineStr"/>
+      <c r="L6" s="66" t="inlineStr"/>
+      <c r="M6" s="66" t="inlineStr"/>
+      <c r="N6" s="68" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="28" customHeight="1">
+    <row r="7" ht="26" customHeight="1">
       <c r="A7" s="55" t="inlineStr">
         <is>
-          <t>Số test được đối chiếu tự động với target/surefire-reports khi sinh lại sheet bằng tools/gen_sheets_bo_sung.py — source chạy ra số khác thì script dừng và báo lỗi. Chạy lại để kiểm chứng:  mvnw test -Dtest=TranscriptFileDecisionTableTest</t>
+          <t>Số test được đối chiếu tự động với target/surefire-reports khi sinh lại sheet bằng tools/chuan_hoa_sheet_dt_st.py — source chạy ra số khác thì script dừng và báo lỗi. Chạy lại để kiểm chứng:  mvnw test -Dtest=TranscriptFileDecisionTableTest</t>
         </is>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>VÌ SAO CHỌN HÀM NÀY — CON SỐ ĐO ĐƯỢC</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>Chỉ số OnboardingService</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>Trước khi có bảng này</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>Sau khi có bảng này</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr"/>
-      <c r="E10" s="4" t="inlineStr"/>
-      <c r="F10" s="4" t="inlineStr"/>
-      <c r="G10" s="4" t="inlineStr"/>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>Nguồn</t>
+          <t>BẢNG QUYẾT ĐỊNH ĐẦY ĐỦ — mẫu slide 44 · 24 rule = 2 × 6 × 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="26" customHeight="1">
+      <c r="A10" s="55" t="inlineStr">
+        <is>
+          <t>Số rule tối đa = tích số giá trị của các điều kiện. C2 có SÁU giá trị chứ không nhị phân, nên dùng tích số chứ không dùng 2^n. Bảng chia làm hai khối 12 cột cho vừa bề ngang.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>Bao phủ nhánh</t>
-        </is>
-      </c>
-      <c r="B11" s="20" t="inlineStr">
-        <is>
-          <t>75,0 %  (9/12)</t>
-        </is>
-      </c>
-      <c r="C11" s="18" t="inlineStr">
-        <is>
-          <t>100,0 %  (14/14)</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="5" t="inlineStr"/>
-      <c r="G11" s="5" t="inlineStr"/>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>target/site/jacoco/jacoco.csv</t>
+      <c r="A11" s="65" t="inlineStr">
+        <is>
+          <t>Condition / Action</t>
+        </is>
+      </c>
+      <c r="B11" s="65" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="C11" s="65" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="D11" s="65" t="inlineStr">
+        <is>
+          <t>R3</t>
+        </is>
+      </c>
+      <c r="E11" s="65" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
+      <c r="F11" s="65" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
+      <c r="G11" s="65" t="inlineStr">
+        <is>
+          <t>R6</t>
+        </is>
+      </c>
+      <c r="H11" s="65" t="inlineStr">
+        <is>
+          <t>R7</t>
+        </is>
+      </c>
+      <c r="I11" s="65" t="inlineStr">
+        <is>
+          <t>R8</t>
+        </is>
+      </c>
+      <c r="J11" s="65" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="K11" s="65" t="inlineStr">
+        <is>
+          <t>R10</t>
+        </is>
+      </c>
+      <c r="L11" s="65" t="inlineStr">
+        <is>
+          <t>R11</t>
+        </is>
+      </c>
+      <c r="M11" s="65" t="inlineStr">
+        <is>
+          <t>R12</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="inlineStr">
-        <is>
-          <t>Bao phủ dòng</t>
-        </is>
-      </c>
-      <c r="B12" s="20" t="inlineStr">
-        <is>
-          <t>94,7 %  (18/19)</t>
-        </is>
-      </c>
-      <c r="C12" s="18" t="inlineStr">
-        <is>
-          <t>100,0 %  (19/19)</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="5" t="inlineStr"/>
-      <c r="G12" s="5" t="inlineStr"/>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>target/site/jacoco/jacoco.csv</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="56" t="inlineStr">
-        <is>
-          <t>Báo cáo độ bao phủ (docs/coverage/README.md) đã chỉ đích danh: ba nhánh còn thiếu của OnboardingService nằm gọn ở dòng kiểm đuôi tệp, vì MỌI test trước đây đều đặt tên tệp là 'transcript.pdf' — ba nhánh .png, .jpg, .jpeg chưa bao giờ được thử. Mẫu số tăng từ 12 lên 14 vì bản sửa DEF-011 thêm một nhánh mới.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>BẢNG QUYẾT ĐỊNH ĐẦY ĐỦ — mẫu slide 44 · 8 rule sau khi rút gọn</t>
+      <c r="A12" s="66" t="inlineStr">
+        <is>
+          <t>C1 · Tên tệp = null</t>
+        </is>
+      </c>
+      <c r="B12" s="69" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="C12" s="69" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D12" s="69" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E12" s="69" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F12" s="69" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G12" s="69" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H12" s="69" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I12" s="69" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J12" s="69" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K12" s="69" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L12" s="69" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M12" s="69" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="66" t="inlineStr">
+        <is>
+          <t>C2 · Đuôi tệp</t>
+        </is>
+      </c>
+      <c r="B13" s="69" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="C13" s="69" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="D13" s="69" t="inlineStr">
+        <is>
+          <t>.png</t>
+        </is>
+      </c>
+      <c r="E13" s="69" t="inlineStr">
+        <is>
+          <t>.png</t>
+        </is>
+      </c>
+      <c r="F13" s="69" t="inlineStr">
+        <is>
+          <t>.jpg</t>
+        </is>
+      </c>
+      <c r="G13" s="69" t="inlineStr">
+        <is>
+          <t>.jpg</t>
+        </is>
+      </c>
+      <c r="H13" s="69" t="inlineStr">
+        <is>
+          <t>.jpeg</t>
+        </is>
+      </c>
+      <c r="I13" s="69" t="inlineStr">
+        <is>
+          <t>.jpeg</t>
+        </is>
+      </c>
+      <c r="J13" s="69" t="inlineStr">
+        <is>
+          <t>khác</t>
+        </is>
+      </c>
+      <c r="K13" s="69" t="inlineStr">
+        <is>
+          <t>khác</t>
+        </is>
+      </c>
+      <c r="L13" s="69" t="inlineStr">
+        <is>
+          <t>không có dấu chấm</t>
+        </is>
+      </c>
+      <c r="M13" s="69" t="inlineStr">
+        <is>
+          <t>không có dấu chấm</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="66" t="inlineStr">
+        <is>
+          <t>C3 · Dung lượng ≤ 10MB</t>
+        </is>
+      </c>
+      <c r="B14" s="69" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="C14" s="69" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D14" s="69" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E14" s="69" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F14" s="69" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G14" s="69" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H14" s="69" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I14" s="69" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J14" s="69" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K14" s="69" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L14" s="69" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M14" s="69" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="70" t="inlineStr">
+        <is>
+          <t>A1 · Lưu tệp, trả đường dẫn</t>
+        </is>
+      </c>
+      <c r="B15" s="67" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C15" s="67" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="D15" s="67" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E15" s="67" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F15" s="67" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G15" s="67" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="H15" s="67" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I15" s="67" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J15" s="67" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="K15" s="67" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="L15" s="67" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M15" s="67" t="inlineStr">
+        <is>
+          <t>–</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="70" t="inlineStr">
+        <is>
+          <t>A2 · Lỗi "Tên file không hợp lệ"</t>
+        </is>
+      </c>
+      <c r="B16" s="71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C16" s="71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D16" s="71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E16" s="71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F16" s="71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="G16" s="71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H16" s="71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I16" s="71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J16" s="71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K16" s="71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L16" s="71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M16" s="71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="70" t="inlineStr">
+        <is>
+          <t>A3 · Lỗi "Vượt quá dung lượng 10MB"</t>
+        </is>
+      </c>
+      <c r="B17" s="67" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C17" s="67" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="D17" s="67" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E17" s="67" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F17" s="67" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G17" s="67" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="H17" s="67" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I17" s="67" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J17" s="67" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="K17" s="67" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="L17" s="67" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M17" s="67" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="70" t="inlineStr">
+        <is>
+          <t>A4 · Lỗi "Chỉ chấp nhận PDF, PNG hoặc JPG"</t>
+        </is>
+      </c>
+      <c r="B18" s="67" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C18" s="67" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="D18" s="67" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E18" s="67" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F18" s="67" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G18" s="67" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="H18" s="67" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I18" s="67" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J18" s="67" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="K18" s="67" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="L18" s="67" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M18" s="67" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="65" t="inlineStr">
         <is>
           <t>Condition / Action</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>R3</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>R4</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>R5</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>R6</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>R7</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="B20" s="65" t="inlineStr">
+        <is>
+          <t>R13</t>
+        </is>
+      </c>
+      <c r="C20" s="65" t="inlineStr">
+        <is>
+          <t>R14</t>
+        </is>
+      </c>
+      <c r="D20" s="65" t="inlineStr">
+        <is>
+          <t>R15</t>
+        </is>
+      </c>
+      <c r="E20" s="65" t="inlineStr">
+        <is>
+          <t>R16</t>
+        </is>
+      </c>
+      <c r="F20" s="65" t="inlineStr">
+        <is>
+          <t>R17</t>
+        </is>
+      </c>
+      <c r="G20" s="65" t="inlineStr">
+        <is>
+          <t>R18</t>
+        </is>
+      </c>
+      <c r="H20" s="65" t="inlineStr">
+        <is>
+          <t>R19</t>
+        </is>
+      </c>
+      <c r="I20" s="65" t="inlineStr">
+        <is>
+          <t>R20</t>
+        </is>
+      </c>
+      <c r="J20" s="65" t="inlineStr">
+        <is>
+          <t>R21</t>
+        </is>
+      </c>
+      <c r="K20" s="65" t="inlineStr">
+        <is>
+          <t>R22</t>
+        </is>
+      </c>
+      <c r="L20" s="65" t="inlineStr">
+        <is>
+          <t>R23</t>
+        </is>
+      </c>
+      <c r="M20" s="65" t="inlineStr">
+        <is>
+          <t>R24</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="66" t="inlineStr">
         <is>
           <t>C1 · Tên tệp = null</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B21" s="69" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C21" s="69" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D21" s="69" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E21" s="69" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F21" s="69" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G21" s="69" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H21" s="69" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I21" s="69" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J21" s="69" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K21" s="69" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L21" s="69" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M21" s="69" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="66" t="inlineStr">
+        <is>
+          <t>C2 · Đuôi tệp</t>
+        </is>
+      </c>
+      <c r="B22" s="69" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="C22" s="69" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="D22" s="69" t="inlineStr">
+        <is>
+          <t>.png</t>
+        </is>
+      </c>
+      <c r="E22" s="69" t="inlineStr">
+        <is>
+          <t>.png</t>
+        </is>
+      </c>
+      <c r="F22" s="69" t="inlineStr">
+        <is>
+          <t>.jpg</t>
+        </is>
+      </c>
+      <c r="G22" s="69" t="inlineStr">
+        <is>
+          <t>.jpg</t>
+        </is>
+      </c>
+      <c r="H22" s="69" t="inlineStr">
+        <is>
+          <t>.jpeg</t>
+        </is>
+      </c>
+      <c r="I22" s="69" t="inlineStr">
+        <is>
+          <t>.jpeg</t>
+        </is>
+      </c>
+      <c r="J22" s="69" t="inlineStr">
+        <is>
+          <t>khác</t>
+        </is>
+      </c>
+      <c r="K22" s="69" t="inlineStr">
+        <is>
+          <t>khác</t>
+        </is>
+      </c>
+      <c r="L22" s="69" t="inlineStr">
+        <is>
+          <t>không có dấu chấm</t>
+        </is>
+      </c>
+      <c r="M22" s="69" t="inlineStr">
+        <is>
+          <t>không có dấu chấm</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="66" t="inlineStr">
+        <is>
+          <t>C3 · Dung lượng ≤ 10MB</t>
+        </is>
+      </c>
+      <c r="B23" s="69" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C23" s="69" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D23" s="69" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E23" s="69" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="F23" s="69" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G23" s="69" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr">
+      <c r="H23" s="69" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I23" s="69" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="J23" s="69" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K23" s="69" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="H17" s="6" t="inlineStr">
+      <c r="L23" s="69" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="M23" s="69" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="70" t="inlineStr">
+        <is>
+          <t>A1 · Lưu tệp, trả đường dẫn</t>
+        </is>
+      </c>
+      <c r="B24" s="71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C24" s="67" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="D24" s="71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E24" s="67" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F24" s="71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="G24" s="67" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="H24" s="71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I24" s="67" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J24" s="67" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="K24" s="67" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="L24" s="67" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M24" s="67" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="70" t="inlineStr">
+        <is>
+          <t>A2 · Lỗi "Tên file không hợp lệ"</t>
+        </is>
+      </c>
+      <c r="B25" s="67" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C25" s="67" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="D25" s="67" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E25" s="67" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F25" s="67" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G25" s="67" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="H25" s="67" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I25" s="67" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J25" s="67" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="K25" s="67" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="L25" s="67" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M25" s="67" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="70" t="inlineStr">
+        <is>
+          <t>A3 · Lỗi "Vượt quá dung lượng 10MB"</t>
+        </is>
+      </c>
+      <c r="B26" s="67" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C26" s="71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D26" s="67" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E26" s="71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F26" s="67" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G26" s="71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H26" s="67" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I26" s="71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J26" s="67" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="K26" s="67" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="L26" s="67" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M26" s="67" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="70" t="inlineStr">
+        <is>
+          <t>A4 · Lỗi "Chỉ chấp nhận PDF, PNG hoặc JPG"</t>
+        </is>
+      </c>
+      <c r="B27" s="67" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C27" s="67" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="D27" s="67" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E27" s="67" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="F27" s="67" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G27" s="67" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="H27" s="67" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I27" s="67" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J27" s="71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K27" s="71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L27" s="71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M27" s="71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="24" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>BẢNG SAU KHI RÚT GỌN — bước 6 slide 42 · 24 rule → 8 rule</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="65" t="inlineStr">
+        <is>
+          <t>Condition / Action</t>
+        </is>
+      </c>
+      <c r="B30" s="65" t="inlineStr">
+        <is>
+          <t>R1'</t>
+        </is>
+      </c>
+      <c r="C30" s="65" t="inlineStr">
+        <is>
+          <t>R2'</t>
+        </is>
+      </c>
+      <c r="D30" s="65" t="inlineStr">
+        <is>
+          <t>R3'</t>
+        </is>
+      </c>
+      <c r="E30" s="65" t="inlineStr">
+        <is>
+          <t>R4'</t>
+        </is>
+      </c>
+      <c r="F30" s="65" t="inlineStr">
+        <is>
+          <t>R5'</t>
+        </is>
+      </c>
+      <c r="G30" s="65" t="inlineStr">
+        <is>
+          <t>R6'</t>
+        </is>
+      </c>
+      <c r="H30" s="65" t="inlineStr">
+        <is>
+          <t>R7'</t>
+        </is>
+      </c>
+      <c r="I30" s="65" t="inlineStr">
+        <is>
+          <t>R8'</t>
+        </is>
+      </c>
+      <c r="J30" s="65" t="inlineStr">
+        <is>
+          <t>Ghi chú</t>
+        </is>
+      </c>
+      <c r="K30" s="8" t="n"/>
+      <c r="L30" s="8" t="n"/>
+      <c r="M30" s="8" t="n"/>
+      <c r="N30" s="9" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="66" t="inlineStr">
+        <is>
+          <t>C1 · Tên tệp = null</t>
+        </is>
+      </c>
+      <c r="B31" s="69" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="C31" s="69" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D31" s="69" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E31" s="69" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F31" s="69" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G31" s="69" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H31" s="69" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I31" s="69" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J31" s="77" t="inlineStr">
+        <is>
+          <t>2 giá trị</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="66" t="inlineStr">
         <is>
           <t>C2 · Đuôi tệp</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B32" s="72" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C32" s="69" t="inlineStr">
         <is>
           <t>.pdf</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D32" s="69" t="inlineStr">
         <is>
           <t>.png</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="E32" s="69" t="inlineStr">
         <is>
           <t>.jpg</t>
         </is>
       </c>
-      <c r="F18" s="6" t="inlineStr">
+      <c r="F32" s="69" t="inlineStr">
         <is>
           <t>.jpeg</t>
         </is>
       </c>
-      <c r="G18" s="6" t="inlineStr">
+      <c r="G32" s="69" t="inlineStr">
         <is>
           <t>hợp lệ</t>
         </is>
       </c>
-      <c r="H18" s="6" t="inlineStr">
+      <c r="H32" s="69" t="inlineStr">
         <is>
           <t>khác</t>
         </is>
       </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="I32" s="69" t="inlineStr">
+        <is>
+          <t>không có dấu chấm</t>
+        </is>
+      </c>
+      <c r="J32" s="77" t="inlineStr">
+        <is>
+          <t>6 giá trị — đây là lý do dùng tích số chứ không dùng 2^n</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="66" t="inlineStr">
         <is>
           <t>C3 · Dung lượng ≤ 10MB</t>
         </is>
       </c>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="B33" s="72" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C33" s="69" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D33" s="69" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="E33" s="69" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F19" s="6" t="inlineStr">
+      <c r="F33" s="69" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="G19" s="6" t="inlineStr">
+      <c r="G33" s="69" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="H19" s="6" t="inlineStr">
+      <c r="H33" s="72" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="10" t="inlineStr">
+      <c r="I33" s="72" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J33" s="77" t="inlineStr">
+        <is>
+          <t>2 giá trị</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="70" t="inlineStr">
         <is>
           <t>A1 · Lưu tệp, trả đường dẫn</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B34" s="67" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C34" s="71" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D34" s="71" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="E20" s="6" t="inlineStr">
+      <c r="E34" s="71" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="F20" s="6" t="inlineStr">
+      <c r="F34" s="71" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="G20" s="6" t="inlineStr">
+      <c r="G34" s="67" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="H20" s="6" t="inlineStr">
+      <c r="H34" s="67" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="10" t="inlineStr">
-        <is>
-          <t>A2 · Lỗi 'Tên file không hợp lệ'</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="I34" s="67" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="70" t="inlineStr">
+        <is>
+          <t>A2 · Lỗi "Tên file không hợp lệ"</t>
+        </is>
+      </c>
+      <c r="B35" s="71" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C35" s="67" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D35" s="67" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="E35" s="67" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="F21" s="6" t="inlineStr">
+      <c r="F35" s="67" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="G21" s="6" t="inlineStr">
+      <c r="G35" s="67" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="H21" s="6" t="inlineStr">
+      <c r="H35" s="67" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="10" t="inlineStr">
-        <is>
-          <t>A3 · Lỗi 'Vượt quá 10MB'</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="I35" s="67" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+    </row>
+    <row r="36">
+      <c r="A36" s="70" t="inlineStr">
+        <is>
+          <t>A3 · Lỗi "Vượt quá dung lượng 10MB"</t>
+        </is>
+      </c>
+      <c r="B36" s="67" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="C36" s="67" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="E22" s="6" t="inlineStr">
+      <c r="D36" s="67" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="F22" s="6" t="inlineStr">
+      <c r="E36" s="67" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="G22" s="6" t="inlineStr">
+      <c r="F36" s="67" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G36" s="71" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="H22" s="6" t="inlineStr">
+      <c r="H36" s="67" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="10" t="inlineStr">
-        <is>
-          <t>A4 · Lỗi 'Chỉ chấp nhận PDF, PNG hoặc JPG'</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="I36" s="67" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+    </row>
+    <row r="37">
+      <c r="A37" s="70" t="inlineStr">
+        <is>
+          <t>A4 · Lỗi "Chỉ chấp nhận PDF, PNG hoặc JPG"</t>
+        </is>
+      </c>
+      <c r="B37" s="67" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="C37" s="67" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="D37" s="67" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="F23" s="6" t="inlineStr">
+      <c r="E37" s="67" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="G23" s="6" t="inlineStr">
+      <c r="F37" s="67" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="H23" s="6" t="inlineStr">
+      <c r="G37" s="67" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="H37" s="71" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="10" t="inlineStr">
+      <c r="I37" s="71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J37" s="77" t="inlineStr">
+        <is>
+          <t>R8' là cột phát hiện khiếm khuyết DEF-011</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="70" t="inlineStr">
         <is>
           <t>Kết quả chạy test</t>
         </is>
       </c>
-      <c r="B24" s="13" t="inlineStr">
+      <c r="B38" s="68" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="C24" s="13" t="inlineStr">
+      <c r="C38" s="68" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="D24" s="13" t="inlineStr">
+      <c r="D38" s="68" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="E24" s="13" t="inlineStr">
+      <c r="E38" s="68" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="F24" s="13" t="inlineStr">
+      <c r="F38" s="68" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="G24" s="13" t="inlineStr">
+      <c r="G38" s="68" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="H24" s="13" t="inlineStr">
+      <c r="H38" s="68" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="10" t="inlineStr">
+      <c r="I38" s="68" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="70" t="inlineStr">
         <is>
           <t>Method trong code</t>
         </is>
       </c>
-      <c r="B25" s="58" t="inlineStr">
+      <c r="B39" s="73" t="inlineStr">
         <is>
           <t>rule1_tenTepNull_tuChoi</t>
         </is>
       </c>
-      <c r="C25" s="58" t="inlineStr">
+      <c r="C39" s="73" t="inlineStr">
         <is>
           <t>rule2_duoiPdf_luuThanhCong</t>
         </is>
       </c>
-      <c r="D25" s="58" t="inlineStr">
+      <c r="D39" s="73" t="inlineStr">
         <is>
           <t>rule3_duoiPng_luuThanhCong</t>
         </is>
       </c>
-      <c r="E25" s="58" t="inlineStr">
+      <c r="E39" s="73" t="inlineStr">
         <is>
           <t>rule4_duoiJpg_luuThanhCong</t>
         </is>
       </c>
-      <c r="F25" s="58" t="inlineStr">
+      <c r="F39" s="73" t="inlineStr">
         <is>
           <t>rule5_duoiJpeg_luuThanhCong</t>
         </is>
       </c>
-      <c r="G25" s="58" t="inlineStr">
+      <c r="G39" s="73" t="inlineStr">
         <is>
           <t>rule6_duoiHopLe_dungLuongQuaLon_tuChoi</t>
         </is>
       </c>
-      <c r="H25" s="58" t="inlineStr">
+      <c r="H39" s="73" t="inlineStr">
         <is>
           <t>rule7_duoiKhongHopLe_tuChoi</t>
         </is>
       </c>
-    </row>
-    <row r="26" ht="24" customHeight="1">
-      <c r="A26" s="59" t="inlineStr">
-        <is>
-          <t>RULE R8 — CỘT TÁCH RIÊNG VÌ NÓ BUỘC PHẢI SỬA MỘT KHIẾM KHUYẾT</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>Condition / Action</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>R8</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>Hành vi TRƯỚC khi sửa</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>Hành vi SAU khi sửa</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr"/>
-      <c r="F27" s="4" t="inlineStr"/>
-      <c r="G27" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="H27" s="4" t="inlineStr">
-        <is>
-          <t>Method trong code</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>C1 · Tên tệp = null</t>
-        </is>
-      </c>
-      <c r="B28" s="20" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="inlineStr"/>
-      <c r="D28" s="5" t="inlineStr"/>
-      <c r="E28" s="5" t="inlineStr"/>
-      <c r="F28" s="5" t="inlineStr"/>
-      <c r="G28" s="6" t="inlineStr"/>
-      <c r="H28" s="58" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>C2 · Đuôi tệp</t>
-        </is>
-      </c>
-      <c r="B29" s="20" t="inlineStr">
-        <is>
-          <t>không có dấu chấm</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr"/>
-      <c r="D29" s="5" t="inlineStr"/>
-      <c r="E29" s="5" t="inlineStr"/>
-      <c r="F29" s="5" t="inlineStr"/>
-      <c r="G29" s="6" t="inlineStr"/>
-      <c r="H29" s="58" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>C3 · Dung lượng ≤ 10MB</t>
-        </is>
-      </c>
-      <c r="B30" s="20" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="inlineStr"/>
-      <c r="D30" s="5" t="inlineStr"/>
-      <c r="E30" s="5" t="inlineStr"/>
-      <c r="F30" s="5" t="inlineStr"/>
-      <c r="G30" s="6" t="inlineStr"/>
-      <c r="H30" s="58" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="10" t="inlineStr">
-        <is>
-          <t>A4 · Lỗi 'Chỉ chấp nhận PDF, PNG hoặc JPG'</t>
-        </is>
-      </c>
-      <c r="B31" s="20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C31" s="25" t="inlineStr">
-        <is>
-          <t>StringIndexOutOfBoundsException → lỗi 500</t>
-        </is>
-      </c>
-      <c r="D31" s="60" t="inlineStr">
-        <is>
-          <t>IllegalArgumentException → lỗi 400</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="inlineStr"/>
-      <c r="F31" s="5" t="inlineStr"/>
-      <c r="G31" s="13" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H31" s="58" t="inlineStr">
+      <c r="I39" s="73" t="inlineStr">
         <is>
           <t>rule8_tenTepKhongCoDuoi_tuChoi</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="24" customHeight="1">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>GHI CHÚ TRUNG THỰC VỀ DEF-011 — AI PHÁT HIỆN, AI SỬA</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="42" customHeight="1">
-      <c r="A34" s="56" t="inlineStr">
-        <is>
-          <t>Bảng quyết định KHÔNG phải nơi phát hiện lỗi này. Test hộp trắng OnboardingServiceTest đã ghi đúng nguyên nhân từ trước, nguyên văn trong mã nguồn: "BUG?: filename thiếu phần mở rộng (vd 'resume') làm substring(lastIndexOf('.')) với index=-1 ném StringIndexOutOfBoundsException. Nên guard lastIndexOf('.') &lt; 0 để trả IllegalArgumentException cho đồng nhất."</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="42" customHeight="1">
-      <c r="A35" s="56" t="inlineStr">
-        <is>
-          <t>Nhưng chính test đó lại CHỐT HÀNH VI LỖI: assertThatThrownBy(...).isInstanceOf(StringIndexOutOfBoundsException.class). Bộ test vì thế vẫn xanh, và khiếm khuyết nằm im suốt thời gian đó — một ghi chú 'BUG?' có thể sống mãi trong mã nguồn mà không ai bị buộc phải xử lý.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="42" customHeight="1">
-      <c r="A36" s="56" t="inlineStr">
-        <is>
-          <t>ĐÓNG GÓP THẬT CỦA KỸ THUẬT NÀY là buộc phải sửa: mỗi cột của bảng quyết định phải ứng với một hành động xác định trong nhóm A1–A4. Không thể để một ô là 'sập 500'. Một ô trống trong bảng quyết định thì không sống sót qua khâu duyệt như một dòng chú thích.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="42" customHeight="1">
-      <c r="A37" s="56" t="inlineStr">
-        <is>
-          <t>Kiểm chứng: chạy test R8 trên bản mã CHƯA sửa → đỏ (nhận StringIndexOutOfBoundsException). Chạy trên bản đã sửa → xanh. Test cũ trong OnboardingServiceTest cũng đã được đổi sang khẳng định hành vi ĐÚNG thay vì khoá hành vi lỗi.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="24" customHeight="1">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>VỀ SỐ RULE — VÌ SAO 24 RÚT CÒN 8</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="42" customHeight="1">
-      <c r="A40" s="56" t="inlineStr">
-        <is>
-          <t>Số rule tối đa = 2 (C1) × 6 (C2) × 2 (C3) = 24. Khác hai bảng quyết định trước, ở đây điều kiện C2 có SÁU giá trị chứ không nhị phân, nên công thức 2^n không dùng được — phải NHÂN số giá trị của từng điều kiện, đúng như bảng ProgressService ở sheet 03 (3 × 2 = 6).</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="42" customHeight="1">
-      <c r="A41" s="56" t="inlineStr">
-        <is>
-          <t>Rút gọn về 8 nhờ mã nguồn kiểm ba điều kiện TUẦN TỰ và thoát ngay khi gặp lỗi: khi một điều kiện phía trước đã quyết định kết quả thì các điều kiện phía sau thành 'không quan tâm' (dấu –). R1 gộp 12 tổ hợp (tên null thì đuôi và dung lượng vô nghĩa); R7 và R8 mỗi cột gộp 2 tổ hợp (đuôi sai thì chặn trước khi tới phép kiểm dung lượng).</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="42" customHeight="1">
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="55" t="inlineStr">
+        <is>
+          <t>Ô tô vàng là ô "không quan tâm" (–) sinh ra khi gộp rule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="44" customHeight="1">
       <c r="A42" s="56" t="inlineStr">
         <is>
-          <t>R6 LÀ RULE GỘP THEO KIỂU KHÁC: bốn đuôi hợp lệ khi vượt dung lượng đều cho cùng một hành động, nên bốn rule con thu về một, ô C2 ghi 'hợp lệ' thay vì một đuôi cụ thể. Đây đúng là bước rút gọn bảng quyết định của chương IV — giống cách sheet 03b gộp R2, R3, R4.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="42" customHeight="1">
+          <t>VÌ SAO GỘP ĐƯỢC: mã nguồn kiểm ba điều kiện TUẦN TỰ và thoát ngay khi gặp lỗi. Khi một điều kiện phía trước đã quyết định kết quả thì điều kiện phía sau không còn ảnh hưởng, đánh dấu "–". R1' gộp 12 rule (tên tệp null thì đuôi và dung lượng vô nghĩa); R7' và R8' mỗi cột gộp 2 rule (đuôi sai thì chặn trước khi xét dung lượng).</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="44" customHeight="1">
       <c r="A43" s="56" t="inlineStr">
         <is>
-          <t>QUAN HỆ VỚI SHEET GIÁ TRỊ BIÊN: điều kiện C3 ở bảng này chỉ lấy giá trị NOMINAL (1 byte và 11 MB) để phân biệt nhánh. Các giá trị sát biên 10 MB (max-1, max, max+1) thuộc về OnboardingFileSizeBvaTest ở sheet 01. Hai kỹ thuật bổ sung nhau chứ không trùng: bảng quyết định hỏi 'tổ hợp nào dẫn tới hành động nào', giá trị biên hỏi 'lằn ranh nằm chính xác ở đâu'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="24" customHeight="1">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>KIỂM TRA BỔ SUNG — ngoài bảng quyết định</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="4" t="inlineStr">
-        <is>
-          <t>Trường hợp</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="inlineStr">
-        <is>
-          <t>Đầu vào</t>
-        </is>
-      </c>
-      <c r="C46" s="4" t="inlineStr">
-        <is>
-          <t>Expected Output</t>
-        </is>
-      </c>
-      <c r="D46" s="4" t="inlineStr"/>
-      <c r="E46" s="4" t="inlineStr"/>
-      <c r="F46" s="4" t="inlineStr">
-        <is>
-          <t>Kết quả thực tế</t>
-        </is>
-      </c>
-      <c r="G46" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="H46" s="4" t="inlineStr">
-        <is>
-          <t>Method trong code</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="5" t="inlineStr">
-        <is>
-          <t>Đuôi viết HOA</t>
-        </is>
-      </c>
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>BANGDIEM.PDF</t>
-        </is>
-      </c>
-      <c r="C47" s="5" t="inlineStr">
-        <is>
-          <t>Được chấp nhận (mã gọi toLowerCase)</t>
-        </is>
-      </c>
-      <c r="D47" s="5" t="inlineStr"/>
-      <c r="E47" s="5" t="inlineStr"/>
-      <c r="F47" s="5" t="inlineStr">
-        <is>
-          <t>Đúng như mong đợi</t>
-        </is>
-      </c>
-      <c r="G47" s="13" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H47" s="5" t="inlineStr">
-        <is>
-          <t>boSung_duoiVietHoa_duocChapNhan</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="26" customHeight="1">
-      <c r="A48" s="55" t="inlineStr">
-        <is>
-          <t>Không đưa vào bảng vì đây là biến thể TRÌNH BÀY của C2, không phải rule độc lập: nếu tách ra thì bảng phải nhân đôi số cột mà không sinh thêm hành động mới nào.</t>
+          <t>R6' GỘP THEO KIỂU KHÁC: bốn đuôi hợp lệ khi vượt dung lượng đều cho cùng một hành động, nên bốn rule con thu về một, ô C2 ghi "hợp lệ" thay vì một đuôi cụ thể.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="44" customHeight="1">
+      <c r="A44" s="56" t="inlineStr">
+        <is>
+          <t>KHIẾM KHUYẾT DEF-011 — cột R8'. Tệp không có dấu chấm làm lastIndexOf(".") trả -1, kéo theo substring(-1) ném StringIndexOutOfBoundsException, người dùng nhận lỗi 500 thay vì thông báo 400. Nói rõ để không nhận công sai: test hộp trắng đã ghi đúng nguyên nhân từ trước nhưng lại CHỐT hành vi lỗi bằng một khẳng định, nên bộ test vẫn xanh. Đóng góp của kỹ thuật này là BUỘC PHẢI SỬA — mỗi cột của bảng phải ứng với một hành động xác định trong nhóm A1–A4, không thể để một ô là "sập 500".</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="44" customHeight="1">
+      <c r="A45" s="56" t="inlineStr">
+        <is>
+          <t>CON SỐ ĐO ĐƯỢC: nhánh OnboardingService 75,0% (9/12) → 100,0% (14/14); dòng 94,7% (18/19) → 100,0% (19/19). Nguồn: target/site/jacoco/jacoco.csv.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="44" customHeight="1">
+      <c r="A46" s="56" t="inlineStr">
+        <is>
+          <t>QUAN HỆ VỚI SHEET GIÁ TRỊ BIÊN: điều kiện C3 ở bảng này chỉ lấy giá trị NOMINAL (1 byte và 11 MB) để phân biệt nhánh. Các giá trị sát biên 10 MB thuộc về sheet 01.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="44" customHeight="1">
+      <c r="A47" s="56" t="inlineStr">
+        <is>
+          <t>KIỂM TRA BỔ SUNG ngoài bảng: đuôi viết HOA "BANGDIEM.PDF" được chấp nhận vì mã gọi toLowerCase — method boSung_duoiVietHoa_duocChapNhan, PASS. Không đưa vào bảng vì đây là biến thể trình bày của C2, không sinh thêm hành động mới.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="A9:H9"/>
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A48:H48"/>
-    <mergeCell ref="A26:H26"/>
-    <mergeCell ref="A39:H39"/>
-    <mergeCell ref="A15:H15"/>
-    <mergeCell ref="A7:H7"/>
-    <mergeCell ref="A35:H35"/>
-    <mergeCell ref="A43:H43"/>
-    <mergeCell ref="A40:H40"/>
-    <mergeCell ref="A42:H42"/>
-    <mergeCell ref="A41:H41"/>
-    <mergeCell ref="A13:H13"/>
-    <mergeCell ref="A33:H33"/>
-    <mergeCell ref="A36:H36"/>
-    <mergeCell ref="A45:H45"/>
-    <mergeCell ref="A37:H37"/>
-    <mergeCell ref="A34:H34"/>
+  <mergeCells count="17">
+    <mergeCell ref="A9:N9"/>
+    <mergeCell ref="J30:N30"/>
+    <mergeCell ref="A4:N4"/>
+    <mergeCell ref="A45:N45"/>
+    <mergeCell ref="J37:N37"/>
+    <mergeCell ref="A47:N47"/>
+    <mergeCell ref="A29:N29"/>
+    <mergeCell ref="A7:N7"/>
+    <mergeCell ref="J32:N32"/>
+    <mergeCell ref="A43:N43"/>
+    <mergeCell ref="A41:N41"/>
+    <mergeCell ref="J33:N33"/>
+    <mergeCell ref="A10:N10"/>
+    <mergeCell ref="A42:N42"/>
+    <mergeCell ref="A46:N46"/>
+    <mergeCell ref="J31:N31"/>
+    <mergeCell ref="A44:N44"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14350,17 +15258,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14371,540 +15279,756 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="53" t="inlineStr">
         <is>
           <t>Máy trạng thái tiến độ học một node kỹ năng (ProgressStatus). Bảng thiết kế theo mẫu slide 39.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>TỔNG KẾT THI HÀNH — 9 test đã chạy, 9 PASS, 0 fail. Bảng thiết kế bên dưới có cột ghi rõ method nào thi hành dòng nào.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="26" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="54" t="inlineStr">
+        <is>
+          <t>TỔNG KẾT THI HÀNH — 9 test đã chạy, 9 PASS, 0 fail.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="65" t="inlineStr">
         <is>
           <t>Lớp test trong source</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="65" t="inlineStr">
         <is>
           <t>Số test</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="65" t="inlineStr">
         <is>
           <t>Kỹ thuật áp dụng</t>
         </is>
       </c>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="n"/>
-      <c r="F5" s="4" t="n"/>
-      <c r="G5" s="4" t="n"/>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="D5" s="65" t="inlineStr"/>
+      <c r="E5" s="65" t="inlineStr"/>
+      <c r="F5" s="65" t="inlineStr"/>
+      <c r="G5" s="65" t="inlineStr"/>
+      <c r="H5" s="65" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="26" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="66" t="inlineStr">
         <is>
           <t>ProgressStateTransitionTest</t>
         </is>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B6" s="67" t="n">
         <v>9</v>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="66" t="inlineStr">
         <is>
           <t>Chuyển đổi trạng thái · 9 case</t>
         </is>
       </c>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5" t="n"/>
-      <c r="G6" s="5" t="n"/>
-      <c r="H6" s="13" t="inlineStr">
+      <c r="D6" s="66" t="inlineStr"/>
+      <c r="E6" s="66" t="inlineStr"/>
+      <c r="F6" s="66" t="inlineStr"/>
+      <c r="G6" s="66" t="inlineStr"/>
+      <c r="H6" s="68" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
-      <c r="A7" s="11" t="inlineStr">
-        <is>
-          <t>Số test được đối chiếu tự động với target/surefire-reports khi sinh lại sheet bằng tools/gen_sheets_dt_st.py — source chạy ra số khác thì script dừng và báo lỗi. Chạy lại để kiểm chứng:  mvnw test -Dtest=ProgressStateTransitionTest -DshowCases</t>
+    <row r="7" ht="26" customHeight="1">
+      <c r="A7" s="55" t="inlineStr">
+        <is>
+          <t>Số test được đối chiếu tự động với target/surefire-reports khi sinh lại sheet bằng tools/chuan_hoa_sheet_dt_st.py — source chạy ra số khác thì script dừng và báo lỗi. Chạy lại để kiểm chứng:  mvnw test -Dtest=ProgressStateTransitionTest</t>
         </is>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
+          <t>SƠ ĐỒ TRẠNG THÁI</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        NOT_STARTED  ◄────[bỏ đánh dấu]────  IN_PROGRESS  ◄────[hạ xuống]────  DONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">             │                                     ▲                            ▲</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">             └──────[đánh dấu đang học]────────────┘                            │</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">             └──────[đánh dấu hoàn thành, nhảy cóc]──────────────────────────────┘</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="62" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Ba cạnh vào IN_PROGRESS và DONE đều bị chặn 403 khi node còn KHOÁ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="24" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>MA TRẬN TRẠNG THÁI × SỰ KIỆN — liệt kê TRỌN VẸN mọi ô</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="34" customHeight="1">
+      <c r="A18" s="74" t="inlineStr">
+        <is>
+          <t>Trạng thái hiện tại</t>
+        </is>
+      </c>
+      <c r="B18" s="74" t="inlineStr">
+        <is>
+          <t>Đặt NOT_STARTED
+(node mở)</t>
+        </is>
+      </c>
+      <c r="C18" s="74" t="inlineStr">
+        <is>
+          <t>Đặt NOT_STARTED
+(node KHOÁ)</t>
+        </is>
+      </c>
+      <c r="D18" s="74" t="inlineStr">
+        <is>
+          <t>Đặt IN_PROGRESS
+(node mở)</t>
+        </is>
+      </c>
+      <c r="E18" s="74" t="inlineStr">
+        <is>
+          <t>Đặt IN_PROGRESS
+(node KHOÁ)</t>
+        </is>
+      </c>
+      <c r="F18" s="74" t="inlineStr">
+        <is>
+          <t>Đặt DONE
+(node mở)</t>
+        </is>
+      </c>
+      <c r="G18" s="74" t="inlineStr">
+        <is>
+          <t>Đặt DONE
+(node KHOÁ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="75" t="inlineStr">
+        <is>
+          <t>NOT_STARTED</t>
+        </is>
+      </c>
+      <c r="B19" s="69" t="inlineStr">
+        <is>
+          <t>NOT_STARTED
+(tự lặp)</t>
+        </is>
+      </c>
+      <c r="C19" s="69" t="inlineStr">
+        <is>
+          <t>NOT_STARTED
+(tự lặp)</t>
+        </is>
+      </c>
+      <c r="D19" s="69" t="inlineStr">
+        <is>
+          <t>IN_PROGRESS</t>
+        </is>
+      </c>
+      <c r="E19" s="76" t="inlineStr">
+        <is>
+          <t>Bị chặn 403</t>
+        </is>
+      </c>
+      <c r="F19" s="69" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="G19" s="76" t="inlineStr">
+        <is>
+          <t>Bị chặn 403</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="75" t="inlineStr">
+        <is>
+          <t>IN_PROGRESS</t>
+        </is>
+      </c>
+      <c r="B20" s="69" t="inlineStr">
+        <is>
+          <t>NOT_STARTED</t>
+        </is>
+      </c>
+      <c r="C20" s="69" t="inlineStr">
+        <is>
+          <t>NOT_STARTED</t>
+        </is>
+      </c>
+      <c r="D20" s="69" t="inlineStr">
+        <is>
+          <t>IN_PROGRESS
+(tự lặp)</t>
+        </is>
+      </c>
+      <c r="E20" s="76" t="inlineStr">
+        <is>
+          <t>Bị chặn 403</t>
+        </is>
+      </c>
+      <c r="F20" s="69" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="G20" s="76" t="inlineStr">
+        <is>
+          <t>Bị chặn 403</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="75" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="B21" s="69" t="inlineStr">
+        <is>
+          <t>NOT_STARTED</t>
+        </is>
+      </c>
+      <c r="C21" s="69" t="inlineStr">
+        <is>
+          <t>NOT_STARTED</t>
+        </is>
+      </c>
+      <c r="D21" s="69" t="inlineStr">
+        <is>
+          <t>IN_PROGRESS</t>
+        </is>
+      </c>
+      <c r="E21" s="76" t="inlineStr">
+        <is>
+          <t>Bị chặn 403</t>
+        </is>
+      </c>
+      <c r="F21" s="69" t="inlineStr">
+        <is>
+          <t>DONE
+(tự lặp)</t>
+        </is>
+      </c>
+      <c r="G21" s="76" t="inlineStr">
+        <is>
+          <t>Bị chặn 403</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="40" customHeight="1">
+      <c r="A22" s="56" t="inlineStr">
+        <is>
+          <t>Ma trận 3 trạng thái × 6 sự kiện = 18 ô, liệt kê TRỌN VẸN, kể cả ô tự lặp và ô bị chặn. Đọc mã nguồn thấy ngay một tính chất đáng chú ý: quyết định chỉ phụ thuộc (trạng thái MUỐN ĐẶT, node có khoá), hoàn toàn KHÔNG phụ thuộc trạng thái hiện tại — nên ba hàng giống hệt nhau, chỉ khác ở ô tự lặp. Đó là lý do bảng thiết kế bên dưới chỉ cần 9 test chứ không cần đủ 18.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="24" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
           <t>BẢNG CHUYỂN TRẠNG THÁI — mẫu slide 39</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="65" t="inlineStr">
         <is>
           <t>Test Case No.</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B25" s="65" t="inlineStr">
         <is>
           <t>Start State</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C25" s="65" t="inlineStr">
         <is>
           <t>Event / Input</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D25" s="65" t="inlineStr">
         <is>
           <t>End State / Exp Output</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E25" s="65" t="inlineStr">
         <is>
           <t>Hợp lệ</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="F25" s="65" t="inlineStr">
         <is>
           <t>Tác dụng phụ kiểm chứng</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="G25" s="65" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="H25" s="65" t="inlineStr">
         <is>
           <t>Method trong code</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="B26" s="66" t="inlineStr">
         <is>
           <t>NOT_STARTED</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C26" s="66" t="inlineStr">
         <is>
           <t>Đánh dấu IN_PROGRESS (node mở)</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D26" s="66" t="inlineStr">
         <is>
           <t>IN_PROGRESS</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E26" s="67" t="inlineStr">
         <is>
           <t>Có</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F26" s="66" t="inlineStr">
         <is>
           <t>completedAt vẫn null</t>
         </is>
       </c>
-      <c r="G11" s="13" t="inlineStr">
+      <c r="G26" s="68" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="H11" s="5" t="inlineStr">
+      <c r="H26" s="73" t="inlineStr">
         <is>
           <t>st01_notStarted_toInProgress</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="67" t="n">
+        <v>2</v>
+      </c>
+      <c r="B27" s="66" t="inlineStr">
         <is>
           <t>NOT_STARTED</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C27" s="66" t="inlineStr">
         <is>
           <t>Đánh dấu DONE (node mở, nhảy cóc)</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D27" s="66" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="E27" s="67" t="inlineStr">
         <is>
           <t>Có</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F27" s="66" t="inlineStr">
         <is>
           <t>Ghi completedAt + nhật ký</t>
         </is>
       </c>
-      <c r="G12" s="13" t="inlineStr">
+      <c r="G27" s="68" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="H12" s="5" t="inlineStr">
+      <c r="H27" s="73" t="inlineStr">
         <is>
           <t>st05_notStarted_toDone</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="67" t="n">
+        <v>3</v>
+      </c>
+      <c r="B28" s="66" t="inlineStr">
         <is>
           <t>NOT_STARTED</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C28" s="66" t="inlineStr">
         <is>
           <t>Đánh dấu DONE khi node KHOÁ</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D28" s="66" t="inlineStr">
         <is>
           <t>Bị chặn (403)</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E28" s="67" t="inlineStr">
         <is>
           <t>KHÔNG</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="F28" s="66" t="inlineStr">
         <is>
           <t>Không lưu gì</t>
         </is>
       </c>
-      <c r="G13" s="13" t="inlineStr">
+      <c r="G28" s="68" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="H13" s="5" t="inlineStr">
+      <c r="H28" s="73" t="inlineStr">
         <is>
           <t>st07_notStarted_toDone_nodeLocked_biChan</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="67" t="n">
+        <v>4</v>
+      </c>
+      <c r="B29" s="66" t="inlineStr">
         <is>
           <t>IN_PROGRESS</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C29" s="66" t="inlineStr">
         <is>
           <t>Đánh dấu DONE (node mở)</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D29" s="66" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="E29" s="67" t="inlineStr">
         <is>
           <t>Có</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F29" s="66" t="inlineStr">
         <is>
           <t>Ghi completedAt + nhật ký</t>
         </is>
       </c>
-      <c r="G14" s="13" t="inlineStr">
+      <c r="G29" s="68" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="H14" s="5" t="inlineStr">
+      <c r="H29" s="73" t="inlineStr">
         <is>
           <t>st02_inProgress_toDone</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="67" t="n">
+        <v>5</v>
+      </c>
+      <c r="B30" s="66" t="inlineStr">
         <is>
           <t>IN_PROGRESS</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C30" s="66" t="inlineStr">
         <is>
           <t>Bỏ đánh dấu</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D30" s="66" t="inlineStr">
         <is>
           <t>NOT_STARTED</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="E30" s="67" t="inlineStr">
         <is>
           <t>Có</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F30" s="66" t="inlineStr">
         <is>
           <t>Không hỏi khoá</t>
         </is>
       </c>
-      <c r="G15" s="13" t="inlineStr">
+      <c r="G30" s="68" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="H15" s="5" t="inlineStr">
+      <c r="H30" s="73" t="inlineStr">
         <is>
           <t>st06_inProgress_toNotStarted</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="67" t="n">
+        <v>6</v>
+      </c>
+      <c r="B31" s="66" t="inlineStr">
         <is>
           <t>IN_PROGRESS</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C31" s="66" t="inlineStr">
         <is>
           <t>Đánh dấu DONE khi node KHOÁ</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D31" s="66" t="inlineStr">
         <is>
           <t>Bị chặn (403)</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="E31" s="67" t="inlineStr">
         <is>
           <t>KHÔNG</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F31" s="66" t="inlineStr">
         <is>
           <t>Không lưu, không ghi log</t>
         </is>
       </c>
-      <c r="G16" s="13" t="inlineStr">
+      <c r="G31" s="68" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="H16" s="5" t="inlineStr">
+      <c r="H31" s="73" t="inlineStr">
         <is>
           <t>st08_inProgress_toDone_nodeLocked_biChan</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="67" t="n">
+        <v>7</v>
+      </c>
+      <c r="B32" s="66" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C32" s="66" t="inlineStr">
         <is>
           <t>Bỏ đánh dấu</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D32" s="66" t="inlineStr">
         <is>
           <t>NOT_STARTED</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="E32" s="67" t="inlineStr">
         <is>
           <t>Có</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F32" s="66" t="inlineStr">
         <is>
           <t>XOÁ completedAt</t>
         </is>
       </c>
-      <c r="G17" s="13" t="inlineStr">
+      <c r="G32" s="68" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="H17" s="5" t="inlineStr">
+      <c r="H32" s="73" t="inlineStr">
         <is>
           <t>st03_done_toNotStarted</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="67" t="n">
+        <v>8</v>
+      </c>
+      <c r="B33" s="66" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C33" s="66" t="inlineStr">
         <is>
           <t>Hạ xuống IN_PROGRESS</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D33" s="66" t="inlineStr">
         <is>
           <t>IN_PROGRESS</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="E33" s="67" t="inlineStr">
         <is>
           <t>Có</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F33" s="66" t="inlineStr">
         <is>
           <t>XOÁ completedAt</t>
         </is>
       </c>
-      <c r="G18" s="13" t="inlineStr">
+      <c r="G33" s="68" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="H18" s="5" t="inlineStr">
+      <c r="H33" s="73" t="inlineStr">
         <is>
           <t>st04_done_toInProgress</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="67" t="n">
+        <v>9</v>
+      </c>
+      <c r="B34" s="66" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C34" s="66" t="inlineStr">
         <is>
           <t>Hạ về IN_PROGRESS khi node KHOÁ</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D34" s="66" t="inlineStr">
         <is>
           <t>Bị chặn (403)</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="E34" s="67" t="inlineStr">
         <is>
           <t>KHÔNG</t>
         </is>
       </c>
-      <c r="F19" s="6" t="inlineStr">
+      <c r="F34" s="66" t="inlineStr">
         <is>
           <t>Không lưu gì</t>
         </is>
       </c>
-      <c r="G19" s="13" t="inlineStr">
+      <c r="G34" s="68" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="H19" s="5" t="inlineStr">
+      <c r="H34" s="73" t="inlineStr">
         <is>
           <t>st09_done_toInProgress_nodeLocked_biChan</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="44" customHeight="1">
-      <c r="A21" s="11" t="inlineStr">
-        <is>
-          <t>TIÊU CHÍ ĐỦ của kỹ thuật này: phủ hết CẠNH của sơ đồ. Ba trạng thái sinh ra 3 × 2 = 6 cặp có thứ tự, tức 6 cạnh. Dòng 1–6 phủ đủ 6 cạnh đó. Dòng 7–8 là chuyển đổi bị chặn.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="44" customHeight="1">
-      <c r="A22" s="11" t="inlineStr">
-        <is>
-          <t>CẤU TRÚC BẢNG: nhóm theo Start State, mỗi nhóm đúng 3 dòng gồm 2 chuyển đổi hợp lệ và 1 chuyển đổi bị chặn khi node khoá. Sáu dòng hợp lệ phủ trọn 6 cạnh của sơ đồ (3 trạng thái x 2 đích = 6). Ba dòng bị chặn kiểm chứng chốt chặn hoạt động từ cả ba trạng thái xuất phát.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="44" customHeight="1">
-      <c r="A23" s="11" t="inlineStr">
-        <is>
-          <t>LƯU Ý VỀ TẦNG KIỂM THỬ: bảng này thiết kế ở TẦNG DỊCH VỤ, nơi luật nghiệp vụ thực sự được thi hành. Giao diện roadmap chỉ có 4 nút (NOT_STARTED→IN_PROGRESS, IN_PROGRESS→DONE, IN_PROGRESS→NOT_STARTED, DONE→IN_PROGRESS), tức 2 trong 6 cạnh không bấm được từ màn hình. Nhưng cả 6 đều gọi được qua POST /roadmap/progress, nên vẫn phải kiểm thử đủ — ẩn nút chỉ là rào chắn mềm phía client, không phải bảo vệ thật.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="44" customHeight="1">
-      <c r="A24" s="11" t="inlineStr">
-        <is>
-          <t>SƠ ĐỒ TRẠNG THÁI: xem tệp SoDo-ChuyenTrangThai.drawio ở thư mục gốc dự án — 3 trạng thái, đủ 6 cạnh chuyển, phân biệt bằng màu: đỏ nét đứt là chuyển đổi bị chặn khi node khoá, xanh nét liền là luôn được phép.</t>
+    <row r="36" ht="40" customHeight="1">
+      <c r="A36" s="56" t="inlineStr">
+        <is>
+          <t>TIÊU CHÍ ĐỦ: phủ hết CẠNH của sơ đồ. Ba trạng thái sinh ra 3 × 2 = 6 cặp có thứ tự, tức 6 cạnh; dòng 1–2, 4–5, 7–8 phủ đủ sáu cạnh đó. Ba dòng còn lại là chuyển đổi BỊ CHẶN khi node khoá — phần mà kiểm thử đi đường thuận sẽ bỏ sót.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="40" customHeight="1">
+      <c r="A37" s="56" t="inlineStr">
+        <is>
+          <t>VÌ SAO BẢNG THIẾT KẾ CHỈ CÓ 9 DÒNG MÀ MA TRẬN CÓ 18 Ô: ma trận cho thấy ba hàng giống hệt nhau và các ô tự lặp không sinh hành vi mới, nên chín ô còn lại không cần test riêng. Ma trận ở trên là bằng chứng cho khẳng định đó — không phải lọc theo cảm tính.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="40" customHeight="1">
+      <c r="A38" s="56" t="inlineStr">
+        <is>
+          <t>CẤU TRÚC BẢNG: nhóm theo Start State, mỗi nhóm đúng 3 dòng gồm 2 chuyển đổi hợp lệ và 1 chuyển đổi bị chặn khi node khoá.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="40" customHeight="1">
+      <c r="A39" s="56" t="inlineStr">
+        <is>
+          <t>TẦNG KIỂM THỬ: bảng này thiết kế ở TẦNG DỊCH VỤ, nơi luật nghiệp vụ thực sự được thi hành, chứ không phải ở giao diện.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="40" customHeight="1">
+      <c r="A40" s="56" t="inlineStr">
+        <is>
+          <t>SƠ ĐỒ ĐẦY ĐỦ dạng hình: xem tệp SoDo-ChuyenTrangThai.drawio ở thư mục gốc dự án.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="17">
     <mergeCell ref="A9:H9"/>
     <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A21:H21"/>
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="A39:H39"/>
+    <mergeCell ref="A15:H15"/>
     <mergeCell ref="A7:H7"/>
     <mergeCell ref="A24:H24"/>
-    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="A38:H38"/>
+    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="A40:H40"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A11:H11"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A36:H36"/>
+    <mergeCell ref="A37:H37"/>
     <mergeCell ref="A22:H22"/>
+    <mergeCell ref="A17:H17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14916,17 +16040,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="32" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14937,606 +16061,677 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="53" t="inlineStr">
         <is>
           <t>Máy trạng thái của một token đặt lại mật khẩu. Bảng thiết kế theo mẫu slide 39.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="26" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="54" t="inlineStr">
         <is>
           <t>TỔNG KẾT THI HÀNH — 7 test đã chạy, 7 PASS, 0 fail.</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="65" t="inlineStr">
         <is>
           <t>Lớp test trong source</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="65" t="inlineStr">
         <is>
           <t>Số test</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="65" t="inlineStr">
         <is>
           <t>Kỹ thuật áp dụng</t>
         </is>
       </c>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="n"/>
-      <c r="F5" s="4" t="n"/>
-      <c r="G5" s="4" t="n"/>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="D5" s="65" t="inlineStr"/>
+      <c r="E5" s="65" t="inlineStr"/>
+      <c r="F5" s="65" t="inlineStr"/>
+      <c r="G5" s="65" t="inlineStr"/>
+      <c r="H5" s="65" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="26" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="66" t="inlineStr">
         <is>
           <t>TokenStateTransitionTest</t>
         </is>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B6" s="67" t="n">
         <v>7</v>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="66" t="inlineStr">
         <is>
           <t>Chuyển đổi trạng thái · 7 case</t>
         </is>
       </c>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5" t="n"/>
-      <c r="G6" s="5" t="n"/>
-      <c r="H6" s="13" t="inlineStr">
+      <c r="D6" s="66" t="inlineStr"/>
+      <c r="E6" s="66" t="inlineStr"/>
+      <c r="F6" s="66" t="inlineStr"/>
+      <c r="G6" s="66" t="inlineStr"/>
+      <c r="H6" s="68" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>BẢNG 1 — VÌ SAO KIỂM CÙNG MỘT ĐỐI TƯỢNG BẰNG HAI KỸ THUẬT</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>Kỹ thuật</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Sheet</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Câu hỏi nó trả lời</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="n"/>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>Tính chất</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="n"/>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>Điều nó KHÔNG nói được</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="n"/>
-    </row>
-    <row r="10" ht="56" customHeight="1">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>Bảng quyết định</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>03b</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>Token này TẠI THỜI ĐIỂM NÀY có hợp lệ không?</t>
-        </is>
-      </c>
-      <c r="D10" s="9" t="n"/>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>Tĩnh — chụp một khoảnh khắc</t>
-        </is>
-      </c>
-      <c r="F10" s="9" t="n"/>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>Không nói được cờ used đi tới bằng con đường nào, cũng không cấm nó quay ngược lại.</t>
-        </is>
-      </c>
-      <c r="H10" s="9" t="n"/>
-    </row>
-    <row r="11" ht="56" customHeight="1">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>Chuyển đổi trạng thái</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>04b</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>Token đi qua được những CHUỖI SỰ KIỆN nào?</t>
-        </is>
-      </c>
-      <c r="D11" s="9" t="n"/>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>Theo thời gian — ràng buộc thứ tự</t>
-        </is>
-      </c>
-      <c r="F11" s="9" t="n"/>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>Không liệt kê đủ mọi tổ hợp cờ như bảng quyết định làm.</t>
-        </is>
-      </c>
-      <c r="H11" s="9" t="n"/>
-    </row>
-    <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
+    <row r="7" ht="26" customHeight="1">
+      <c r="A7" s="55" t="inlineStr">
+        <is>
+          <t>Số test được đối chiếu tự động với target/surefire-reports khi sinh lại sheet bằng tools/chuan_hoa_sheet_dt_st.py — source chạy ra số khác thì script dừng và báo lỗi. Chạy lại để kiểm chứng:  mvnw test -Dtest=TokenStateTransitionTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>SƠ ĐỒ TRẠNG THÁI</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                          [người dùng yêu cầu đặt lại mật khẩu]</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                                        ↓</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                          HỢP LỆ  (used = false, còn hạn)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                             ↓                    ↓</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                 [đặt lại mật khẩu]          [quá 30 phút]</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                             ↓                    ↓</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                        ĐÃ DÙNG               HẾT HẠN</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="23" t="n"/>
-    </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="24" t="inlineStr">
-        <is>
-          <t>Hai cạnh ra khỏi HỢP LỆ đều MỘT CHIỀU: không sự kiện nào đưa token quay lại hợp lệ.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="24" customHeight="1">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>BẢNG CHUYỂN TRẠNG THÁI — mẫu slide 39 · 3 cạnh hợp lệ, 3 cạnh bị chặn</t>
+    <row r="10">
+      <c r="A10" s="62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                      [người dùng yêu cầu đặt lại mật khẩu]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                    ↓</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                      HỢP LỆ  (used = false, còn hạn)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                         ↓                    ↓</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">             [đặt lại mật khẩu]          [quá 30 phút]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                         ↓                    ↓</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                    ĐÃ DÙNG               HẾT HẠN</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="62" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Hai cạnh ra khỏi HỢP LỆ đều MỘT CHIỀU — không sự kiện nào quay lại.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>MA TRẬN TRẠNG THÁI × SỰ KIỆN — liệt kê TRỌN VẸN mọi ô</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="34" customHeight="1">
+      <c r="A21" s="74" t="inlineStr">
+        <is>
+          <t>Trạng thái hiện tại</t>
+        </is>
+      </c>
+      <c r="B21" s="74" t="inlineStr">
+        <is>
+          <t>Yêu cầu đặt lại
+mật khẩu</t>
+        </is>
+      </c>
+      <c r="C21" s="74" t="inlineStr">
+        <is>
+          <t>Đặt lại mật khẩu
+bằng token</t>
+        </is>
+      </c>
+      <c r="D21" s="74" t="inlineStr">
+        <is>
+          <t>Quá 30 phút</t>
+        </is>
+      </c>
+      <c r="E21" s="74" t="inlineStr">
+        <is>
+          <t>Gọi validateToken</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="75" t="inlineStr">
+        <is>
+          <t>(chưa có token)</t>
+        </is>
+      </c>
+      <c r="B22" s="69" t="inlineStr">
+        <is>
+          <t>HỢP LỆ</t>
+        </is>
+      </c>
+      <c r="C22" s="69" t="inlineStr">
+        <is>
+          <t>— không có token</t>
+        </is>
+      </c>
+      <c r="D22" s="69" t="inlineStr">
+        <is>
+          <t>— không có token</t>
+        </is>
+      </c>
+      <c r="E22" s="69" t="inlineStr">
+        <is>
+          <t>— không có token</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="75" t="inlineStr">
+        <is>
+          <t>HỢP LỆ</t>
+        </is>
+      </c>
+      <c r="B23" s="69" t="inlineStr">
+        <is>
+          <t>HỢP LỆ
+(token mới thay token cũ)</t>
+        </is>
+      </c>
+      <c r="C23" s="69" t="inlineStr">
+        <is>
+          <t>ĐÃ DÙNG</t>
+        </is>
+      </c>
+      <c r="D23" s="69" t="inlineStr">
+        <is>
+          <t>HẾT HẠN</t>
+        </is>
+      </c>
+      <c r="E23" s="69" t="inlineStr">
+        <is>
+          <t>Đi qua</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="75" t="inlineStr">
+        <is>
+          <t>ĐÃ DÙNG</t>
+        </is>
+      </c>
+      <c r="B24" s="69" t="inlineStr">
+        <is>
+          <t>HỢP LỆ
+(token mới)</t>
+        </is>
+      </c>
+      <c r="C24" s="76" t="inlineStr">
+        <is>
+          <t>Bị chặn
+(IllegalState)</t>
+        </is>
+      </c>
+      <c r="D24" s="69" t="inlineStr">
+        <is>
+          <t>ĐÃ DÙNG + HẾT HẠN</t>
+        </is>
+      </c>
+      <c r="E24" s="76" t="inlineStr">
+        <is>
+          <t>Bị lọc bỏ</t>
         </is>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="A25" s="75" t="inlineStr">
+        <is>
+          <t>HẾT HẠN</t>
+        </is>
+      </c>
+      <c r="B25" s="69" t="inlineStr">
+        <is>
+          <t>HỢP LỆ
+(token mới)</t>
+        </is>
+      </c>
+      <c r="C25" s="76" t="inlineStr">
+        <is>
+          <t>Bị chặn
+(IllegalState)</t>
+        </is>
+      </c>
+      <c r="D25" s="69" t="inlineStr">
+        <is>
+          <t>HẾT HẠN
+(tự lặp)</t>
+        </is>
+      </c>
+      <c r="E25" s="76" t="inlineStr">
+        <is>
+          <t>Bị lọc bỏ</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="40" customHeight="1">
+      <c r="A26" s="56" t="inlineStr">
+        <is>
+          <t>Ma trận 4 trạng thái × 4 sự kiện = 16 ô. Điểm cốt lõi đọc được từ ma trận: KHÔNG ô nào đưa token quay lại HỢP LỆ, trừ khi tạo token MỚI — tức đây là máy trạng thái MỘT CHIỀU. Chính vì vậy số cạnh không phải 3 × 2 = 6 như trường hợp tổng quát.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="24" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>BẢNG CHUYỂN TRẠNG THÁI — mẫu slide 39</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="65" t="inlineStr">
         <is>
           <t>Test Case No.</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B29" s="65" t="inlineStr">
         <is>
           <t>Start State</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C29" s="65" t="inlineStr">
         <is>
           <t>Event / Input</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D29" s="65" t="inlineStr">
         <is>
           <t>End State / Exp Output</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
+      <c r="E29" s="65" t="inlineStr">
         <is>
           <t>Hợp lệ</t>
         </is>
       </c>
-      <c r="F25" s="4" t="inlineStr">
+      <c r="F29" s="65" t="inlineStr">
         <is>
           <t>Tác dụng phụ kiểm chứng</t>
         </is>
       </c>
-      <c r="G25" s="4" t="inlineStr">
+      <c r="G29" s="65" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="H25" s="4" t="inlineStr">
+      <c r="H29" s="65" t="inlineStr">
         <is>
           <t>Method trong code</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="34" customHeight="1">
-      <c r="A26" s="6" t="n">
+    <row r="30">
+      <c r="A30" s="67" t="n">
         <v>1</v>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B30" s="66" t="inlineStr">
         <is>
           <t>(chưa có token)</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="C30" s="66" t="inlineStr">
         <is>
           <t>Người dùng yêu cầu đặt lại mật khẩu</t>
         </is>
       </c>
-      <c r="D26" s="5" t="inlineStr">
+      <c r="D30" s="66" t="inlineStr">
         <is>
           <t>HỢP LỆ</t>
         </is>
       </c>
-      <c r="E26" s="6" t="inlineStr">
+      <c r="E30" s="67" t="inlineStr">
         <is>
           <t>Có</t>
         </is>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="F30" s="66" t="inlineStr">
         <is>
           <t>used = false, còn 30 phút</t>
         </is>
       </c>
-      <c r="G26" s="13" t="inlineStr">
+      <c r="G30" s="68" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="H26" s="5" t="inlineStr">
+      <c r="H30" s="73" t="inlineStr">
         <is>
           <t>st01_taoToken_sangTrangThaiHopLe</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="34" customHeight="1">
-      <c r="A27" s="6" t="n">
+    <row r="31">
+      <c r="A31" s="67" t="n">
         <v>2</v>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B31" s="66" t="inlineStr">
         <is>
           <t>HỢP LỆ</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="C31" s="66" t="inlineStr">
         <is>
           <t>Đặt lại mật khẩu bằng token</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
+      <c r="D31" s="66" t="inlineStr">
         <is>
           <t>ĐÃ DÙNG</t>
         </is>
       </c>
-      <c r="E27" s="6" t="inlineStr">
+      <c r="E31" s="67" t="inlineStr">
         <is>
           <t>Có</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="F31" s="66" t="inlineStr">
         <is>
           <t>Ghi mật khẩu mới, bật cờ used</t>
         </is>
       </c>
-      <c r="G27" s="13" t="inlineStr">
+      <c r="G31" s="68" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="H27" s="5" t="inlineStr">
+      <c r="H31" s="73" t="inlineStr">
         <is>
           <t>st02_hopLe_sangDaDung</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="34" customHeight="1">
-      <c r="A28" s="6" t="n">
+    <row r="32">
+      <c r="A32" s="67" t="n">
         <v>3</v>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B32" s="66" t="inlineStr">
         <is>
           <t>HỢP LỆ</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
+      <c r="C32" s="66" t="inlineStr">
         <is>
           <t>Quá 30 phút</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
+      <c r="D32" s="66" t="inlineStr">
         <is>
           <t>HẾT HẠN</t>
         </is>
       </c>
-      <c r="E28" s="6" t="inlineStr">
+      <c r="E32" s="67" t="inlineStr">
         <is>
           <t>Có</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="F32" s="66" t="inlineStr">
         <is>
           <t>used vẫn false — hết hạn không kéo theo đã dùng</t>
         </is>
       </c>
-      <c r="G28" s="13" t="inlineStr">
+      <c r="G32" s="68" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="H28" s="5" t="inlineStr">
+      <c r="H32" s="73" t="inlineStr">
         <is>
           <t>st03_hopLe_sangHetHan</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="34" customHeight="1">
-      <c r="A29" s="6" t="n">
+    <row r="33">
+      <c r="A33" s="67" t="n">
         <v>4</v>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B33" s="66" t="inlineStr">
         <is>
           <t>ĐÃ DÙNG</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="C33" s="66" t="inlineStr">
         <is>
           <t>Đặt lại mật khẩu LẦN NỮA</t>
         </is>
       </c>
-      <c r="D29" s="25" t="inlineStr">
+      <c r="D33" s="66" t="inlineStr">
         <is>
           <t>Bị chặn (IllegalState)</t>
         </is>
       </c>
-      <c r="E29" s="17" t="inlineStr">
+      <c r="E33" s="67" t="inlineStr">
         <is>
           <t>KHÔNG</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="F33" s="66" t="inlineStr">
         <is>
           <t>Mật khẩu chỉ đổi đúng một lần</t>
         </is>
       </c>
-      <c r="G29" s="13" t="inlineStr">
+      <c r="G33" s="68" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="H29" s="5" t="inlineStr">
+      <c r="H33" s="73" t="inlineStr">
         <is>
           <t>st04_daDung_dungLaiBiChan</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="34" customHeight="1">
-      <c r="A30" s="6" t="n">
+    <row r="34">
+      <c r="A34" s="67" t="n">
         <v>5</v>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B34" s="66" t="inlineStr">
         <is>
           <t>HẾT HẠN</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
+      <c r="C34" s="66" t="inlineStr">
         <is>
           <t>Đặt lại mật khẩu</t>
         </is>
       </c>
-      <c r="D30" s="25" t="inlineStr">
+      <c r="D34" s="66" t="inlineStr">
         <is>
           <t>Bị chặn (IllegalState)</t>
         </is>
       </c>
-      <c r="E30" s="17" t="inlineStr">
+      <c r="E34" s="67" t="inlineStr">
         <is>
           <t>KHÔNG</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr">
+      <c r="F34" s="66" t="inlineStr">
         <is>
           <t>Không bật cờ used, không đổi mật khẩu</t>
         </is>
       </c>
-      <c r="G30" s="13" t="inlineStr">
+      <c r="G34" s="68" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="H30" s="5" t="inlineStr">
+      <c r="H34" s="73" t="inlineStr">
         <is>
           <t>st05_hetHan_dungBiChan</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="34" customHeight="1">
-      <c r="A31" s="6" t="n">
+    <row r="35">
+      <c r="A35" s="67" t="n">
         <v>6</v>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B35" s="66" t="inlineStr">
         <is>
           <t>ĐÃ DÙNG</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
+      <c r="C35" s="66" t="inlineStr">
         <is>
           <t>Quá 30 phút</t>
         </is>
       </c>
-      <c r="D31" s="25" t="inlineStr">
+      <c r="D35" s="66" t="inlineStr">
         <is>
           <t>ĐÃ DÙNG + HẾT HẠN</t>
         </is>
       </c>
-      <c r="E31" s="17" t="inlineStr">
+      <c r="E35" s="67" t="inlineStr">
         <is>
           <t>KHÔNG</t>
         </is>
       </c>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="F35" s="66" t="inlineStr">
         <is>
           <t>Hai cờ cùng bật, càng không hợp lệ</t>
         </is>
       </c>
-      <c r="G31" s="13" t="inlineStr">
+      <c r="G35" s="68" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="H31" s="5" t="inlineStr">
+      <c r="H35" s="73" t="inlineStr">
         <is>
           <t>st06_daDung_hetHanVanKhongHopLe</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="34" customHeight="1">
-      <c r="A32" s="6" t="n">
+    <row r="36">
+      <c r="A36" s="67" t="n">
         <v>7</v>
       </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B36" s="66" t="inlineStr">
         <is>
           <t>Mọi trạng thái</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr">
+      <c r="C36" s="66" t="inlineStr">
         <is>
           <t>Gọi validateToken</t>
         </is>
       </c>
-      <c r="D32" s="5" t="inlineStr">
+      <c r="D36" s="66" t="inlineStr">
         <is>
           <t>Chỉ HỢP LỆ đi qua</t>
         </is>
       </c>
-      <c r="E32" s="6" t="inlineStr">
+      <c r="E36" s="67" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F32" s="5" t="inlineStr">
+      <c r="F36" s="66" t="inlineStr">
         <is>
           <t>Hai trạng thái kia bị lọc bỏ</t>
         </is>
       </c>
-      <c r="G32" s="13" t="inlineStr">
+      <c r="G36" s="68" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="H32" s="5" t="inlineStr">
+      <c r="H36" s="73" t="inlineStr">
         <is>
           <t>st07_validateToken_chiQuaOTrangThaiHopLe</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="44" customHeight="1">
-      <c r="A34" s="11" t="inlineStr">
-        <is>
-          <t>TIÊU CHÍ ĐỦ: phủ hết cạnh của sơ đồ. Ba trạng thái nhưng KHÔNG phải 3 × 2 = 6 cạnh như trường hợp tổng quát, vì đây là máy trạng thái một chiều — không có cạnh nào đi ngược. Ba cạnh hợp lệ (dòng 1–3) cộng ba cạnh bị chặn (dòng 4–6) là phủ trọn, dòng 7 kiểm thêm cổng vào validateToken.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="44" customHeight="1">
-      <c r="A35" s="11" t="inlineStr">
-        <is>
-          <t>DÒNG 4 LÀ TEST ĐÁNG GIÁ NHẤT. Nó gửi HAI sự kiện liên tiếp: dùng token, rồi dùng lại chính token đó. Bảng quyết định ở sheet 03b không diễn tả nổi phép thử này — nó chỉ mô tả bốn tổ hợp cờ tại một thời điểm, không ràng buộc được thứ tự sự kiện. Đây chính là chỗ hai kỹ thuật bổ sung cho nhau thay vì trùng lặp.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="44" customHeight="1">
-      <c r="A36" s="11" t="inlineStr">
-        <is>
-          <t>GHI CHÚ VỀ ĐIỀU KIỆN CANH: giống bảng ở sheet 04, điều kiện phụ được gộp vào cột Event / Input chứ không tách thành cột riêng — đúng bốn cột lõi của slide 39. Ví dụ TC-ST-01 chỉ áp dụng cho tài khoản đăng nhập bằng mật khẩu; tài khoản đăng nhập bằng Google không tạo được token vì mật khẩu do Google giữ. Lần chạy đầu tiên đã đỏ đúng vì quên đặt authProvider = LOCAL.</t>
+    <row r="38" ht="40" customHeight="1">
+      <c r="A38" s="56" t="inlineStr">
+        <is>
+          <t>TIÊU CHÍ ĐỦ: phủ hết cạnh của sơ đồ. Ba trạng thái nhưng KHÔNG phải 3 × 2 = 6 cạnh như trường hợp tổng quát, vì đây là máy trạng thái một chiều — ma trận ở trên cho thấy không ô nào đưa token quay lại HỢP LỆ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="40" customHeight="1">
+      <c r="A39" s="56" t="inlineStr">
+        <is>
+          <t>DÒNG 4 LÀ TEST ĐÁNG GIÁ NHẤT. Nó gửi HAI sự kiện liên tiếp: dùng token, rồi dùng lại chính token đó. Bảng quyết định ở sheet 03b không diễn tả nổi phép thử này — nó chỉ mô tả bốn tổ hợp cờ tại một thời điểm, không có trục thời gian.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="40" customHeight="1">
+      <c r="A40" s="56" t="inlineStr">
+        <is>
+          <t>SO VỚI SHEET 03b — CÙNG ĐỐI TƯỢNG, HAI KỸ THUẬT: bảng quyết định trả lời "token này TẠI THỜI ĐIỂM NÀY có hợp lệ không", tĩnh, chụp một khoảnh khắc; chuyển đổi trạng thái trả lời "token đi qua được những CHUỖI SỰ KIỆN nào", có ràng buộc thứ tự. Cái trước không nói được cờ used đi tới bằng con đường nào; cái sau không liệt kê đủ mọi tổ hợp cờ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="40" customHeight="1">
+      <c r="A41" s="56" t="inlineStr">
+        <is>
+          <t>ĐIỀU KIỆN CANH: giống sheet 04, điều kiện phụ gộp vào cột Event / Input chứ không tách thành cột riêng — đúng bốn cột lõi của slide 39. Dòng 1 chỉ áp dụng cho tài khoản LOCAL; tài khoản Google không đặt lại mật khẩu ở đây.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="19">
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A39:H39"/>
     <mergeCell ref="A15:H15"/>
-    <mergeCell ref="A24:H24"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="A36:H36"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="A11:H11"/>
+    <mergeCell ref="A7:H7"/>
     <mergeCell ref="A16:H16"/>
+    <mergeCell ref="A41:H41"/>
+    <mergeCell ref="A12:H12"/>
     <mergeCell ref="A18:H18"/>
-    <mergeCell ref="A21:H21"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="A26:H26"/>
     <mergeCell ref="A14:H14"/>
-    <mergeCell ref="A8:H8"/>
-    <mergeCell ref="A22:H22"/>
     <mergeCell ref="A17:H17"/>
     <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A35:H35"/>
     <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A38:H38"/>
+    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="A28:H28"/>
     <mergeCell ref="A13:H13"/>
-    <mergeCell ref="A19:H19"/>
-    <mergeCell ref="A34:H34"/>
+    <mergeCell ref="A40:H40"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15548,23 +16743,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H52"/>
+  <dimension ref="A1:H42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="12" t="inlineStr">
         <is>
-          <t>State Transition Testing — bảng thứ ba: ba bước khai báo hồ sơ</t>
+          <t>State Transition Testing — ba bước khai báo hồ sơ lần đầu</t>
         </is>
       </c>
     </row>
@@ -15575,864 +16770,758 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="30" customHeight="1">
+    <row r="4" ht="22" customHeight="1">
       <c r="A4" s="54" t="inlineStr">
         <is>
-          <t>TỔNG KẾT THI HÀNH — 12 test đã chạy, 12 PASS, 0 fail. Dòng ST-06 là test tham số hoá, chạy 5 lần cho 5 điểm vào nên 8 dòng thiết kế sinh ra 12 test thực tế.</t>
+          <t>TỔNG KẾT THI HÀNH — 12 test đã chạy, 12 PASS, 0 fail.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="65" t="inlineStr">
         <is>
           <t>Lớp test trong source</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="65" t="inlineStr">
         <is>
           <t>Số test</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="65" t="inlineStr">
         <is>
           <t>Kỹ thuật áp dụng</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr"/>
-      <c r="E5" s="4" t="inlineStr"/>
-      <c r="F5" s="4" t="inlineStr"/>
-      <c r="G5" s="4" t="inlineStr"/>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="D5" s="65" t="inlineStr"/>
+      <c r="E5" s="65" t="inlineStr"/>
+      <c r="F5" s="65" t="inlineStr"/>
+      <c r="G5" s="65" t="inlineStr"/>
+      <c r="H5" s="65" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="66" t="inlineStr">
         <is>
           <t>OnboardingStateTransitionTest</t>
         </is>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B6" s="67" t="n">
         <v>12</v>
       </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>Chuyển đổi trạng thái · 8 dòng thiết kế</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="13" t="inlineStr">
+      <c r="C6" s="66" t="inlineStr">
+        <is>
+          <t>Chuyển đổi trạng thái · 12 case</t>
+        </is>
+      </c>
+      <c r="D6" s="66" t="inlineStr"/>
+      <c r="E6" s="66" t="inlineStr"/>
+      <c r="F6" s="66" t="inlineStr"/>
+      <c r="G6" s="66" t="inlineStr"/>
+      <c r="H6" s="68" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="28" customHeight="1">
+    <row r="7" ht="26" customHeight="1">
       <c r="A7" s="55" t="inlineStr">
         <is>
-          <t>Số test được đối chiếu tự động với target/surefire-reports khi sinh lại sheet bằng tools/gen_sheets_bo_sung.py — source chạy ra số khác thì script dừng và báo lỗi. Chạy lại để kiểm chứng:  mvnw test -Dtest=OnboardingStateTransitionTest</t>
+          <t>Số test được đối chiếu tự động với target/surefire-reports khi sinh lại sheet bằng tools/chuan_hoa_sheet_dt_st.py — source chạy ra số khác thì script dừng và báo lỗi. Chạy lại để kiểm chứng:  mvnw test -Dtest=OnboardingStateTransitionTest</t>
         </is>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>BẢNG 1 — MÁY TRẠNG THÁI NÀY KHÁC HAI MÁY TRƯỚC Ở ĐÂU</t>
+          <t>SƠ ĐỒ TRẠNG THÁI</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>Máy trạng thái</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>Sheet</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>Trạng thái nằm ở đâu</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr"/>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>Số trạng thái</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr"/>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>Đặc điểm riêng</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr"/>
+      <c r="A10" s="62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    S1 MOI_TAO ──[POST step1, chọn nghề]──► S2 DA_CHON_NGHE ──[POST step2]──► S3 DA_NAP_NGUON</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>Tiến độ node kỹ năng</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>04</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>Một cột enum ProgressStatus</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="6" t="n">
+      <c r="A11" s="62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">       │   ▲                                                                        │</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">       │   └──[không chọn gì] / [bấm Bỏ qua]                             [POST step3]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">       │                                                                            ▼</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">       └────────────[GET step3, nhảy cóc]────────────────────────►      S4 HOAN_TAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                                                             │    ▲</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                                                             └────┘</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                                                        mọi điểm vào đều chuyển về /</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="24" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>MA TRẬN TRẠNG THÁI × SỰ KIỆN — liệt kê TRỌN VẸN mọi ô</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="34" customHeight="1">
+      <c r="A20" s="74" t="inlineStr">
+        <is>
+          <t>Trạng thái hiện tại</t>
+        </is>
+      </c>
+      <c r="B20" s="74" t="inlineStr">
+        <is>
+          <t>GET step1</t>
+        </is>
+      </c>
+      <c r="C20" s="74" t="inlineStr">
+        <is>
+          <t>GET step2</t>
+        </is>
+      </c>
+      <c r="D20" s="74" t="inlineStr">
+        <is>
+          <t>GET step3</t>
+        </is>
+      </c>
+      <c r="E20" s="74" t="inlineStr">
+        <is>
+          <t>POST step1</t>
+        </is>
+      </c>
+      <c r="F20" s="74" t="inlineStr">
+        <is>
+          <t>POST step2</t>
+        </is>
+      </c>
+      <c r="G20" s="74" t="inlineStr">
+        <is>
+          <t>POST step3</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="75" t="inlineStr">
+        <is>
+          <t>S1 MOI_TAO</t>
+        </is>
+      </c>
+      <c r="B21" s="69" t="inlineStr">
+        <is>
+          <t>Hiện bước 1</t>
+        </is>
+      </c>
+      <c r="C21" s="69" t="inlineStr">
+        <is>
+          <t>Hiện bước 2</t>
+        </is>
+      </c>
+      <c r="D21" s="69" t="inlineStr">
+        <is>
+          <t>Hiện bước 3</t>
+        </is>
+      </c>
+      <c r="E21" s="69" t="inlineStr">
+        <is>
+          <t>→ bước 2
+(lưu định hướng)</t>
+        </is>
+      </c>
+      <c r="F21" s="69" t="inlineStr">
+        <is>
+          <t>→ bước 3</t>
+        </is>
+      </c>
+      <c r="G21" s="69" t="inlineStr">
+        <is>
+          <t>→ HOÀN TẤT</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="75" t="inlineStr">
+        <is>
+          <t>S2 DA_CHON_NGHE</t>
+        </is>
+      </c>
+      <c r="B22" s="69" t="inlineStr">
+        <is>
+          <t>Hiện bước 1</t>
+        </is>
+      </c>
+      <c r="C22" s="69" t="inlineStr">
+        <is>
+          <t>Hiện bước 2</t>
+        </is>
+      </c>
+      <c r="D22" s="69" t="inlineStr">
+        <is>
+          <t>Hiện bước 3</t>
+        </is>
+      </c>
+      <c r="E22" s="69" t="inlineStr">
+        <is>
+          <t>→ bước 2</t>
+        </is>
+      </c>
+      <c r="F22" s="69" t="inlineStr">
+        <is>
+          <t>→ bước 3</t>
+        </is>
+      </c>
+      <c r="G22" s="69" t="inlineStr">
+        <is>
+          <t>→ HOÀN TẤT</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="75" t="inlineStr">
+        <is>
+          <t>S3 DA_NAP_NGUON</t>
+        </is>
+      </c>
+      <c r="B23" s="69" t="inlineStr">
+        <is>
+          <t>Hiện bước 1</t>
+        </is>
+      </c>
+      <c r="C23" s="69" t="inlineStr">
+        <is>
+          <t>Hiện bước 2</t>
+        </is>
+      </c>
+      <c r="D23" s="69" t="inlineStr">
+        <is>
+          <t>Hiện bước 3</t>
+        </is>
+      </c>
+      <c r="E23" s="69" t="inlineStr">
+        <is>
+          <t>→ bước 2</t>
+        </is>
+      </c>
+      <c r="F23" s="69" t="inlineStr">
+        <is>
+          <t>→ bước 3</t>
+        </is>
+      </c>
+      <c r="G23" s="69" t="inlineStr">
+        <is>
+          <t>→ HOÀN TẤT</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="75" t="inlineStr">
+        <is>
+          <t>S4 HOAN_TAT</t>
+        </is>
+      </c>
+      <c r="B24" s="76" t="inlineStr">
+        <is>
+          <t>Chuyển về /</t>
+        </is>
+      </c>
+      <c r="C24" s="76" t="inlineStr">
+        <is>
+          <t>Chuyển về /</t>
+        </is>
+      </c>
+      <c r="D24" s="76" t="inlineStr">
+        <is>
+          <t>Chuyển về /</t>
+        </is>
+      </c>
+      <c r="E24" s="76" t="inlineStr">
+        <is>
+          <t>Chuyển về /</t>
+        </is>
+      </c>
+      <c r="F24" s="76" t="inlineStr">
+        <is>
+          <t>Chuyển về /</t>
+        </is>
+      </c>
+      <c r="G24" s="76" t="inlineStr">
+        <is>
+          <t>Chuyển về /</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="40" customHeight="1">
+      <c r="A25" s="56" t="inlineStr">
+        <is>
+          <t>Ma trận 4 trạng thái × 6 sự kiện = 24 ô. Hàng S4 toàn bộ là "chuyển về /" — đó chính là hình ảnh của TRẠNG THÁI HẤP THỤ: vào rồi thì không sự kiện nào đưa ra được. Ba hàng trên giống nhau vì mọi bước đều cho phép bỏ qua, nên nhảy cóc không giành thêm quyền gì.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>BẢNG CHUYỂN TRẠNG THÁI — mẫu slide 39</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="65" t="inlineStr">
+        <is>
+          <t>Test Case No.</t>
+        </is>
+      </c>
+      <c r="B28" s="65" t="inlineStr">
+        <is>
+          <t>Start State</t>
+        </is>
+      </c>
+      <c r="C28" s="65" t="inlineStr">
+        <is>
+          <t>Event / Input</t>
+        </is>
+      </c>
+      <c r="D28" s="65" t="inlineStr">
+        <is>
+          <t>End State / Exp Output</t>
+        </is>
+      </c>
+      <c r="E28" s="65" t="inlineStr">
+        <is>
+          <t>Hợp lệ</t>
+        </is>
+      </c>
+      <c r="F28" s="65" t="inlineStr">
+        <is>
+          <t>Tác dụng phụ kiểm chứng</t>
+        </is>
+      </c>
+      <c r="G28" s="65" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="H28" s="65" t="inlineStr">
+        <is>
+          <t>Method trong code</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="B29" s="66" t="inlineStr">
+        <is>
+          <t>S1 MOI_TAO</t>
+        </is>
+      </c>
+      <c r="C29" s="66" t="inlineStr">
+        <is>
+          <t>POST step1 — chọn nghề hợp lệ</t>
+        </is>
+      </c>
+      <c r="D29" s="66" t="inlineStr">
+        <is>
+          <t>S2 DA_CHON_NGHE</t>
+        </is>
+      </c>
+      <c r="E29" s="67" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="F29" s="66" t="inlineStr">
+        <is>
+          <t>Gọi setTargetRole, sang bước 2</t>
+        </is>
+      </c>
+      <c r="G29" s="68" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H29" s="73" t="inlineStr">
+        <is>
+          <t>st01_moiTao_chonNghe_sangBuoc2</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="67" t="n">
+        <v>2</v>
+      </c>
+      <c r="B30" s="66" t="inlineStr">
+        <is>
+          <t>S1 MOI_TAO</t>
+        </is>
+      </c>
+      <c r="C30" s="66" t="inlineStr">
+        <is>
+          <t>POST step1 — không chọn gì</t>
+        </is>
+      </c>
+      <c r="D30" s="66" t="inlineStr">
+        <is>
+          <t>S1 MOI_TAO (tự lặp)</t>
+        </is>
+      </c>
+      <c r="E30" s="67" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="F30" s="66" t="inlineStr">
+        <is>
+          <t>Hiện lỗi, KHÔNG ghi hồ sơ</t>
+        </is>
+      </c>
+      <c r="G30" s="68" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H30" s="73" t="inlineStr">
+        <is>
+          <t>st02_moiTao_khongChonGi_tuLap</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="67" t="n">
         <v>3</v>
       </c>
-      <c r="F11" s="5" t="inlineStr"/>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>Đủ cả 6 cạnh hai chiều giữa 3 trạng thái</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="10" t="inlineStr">
-        <is>
-          <t>Vòng đời token</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>04b</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>Hai cờ boolean: used, expiresAt</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F12" s="5" t="inlineStr"/>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>Một chiều — không cạnh nào đi ngược</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="10" t="inlineStr">
-        <is>
-          <t>Khai báo hồ sơ lần đầu</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>04c</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>TỔ HỢP nhiều cờ trên bản ghi User</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr"/>
-      <c r="E13" s="6" t="n">
+      <c r="B31" s="66" t="inlineStr">
+        <is>
+          <t>S1 MOI_TAO</t>
+        </is>
+      </c>
+      <c r="C31" s="66" t="inlineStr">
+        <is>
+          <t>POST step1 — bấm Bỏ qua</t>
+        </is>
+      </c>
+      <c r="D31" s="66" t="inlineStr">
+        <is>
+          <t>S1 MOI_TAO (tự lặp)</t>
+        </is>
+      </c>
+      <c r="E31" s="67" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="F31" s="66" t="inlineStr">
+        <is>
+          <t>Sang bước 2 nhưng KHÔNG lưu định hướng</t>
+        </is>
+      </c>
+      <c r="G31" s="68" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H31" s="73" t="inlineStr">
+        <is>
+          <t>st03_moiTao_boQua_tuLap</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="67" t="n">
         <v>4</v>
       </c>
-      <c r="F13" s="5" t="inlineStr"/>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>Có trạng thái HẤP THỤ: vào rồi không ra được</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="inlineStr"/>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="55" t="inlineStr">
-        <is>
-          <t>Điểm mới của bảng này: trạng thái KHÔNG nằm trong một cột enum mà là tổ hợp cờ targetRoleId + transcriptPath/githubUsername + onboardingCompleted. Phải tự đặt tên bốn trạng thái trước khi vẽ được sơ đồ — bước mà hai máy trước không cần làm.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>BỐN TRẠNG THÁI</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>Mã</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>Tên trạng thái</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>Định nghĩa bằng dữ liệu</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr"/>
-      <c r="E17" s="4" t="inlineStr"/>
-      <c r="F17" s="4" t="inlineStr"/>
-      <c r="G17" s="4" t="inlineStr"/>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>Ghi chú</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="61" t="inlineStr">
-        <is>
-          <t>S1</t>
-        </is>
-      </c>
-      <c r="B18" s="10" t="inlineStr">
-        <is>
-          <t>MOI_TAO</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>onboardingCompleted = false, chưa qua bước nào</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="inlineStr"/>
-      <c r="F18" s="5" t="inlineStr"/>
-      <c r="G18" s="5" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>trạng thái khởi đầu</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="61" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="B19" s="10" t="inlineStr">
-        <is>
-          <t>DA_CHON_NGHE</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>đã gửi bước 1</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr"/>
-      <c r="E19" s="5" t="inlineStr"/>
-      <c r="F19" s="5" t="inlineStr"/>
-      <c r="G19" s="5" t="inlineStr"/>
-      <c r="H19" s="5" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="61" t="inlineStr">
-        <is>
-          <t>S3</t>
-        </is>
-      </c>
-      <c r="B20" s="10" t="inlineStr">
-        <is>
-          <t>DA_NAP_NGUON</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>đã gửi bước 2 (bảng điểm và/hoặc GitHub)</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr"/>
-      <c r="E20" s="5" t="inlineStr"/>
-      <c r="F20" s="5" t="inlineStr"/>
-      <c r="G20" s="5" t="inlineStr"/>
-      <c r="H20" s="5" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="61" t="inlineStr">
-        <is>
-          <t>S4</t>
-        </is>
-      </c>
-      <c r="B21" s="10" t="inlineStr">
-        <is>
-          <t>HOAN_TAT</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>onboardingCompleted = true</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr"/>
-      <c r="E21" s="5" t="inlineStr"/>
-      <c r="F21" s="5" t="inlineStr"/>
-      <c r="G21" s="5" t="inlineStr"/>
-      <c r="H21" s="25" t="inlineStr">
-        <is>
-          <t>TRẠNG THÁI HẤP THỤ — không có đường ra</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="24" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>SƠ ĐỒ TRẠNG THÁI</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        S1 MOI_TAO  ──[POST step1, chọn nghề]──►  S2 DA_CHON_NGHE</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         │    ▲                                          │</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         │    └──[không chọn gì] / [bấm Bỏ qua]          │  [POST step2]</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         │                                                ▼</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         └──────[GET step3, nhảy cóc]───────►  S3 DA_NAP_NGUON</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                                                          │  [POST step3]</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                                                          ▼</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                                              S4 HOAN_TAT  ◄──┐</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                                                   │          │</t>
+      <c r="B32" s="66" t="inlineStr">
+        <is>
+          <t>S2 DA_CHON_NGHE</t>
+        </is>
+      </c>
+      <c r="C32" s="66" t="inlineStr">
+        <is>
+          <t>POST step2 — không nạp gì</t>
+        </is>
+      </c>
+      <c r="D32" s="66" t="inlineStr">
+        <is>
+          <t>S3 DA_NAP_NGUON</t>
+        </is>
+      </c>
+      <c r="E32" s="67" t="inlineStr">
+        <is>
+          <t>Có</t>
+        </is>
+      </c>
+      <c r="F32" s="66" t="inlineStr">
+        <is>
+          <t>Bước 2 hoàn toàn tuỳ chọn</t>
+        </is>
+      </c>
+      <c r="G32" s="68" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H32" s="73" t="inlineStr">
+        <is>
+          <t>st04_daChonNghe_napNguon_sangBuoc3</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                                                   └──[mọi điểm vào]──┘  → chuyển hướng về /</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="26" customHeight="1">
-      <c r="A34" s="55" t="inlineStr">
-        <is>
-          <t>Hai cạnh tự lặp ở S1 cùng đích nhưng KHÁC hành động, nên bảng bên dưới tách thành hai dòng ST-02 và ST-03. Cạnh vòng ở S4 là cạnh quan trọng nhất của cả sơ đồ.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="24" customHeight="1">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>BẢNG CHUYỂN TRẠNG THÁI — mẫu slide 39 · 5 cạnh hợp lệ, 2 nhóm cạnh bị chặn</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="4" t="inlineStr">
-        <is>
-          <t>Test Case No.</t>
-        </is>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>Start State</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t>Event / Input</t>
-        </is>
-      </c>
-      <c r="D37" s="4" t="inlineStr">
-        <is>
-          <t>End State / Exp Output</t>
-        </is>
-      </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>Hợp lệ</t>
-        </is>
-      </c>
-      <c r="F37" s="4" t="inlineStr">
-        <is>
-          <t>Tác dụng phụ kiểm chứng</t>
-        </is>
-      </c>
-      <c r="G37" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="H37" s="4" t="inlineStr">
-        <is>
-          <t>Method trong code</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>ST-01</t>
-        </is>
-      </c>
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>MOI_TAO</t>
-        </is>
-      </c>
-      <c r="C38" s="5" t="inlineStr">
-        <is>
-          <t>POST step1 — chọn nghề hợp lệ</t>
-        </is>
-      </c>
-      <c r="D38" s="5" t="inlineStr">
-        <is>
-          <t>DA_CHON_NGHE</t>
-        </is>
-      </c>
-      <c r="E38" s="6" t="inlineStr">
+      <c r="A33" s="67" t="n">
+        <v>5</v>
+      </c>
+      <c r="B33" s="66" t="inlineStr">
+        <is>
+          <t>S3 DA_NAP_NGUON</t>
+        </is>
+      </c>
+      <c r="C33" s="66" t="inlineStr">
+        <is>
+          <t>POST step3 — chọn kỹ năng</t>
+        </is>
+      </c>
+      <c r="D33" s="66" t="inlineStr">
+        <is>
+          <t>S4 HOAN_TAT</t>
+        </is>
+      </c>
+      <c r="E33" s="67" t="inlineStr">
         <is>
           <t>Có</t>
         </is>
       </c>
-      <c r="F38" s="5" t="inlineStr">
-        <is>
-          <t>Gọi setTargetRole, chuyển sang bước 2</t>
-        </is>
-      </c>
-      <c r="G38" s="13" t="inlineStr">
+      <c r="F33" s="66" t="inlineStr">
+        <is>
+          <t>replaceSkills rồi completeOnboarding</t>
+        </is>
+      </c>
+      <c r="G33" s="68" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="H38" s="58" t="inlineStr">
-        <is>
-          <t>st01_moiTao_chonNghe_sangBuoc2</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>ST-02</t>
-        </is>
-      </c>
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>MOI_TAO</t>
-        </is>
-      </c>
-      <c r="C39" s="5" t="inlineStr">
-        <is>
-          <t>POST step1 — không chọn gì</t>
-        </is>
-      </c>
-      <c r="D39" s="5" t="inlineStr">
-        <is>
-          <t>MOI_TAO (tự lặp)</t>
-        </is>
-      </c>
-      <c r="E39" s="6" t="inlineStr">
+      <c r="H33" s="73" t="inlineStr">
+        <is>
+          <t>st05_daNapNguon_chonKyNang_hoanTat</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="67" t="n">
+        <v>6</v>
+      </c>
+      <c r="B34" s="66" t="inlineStr">
+        <is>
+          <t>S4 HOAN_TAT</t>
+        </is>
+      </c>
+      <c r="C34" s="66" t="inlineStr">
+        <is>
+          <t>GET step1 / step2 / step3, POST step1 / step2</t>
+        </is>
+      </c>
+      <c r="D34" s="66" t="inlineStr">
+        <is>
+          <t>Bị chặn — về /</t>
+        </is>
+      </c>
+      <c r="E34" s="67" t="inlineStr">
+        <is>
+          <t>KHÔNG</t>
+        </is>
+      </c>
+      <c r="F34" s="66" t="inlineStr">
+        <is>
+          <t>5 điểm vào, không điểm nào đụng hồ sơ</t>
+        </is>
+      </c>
+      <c r="G34" s="68" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H34" s="73" t="inlineStr">
+        <is>
+          <t>st06_hoanTat_moiDiemVaoBiChan</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="67" t="n">
+        <v>7</v>
+      </c>
+      <c r="B35" s="66" t="inlineStr">
+        <is>
+          <t>S4 HOAN_TAT</t>
+        </is>
+      </c>
+      <c r="C35" s="66" t="inlineStr">
+        <is>
+          <t>POST step3 lần nữa</t>
+        </is>
+      </c>
+      <c r="D35" s="66" t="inlineStr">
+        <is>
+          <t>Bị chặn — về /</t>
+        </is>
+      </c>
+      <c r="E35" s="67" t="inlineStr">
+        <is>
+          <t>KHÔNG</t>
+        </is>
+      </c>
+      <c r="F35" s="66" t="inlineStr">
+        <is>
+          <t>KHÔNG gọi replaceSkills — kỹ năng cũ nguyên vẹn</t>
+        </is>
+      </c>
+      <c r="G35" s="68" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H35" s="73" t="inlineStr">
+        <is>
+          <t>st07_hoanTat_guiLaiBuoc3_khongXoaKyNang</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="67" t="n">
+        <v>8</v>
+      </c>
+      <c r="B36" s="66" t="inlineStr">
+        <is>
+          <t>S1 MOI_TAO</t>
+        </is>
+      </c>
+      <c r="C36" s="66" t="inlineStr">
+        <is>
+          <t>GET step3 — nhảy cóc bỏ bước 1 và 2</t>
+        </is>
+      </c>
+      <c r="D36" s="66" t="inlineStr">
+        <is>
+          <t>S1 MOI_TAO — vào được</t>
+        </is>
+      </c>
+      <c r="E36" s="67" t="inlineStr">
         <is>
           <t>Có</t>
         </is>
       </c>
-      <c r="F39" s="5" t="inlineStr">
-        <is>
-          <t>Hiện lỗi 'Vui lòng chọn một vị trí nghề nghiệp.', KHÔNG ghi hồ sơ</t>
-        </is>
-      </c>
-      <c r="G39" s="13" t="inlineStr">
+      <c r="F36" s="66" t="inlineStr">
+        <is>
+          <t>Hiển thị bước 3, hành vi CỐ Ý</t>
+        </is>
+      </c>
+      <c r="G36" s="68" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="H39" s="58" t="inlineStr">
-        <is>
-          <t>st02_moiTao_khongChonGi_tuLap</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>ST-03</t>
-        </is>
-      </c>
-      <c r="B40" s="5" t="inlineStr">
-        <is>
-          <t>MOI_TAO</t>
-        </is>
-      </c>
-      <c r="C40" s="5" t="inlineStr">
-        <is>
-          <t>POST step1 — bấm Bỏ qua</t>
-        </is>
-      </c>
-      <c r="D40" s="5" t="inlineStr">
-        <is>
-          <t>MOI_TAO (tự lặp)</t>
-        </is>
-      </c>
-      <c r="E40" s="6" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="F40" s="5" t="inlineStr">
-        <is>
-          <t>Sang bước 2 nhưng KHÔNG lưu định hướng, không báo lỗi</t>
-        </is>
-      </c>
-      <c r="G40" s="13" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H40" s="58" t="inlineStr">
-        <is>
-          <t>st03_moiTao_boQua_tuLap</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t>ST-04</t>
-        </is>
-      </c>
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>DA_CHON_NGHE</t>
-        </is>
-      </c>
-      <c r="C41" s="5" t="inlineStr">
-        <is>
-          <t>POST step2 — không nạp gì</t>
-        </is>
-      </c>
-      <c r="D41" s="5" t="inlineStr">
-        <is>
-          <t>DA_NAP_NGUON</t>
-        </is>
-      </c>
-      <c r="E41" s="6" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="F41" s="5" t="inlineStr">
-        <is>
-          <t>Không gọi storeTranscript, không gọi setGithub — bước 2 hoàn toàn tuỳ chọn</t>
-        </is>
-      </c>
-      <c r="G41" s="13" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H41" s="58" t="inlineStr">
-        <is>
-          <t>st04_daChonNghe_napNguon_sangBuoc3</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>ST-05</t>
-        </is>
-      </c>
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>DA_NAP_NGUON</t>
-        </is>
-      </c>
-      <c r="C42" s="5" t="inlineStr">
-        <is>
-          <t>POST step3 — chọn kỹ năng</t>
-        </is>
-      </c>
-      <c r="D42" s="5" t="inlineStr">
-        <is>
-          <t>HOAN_TAT</t>
-        </is>
-      </c>
-      <c r="E42" s="6" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="F42" s="5" t="inlineStr">
-        <is>
-          <t>Gọi replaceSkills rồi completeOnboarding, về trang chủ</t>
-        </is>
-      </c>
-      <c r="G42" s="13" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H42" s="58" t="inlineStr">
-        <is>
-          <t>st05_daNapNguon_chonKyNang_hoanTat</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>ST-06</t>
-        </is>
-      </c>
-      <c r="B43" s="5" t="inlineStr">
-        <is>
-          <t>HOAN_TAT</t>
-        </is>
-      </c>
-      <c r="C43" s="5" t="inlineStr">
-        <is>
-          <t>GET step1 / GET step2 / GET step3 / POST step1 / POST step2</t>
-        </is>
-      </c>
-      <c r="D43" s="25" t="inlineStr">
-        <is>
-          <t>Bị chặn — chuyển hướng về /</t>
-        </is>
-      </c>
-      <c r="E43" s="20" t="inlineStr">
-        <is>
-          <t>KHÔNG</t>
-        </is>
-      </c>
-      <c r="F43" s="5" t="inlineStr">
-        <is>
-          <t>5 điểm vào, không điểm nào đụng vào hồ sơ đã hoàn tất</t>
-        </is>
-      </c>
-      <c r="G43" s="13" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H43" s="58" t="inlineStr">
-        <is>
-          <t>st06_hoanTat_moiDiemVaoBiChan</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="5" t="inlineStr">
-        <is>
-          <t>ST-07</t>
-        </is>
-      </c>
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>HOAN_TAT</t>
-        </is>
-      </c>
-      <c r="C44" s="5" t="inlineStr">
-        <is>
-          <t>POST step3 lần nữa</t>
-        </is>
-      </c>
-      <c r="D44" s="25" t="inlineStr">
-        <is>
-          <t>Bị chặn — chuyển hướng về /</t>
-        </is>
-      </c>
-      <c r="E44" s="20" t="inlineStr">
-        <is>
-          <t>KHÔNG</t>
-        </is>
-      </c>
-      <c r="F44" s="5" t="inlineStr">
-        <is>
-          <t>KHÔNG gọi replaceSkills — danh sách kỹ năng cũ nguyên vẹn</t>
-        </is>
-      </c>
-      <c r="G44" s="13" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H44" s="58" t="inlineStr">
-        <is>
-          <t>st07_hoanTat_guiLaiBuoc3_khongXoaKyNang</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t>ST-08</t>
-        </is>
-      </c>
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>MOI_TAO</t>
-        </is>
-      </c>
-      <c r="C45" s="5" t="inlineStr">
-        <is>
-          <t>GET step3 — nhảy cóc bỏ bước 1 và 2</t>
-        </is>
-      </c>
-      <c r="D45" s="5" t="inlineStr">
-        <is>
-          <t>MOI_TAO — vào được</t>
-        </is>
-      </c>
-      <c r="E45" s="6" t="inlineStr">
-        <is>
-          <t>Có</t>
-        </is>
-      </c>
-      <c r="F45" s="5" t="inlineStr">
-        <is>
-          <t>Hiển thị bước 3 với currentStep = 3 (hành vi CỐ Ý, xem ghi chú)</t>
-        </is>
-      </c>
-      <c r="G45" s="13" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H45" s="58" t="inlineStr">
+      <c r="H36" s="73" t="inlineStr">
         <is>
           <t>st08_moiTao_nhayCocSangBuoc3_duocPhep</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="24" customHeight="1">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>TIÊU CHÍ ĐỦ VÀ HAI GHI CHÚ QUAN TRỌNG</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="44" customHeight="1">
-      <c r="A48" s="56" t="inlineStr">
-        <is>
-          <t>TIÊU CHÍ ĐỦ: phủ hết cạnh của sơ đồ. ST-01 → ST-05 phủ trọn đường đi thuận S1 → S2 → S3 → S4, cộng hai cạnh tự lặp. ST-06 và ST-07 phủ cạnh vòng ở trạng thái hấp thụ.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="44" customHeight="1">
-      <c r="A49" s="56" t="inlineStr">
-        <is>
-          <t>ST-06 VÀ ST-07 LÀ PHẦN ĐẮT GIÁ NHẤT. S4 phải là trạng thái hấp thụ: cả SÁU điểm vào (GET và POST của ba bước) đều phải chặn — ST-06 phủ năm điểm, ST-07 phủ điểm thứ sáu. Tách riêng vì nếu bỏ sót chốt chặn ở đúng điểm thứ sáu ấy — POST step3 — thì replaceSkills() sẽ XOÁ SẠCH danh sách kỹ năng người dùng đã chọn. Kiểm thử chỉ đi đường thuận không bao giờ chạm tới cạnh này, vì đường thuận kết thúc ngay khi vào S4.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="44" customHeight="1">
-      <c r="A50" s="56" t="inlineStr">
-        <is>
-          <t>ST-08 — ĐIỀU ĐÃ KIỂM CHỨNG VÀ BÁC BỎ. Ban đầu việc GET step3 thiếu chốt chặn bị NGHI là khiếm khuyết: gõ thẳng URL là vào được bước 3 mà chưa qua bước 1 và 2. Dựng máy trạng thái xong mới thấy KHÔNG phải lỗi — bước 1 có sẵn nút 'Bỏ qua' (skip=true) và mọi trường ở bước 2 đều tuỳ chọn, nên đi đúng luồng giao diện cũng tới được bước 3 với hồ sơ trống. Nhảy cóc không giành thêm quyền gì. ST-08 được giữ lại làm test hồi quy, chốt rằng đây là hành vi CỐ Ý chứ không phải sơ suất.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="44" customHeight="1">
-      <c r="A51" s="56" t="inlineStr">
-        <is>
-          <t>Ghi ST-08 vào báo cáo dù nó KHÔNG tìm ra lỗi là có chủ đích: một nghi vấn đã kiểm chứng và bác bỏ cũng là kết quả kiểm thử. Nếu về sau ai đó thêm chốt chặn vào GET step3 mà không hiểu ngữ cảnh, test này đỏ và buộc họ đọc lại lý do.</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="44" customHeight="1">
-      <c r="A52" s="56" t="inlineStr">
-        <is>
-          <t>GHI CHÚ VỀ ĐIỀU KIỆN CANH: giống bảng ở sheet 04 và 04b, điều kiện phụ được gộp vào cột Event / Input chứ không tách thành cột riêng — giữ đúng bốn cột lõi của slide 39.</t>
+    <row r="38" ht="40" customHeight="1">
+      <c r="A38" s="56" t="inlineStr">
+        <is>
+          <t>TIÊU CHÍ ĐỦ: phủ hết cạnh của sơ đồ. Dòng 1–5 phủ trọn đường đi thuận S1 → S2 → S3 → S4 cộng hai cạnh tự lặp; dòng 6–7 phủ cạnh vòng ở trạng thái hấp thụ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="40" customHeight="1">
+      <c r="A39" s="56" t="inlineStr">
+        <is>
+          <t>DÒNG 6 VÀ 7 LÀ PHẦN ĐẮT GIÁ NHẤT. S4 phải là trạng thái HẤP THỤ: cả sáu điểm vào đều phải chặn — dòng 6 phủ năm điểm, dòng 7 phủ điểm thứ sáu. Tách riêng vì nếu bỏ sót chốt chặn ở đúng điểm thứ sáu ấy (POST step3) thì replaceSkills() sẽ XOÁ SẠCH danh sách kỹ năng người dùng đã chọn. Kiểm thử đi đường thuận không bao giờ chạm tới cạnh này vì đường thuận kết thúc ngay khi vào S4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="40" customHeight="1">
+      <c r="A40" s="56" t="inlineStr">
+        <is>
+          <t>DÒNG 8 — ĐIỀU ĐÃ KIỂM CHỨNG VÀ BÁC BỎ. Ban đầu việc GET step3 thiếu chốt chặn bị NGHI là khiếm khuyết. Dựng ma trận xong mới thấy KHÔNG phải lỗi: ba hàng S1, S2, S3 giống hệt nhau vì bước 1 có nút "Bỏ qua" và mọi trường ở bước 2 đều tuỳ chọn, nên đi đúng luồng giao diện cũng tới được bước 3 với hồ sơ trống. Giữ lại làm test hồi quy, chốt rằng đây là hành vi CỐ Ý.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="40" customHeight="1">
+      <c r="A41" s="56" t="inlineStr">
+        <is>
+          <t>VÌ SAO 8 DÒNG THIẾT KẾ SINH RA 12 TEST: dòng 6 là test tham số hoá, chạy 5 lần cho 5 điểm vào khác nhau.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="40" customHeight="1">
+      <c r="A42" s="56" t="inlineStr">
+        <is>
+          <t>ĐIỂM KHÁC HAI MÁY TRẠNG THÁI TRƯỚC: ở đây trạng thái KHÔNG nằm trong một cột enum mà là tổ hợp cờ trên bản ghi người dùng (targetRoleId, transcriptPath/githubUsername, onboardingCompleted), nên phải tự đặt tên bốn trạng thái trước khi vẽ được sơ đồ.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="24">
+  <mergeCells count="19">
     <mergeCell ref="A9:H9"/>
-    <mergeCell ref="A48:H48"/>
-    <mergeCell ref="A30:H30"/>
-    <mergeCell ref="A24:H24"/>
-    <mergeCell ref="A51:H51"/>
-    <mergeCell ref="A36:H36"/>
-    <mergeCell ref="A49:H49"/>
+    <mergeCell ref="A39:H39"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A11:H11"/>
     <mergeCell ref="A7:H7"/>
     <mergeCell ref="A25:H25"/>
     <mergeCell ref="A16:H16"/>
+    <mergeCell ref="A41:H41"/>
     <mergeCell ref="A27:H27"/>
-    <mergeCell ref="A50:H50"/>
-    <mergeCell ref="A26:H26"/>
-    <mergeCell ref="A33:H33"/>
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="A42:H42"/>
     <mergeCell ref="A14:H14"/>
-    <mergeCell ref="A47:H47"/>
-    <mergeCell ref="A23:H23"/>
-    <mergeCell ref="A32:H32"/>
+    <mergeCell ref="A17:H17"/>
     <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A29:H29"/>
-    <mergeCell ref="A52:H52"/>
-    <mergeCell ref="A28:H28"/>
-    <mergeCell ref="A31:H31"/>
-    <mergeCell ref="A34:H34"/>
+    <mergeCell ref="A38:H38"/>
+    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="A40:H40"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BaoCao-KiemThu-CareerCompass.xlsx
+++ b/BaoCao-KiemThu-CareerCompass.xlsx
@@ -33,7 +33,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="29">
+  <fonts count="30">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -172,6 +172,10 @@
     <font>
       <color rgb="00808080"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <color rgb="00808080"/>
+      <sz val="8"/>
     </font>
   </fonts>
   <fills count="16">
@@ -380,7 +384,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -596,6 +600,9 @@
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -13478,7 +13485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N47"/>
+  <dimension ref="A1:N49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -13561,7 +13568,7 @@
       </c>
       <c r="C6" s="66" t="inlineStr">
         <is>
-          <t>Bảng quyết định · 24 rule → 8 rule</t>
+          <t>Bảng quyết định · 24 rule → 4 rule</t>
         </is>
       </c>
       <c r="D6" s="66" t="inlineStr"/>
@@ -14676,7 +14683,7 @@
     <row r="29" ht="24" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>BẢNG SAU KHI RÚT GỌN — bước 6 slide 42 · 24 rule → 8 rule</t>
+          <t>BẢNG SAU KHI RÚT GỌN — bước 6 slide 42 · 24 rule → 4 rule</t>
         </is>
       </c>
     </row>
@@ -14704,26 +14711,6 @@
       <c r="E30" s="65" t="inlineStr">
         <is>
           <t>R4'</t>
-        </is>
-      </c>
-      <c r="F30" s="65" t="inlineStr">
-        <is>
-          <t>R5'</t>
-        </is>
-      </c>
-      <c r="G30" s="65" t="inlineStr">
-        <is>
-          <t>R6'</t>
-        </is>
-      </c>
-      <c r="H30" s="65" t="inlineStr">
-        <is>
-          <t>R7'</t>
-        </is>
-      </c>
-      <c r="I30" s="65" t="inlineStr">
-        <is>
-          <t>R8'</t>
         </is>
       </c>
       <c r="J30" s="65" t="inlineStr">
@@ -14762,26 +14749,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="F31" s="69" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G31" s="69" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H31" s="69" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I31" s="69" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
       <c r="J31" s="77" t="inlineStr">
         <is>
           <t>2 giá trị</t>
@@ -14801,37 +14768,17 @@
       </c>
       <c r="C32" s="69" t="inlineStr">
         <is>
-          <t>.pdf</t>
+          <t>hợp lệ</t>
         </is>
       </c>
       <c r="D32" s="69" t="inlineStr">
         <is>
-          <t>.png</t>
+          <t>hợp lệ</t>
         </is>
       </c>
       <c r="E32" s="69" t="inlineStr">
         <is>
-          <t>.jpg</t>
-        </is>
-      </c>
-      <c r="F32" s="69" t="inlineStr">
-        <is>
-          <t>.jpeg</t>
-        </is>
-      </c>
-      <c r="G32" s="69" t="inlineStr">
-        <is>
-          <t>hợp lệ</t>
-        </is>
-      </c>
-      <c r="H32" s="69" t="inlineStr">
-        <is>
-          <t>khác</t>
-        </is>
-      </c>
-      <c r="I32" s="69" t="inlineStr">
-        <is>
-          <t>không có dấu chấm</t>
+          <t>không hợp lệ</t>
         </is>
       </c>
       <c r="J32" s="77" t="inlineStr">
@@ -14858,30 +14805,10 @@
       </c>
       <c r="D33" s="69" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E33" s="69" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="F33" s="69" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G33" s="69" t="inlineStr">
-        <is>
           <t>N</t>
         </is>
       </c>
-      <c r="H33" s="72" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I33" s="72" t="inlineStr">
+      <c r="E33" s="72" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -14908,32 +14835,12 @@
           <t>X</t>
         </is>
       </c>
-      <c r="D34" s="71" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E34" s="71" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F34" s="71" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G34" s="67" t="inlineStr">
+      <c r="D34" s="67" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="H34" s="67" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I34" s="67" t="inlineStr">
+      <c r="E34" s="67" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -14965,26 +14872,6 @@
           <t>–</t>
         </is>
       </c>
-      <c r="F35" s="67" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="G35" s="67" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="H35" s="67" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I35" s="67" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
     </row>
     <row r="36">
       <c r="A36" s="70" t="inlineStr">
@@ -15002,32 +14889,12 @@
           <t>–</t>
         </is>
       </c>
-      <c r="D36" s="67" t="inlineStr">
-        <is>
-          <t>–</t>
+      <c r="D36" s="71" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
       <c r="E36" s="67" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F36" s="67" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="G36" s="71" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H36" s="67" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I36" s="67" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -15054,34 +14921,14 @@
           <t>–</t>
         </is>
       </c>
-      <c r="E37" s="67" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F37" s="67" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="G37" s="67" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="H37" s="71" t="inlineStr">
+      <c r="E37" s="71" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="I37" s="71" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
       <c r="J37" s="77" t="inlineStr">
         <is>
-          <t>R8' là cột phát hiện khiếm khuyết DEF-011</t>
+          <t>R4' gộp cả ô đã phát hiện DEF-011 — xem ghi chú bên dưới</t>
         </is>
       </c>
     </row>
@@ -15111,31 +14958,11 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="F38" s="68" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="G38" s="68" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H38" s="68" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I38" s="68" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
+    </row>
+    <row r="39" ht="56" customHeight="1">
       <c r="A39" s="70" t="inlineStr">
         <is>
-          <t>Method trong code</t>
+          <t>Test thi hành rule này</t>
         </is>
       </c>
       <c r="B39" s="73" t="inlineStr">
@@ -15145,102 +14972,121 @@
       </c>
       <c r="C39" s="73" t="inlineStr">
         <is>
-          <t>rule2_duoiPdf_luuThanhCong</t>
+          <t>rule2_duoiPdf_luuThanhCong
+rule3_duoiPng_luuThanhCong
+rule4_duoiJpg_luuThanhCong
+rule5_duoiJpeg_luuThanhCong</t>
         </is>
       </c>
       <c r="D39" s="73" t="inlineStr">
         <is>
-          <t>rule3_duoiPng_luuThanhCong</t>
+          <t>rule6_duoiHopLe_dungLuongQuaLon_tuChoi</t>
         </is>
       </c>
       <c r="E39" s="73" t="inlineStr">
         <is>
-          <t>rule4_duoiJpg_luuThanhCong</t>
-        </is>
-      </c>
-      <c r="F39" s="73" t="inlineStr">
-        <is>
-          <t>rule5_duoiJpeg_luuThanhCong</t>
-        </is>
-      </c>
-      <c r="G39" s="73" t="inlineStr">
-        <is>
-          <t>rule6_duoiHopLe_dungLuongQuaLon_tuChoi</t>
-        </is>
-      </c>
-      <c r="H39" s="73" t="inlineStr">
-        <is>
-          <t>rule7_duoiKhongHopLe_tuChoi</t>
-        </is>
-      </c>
-      <c r="I39" s="73" t="inlineStr">
-        <is>
-          <t>rule8_tenTepKhongCoDuoi_tuChoi</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="20" customHeight="1">
-      <c r="A41" s="55" t="inlineStr">
+          <t>rule7_duoiKhongHopLe_tuChoi
+rule8_tenTepKhongCoDuoi_tuChoi</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="70" t="inlineStr">
+        <is>
+          <t>Gộp từ rule nào</t>
+        </is>
+      </c>
+      <c r="B40" s="78" t="inlineStr">
+        <is>
+          <t>gộp R1–R12</t>
+        </is>
+      </c>
+      <c r="C40" s="78" t="inlineStr">
+        <is>
+          <t>gộp R13, R15, R17, R19</t>
+        </is>
+      </c>
+      <c r="D40" s="78" t="inlineStr">
+        <is>
+          <t>gộp R14, R16, R18, R20</t>
+        </is>
+      </c>
+      <c r="E40" s="78" t="inlineStr">
+        <is>
+          <t>gộp R21–R24</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="55" t="inlineStr">
         <is>
           <t>Ô tô vàng là ô "không quan tâm" (–) sinh ra khi gộp rule.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="44" customHeight="1">
-      <c r="A42" s="56" t="inlineStr">
-        <is>
-          <t>VÌ SAO GỘP ĐƯỢC: mã nguồn kiểm ba điều kiện TUẦN TỰ và thoát ngay khi gặp lỗi. Khi một điều kiện phía trước đã quyết định kết quả thì điều kiện phía sau không còn ảnh hưởng, đánh dấu "–". R1' gộp 12 rule (tên tệp null thì đuôi và dung lượng vô nghĩa); R7' và R8' mỗi cột gộp 2 rule (đuôi sai thì chặn trước khi xét dung lượng).</t>
         </is>
       </c>
     </row>
     <row r="43" ht="44" customHeight="1">
       <c r="A43" s="56" t="inlineStr">
         <is>
-          <t>R6' GỘP THEO KIỂU KHÁC: bốn đuôi hợp lệ khi vượt dung lượng đều cho cùng một hành động, nên bốn rule con thu về một, ô C2 ghi "hợp lệ" thay vì một đuôi cụ thể.</t>
+          <t>BẢNG RÚT GỌN NÓI ÍT HƠN BẢNG ĐẦY ĐỦ — và đó là lý do vẫn phải giữ cả hai. Rút gọn xong chỉ còn 4 rule, nhưng bộ kiểm thử có 8 test. Chênh lệch nằm ở chỗ: xét theo ĐẶC TẢ thì bốn đuôi .pdf, .png, .jpg, .jpeg là MỘT lớp tương đương (cùng được chấp nhận), nên rút gọn gộp chúng làm một ô "hợp lệ". Nhưng xét theo MÃ NGUỒN thì mỗi đuôi là một nhánh riêng của chuỗi &amp;&amp; , và báo cáo bao phủ đã chỉ đích danh ba nhánh chưa ai chạm tới. Nếu chỉ nhìn bảng rút gọn mà viết test thì ba nhánh đó vẫn nằm im.</t>
         </is>
       </c>
     </row>
     <row r="44" ht="44" customHeight="1">
       <c r="A44" s="56" t="inlineStr">
         <is>
-          <t>KHIẾM KHUYẾT DEF-011 — cột R8'. Tệp không có dấu chấm làm lastIndexOf(".") trả -1, kéo theo substring(-1) ném StringIndexOutOfBoundsException, người dùng nhận lỗi 500 thay vì thông báo 400. Nói rõ để không nhận công sai: test hộp trắng đã ghi đúng nguyên nhân từ trước nhưng lại CHỐT hành vi lỗi bằng một khẳng định, nên bộ test vẫn xanh. Đóng góp của kỹ thuật này là BUỘC PHẢI SỬA — mỗi cột của bảng phải ứng với một hành động xác định trong nhóm A1–A4, không thể để một ô là "sập 500".</t>
+          <t>RÚT GỌN CÒN CHE MẤT TRƯỜNG HỢP ĐÃ TÌM RA LỖI: "không có dấu chấm" bị gộp vào R4' cùng với "đuôi khác" vì hai bên cho cùng hành động A4. Nhưng chính ô đó mới là ô làm lộ DEF-011 — trước khi sửa, nó không trả lỗi 400 mà ném StringIndexOutOfBoundsException thành lỗi 500. Bảng đầy đủ giữ nó ở cột R23–R24 nên còn nhìn thấy; bảng rút gọn thì không.</t>
         </is>
       </c>
     </row>
     <row r="45" ht="44" customHeight="1">
       <c r="A45" s="56" t="inlineStr">
         <is>
-          <t>CON SỐ ĐO ĐƯỢC: nhánh OnboardingService 75,0% (9/12) → 100,0% (14/14); dòng 94,7% (18/19) → 100,0% (19/19). Nguồn: target/site/jacoco/jacoco.csv.</t>
+          <t>VÌ SAO GỘP ĐƯỢC: mã nguồn kiểm ba điều kiện TUẦN TỰ và thoát ngay khi gặp lỗi. Khi một điều kiện phía trước đã quyết định kết quả thì điều kiện phía sau không còn ảnh hưởng, đánh dấu "–". R1' gộp 12 rule (tên tệp null thì đuôi và dung lượng vô nghĩa); R7' và R8' mỗi cột gộp 2 rule (đuôi sai thì chặn trước khi xét dung lượng).</t>
         </is>
       </c>
     </row>
     <row r="46" ht="44" customHeight="1">
       <c r="A46" s="56" t="inlineStr">
         <is>
-          <t>QUAN HỆ VỚI SHEET GIÁ TRỊ BIÊN: điều kiện C3 ở bảng này chỉ lấy giá trị NOMINAL (1 byte và 11 MB) để phân biệt nhánh. Các giá trị sát biên 10 MB thuộc về sheet 01.</t>
+          <t>KHIẾM KHUYẾT DEF-011 — cột R23–R24 của bảng đầy đủ. Tệp không có dấu chấm làm lastIndexOf(".") trả -1, kéo theo substring(-1) ném StringIndexOutOfBoundsException, người dùng nhận lỗi 500 thay vì thông báo 400. Nói rõ để không nhận công sai: test hộp trắng đã ghi đúng nguyên nhân từ trước nhưng lại CHỐT hành vi lỗi bằng một khẳng định, nên bộ test vẫn xanh. Đóng góp của kỹ thuật này là BUỘC PHẢI SỬA — mỗi cột của bảng phải ứng với một hành động xác định trong nhóm A1–A4, không thể để một ô là "sập 500".</t>
         </is>
       </c>
     </row>
     <row r="47" ht="44" customHeight="1">
       <c r="A47" s="56" t="inlineStr">
         <is>
+          <t>CON SỐ ĐO ĐƯỢC: nhánh OnboardingService 75,0% (9/12) → 100,0% (14/14); dòng 94,7% (18/19) → 100,0% (19/19). Nguồn: target/site/jacoco/jacoco.csv.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="44" customHeight="1">
+      <c r="A48" s="56" t="inlineStr">
+        <is>
+          <t>QUAN HỆ VỚI SHEET GIÁ TRỊ BIÊN: điều kiện C3 ở bảng này chỉ lấy giá trị NOMINAL (1 byte và 11 MB) để phân biệt nhánh. Các giá trị sát biên 10 MB thuộc về sheet 01.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="44" customHeight="1">
+      <c r="A49" s="56" t="inlineStr">
+        <is>
           <t>KIỂM TRA BỔ SUNG ngoài bảng: đuôi viết HOA "BANGDIEM.PDF" được chấp nhận vì mã gọi toLowerCase — method boSung_duoiVietHoa_duocChapNhan, PASS. Không đưa vào bảng vì đây là biến thể trình bày của C2, không sinh thêm hành động mới.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="18">
     <mergeCell ref="A9:N9"/>
     <mergeCell ref="J30:N30"/>
     <mergeCell ref="A4:N4"/>
     <mergeCell ref="A45:N45"/>
+    <mergeCell ref="A48:N48"/>
     <mergeCell ref="J37:N37"/>
     <mergeCell ref="A47:N47"/>
     <mergeCell ref="A29:N29"/>
     <mergeCell ref="A7:N7"/>
     <mergeCell ref="J32:N32"/>
     <mergeCell ref="A43:N43"/>
-    <mergeCell ref="A41:N41"/>
+    <mergeCell ref="A49:N49"/>
     <mergeCell ref="J33:N33"/>
     <mergeCell ref="A10:N10"/>
     <mergeCell ref="A42:N42"/>

--- a/BaoCao-KiemThu-CareerCompass.xlsx
+++ b/BaoCao-KiemThu-CareerCompass.xlsx
@@ -384,7 +384,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -603,6 +603,12 @@
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1702,8 +1708,8 @@
     <mergeCell ref="F8:H8"/>
     <mergeCell ref="F17:H17"/>
     <mergeCell ref="F23:H23"/>
+    <mergeCell ref="F28:H28"/>
     <mergeCell ref="F22:H22"/>
-    <mergeCell ref="F28:H28"/>
     <mergeCell ref="F13:H13"/>
     <mergeCell ref="F30:H30"/>
     <mergeCell ref="F9:H9"/>
@@ -13485,7 +13491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N49"/>
+  <dimension ref="A1:N48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -13568,7 +13574,7 @@
       </c>
       <c r="C6" s="66" t="inlineStr">
         <is>
-          <t>Bảng quyết định · 24 rule → 4 rule</t>
+          <t>Bảng quyết định · 8 rule → 4 rule</t>
         </is>
       </c>
       <c r="D6" s="66" t="inlineStr"/>
@@ -13597,14 +13603,14 @@
     <row r="9" ht="24" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>BẢNG QUYẾT ĐỊNH ĐẦY ĐỦ — mẫu slide 44 · 24 rule = 2 × 6 × 2</t>
+          <t>BẢNG QUYẾT ĐỊNH ĐẦY ĐỦ — mẫu slide 44 · 8 rule = 2 × 2 × 2</t>
         </is>
       </c>
     </row>
     <row r="10" ht="26" customHeight="1">
       <c r="A10" s="55" t="inlineStr">
         <is>
-          <t>Số rule tối đa = tích số giá trị của các điều kiện. C2 có SÁU giá trị chứ không nhị phân, nên dùng tích số chứ không dùng 2^n. Bảng chia làm hai khối 12 cột cho vừa bề ngang.</t>
+          <t>Số rule tối đa = tích số giá trị của các điều kiện = 2 × 2 × 2 = 8. Cả ba điều kiện đều nhị phân nên ở bảng này công thức 2^n dùng được — khác bảng ProgressService ở sheet 03, nơi điều kiện trạng thái có ba giá trị nên phải nhân chứ không luỹ thừa.</t>
         </is>
       </c>
     </row>
@@ -13654,26 +13660,6 @@
           <t>R8</t>
         </is>
       </c>
-      <c r="J11" s="65" t="inlineStr">
-        <is>
-          <t>R9</t>
-        </is>
-      </c>
-      <c r="K11" s="65" t="inlineStr">
-        <is>
-          <t>R10</t>
-        </is>
-      </c>
-      <c r="L11" s="65" t="inlineStr">
-        <is>
-          <t>R11</t>
-        </is>
-      </c>
-      <c r="M11" s="65" t="inlineStr">
-        <is>
-          <t>R12</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" s="66" t="inlineStr">
@@ -13681,131 +13667,91 @@
           <t>C1 · Tên tệp = null</t>
         </is>
       </c>
-      <c r="B12" s="69" t="inlineStr">
+      <c r="B12" s="67" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="C12" s="69" t="inlineStr">
+      <c r="C12" s="67" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="D12" s="69" t="inlineStr">
+      <c r="D12" s="67" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="E12" s="69" t="inlineStr">
+      <c r="E12" s="67" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="F12" s="69" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G12" s="69" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="H12" s="69" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I12" s="69" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J12" s="69" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K12" s="69" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="L12" s="69" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M12" s="69" t="inlineStr">
-        <is>
-          <t>Y</t>
+      <c r="F12" s="67" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="G12" s="67" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="H12" s="67" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I12" s="67" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="66" t="inlineStr">
         <is>
-          <t>C2 · Đuôi tệp</t>
-        </is>
-      </c>
-      <c r="B13" s="69" t="inlineStr">
-        <is>
-          <t>.pdf</t>
-        </is>
-      </c>
-      <c r="C13" s="69" t="inlineStr">
-        <is>
-          <t>.pdf</t>
-        </is>
-      </c>
-      <c r="D13" s="69" t="inlineStr">
-        <is>
-          <t>.png</t>
-        </is>
-      </c>
-      <c r="E13" s="69" t="inlineStr">
-        <is>
-          <t>.png</t>
-        </is>
-      </c>
-      <c r="F13" s="69" t="inlineStr">
-        <is>
-          <t>.jpg</t>
-        </is>
-      </c>
-      <c r="G13" s="69" t="inlineStr">
-        <is>
-          <t>.jpg</t>
-        </is>
-      </c>
-      <c r="H13" s="69" t="inlineStr">
-        <is>
-          <t>.jpeg</t>
-        </is>
-      </c>
-      <c r="I13" s="69" t="inlineStr">
-        <is>
-          <t>.jpeg</t>
-        </is>
-      </c>
-      <c r="J13" s="69" t="inlineStr">
-        <is>
-          <t>khác</t>
-        </is>
-      </c>
-      <c r="K13" s="69" t="inlineStr">
-        <is>
-          <t>khác</t>
-        </is>
-      </c>
-      <c r="L13" s="69" t="inlineStr">
-        <is>
-          <t>không có dấu chấm</t>
-        </is>
-      </c>
-      <c r="M13" s="69" t="inlineStr">
-        <is>
-          <t>không có dấu chấm</t>
+          <t>C2 · Đuôi tệp thuộc {.pdf, .png, .jpg, .jpeg}</t>
+        </is>
+      </c>
+      <c r="B13" s="67" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="C13" s="67" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D13" s="67" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E13" s="67" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F13" s="67" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G13" s="67" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H13" s="67" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="I13" s="67" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
     </row>
@@ -13815,62 +13761,42 @@
           <t>C3 · Dung lượng ≤ 10MB</t>
         </is>
       </c>
-      <c r="B14" s="69" t="inlineStr">
+      <c r="B14" s="67" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="C14" s="69" t="inlineStr">
+      <c r="C14" s="67" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="D14" s="69" t="inlineStr">
+      <c r="D14" s="67" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="E14" s="69" t="inlineStr">
+      <c r="E14" s="67" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="F14" s="69" t="inlineStr">
+      <c r="F14" s="67" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="G14" s="69" t="inlineStr">
+      <c r="G14" s="67" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="H14" s="69" t="inlineStr">
+      <c r="H14" s="67" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="I14" s="69" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="J14" s="69" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K14" s="69" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L14" s="69" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M14" s="69" t="inlineStr">
+      <c r="I14" s="67" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -13902,42 +13828,22 @@
           <t>–</t>
         </is>
       </c>
-      <c r="F15" s="67" t="inlineStr">
+      <c r="F15" s="71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="G15" s="67" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="G15" s="67" t="inlineStr">
+      <c r="H15" s="67" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="H15" s="67" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
       <c r="I15" s="67" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="J15" s="67" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="K15" s="67" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="L15" s="67" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="M15" s="67" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -13969,44 +13875,24 @@
           <t>X</t>
         </is>
       </c>
-      <c r="F16" s="71" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G16" s="71" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H16" s="71" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I16" s="71" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J16" s="71" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K16" s="71" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L16" s="71" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M16" s="71" t="inlineStr">
-        <is>
-          <t>X</t>
+      <c r="F16" s="67" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="G16" s="67" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="H16" s="67" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="I16" s="67" t="inlineStr">
+        <is>
+          <t>–</t>
         </is>
       </c>
     </row>
@@ -14041,37 +13927,17 @@
           <t>–</t>
         </is>
       </c>
-      <c r="G17" s="67" t="inlineStr">
+      <c r="G17" s="71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="H17" s="67" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="H17" s="67" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
       <c r="I17" s="67" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="J17" s="67" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="K17" s="67" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="L17" s="67" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="M17" s="67" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -14113,376 +13979,160 @@
           <t>–</t>
         </is>
       </c>
-      <c r="H18" s="67" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I18" s="67" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="J18" s="67" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="K18" s="67" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="L18" s="67" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="M18" s="67" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="65" t="inlineStr">
+      <c r="H18" s="71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I18" s="71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>BẢNG SAU KHI RÚT GỌN — bước 6 slide 42 · 8 rule → 4 rule</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="65" t="inlineStr">
         <is>
           <t>Condition / Action</t>
         </is>
       </c>
-      <c r="B20" s="65" t="inlineStr">
-        <is>
-          <t>R13</t>
-        </is>
-      </c>
-      <c r="C20" s="65" t="inlineStr">
-        <is>
-          <t>R14</t>
-        </is>
-      </c>
-      <c r="D20" s="65" t="inlineStr">
-        <is>
-          <t>R15</t>
-        </is>
-      </c>
-      <c r="E20" s="65" t="inlineStr">
-        <is>
-          <t>R16</t>
-        </is>
-      </c>
-      <c r="F20" s="65" t="inlineStr">
-        <is>
-          <t>R17</t>
-        </is>
-      </c>
-      <c r="G20" s="65" t="inlineStr">
-        <is>
-          <t>R18</t>
-        </is>
-      </c>
-      <c r="H20" s="65" t="inlineStr">
-        <is>
-          <t>R19</t>
-        </is>
-      </c>
-      <c r="I20" s="65" t="inlineStr">
-        <is>
-          <t>R20</t>
-        </is>
-      </c>
-      <c r="J20" s="65" t="inlineStr">
-        <is>
-          <t>R21</t>
-        </is>
-      </c>
-      <c r="K20" s="65" t="inlineStr">
-        <is>
-          <t>R22</t>
-        </is>
-      </c>
-      <c r="L20" s="65" t="inlineStr">
-        <is>
-          <t>R23</t>
-        </is>
-      </c>
-      <c r="M20" s="65" t="inlineStr">
-        <is>
-          <t>R24</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="66" t="inlineStr">
-        <is>
-          <t>C1 · Tên tệp = null</t>
-        </is>
-      </c>
-      <c r="B21" s="69" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="C21" s="69" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="D21" s="69" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E21" s="69" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F21" s="69" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G21" s="69" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H21" s="69" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I21" s="69" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="J21" s="69" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K21" s="69" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L21" s="69" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M21" s="69" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+      <c r="B21" s="65" t="inlineStr">
+        <is>
+          <t>R1'</t>
+        </is>
+      </c>
+      <c r="C21" s="65" t="inlineStr">
+        <is>
+          <t>R2'</t>
+        </is>
+      </c>
+      <c r="D21" s="65" t="inlineStr">
+        <is>
+          <t>R3'</t>
+        </is>
+      </c>
+      <c r="E21" s="65" t="inlineStr">
+        <is>
+          <t>R4'</t>
+        </is>
+      </c>
+      <c r="J21" s="65" t="inlineStr">
+        <is>
+          <t>Ghi chú</t>
+        </is>
+      </c>
+      <c r="K21" s="8" t="n"/>
+      <c r="L21" s="8" t="n"/>
+      <c r="M21" s="8" t="n"/>
+      <c r="N21" s="9" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="66" t="inlineStr">
         <is>
-          <t>C2 · Đuôi tệp</t>
+          <t>C1 · Tên tệp = null</t>
         </is>
       </c>
       <c r="B22" s="69" t="inlineStr">
         <is>
-          <t>.pdf</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="C22" s="69" t="inlineStr">
         <is>
-          <t>.pdf</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D22" s="69" t="inlineStr">
         <is>
-          <t>.png</t>
+          <t>N</t>
         </is>
       </c>
       <c r="E22" s="69" t="inlineStr">
         <is>
-          <t>.png</t>
-        </is>
-      </c>
-      <c r="F22" s="69" t="inlineStr">
-        <is>
-          <t>.jpg</t>
-        </is>
-      </c>
-      <c r="G22" s="69" t="inlineStr">
-        <is>
-          <t>.jpg</t>
-        </is>
-      </c>
-      <c r="H22" s="69" t="inlineStr">
-        <is>
-          <t>.jpeg</t>
-        </is>
-      </c>
-      <c r="I22" s="69" t="inlineStr">
-        <is>
-          <t>.jpeg</t>
-        </is>
-      </c>
-      <c r="J22" s="69" t="inlineStr">
-        <is>
-          <t>khác</t>
-        </is>
-      </c>
-      <c r="K22" s="69" t="inlineStr">
-        <is>
-          <t>khác</t>
-        </is>
-      </c>
-      <c r="L22" s="69" t="inlineStr">
-        <is>
-          <t>không có dấu chấm</t>
-        </is>
-      </c>
-      <c r="M22" s="69" t="inlineStr">
-        <is>
-          <t>không có dấu chấm</t>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J22" s="77" t="inlineStr">
+        <is>
+          <t>2 giá trị</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="66" t="inlineStr">
         <is>
+          <t>C2 · Đuôi tệp thuộc {.pdf, .png, .jpg, .jpeg}</t>
+        </is>
+      </c>
+      <c r="B23" s="72" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C23" s="69" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D23" s="69" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E23" s="69" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J23" s="77" t="inlineStr">
+        <is>
+          <t>2 giá trị — đặc tả không phân biệt bốn đuôi với nhau</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="66" t="inlineStr">
+        <is>
           <t>C3 · Dung lượng ≤ 10MB</t>
         </is>
       </c>
-      <c r="B23" s="69" t="inlineStr">
+      <c r="B24" s="72" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C24" s="69" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="C23" s="69" t="inlineStr">
+      <c r="D24" s="69" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="D23" s="69" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E23" s="69" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="F23" s="69" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G23" s="69" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H23" s="69" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I23" s="69" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="J23" s="69" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K23" s="69" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L23" s="69" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M23" s="69" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="70" t="inlineStr">
-        <is>
-          <t>A1 · Lưu tệp, trả đường dẫn</t>
-        </is>
-      </c>
-      <c r="B24" s="71" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C24" s="67" t="inlineStr">
+      <c r="E24" s="72" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="D24" s="71" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E24" s="67" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F24" s="71" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G24" s="67" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="H24" s="71" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I24" s="67" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="J24" s="67" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="K24" s="67" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="L24" s="67" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="M24" s="67" t="inlineStr">
-        <is>
-          <t>–</t>
+      <c r="J24" s="77" t="inlineStr">
+        <is>
+          <t>2 giá trị</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="70" t="inlineStr">
         <is>
-          <t>A2 · Lỗi "Tên file không hợp lệ"</t>
+          <t>A1 · Lưu tệp, trả đường dẫn</t>
         </is>
       </c>
       <c r="B25" s="67" t="inlineStr">
@@ -14490,57 +14140,17 @@
           <t>–</t>
         </is>
       </c>
-      <c r="C25" s="67" t="inlineStr">
+      <c r="C25" s="71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D25" s="67" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="D25" s="67" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
       <c r="E25" s="67" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F25" s="67" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="G25" s="67" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="H25" s="67" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I25" s="67" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="J25" s="67" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="K25" s="67" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="L25" s="67" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="M25" s="67" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -14549,65 +14159,25 @@
     <row r="26">
       <c r="A26" s="70" t="inlineStr">
         <is>
-          <t>A3 · Lỗi "Vượt quá dung lượng 10MB"</t>
-        </is>
-      </c>
-      <c r="B26" s="67" t="inlineStr">
+          <t>A2 · Lỗi "Tên file không hợp lệ"</t>
+        </is>
+      </c>
+      <c r="B26" s="71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C26" s="67" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="C26" s="71" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
       <c r="D26" s="67" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="E26" s="71" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F26" s="67" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="G26" s="71" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="H26" s="67" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I26" s="71" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J26" s="67" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="K26" s="67" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="L26" s="67" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="M26" s="67" t="inlineStr">
+      <c r="E26" s="67" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -14616,361 +14186,101 @@
     <row r="27">
       <c r="A27" s="70" t="inlineStr">
         <is>
+          <t>A3 · Lỗi "Vượt quá dung lượng 10MB"</t>
+        </is>
+      </c>
+      <c r="B27" s="67" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C27" s="67" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="D27" s="71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E27" s="67" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="70" t="inlineStr">
+        <is>
           <t>A4 · Lỗi "Chỉ chấp nhận PDF, PNG hoặc JPG"</t>
         </is>
       </c>
-      <c r="B27" s="67" t="inlineStr">
+      <c r="B28" s="67" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="C27" s="67" t="inlineStr">
+      <c r="C28" s="67" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="D27" s="67" t="inlineStr">
+      <c r="D28" s="67" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="E27" s="67" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="F27" s="67" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="G27" s="67" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="H27" s="67" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="I27" s="67" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="J27" s="71" t="inlineStr">
+      <c r="E28" s="71" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="K27" s="71" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L27" s="71" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M27" s="71" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="24" customHeight="1">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>BẢNG SAU KHI RÚT GỌN — bước 6 slide 42 · 24 rule → 4 rule</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="65" t="inlineStr">
-        <is>
-          <t>Condition / Action</t>
-        </is>
-      </c>
-      <c r="B30" s="65" t="inlineStr">
-        <is>
-          <t>R1'</t>
-        </is>
-      </c>
-      <c r="C30" s="65" t="inlineStr">
-        <is>
-          <t>R2'</t>
-        </is>
-      </c>
-      <c r="D30" s="65" t="inlineStr">
-        <is>
-          <t>R3'</t>
-        </is>
-      </c>
-      <c r="E30" s="65" t="inlineStr">
-        <is>
-          <t>R4'</t>
-        </is>
-      </c>
-      <c r="J30" s="65" t="inlineStr">
-        <is>
-          <t>Ghi chú</t>
-        </is>
-      </c>
-      <c r="K30" s="8" t="n"/>
-      <c r="L30" s="8" t="n"/>
-      <c r="M30" s="8" t="n"/>
-      <c r="N30" s="9" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="66" t="inlineStr">
-        <is>
-          <t>C1 · Tên tệp = null</t>
-        </is>
-      </c>
-      <c r="B31" s="69" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="C31" s="69" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="D31" s="69" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E31" s="69" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="J31" s="77" t="inlineStr">
-        <is>
-          <t>2 giá trị</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="66" t="inlineStr">
-        <is>
-          <t>C2 · Đuôi tệp</t>
-        </is>
-      </c>
-      <c r="B32" s="72" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C32" s="69" t="inlineStr">
-        <is>
-          <t>hợp lệ</t>
-        </is>
-      </c>
-      <c r="D32" s="69" t="inlineStr">
-        <is>
-          <t>hợp lệ</t>
-        </is>
-      </c>
-      <c r="E32" s="69" t="inlineStr">
-        <is>
-          <t>không hợp lệ</t>
-        </is>
-      </c>
-      <c r="J32" s="77" t="inlineStr">
-        <is>
-          <t>6 giá trị — đây là lý do dùng tích số chứ không dùng 2^n</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="66" t="inlineStr">
-        <is>
-          <t>C3 · Dung lượng ≤ 10MB</t>
-        </is>
-      </c>
-      <c r="B33" s="72" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C33" s="69" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D33" s="69" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E33" s="72" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="J33" s="77" t="inlineStr">
-        <is>
-          <t>2 giá trị</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="70" t="inlineStr">
-        <is>
-          <t>A1 · Lưu tệp, trả đường dẫn</t>
-        </is>
-      </c>
-      <c r="B34" s="67" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C34" s="71" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D34" s="67" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="E34" s="67" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="70" t="inlineStr">
-        <is>
-          <t>A2 · Lỗi "Tên file không hợp lệ"</t>
-        </is>
-      </c>
-      <c r="B35" s="71" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C35" s="67" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="D35" s="67" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="E35" s="67" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="70" t="inlineStr">
-        <is>
-          <t>A3 · Lỗi "Vượt quá dung lượng 10MB"</t>
-        </is>
-      </c>
-      <c r="B36" s="67" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C36" s="67" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="D36" s="71" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E36" s="67" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="70" t="inlineStr">
-        <is>
-          <t>A4 · Lỗi "Chỉ chấp nhận PDF, PNG hoặc JPG"</t>
-        </is>
-      </c>
-      <c r="B37" s="67" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C37" s="67" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="D37" s="67" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="E37" s="71" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J37" s="77" t="inlineStr">
+      <c r="J28" s="77" t="inlineStr">
         <is>
           <t>R4' gộp cả ô đã phát hiện DEF-011 — xem ghi chú bên dưới</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="70" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="70" t="inlineStr">
         <is>
           <t>Kết quả chạy test</t>
         </is>
       </c>
-      <c r="B38" s="68" t="inlineStr">
+      <c r="B29" s="68" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="C38" s="68" t="inlineStr">
+      <c r="C29" s="68" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="D38" s="68" t="inlineStr">
+      <c r="D29" s="68" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="E38" s="68" t="inlineStr">
+      <c r="E29" s="68" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="56" customHeight="1">
-      <c r="A39" s="70" t="inlineStr">
+    <row r="30" ht="56" customHeight="1">
+      <c r="A30" s="70" t="inlineStr">
         <is>
           <t>Test thi hành rule này</t>
         </is>
       </c>
-      <c r="B39" s="73" t="inlineStr">
+      <c r="B30" s="73" t="inlineStr">
         <is>
           <t>rule1_tenTepNull_tuChoi</t>
         </is>
       </c>
-      <c r="C39" s="73" t="inlineStr">
+      <c r="C30" s="73" t="inlineStr">
         <is>
           <t>rule2_duoiPdf_luuThanhCong
 rule3_duoiPng_luuThanhCong
@@ -14978,120 +14288,282 @@
 rule5_duoiJpeg_luuThanhCong</t>
         </is>
       </c>
-      <c r="D39" s="73" t="inlineStr">
+      <c r="D30" s="73" t="inlineStr">
         <is>
           <t>rule6_duoiHopLe_dungLuongQuaLon_tuChoi</t>
         </is>
       </c>
-      <c r="E39" s="73" t="inlineStr">
+      <c r="E30" s="73" t="inlineStr">
         <is>
           <t>rule7_duoiKhongHopLe_tuChoi
 rule8_tenTepKhongCoDuoi_tuChoi</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="70" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="70" t="inlineStr">
         <is>
           <t>Gộp từ rule nào</t>
         </is>
       </c>
-      <c r="B40" s="78" t="inlineStr">
-        <is>
-          <t>gộp R1–R12</t>
-        </is>
-      </c>
-      <c r="C40" s="78" t="inlineStr">
-        <is>
-          <t>gộp R13, R15, R17, R19</t>
-        </is>
-      </c>
-      <c r="D40" s="78" t="inlineStr">
-        <is>
-          <t>gộp R14, R16, R18, R20</t>
-        </is>
-      </c>
-      <c r="E40" s="78" t="inlineStr">
-        <is>
-          <t>gộp R21–R24</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="20" customHeight="1">
-      <c r="A42" s="55" t="inlineStr">
+      <c r="B31" s="78" t="inlineStr">
+        <is>
+          <t>gộp R1–R4</t>
+        </is>
+      </c>
+      <c r="C31" s="78" t="inlineStr">
+        <is>
+          <t>chính là R5</t>
+        </is>
+      </c>
+      <c r="D31" s="78" t="inlineStr">
+        <is>
+          <t>chính là R6</t>
+        </is>
+      </c>
+      <c r="E31" s="78" t="inlineStr">
+        <is>
+          <t>gộp R7 + R8</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="24" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>GIÁ TRỊ ĐẠI DIỆN CHO TỪNG LỚP — vì sao 4 rule mà có 8 test</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="65" t="inlineStr">
+        <is>
+          <t>Điều kiện</t>
+        </is>
+      </c>
+      <c r="B34" s="65" t="inlineStr">
+        <is>
+          <t>Lớp</t>
+        </is>
+      </c>
+      <c r="C34" s="65" t="inlineStr">
+        <is>
+          <t>Giá trị đại diện được kiểm</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="n"/>
+      <c r="E34" s="65" t="inlineStr">
+        <is>
+          <t>Số test</t>
+        </is>
+      </c>
+      <c r="F34" s="65" t="inlineStr">
+        <is>
+          <t>Lý do tách riêng</t>
+        </is>
+      </c>
+      <c r="G34" s="8" t="n"/>
+      <c r="H34" s="8" t="n"/>
+      <c r="I34" s="8" t="n"/>
+      <c r="J34" s="8" t="n"/>
+      <c r="K34" s="8" t="n"/>
+      <c r="L34" s="8" t="n"/>
+      <c r="M34" s="8" t="n"/>
+      <c r="N34" s="9" t="n"/>
+    </row>
+    <row r="35" ht="34" customHeight="1">
+      <c r="A35" s="66" t="inlineStr">
+        <is>
+          <t>C2 · Đuôi tệp</t>
+        </is>
+      </c>
+      <c r="B35" s="67" t="inlineStr">
+        <is>
+          <t>Hợp lệ (Y)</t>
+        </is>
+      </c>
+      <c r="C35" s="67" t="inlineStr">
+        <is>
+          <t>.pdf · .png · .jpg · .jpeg</t>
+        </is>
+      </c>
+      <c r="E35" s="79" t="n">
+        <v>4</v>
+      </c>
+      <c r="F35" s="80" t="inlineStr">
+        <is>
+          <t>Mã nguồn so sánh từng đuôi bằng một chuỗi &amp;&amp; — bốn nhánh riêng. Báo cáo bao phủ chỉ đích danh ba nhánh chưa ai chạm tới, nên phải kiểm đủ bốn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="34" customHeight="1">
+      <c r="A36" s="66" t="inlineStr">
+        <is>
+          <t>C2 · Đuôi tệp</t>
+        </is>
+      </c>
+      <c r="B36" s="67" t="inlineStr">
+        <is>
+          <t>Không hợp lệ (N)</t>
+        </is>
+      </c>
+      <c r="C36" s="67" t="inlineStr">
+        <is>
+          <t>.exe · tên không có dấu chấm</t>
+        </is>
+      </c>
+      <c r="E36" s="79" t="n">
+        <v>2</v>
+      </c>
+      <c r="F36" s="80" t="inlineStr">
+        <is>
+          <t>Hai giá trị này TRƯỚC KHI SỬA cho hai kết quả khác nhau: .exe trả lỗi 400 đúng như đặc tả, còn tên không có dấu chấm ném StringIndexOutOfBoundsException thành lỗi 500 — chính là DEF-011. Sau khi sửa mới thật sự cùng một lớp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="34" customHeight="1">
+      <c r="A37" s="66" t="inlineStr">
+        <is>
+          <t>C1 · Tên tệp null</t>
+        </is>
+      </c>
+      <c r="B37" s="67" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="C37" s="67" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="E37" s="79" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" s="80" t="inlineStr">
+        <is>
+          <t>Một giá trị duy nhất, không có gì để tách.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="34" customHeight="1">
+      <c r="A38" s="66" t="inlineStr">
+        <is>
+          <t>C3 · Dung lượng</t>
+        </is>
+      </c>
+      <c r="B38" s="67" t="inlineStr">
+        <is>
+          <t>Y và N</t>
+        </is>
+      </c>
+      <c r="C38" s="67" t="inlineStr">
+        <is>
+          <t>1 byte · 11 MB</t>
+        </is>
+      </c>
+      <c r="E38" s="79" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" s="80" t="inlineStr">
+        <is>
+          <t>Chỉ lấy giá trị nominal để phân biệt nhánh. Các giá trị sát biên 10 MB thuộc về sheet 01 — kỹ thuật giá trị biên, không phải bảng quyết định.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="30" customHeight="1">
+      <c r="A39" s="56" t="inlineStr">
+        <is>
+          <t>Bảng quyết định trả lời "tổ hợp điều kiện nào dẫn tới hành động nào" — nó dừng ở mức LỚP. Việc chọn giá trị nào làm đại diện cho mỗi lớp là việc của phân hoạch lớp tương đương và bao phủ nhánh. Đó là lý do 4 rule sinh ra 8 test chứ không phải 4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="55" t="inlineStr">
         <is>
           <t>Ô tô vàng là ô "không quan tâm" (–) sinh ra khi gộp rule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="44" customHeight="1">
+      <c r="A42" s="56" t="inlineStr">
+        <is>
+          <t>BẢNG RÚT GỌN NÓI ÍT HƠN BẢNG ĐẦY ĐỦ — và đó là lý do vẫn phải giữ cả hai. Rút gọn xong chỉ còn 4 rule, nhưng bộ kiểm thử có 8 test. Chênh lệch nằm ở chỗ: xét theo ĐẶC TẢ thì bốn đuôi .pdf, .png, .jpg, .jpeg là MỘT lớp tương đương (cùng được chấp nhận), nên rút gọn gộp chúng làm một ô "hợp lệ". Nhưng xét theo MÃ NGUỒN thì mỗi đuôi là một nhánh riêng của chuỗi &amp;&amp; , và báo cáo bao phủ đã chỉ đích danh ba nhánh chưa ai chạm tới. Nếu chỉ nhìn bảng rút gọn mà viết test thì ba nhánh đó vẫn nằm im.</t>
         </is>
       </c>
     </row>
     <row r="43" ht="44" customHeight="1">
       <c r="A43" s="56" t="inlineStr">
         <is>
-          <t>BẢNG RÚT GỌN NÓI ÍT HƠN BẢNG ĐẦY ĐỦ — và đó là lý do vẫn phải giữ cả hai. Rút gọn xong chỉ còn 4 rule, nhưng bộ kiểm thử có 8 test. Chênh lệch nằm ở chỗ: xét theo ĐẶC TẢ thì bốn đuôi .pdf, .png, .jpg, .jpeg là MỘT lớp tương đương (cùng được chấp nhận), nên rút gọn gộp chúng làm một ô "hợp lệ". Nhưng xét theo MÃ NGUỒN thì mỗi đuôi là một nhánh riêng của chuỗi &amp;&amp; , và báo cáo bao phủ đã chỉ đích danh ba nhánh chưa ai chạm tới. Nếu chỉ nhìn bảng rút gọn mà viết test thì ba nhánh đó vẫn nằm im.</t>
+          <t>RÚT GỌN CÒN CHE MẤT TRƯỜNG HỢP ĐÃ TÌM RA LỖI: "không có dấu chấm" bị gộp vào R4' cùng với "đuôi khác" vì hai bên cho cùng hành động A4. Nhưng chính ô đó mới là ô làm lộ DEF-011 — trước khi sửa, nó không trả lỗi 400 mà ném StringIndexOutOfBoundsException thành lỗi 500. Bảng đầy đủ giữ nó ở cột R23–R24 nên còn nhìn thấy; bảng rút gọn thì không.</t>
         </is>
       </c>
     </row>
     <row r="44" ht="44" customHeight="1">
       <c r="A44" s="56" t="inlineStr">
         <is>
-          <t>RÚT GỌN CÒN CHE MẤT TRƯỜNG HỢP ĐÃ TÌM RA LỖI: "không có dấu chấm" bị gộp vào R4' cùng với "đuôi khác" vì hai bên cho cùng hành động A4. Nhưng chính ô đó mới là ô làm lộ DEF-011 — trước khi sửa, nó không trả lỗi 400 mà ném StringIndexOutOfBoundsException thành lỗi 500. Bảng đầy đủ giữ nó ở cột R23–R24 nên còn nhìn thấy; bảng rút gọn thì không.</t>
+          <t>VÌ SAO GỘP ĐƯỢC: mã nguồn kiểm ba điều kiện TUẦN TỰ và thoát ngay khi gặp lỗi. Khi một điều kiện phía trước đã quyết định kết quả thì điều kiện phía sau không còn ảnh hưởng, đánh dấu "–". R1' gộp 12 rule (tên tệp null thì đuôi và dung lượng vô nghĩa); R7' và R8' mỗi cột gộp 2 rule (đuôi sai thì chặn trước khi xét dung lượng).</t>
         </is>
       </c>
     </row>
     <row r="45" ht="44" customHeight="1">
       <c r="A45" s="56" t="inlineStr">
         <is>
-          <t>VÌ SAO GỘP ĐƯỢC: mã nguồn kiểm ba điều kiện TUẦN TỰ và thoát ngay khi gặp lỗi. Khi một điều kiện phía trước đã quyết định kết quả thì điều kiện phía sau không còn ảnh hưởng, đánh dấu "–". R1' gộp 12 rule (tên tệp null thì đuôi và dung lượng vô nghĩa); R7' và R8' mỗi cột gộp 2 rule (đuôi sai thì chặn trước khi xét dung lượng).</t>
+          <t>KHIẾM KHUYẾT DEF-011 — nằm trong lớp C2 = N. Tệp không có dấu chấm làm lastIndexOf(".") trả -1, kéo theo substring(-1) ném StringIndexOutOfBoundsException, người dùng nhận lỗi 500 thay vì thông báo 400. Nói rõ để không nhận công sai: test hộp trắng đã ghi đúng nguyên nhân từ trước nhưng lại CHỐT hành vi lỗi bằng một khẳng định, nên bộ test vẫn xanh. Đóng góp của kỹ thuật này là BUỘC PHẢI SỬA — mỗi cột của bảng phải ứng với một hành động xác định trong nhóm A1–A4, không thể để một ô là "sập 500".</t>
         </is>
       </c>
     </row>
     <row r="46" ht="44" customHeight="1">
       <c r="A46" s="56" t="inlineStr">
         <is>
-          <t>KHIẾM KHUYẾT DEF-011 — cột R23–R24 của bảng đầy đủ. Tệp không có dấu chấm làm lastIndexOf(".") trả -1, kéo theo substring(-1) ném StringIndexOutOfBoundsException, người dùng nhận lỗi 500 thay vì thông báo 400. Nói rõ để không nhận công sai: test hộp trắng đã ghi đúng nguyên nhân từ trước nhưng lại CHỐT hành vi lỗi bằng một khẳng định, nên bộ test vẫn xanh. Đóng góp của kỹ thuật này là BUỘC PHẢI SỬA — mỗi cột của bảng phải ứng với một hành động xác định trong nhóm A1–A4, không thể để một ô là "sập 500".</t>
+          <t>CON SỐ ĐO ĐƯỢC: nhánh OnboardingService 75,0% (9/12) → 100,0% (14/14); dòng 94,7% (18/19) → 100,0% (19/19). Nguồn: target/site/jacoco/jacoco.csv.</t>
         </is>
       </c>
     </row>
     <row r="47" ht="44" customHeight="1">
       <c r="A47" s="56" t="inlineStr">
         <is>
-          <t>CON SỐ ĐO ĐƯỢC: nhánh OnboardingService 75,0% (9/12) → 100,0% (14/14); dòng 94,7% (18/19) → 100,0% (19/19). Nguồn: target/site/jacoco/jacoco.csv.</t>
+          <t>QUAN HỆ VỚI SHEET GIÁ TRỊ BIÊN: điều kiện C3 ở bảng này chỉ lấy giá trị NOMINAL (1 byte và 11 MB) để phân biệt nhánh. Các giá trị sát biên 10 MB thuộc về sheet 01.</t>
         </is>
       </c>
     </row>
     <row r="48" ht="44" customHeight="1">
       <c r="A48" s="56" t="inlineStr">
         <is>
-          <t>QUAN HỆ VỚI SHEET GIÁ TRỊ BIÊN: điều kiện C3 ở bảng này chỉ lấy giá trị NOMINAL (1 byte và 11 MB) để phân biệt nhánh. Các giá trị sát biên 10 MB thuộc về sheet 01.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="44" customHeight="1">
-      <c r="A49" s="56" t="inlineStr">
-        <is>
           <t>KIỂM TRA BỔ SUNG ngoài bảng: đuôi viết HOA "BANGDIEM.PDF" được chấp nhận vì mã gọi toLowerCase — method boSung_duoiVietHoa_duocChapNhan, PASS. Không đưa vào bảng vì đây là biến thể trình bày của C2, không sinh thêm hành động mới.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="30">
     <mergeCell ref="A9:N9"/>
-    <mergeCell ref="J30:N30"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="A39:N39"/>
+    <mergeCell ref="A48:N48"/>
+    <mergeCell ref="F36:N36"/>
+    <mergeCell ref="J28:N28"/>
+    <mergeCell ref="F35:N35"/>
+    <mergeCell ref="A45:N45"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="F38:N38"/>
+    <mergeCell ref="J24:N24"/>
+    <mergeCell ref="A7:N7"/>
+    <mergeCell ref="A41:N41"/>
+    <mergeCell ref="A46:N46"/>
+    <mergeCell ref="F37:N37"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="A33:N33"/>
+    <mergeCell ref="A47:N47"/>
+    <mergeCell ref="A42:N42"/>
+    <mergeCell ref="J22:N22"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="J21:N21"/>
+    <mergeCell ref="F34:N34"/>
     <mergeCell ref="A4:N4"/>
-    <mergeCell ref="A45:N45"/>
-    <mergeCell ref="A48:N48"/>
-    <mergeCell ref="J37:N37"/>
-    <mergeCell ref="A47:N47"/>
-    <mergeCell ref="A29:N29"/>
-    <mergeCell ref="A7:N7"/>
-    <mergeCell ref="J32:N32"/>
+    <mergeCell ref="A20:N20"/>
+    <mergeCell ref="C37:D37"/>
     <mergeCell ref="A43:N43"/>
-    <mergeCell ref="A49:N49"/>
-    <mergeCell ref="J33:N33"/>
     <mergeCell ref="A10:N10"/>
-    <mergeCell ref="A42:N42"/>
-    <mergeCell ref="A46:N46"/>
-    <mergeCell ref="J31:N31"/>
+    <mergeCell ref="J23:N23"/>
     <mergeCell ref="A44:N44"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/BaoCao-KiemThu-CareerCompass.xlsx
+++ b/BaoCao-KiemThu-CareerCompass.xlsx
@@ -33,7 +33,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="30">
+  <fonts count="31">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -176,6 +176,11 @@
     <font>
       <color rgb="00808080"/>
       <sz val="8"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="007F6000"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="16">
@@ -384,7 +389,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -609,6 +614,9 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1708,8 +1716,8 @@
     <mergeCell ref="F8:H8"/>
     <mergeCell ref="F17:H17"/>
     <mergeCell ref="F23:H23"/>
+    <mergeCell ref="F22:H22"/>
     <mergeCell ref="F28:H28"/>
-    <mergeCell ref="F22:H22"/>
     <mergeCell ref="F13:H13"/>
     <mergeCell ref="F30:H30"/>
     <mergeCell ref="F9:H9"/>
@@ -10163,7 +10171,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H90"/>
+  <dimension ref="A1:H91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -10190,6 +10198,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -10368,256 +10377,231 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
+    <row r="12" ht="44" customHeight="1">
+      <c r="A12" s="81" t="inlineStr">
+        <is>
+          <t>LỚP NẰM NGOÀI BẢNG TỔNG KẾT: mã nguồn còn RegisterFormDTOBvaTest (27 test) cũng kiểm giá trị biên, nhưng KHÔNG tính vào bảng trên. Lý do: nó chia mỗi trường thành một test case riêng bằng validateProperty, trong khi slide 23 và 33 luôn trình bày test case là MỘT BỘ ĐẦU VÀO ĐẦY ĐỦ — Bảng 2, 3 và 5 của sheet này bám đúng mẫu đó. Các giá trị biên mà lớp kia kiểm đều đã được ba bảng nói trên phủ hết. Chạy riêng:  mvnw test -Dtest=RegisterFormDTOBvaTest  →  27 test.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
+    <row r="14" ht="24" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>BẢNG 1 — ĐỊNH NGHĨA GIÁ TRỊ BIÊN CỦA TỪNG BIẾN (phần ghi chú bên trái slide 23)</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>Giá trị</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>fullName (số ký tự)</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>email (số ký tự)</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>password (số ký tự)</t>
         </is>
       </c>
-      <c r="E14" s="4" t="n"/>
-      <c r="F14" s="4" t="n"/>
-      <c r="G14" s="4" t="n"/>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="E15" s="4" t="n"/>
+      <c r="F15" s="4" t="n"/>
+      <c r="G15" s="4" t="n"/>
+      <c r="H15" s="4" t="inlineStr">
         <is>
           <t>Ghi chú</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="10" t="inlineStr">
-        <is>
-          <t>min</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="D15" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="5" t="n"/>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>giá trị nhỏ nhất hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>min+</t>
+          <t>min</t>
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E16" s="5" t="n"/>
       <c r="F16" s="5" t="n"/>
       <c r="G16" s="5" t="n"/>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>ngay trên min</t>
+          <t>giá trị nhỏ nhất hợp lệ</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>nom</t>
+          <t>min+</t>
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="C17" s="6" t="n">
-        <v>75</v>
+        <v>7</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E17" s="5" t="n"/>
       <c r="F17" s="5" t="n"/>
       <c r="G17" s="5" t="n"/>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>giá trị điển hình, giữa miền</t>
+          <t>ngay trên min</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>max-</t>
+          <t>nom</t>
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>99</v>
+        <v>50</v>
       </c>
       <c r="C18" s="6" t="n">
-        <v>149</v>
+        <v>75</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="E18" s="5" t="n"/>
       <c r="F18" s="5" t="n"/>
       <c r="G18" s="5" t="n"/>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>ngay dưới max</t>
+          <t>giá trị điển hình, giữa miền</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>max</t>
+          <t>max-</t>
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C19" s="6" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E19" s="5" t="n"/>
       <c r="F19" s="5" t="n"/>
       <c r="G19" s="5" t="n"/>
       <c r="H19" s="5" t="inlineStr">
         <is>
+          <t>ngay dưới max</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>150</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
           <t>giá trị lớn nhất hợp lệ</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="48" customHeight="1">
-      <c r="A20" s="11" t="inlineStr">
+    <row r="21" ht="48" customHeight="1">
+      <c r="A21" s="11" t="inlineStr">
         <is>
           <t>Ràng buộc gốc: fullName @NotBlank @Size(max=100) · email @NotBlank @Email @Size(min=6, max=150) · password @NotBlank @Size(min=6, max=30). Biên dưới của fullName do @NotBlank sinh ra: chuỗi rỗng bị chặn nên min = 1. Biên dưới của email là 6, độ dài của email hợp lệ ngắn nhất có thật a@b.co.</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="24" customHeight="1">
-      <c r="A22" s="3" t="inlineStr">
+    <row r="22"/>
+    <row r="23" ht="24" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>BẢNG 2 — STANDARD BVA TEST CASES (mẫu slide 23) · số case = 4n + 1 = 4×3 + 1 = 13</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="4" t="inlineStr">
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>Case</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>fullName</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t>password</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
+      <c r="E24" s="4" t="inlineStr">
         <is>
           <t>Biến đang xét</t>
         </is>
       </c>
-      <c r="F23" s="4" t="inlineStr">
+      <c r="F24" s="4" t="inlineStr">
         <is>
           <t>Expected Output</t>
         </is>
       </c>
-      <c r="G23" s="4" t="inlineStr">
+      <c r="G24" s="4" t="inlineStr">
         <is>
           <t>Kết quả thực tế</t>
         </is>
       </c>
-      <c r="H23" s="4" t="inlineStr">
+      <c r="H24" s="4" t="inlineStr">
         <is>
           <t>Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B24" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="C24" s="6" t="n">
-        <v>75</v>
-      </c>
-      <c r="D24" s="16" t="n">
-        <v>6</v>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>password = min</t>
-        </is>
-      </c>
-      <c r="F24" s="5" t="inlineStr">
-        <is>
-          <t>Hợp lệ</t>
-        </is>
-      </c>
-      <c r="G24" s="5" t="inlineStr">
-        <is>
-          <t>Đúng như mong đợi</t>
-        </is>
-      </c>
-      <c r="H24" s="13" t="inlineStr">
-        <is>
-          <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B25" s="6" t="n">
         <v>50</v>
@@ -10626,11 +10610,11 @@
         <v>75</v>
       </c>
       <c r="D25" s="16" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>password = min+</t>
+          <t>password = min</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
@@ -10651,7 +10635,7 @@
     </row>
     <row r="26">
       <c r="A26" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B26" s="6" t="n">
         <v>50</v>
@@ -10659,12 +10643,12 @@
       <c r="C26" s="6" t="n">
         <v>75</v>
       </c>
-      <c r="D26" s="6" t="n">
-        <v>18</v>
+      <c r="D26" s="16" t="n">
+        <v>7</v>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>TẤT CẢ nominal</t>
+          <t>password = min+</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
@@ -10685,7 +10669,7 @@
     </row>
     <row r="27">
       <c r="A27" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B27" s="6" t="n">
         <v>50</v>
@@ -10693,12 +10677,12 @@
       <c r="C27" s="6" t="n">
         <v>75</v>
       </c>
-      <c r="D27" s="16" t="n">
-        <v>29</v>
+      <c r="D27" s="6" t="n">
+        <v>18</v>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>password = max-</t>
+          <t>TẤT CẢ nominal</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
@@ -10719,7 +10703,7 @@
     </row>
     <row r="28">
       <c r="A28" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B28" s="6" t="n">
         <v>50</v>
@@ -10728,11 +10712,11 @@
         <v>75</v>
       </c>
       <c r="D28" s="16" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>password = max</t>
+          <t>password = max-</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
@@ -10753,20 +10737,20 @@
     </row>
     <row r="29">
       <c r="A29" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B29" s="6" t="n">
         <v>50</v>
       </c>
-      <c r="C29" s="16" t="n">
-        <v>6</v>
-      </c>
-      <c r="D29" s="6" t="n">
-        <v>18</v>
+      <c r="C29" s="6" t="n">
+        <v>75</v>
+      </c>
+      <c r="D29" s="16" t="n">
+        <v>30</v>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>email = min</t>
+          <t>password = max</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
@@ -10787,20 +10771,20 @@
     </row>
     <row r="30">
       <c r="A30" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B30" s="6" t="n">
         <v>50</v>
       </c>
       <c r="C30" s="16" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D30" s="6" t="n">
         <v>18</v>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>email = min+</t>
+          <t>email = min</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
@@ -10821,20 +10805,20 @@
     </row>
     <row r="31">
       <c r="A31" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B31" s="6" t="n">
         <v>50</v>
       </c>
       <c r="C31" s="16" t="n">
-        <v>149</v>
+        <v>7</v>
       </c>
       <c r="D31" s="6" t="n">
         <v>18</v>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>email = max-</t>
+          <t>email = min+</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
@@ -10855,20 +10839,20 @@
     </row>
     <row r="32">
       <c r="A32" s="6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B32" s="6" t="n">
         <v>50</v>
       </c>
       <c r="C32" s="16" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D32" s="6" t="n">
         <v>18</v>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>email = max</t>
+          <t>email = max-</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
@@ -10889,20 +10873,20 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="B33" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C33" s="6" t="n">
-        <v>75</v>
+        <v>9</v>
+      </c>
+      <c r="B33" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="C33" s="16" t="n">
+        <v>150</v>
       </c>
       <c r="D33" s="6" t="n">
         <v>18</v>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>fullName = min</t>
+          <t>email = max</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
@@ -10923,10 +10907,10 @@
     </row>
     <row r="34">
       <c r="A34" s="6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B34" s="16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C34" s="6" t="n">
         <v>75</v>
@@ -10936,7 +10920,7 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>fullName = min+</t>
+          <t>fullName = min</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
@@ -10957,10 +10941,10 @@
     </row>
     <row r="35">
       <c r="A35" s="6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B35" s="16" t="n">
-        <v>99</v>
+        <v>2</v>
       </c>
       <c r="C35" s="6" t="n">
         <v>75</v>
@@ -10970,7 +10954,7 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>fullName = max-</t>
+          <t>fullName = min+</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
@@ -10991,10 +10975,10 @@
     </row>
     <row r="36">
       <c r="A36" s="6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B36" s="16" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C36" s="6" t="n">
         <v>75</v>
@@ -11004,118 +10988,119 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
+          <t>fullName = max-</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>Hợp lệ</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>Đúng như mong đợi</t>
+        </is>
+      </c>
+      <c r="H36" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="B37" s="16" t="n">
+        <v>100</v>
+      </c>
+      <c r="C37" s="6" t="n">
+        <v>75</v>
+      </c>
+      <c r="D37" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
           <t>fullName = max</t>
         </is>
       </c>
-      <c r="F36" s="5" t="inlineStr">
+      <c r="F37" s="5" t="inlineStr">
         <is>
           <t>Hợp lệ</t>
         </is>
       </c>
-      <c r="G36" s="5" t="inlineStr">
+      <c r="G37" s="5" t="inlineStr">
         <is>
           <t>Đúng như mong đợi</t>
         </is>
       </c>
-      <c r="H36" s="13" t="inlineStr">
+      <c r="H37" s="13" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="40" customHeight="1">
-      <c r="A37" s="11" t="inlineStr">
+    <row r="38" ht="40" customHeight="1">
+      <c r="A38" s="11" t="inlineStr">
         <is>
           <t>CÁCH ĐỌC: mỗi hàng là MỘT bộ đầy đủ ba biến. Ô tô tím là biến đang được đẩy tới giá trị biên, hai biến còn lại giữ ở nom. Slide 26 nêu nguyên tắc: tại một thời điểm, BVA chỉ test giá trị biên của 1 biến. Hàng TC3 là bộ tất-cả-nominal, dùng chung cho cả ba biến — đó là lý do công thức là 4n+1 chứ không phải 5n. Code: RegisterStandardBvaTest · standardBva_moiBoDeuHopLe.</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="24" customHeight="1">
-      <c r="A39" s="3" t="inlineStr">
+    <row r="39"/>
+    <row r="40" ht="24" customHeight="1">
+      <c r="A40" s="3" t="inlineStr">
         <is>
           <t>BẢNG 3 — ROBUSTNESS BVA, phần BỔ SUNG (mẫu slide 24) · 6n + 1 = 19 case</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="30" customHeight="1">
-      <c r="A40" s="4" t="inlineStr">
+    <row r="41" ht="30" customHeight="1">
+      <c r="A41" s="4" t="inlineStr">
         <is>
           <t>Case</t>
         </is>
       </c>
-      <c r="B40" s="4" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>fullName</t>
         </is>
       </c>
-      <c r="C40" s="4" t="inlineStr">
+      <c r="C41" s="4" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="D40" s="4" t="inlineStr">
+      <c r="D41" s="4" t="inlineStr">
         <is>
           <t>password</t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr">
+      <c r="E41" s="4" t="inlineStr">
         <is>
           <t>Biến đang xét</t>
         </is>
       </c>
-      <c r="F40" s="4" t="inlineStr">
+      <c r="F41" s="4" t="inlineStr">
         <is>
           <t>Expected Output</t>
         </is>
       </c>
-      <c r="G40" s="4" t="inlineStr">
+      <c r="G41" s="4" t="inlineStr">
         <is>
           <t>Kết quả thực tế</t>
         </is>
       </c>
-      <c r="H40" s="4" t="inlineStr">
+      <c r="H41" s="4" t="inlineStr">
         <is>
           <t>Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="6" t="n">
-        <v>14</v>
-      </c>
-      <c r="B41" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="C41" s="6" t="n">
-        <v>75</v>
-      </c>
-      <c r="D41" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="E41" s="5" t="inlineStr">
-        <is>
-          <t>password = min-</t>
-        </is>
-      </c>
-      <c r="F41" s="5" t="inlineStr">
-        <is>
-          <t>KHÔNG hợp lệ</t>
-        </is>
-      </c>
-      <c r="G41" s="5" t="inlineStr">
-        <is>
-          <t>Đúng như mong đợi</t>
-        </is>
-      </c>
-      <c r="H41" s="13" t="inlineStr">
-        <is>
-          <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B42" s="6" t="n">
         <v>50</v>
@@ -11124,11 +11109,11 @@
         <v>75</v>
       </c>
       <c r="D42" s="17" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>password = max+</t>
+          <t>password = min-</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
@@ -11149,20 +11134,20 @@
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B43" s="6" t="n">
         <v>50</v>
       </c>
-      <c r="C43" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="D43" s="6" t="n">
-        <v>18</v>
+      <c r="C43" s="6" t="n">
+        <v>75</v>
+      </c>
+      <c r="D43" s="17" t="n">
+        <v>31</v>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>email = min-</t>
+          <t>password = max+</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
@@ -11183,20 +11168,20 @@
     </row>
     <row r="44">
       <c r="A44" s="6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B44" s="6" t="n">
         <v>50</v>
       </c>
       <c r="C44" s="17" t="n">
-        <v>151</v>
+        <v>5</v>
       </c>
       <c r="D44" s="6" t="n">
         <v>18</v>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>email = max+</t>
+          <t>email = min-</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
@@ -11217,20 +11202,20 @@
     </row>
     <row r="45">
       <c r="A45" s="6" t="n">
-        <v>18</v>
-      </c>
-      <c r="B45" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C45" s="6" t="n">
-        <v>75</v>
+        <v>17</v>
+      </c>
+      <c r="B45" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="C45" s="17" t="n">
+        <v>151</v>
       </c>
       <c r="D45" s="6" t="n">
         <v>18</v>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>fullName = min-</t>
+          <t>email = max+</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
@@ -11251,10 +11236,10 @@
     </row>
     <row r="46">
       <c r="A46" s="6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B46" s="17" t="n">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="C46" s="6" t="n">
         <v>75</v>
@@ -11264,106 +11249,141 @@
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
+          <t>fullName = min-</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>KHÔNG hợp lệ</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>Đúng như mong đợi</t>
+        </is>
+      </c>
+      <c r="H46" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="B47" s="17" t="n">
+        <v>101</v>
+      </c>
+      <c r="C47" s="6" t="n">
+        <v>75</v>
+      </c>
+      <c r="D47" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
           <t>fullName = max+</t>
         </is>
       </c>
-      <c r="F46" s="5" t="inlineStr">
+      <c r="F47" s="5" t="inlineStr">
         <is>
           <t>KHÔNG hợp lệ</t>
         </is>
       </c>
-      <c r="G46" s="5" t="inlineStr">
+      <c r="G47" s="5" t="inlineStr">
         <is>
           <t>Đúng như mong đợi</t>
         </is>
       </c>
-      <c r="H46" s="13" t="inlineStr">
+      <c r="H47" s="13" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="40" customHeight="1">
-      <c r="A47" s="11" t="inlineStr">
+    <row r="48" ht="40" customHeight="1">
+      <c r="A48" s="11" t="inlineStr">
         <is>
           <t>Slide 24: Robustness BVA giữ nguyên phần clean test cases (min, min+, nom, max-, max) và THÊM hai giá trị nằm ngoài miền hợp lệ là min- và max+. Mười ba case ở Bảng 2 cộng sáu case ở đây là 19 = 6n + 1. Code: RegisterStandardBvaTest · robustnessBva_giaTriNgoaiBien.</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="54" customHeight="1">
-      <c r="A48" s="11" t="inlineStr">
+    <row r="49" ht="54" customHeight="1">
+      <c r="A49" s="11" t="inlineStr">
         <is>
           <t>LỖI DO TC16 PHÁT HIỆN, ĐÃ SỬA: ban đầu email 5 ký tự (min-) được CHẤP NHẬN, vì @Size của email chỉ khai max=150 mà không khai min. Kiểm chứng thêm cho thấy cả a@b (3 ký tự) cũng lọt, trong khi chuỗi đó không thể là hộp thư thật. Đã sửa RegisterFormDTO thành @Size(min=6, max=150); TC16 nay kỳ vọng BỊ TỪ CHỐI và pass. Đây là lỗi nghiệp vụ thật do kỹ thuật giá trị biên tìm ra, không phải lỗi của test.</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="24" customHeight="1">
-      <c r="A50" s="3" t="inlineStr">
+    <row r="50"/>
+    <row r="51" ht="24" customHeight="1">
+      <c r="A51" s="3" t="inlineStr">
         <is>
           <t>BẢNG 4 — PHÂN HOẠCH LỚP TƯƠNG ĐƯƠNG (mẫu slide 32)</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="30" customHeight="1">
-      <c r="A51" s="4" t="inlineStr">
+    <row r="52" ht="30" customHeight="1">
+      <c r="A52" s="4" t="inlineStr">
         <is>
           <t>Conditions</t>
         </is>
       </c>
-      <c r="B51" s="4" t="inlineStr">
+      <c r="B52" s="4" t="inlineStr">
         <is>
           <t>Valid Partitions</t>
         </is>
       </c>
-      <c r="C51" s="4" t="inlineStr">
+      <c r="C52" s="4" t="inlineStr">
         <is>
           <t>Tag</t>
         </is>
       </c>
-      <c r="D51" s="4" t="inlineStr">
+      <c r="D52" s="4" t="inlineStr">
         <is>
           <t>Invalid Partitions</t>
         </is>
       </c>
-      <c r="E51" s="4" t="inlineStr">
+      <c r="E52" s="4" t="inlineStr">
         <is>
           <t>Tag</t>
         </is>
       </c>
-      <c r="F51" s="4" t="inlineStr">
+      <c r="F52" s="4" t="inlineStr">
         <is>
           <t>Valid Boundaries</t>
         </is>
       </c>
-      <c r="G51" s="4" t="inlineStr">
+      <c r="G52" s="4" t="inlineStr">
         <is>
           <t>Tag</t>
         </is>
       </c>
-      <c r="H51" s="4" t="inlineStr">
+      <c r="H52" s="4" t="inlineStr">
         <is>
           <t>Robustness</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="62" customHeight="1">
-      <c r="A52" s="5" t="inlineStr">
+    <row r="53" ht="62" customHeight="1">
+      <c r="A53" s="5" t="inlineStr">
         <is>
           <t>password</t>
         </is>
       </c>
-      <c r="B52" s="5" t="inlineStr">
+      <c r="B53" s="5" t="inlineStr">
         <is>
           <t>6–30 ký tự,
 có ít nhất 1 ký tự không trắng</t>
         </is>
       </c>
-      <c r="C52" s="5" t="inlineStr">
+      <c r="C53" s="5" t="inlineStr">
         <is>
           <t>V1</t>
         </is>
       </c>
-      <c r="D52" s="5" t="inlineStr">
+      <c r="D53" s="5" t="inlineStr">
         <is>
           <t>&lt; 6 ký tự
 &gt; 30 ký tự
@@ -11371,7 +11391,7 @@
 null</t>
         </is>
       </c>
-      <c r="E52" s="5" t="inlineStr">
+      <c r="E53" s="5" t="inlineStr">
         <is>
           <t>X1
 X2
@@ -11379,311 +11399,281 @@
 X4</t>
         </is>
       </c>
-      <c r="F52" s="5" t="inlineStr">
+      <c r="F53" s="5" t="inlineStr">
         <is>
           <t>6, 7, 18, 29, 30</t>
         </is>
       </c>
-      <c r="G52" s="5" t="inlineStr">
+      <c r="G53" s="5" t="inlineStr">
         <is>
           <t>B1–B5</t>
         </is>
       </c>
-      <c r="H52" s="5" t="inlineStr">
+      <c r="H53" s="5" t="inlineStr">
         <is>
           <t>5 và 31 (B6, B7)</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="62" customHeight="1">
-      <c r="A53" s="5" t="inlineStr">
+    <row r="54" ht="62" customHeight="1">
+      <c r="A54" s="5" t="inlineStr">
         <is>
           <t>fullName</t>
         </is>
       </c>
-      <c r="B53" s="5" t="inlineStr">
+      <c r="B54" s="5" t="inlineStr">
         <is>
           <t>1–100 ký tự,
 có ít nhất 1 ký tự không trắng</t>
         </is>
       </c>
-      <c r="C53" s="5" t="inlineStr">
+      <c r="C54" s="5" t="inlineStr">
         <is>
           <t>V2</t>
         </is>
       </c>
-      <c r="D53" s="5" t="inlineStr">
+      <c r="D54" s="5" t="inlineStr">
         <is>
           <t>&gt; 100 ký tự
 toàn khoảng trắng
 null</t>
         </is>
       </c>
-      <c r="E53" s="5" t="inlineStr">
+      <c r="E54" s="5" t="inlineStr">
         <is>
           <t>X5
 X6
 X7</t>
         </is>
       </c>
-      <c r="F53" s="5" t="inlineStr">
+      <c r="F54" s="5" t="inlineStr">
         <is>
           <t>1, 2, 50, 99, 100</t>
         </is>
       </c>
-      <c r="G53" s="5" t="inlineStr">
+      <c r="G54" s="5" t="inlineStr">
         <is>
           <t>B8–B12</t>
         </is>
       </c>
-      <c r="H53" s="5" t="inlineStr">
+      <c r="H54" s="5" t="inlineStr">
         <is>
           <t>rỗng (= min−1) và 101
 (B13, B14)</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="62" customHeight="1">
-      <c r="A54" s="5" t="inlineStr">
+    <row r="55" ht="62" customHeight="1">
+      <c r="A55" s="5" t="inlineStr">
         <is>
           <t>email — điều kiện ĐỘ DÀI</t>
         </is>
       </c>
-      <c r="B54" s="5" t="inlineStr">
+      <c r="B55" s="5" t="inlineStr">
         <is>
           <t>6–150 ký tự</t>
         </is>
       </c>
-      <c r="C54" s="5" t="inlineStr">
+      <c r="C55" s="5" t="inlineStr">
         <is>
           <t>V3</t>
         </is>
       </c>
-      <c r="D54" s="5" t="inlineStr">
+      <c r="D55" s="5" t="inlineStr">
         <is>
           <t>&lt; 6 ký tự
 &gt; 150 ký tự</t>
         </is>
       </c>
-      <c r="E54" s="5" t="inlineStr">
+      <c r="E55" s="5" t="inlineStr">
         <is>
           <t>X8
 X9</t>
         </is>
       </c>
-      <c r="F54" s="5" t="inlineStr">
+      <c r="F55" s="5" t="inlineStr">
         <is>
           <t>6, 7, 75, 149, 150</t>
         </is>
       </c>
-      <c r="G54" s="5" t="inlineStr">
+      <c r="G55" s="5" t="inlineStr">
         <is>
           <t>B15–B19</t>
         </is>
       </c>
-      <c r="H54" s="5" t="inlineStr">
+      <c r="H55" s="5" t="inlineStr">
         <is>
           <t>5 và 151 (B20, B21)</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="62" customHeight="1">
-      <c r="A55" s="5" t="inlineStr">
+    <row r="56" ht="62" customHeight="1">
+      <c r="A56" s="5" t="inlineStr">
         <is>
           <t>email — điều kiện ĐỊNH DẠNG</t>
         </is>
       </c>
-      <c r="B55" s="5" t="inlineStr">
+      <c r="B56" s="5" t="inlineStr">
         <is>
           <t>đúng định dạng email</t>
         </is>
       </c>
-      <c r="C55" s="5" t="inlineStr">
+      <c r="C56" s="5" t="inlineStr">
         <is>
           <t>V4</t>
         </is>
       </c>
-      <c r="D55" s="5" t="inlineStr">
+      <c r="D56" s="5" t="inlineStr">
         <is>
           <t>sai định dạng
 null / rỗng</t>
         </is>
       </c>
-      <c r="E55" s="5" t="inlineStr">
+      <c r="E56" s="5" t="inlineStr">
         <is>
           <t>X10
 X11</t>
         </is>
       </c>
-      <c r="F55" s="5" t="inlineStr">
+      <c r="F56" s="5" t="inlineStr">
         <is>
           <t>(không áp dụng —
 miền rời rạc)</t>
         </is>
       </c>
-      <c r="G55" s="5" t="inlineStr">
+      <c r="G56" s="5" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="H55" s="5" t="inlineStr">
+      <c r="H56" s="5" t="inlineStr">
         <is>
           <t>(không áp dụng)</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="62" customHeight="1">
-      <c r="A56" s="5" t="inlineStr">
+    <row r="57" ht="62" customHeight="1">
+      <c r="A57" s="5" t="inlineStr">
         <is>
           <t>Tệp bảng điểm — DUNG LƯỢNG</t>
         </is>
       </c>
-      <c r="B56" s="5" t="inlineStr">
+      <c r="B57" s="5" t="inlineStr">
         <is>
           <t>0 đến 10 MB</t>
         </is>
       </c>
-      <c r="C56" s="5" t="inlineStr">
+      <c r="C57" s="5" t="inlineStr">
         <is>
           <t>V5</t>
         </is>
       </c>
-      <c r="D56" s="5" t="inlineStr">
+      <c r="D57" s="5" t="inlineStr">
         <is>
           <t>&gt; 10 MB</t>
         </is>
       </c>
-      <c r="E56" s="5" t="inlineStr">
+      <c r="E57" s="5" t="inlineStr">
         <is>
           <t>X12</t>
         </is>
       </c>
-      <c r="F56" s="5" t="inlineStr">
+      <c r="F57" s="5" t="inlineStr">
         <is>
           <t>0, 1 byte, 5 MB,
 10MB−1, 10 MB</t>
         </is>
       </c>
-      <c r="G56" s="5" t="inlineStr">
+      <c r="G57" s="5" t="inlineStr">
         <is>
           <t>B22–B26</t>
         </is>
       </c>
-      <c r="H56" s="5" t="inlineStr">
+      <c r="H57" s="5" t="inlineStr">
         <is>
           <t>10MB + 1 byte (B27)</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="40" customHeight="1">
-      <c r="A57" s="11" t="inlineStr">
-        <is>
-          <t>Slide 32 gộp phân lớp tương đương và giá trị biên vào MỘT bảng. Một trường có thể mang nhiều dòng điều kiện độc lập — trường Customer name ở slide 29 được tách thành độ dài 2-64 và ký tự hợp lệ. Email ở đây cũng vậy: điều kiện ĐỘ DÀI có thứ tự nên áp được giá trị biên, còn điều kiện ĐỊNH DẠNG là miền rời rạc nên chỉ phân lớp được — đó là ý nghĩa của dấu "-" ở cột Tag dòng thứ tư.</t>
         </is>
       </c>
     </row>
     <row r="58" ht="40" customHeight="1">
       <c r="A58" s="11" t="inlineStr">
         <is>
-          <t>CODE KIỂM CHỨNG BẢNG NÀY: cột Valid/Invalid Partitions do RegisterEquivalencePartitionTest kiểm; cột Valid Boundaries B1–B21 do RegisterStandardBvaTest kiểm (xem Bảng 2, Bảng 3); B22–B27 của tệp bảng điểm do OnboardingFileSizeBvaTest kiểm.</t>
+          <t>Slide 32 gộp phân lớp tương đương và giá trị biên vào MỘT bảng. Một trường có thể mang nhiều dòng điều kiện độc lập — trường Customer name ở slide 29 được tách thành độ dài 2-64 và ký tự hợp lệ. Email ở đây cũng vậy: điều kiện ĐỘ DÀI có thứ tự nên áp được giá trị biên, còn điều kiện ĐỊNH DẠNG là miền rời rạc nên chỉ phân lớp được — đó là ý nghĩa của dấu "-" ở cột Tag dòng thứ tư.</t>
         </is>
       </c>
     </row>
     <row r="59" ht="40" customHeight="1">
       <c r="A59" s="11" t="inlineStr">
         <is>
+          <t>CODE KIỂM CHỨNG BẢNG NÀY: cột Valid/Invalid Partitions do RegisterEquivalencePartitionTest kiểm; cột Valid Boundaries B1–B21 do RegisterStandardBvaTest kiểm (xem Bảng 2, Bảng 3); B22–B27 của tệp bảng điểm do OnboardingFileSizeBvaTest kiểm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="40" customHeight="1">
+      <c r="A60" s="11" t="inlineStr">
+        <is>
           <t>PHÁT HIỆN — lớp X3: mật khẩu 8 dấu cách có độ dài 8, THOẢ MÃN @Size(min=6, max=30) nhưng vẫn bị @NotBlank từ chối. Lớp này không nằm ở ranh giới độ dài nào nên giá trị biên không chạm tới — chỉ phân hoạch lớp tương đương mới phát hiện được. Code: RegisterEquivalencePartitionTest · x3_toanKhoangTrang_biTuChoi.</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="24" customHeight="1">
-      <c r="A61" s="3" t="inlineStr">
+    <row r="61"/>
+    <row r="62" ht="24" customHeight="1">
+      <c r="A62" s="3" t="inlineStr">
         <is>
           <t>BẢNG 5 — THIẾT KẾ TEST CASE, GỘP TAG (mẫu slide 33) · 23 case phủ trọn 44 tag</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="30" customHeight="1">
-      <c r="A62" s="4" t="inlineStr">
+    <row r="63" ht="30" customHeight="1">
+      <c r="A63" s="4" t="inlineStr">
         <is>
           <t>Test Case</t>
         </is>
       </c>
-      <c r="B62" s="4" t="inlineStr">
+      <c r="B63" s="4" t="inlineStr">
         <is>
           <t>Input</t>
         </is>
       </c>
-      <c r="C62" s="4" t="inlineStr">
+      <c r="C63" s="4" t="inlineStr">
         <is>
           <t>Expected Outcome</t>
         </is>
       </c>
-      <c r="D62" s="4" t="inlineStr">
+      <c r="D63" s="4" t="inlineStr">
         <is>
           <t>New Tags Covered</t>
         </is>
       </c>
-      <c r="E62" s="4" t="n"/>
-      <c r="F62" s="4" t="n"/>
-      <c r="G62" s="4" t="n"/>
-      <c r="H62" s="4" t="inlineStr">
+      <c r="E63" s="4" t="n"/>
+      <c r="F63" s="4" t="n"/>
+      <c r="G63" s="4" t="n"/>
+      <c r="H63" s="4" t="inlineStr">
         <is>
           <t>Test đã thi hành</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="46" customHeight="1">
-      <c r="A63" s="18" t="n">
+    <row r="64" ht="46" customHeight="1">
+      <c r="A64" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="B63" s="5" t="inlineStr">
+      <c r="B64" s="5" t="inlineStr">
         <is>
           <t>fullName = 1 ký tự
 email = 6 ký tự
 password = 6 ký tự</t>
         </is>
       </c>
-      <c r="C63" s="5" t="inlineStr">
+      <c r="C64" s="5" t="inlineStr">
         <is>
           <t>Đăng ký thành công</t>
         </is>
       </c>
-      <c r="D63" s="19" t="inlineStr">
+      <c r="D64" s="19" t="inlineStr">
         <is>
           <t>V1, V2, V3, V4,
 B1, B8, B15</t>
-        </is>
-      </c>
-      <c r="E63" s="5" t="n"/>
-      <c r="F63" s="5" t="n"/>
-      <c r="G63" s="5" t="n"/>
-      <c r="H63" s="5" t="inlineStr">
-        <is>
-          <t>RegisterTagCoverageTest ·
-tagCoverage_caseHopLe</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="46" customHeight="1">
-      <c r="A64" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="B64" s="5" t="inlineStr">
-        <is>
-          <t>fullName = 2 ký tự
-email = 7 ký tự
-password = 7 ký tự</t>
-        </is>
-      </c>
-      <c r="C64" s="5" t="inlineStr">
-        <is>
-          <t>Đăng ký thành công</t>
-        </is>
-      </c>
-      <c r="D64" s="19" t="inlineStr">
-        <is>
-          <t>B2, B9, B16</t>
         </is>
       </c>
       <c r="E64" s="5" t="n"/>
@@ -11698,13 +11688,13 @@
     </row>
     <row r="65" ht="46" customHeight="1">
       <c r="A65" s="18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>fullName = 50 ký tự
-email = 75 ký tự
-password = 18 ký tự</t>
+          <t>fullName = 2 ký tự
+email = 7 ký tự
+password = 7 ký tự</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
@@ -11714,7 +11704,7 @@
       </c>
       <c r="D65" s="19" t="inlineStr">
         <is>
-          <t>B3, B10, B17</t>
+          <t>B2, B9, B16</t>
         </is>
       </c>
       <c r="E65" s="5" t="n"/>
@@ -11729,13 +11719,13 @@
     </row>
     <row r="66" ht="46" customHeight="1">
       <c r="A66" s="18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>fullName = 99 ký tự
-email = 149 ký tự
-password = 29 ký tự</t>
+          <t>fullName = 50 ký tự
+email = 75 ký tự
+password = 18 ký tự</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
@@ -11745,7 +11735,7 @@
       </c>
       <c r="D66" s="19" t="inlineStr">
         <is>
-          <t>B4, B11, B18</t>
+          <t>B3, B10, B17</t>
         </is>
       </c>
       <c r="E66" s="5" t="n"/>
@@ -11760,13 +11750,13 @@
     </row>
     <row r="67" ht="46" customHeight="1">
       <c r="A67" s="18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>fullName = 100 ký tự
-email = 150 ký tự
-password = 30 ký tự</t>
+          <t>fullName = 99 ký tự
+email = 149 ký tự
+password = 29 ký tự</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
@@ -11776,7 +11766,7 @@
       </c>
       <c r="D67" s="19" t="inlineStr">
         <is>
-          <t>B5, B12, B19</t>
+          <t>B4, B11, B18</t>
         </is>
       </c>
       <c r="E67" s="5" t="n"/>
@@ -11790,23 +11780,24 @@
       </c>
     </row>
     <row r="68" ht="46" customHeight="1">
-      <c r="A68" s="20" t="n">
-        <v>6</v>
+      <c r="A68" s="18" t="n">
+        <v>5</v>
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>password = 5 ký tự
-(hai trường kia ở nom)</t>
+          <t>fullName = 100 ký tự
+email = 150 ký tự
+password = 30 ký tự</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>Từ chối — password phải ≥ 6 ký tự</t>
-        </is>
-      </c>
-      <c r="D68" s="21" t="inlineStr">
-        <is>
-          <t>X1, B6</t>
+          <t>Đăng ký thành công</t>
+        </is>
+      </c>
+      <c r="D68" s="19" t="inlineStr">
+        <is>
+          <t>B5, B12, B19</t>
         </is>
       </c>
       <c r="E68" s="5" t="n"/>
@@ -11815,28 +11806,28 @@
       <c r="H68" s="5" t="inlineStr">
         <is>
           <t>RegisterTagCoverageTest ·
-tagCoverage_caseKhongHopLe</t>
+tagCoverage_caseHopLe</t>
         </is>
       </c>
     </row>
     <row r="69" ht="46" customHeight="1">
       <c r="A69" s="20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>password = 31 ký tự
+          <t>password = 5 ký tự
 (hai trường kia ở nom)</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>Từ chối — password phải ≤ 30 ký tự</t>
+          <t>Từ chối — password phải ≥ 6 ký tự</t>
         </is>
       </c>
       <c r="D69" s="21" t="inlineStr">
         <is>
-          <t>X2, B7</t>
+          <t>X1, B6</t>
         </is>
       </c>
       <c r="E69" s="5" t="n"/>
@@ -11851,22 +11842,22 @@
     </row>
     <row r="70" ht="46" customHeight="1">
       <c r="A70" s="20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>password = 8 dấu cách
+          <t>password = 31 ký tự
 (hai trường kia ở nom)</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>Từ chối — password không được để trống</t>
+          <t>Từ chối — password phải ≤ 30 ký tự</t>
         </is>
       </c>
       <c r="D70" s="21" t="inlineStr">
         <is>
-          <t>X3</t>
+          <t>X2, B7</t>
         </is>
       </c>
       <c r="E70" s="5" t="n"/>
@@ -11881,22 +11872,22 @@
     </row>
     <row r="71" ht="46" customHeight="1">
       <c r="A71" s="20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>password = null
+          <t>password = 8 dấu cách
 (hai trường kia ở nom)</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>Từ chối — password bắt buộc</t>
+          <t>Từ chối — password không được để trống</t>
         </is>
       </c>
       <c r="D71" s="21" t="inlineStr">
         <is>
-          <t>X4</t>
+          <t>X3</t>
         </is>
       </c>
       <c r="E71" s="5" t="n"/>
@@ -11911,22 +11902,22 @@
     </row>
     <row r="72" ht="46" customHeight="1">
       <c r="A72" s="20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>fullName = 101 ký tự
+          <t>password = null
 (hai trường kia ở nom)</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>Từ chối — họ tên phải ≤ 100 ký tự</t>
+          <t>Từ chối — password bắt buộc</t>
         </is>
       </c>
       <c r="D72" s="21" t="inlineStr">
         <is>
-          <t>X5, B14</t>
+          <t>X4</t>
         </is>
       </c>
       <c r="E72" s="5" t="n"/>
@@ -11941,22 +11932,22 @@
     </row>
     <row r="73" ht="46" customHeight="1">
       <c r="A73" s="20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>fullName = 5 dấu cách
+          <t>fullName = 101 ký tự
 (hai trường kia ở nom)</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>Từ chối — họ tên không được để trống</t>
+          <t>Từ chối — họ tên phải ≤ 100 ký tự</t>
         </is>
       </c>
       <c r="D73" s="21" t="inlineStr">
         <is>
-          <t>X6</t>
+          <t>X5, B14</t>
         </is>
       </c>
       <c r="E73" s="5" t="n"/>
@@ -11971,22 +11962,22 @@
     </row>
     <row r="74" ht="46" customHeight="1">
       <c r="A74" s="20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>fullName = null
+          <t>fullName = 5 dấu cách
 (hai trường kia ở nom)</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>Từ chối — họ tên bắt buộc</t>
+          <t>Từ chối — họ tên không được để trống</t>
         </is>
       </c>
       <c r="D74" s="21" t="inlineStr">
         <is>
-          <t>X7</t>
+          <t>X6</t>
         </is>
       </c>
       <c r="E74" s="5" t="n"/>
@@ -12001,22 +11992,22 @@
     </row>
     <row r="75" ht="46" customHeight="1">
       <c r="A75" s="20" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>fullName = chuỗi rỗng
+          <t>fullName = null
 (hai trường kia ở nom)</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>Từ chối — họ tên không được để trống</t>
+          <t>Từ chối — họ tên bắt buộc</t>
         </is>
       </c>
       <c r="D75" s="21" t="inlineStr">
         <is>
-          <t>B13</t>
+          <t>X7</t>
         </is>
       </c>
       <c r="E75" s="5" t="n"/>
@@ -12031,22 +12022,22 @@
     </row>
     <row r="76" ht="46" customHeight="1">
       <c r="A76" s="20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>email = 5 ký tự (a@b.c)
+          <t>fullName = chuỗi rỗng
 (hai trường kia ở nom)</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>Từ chối — email phải ≥ 6 ký tự</t>
+          <t>Từ chối — họ tên không được để trống</t>
         </is>
       </c>
       <c r="D76" s="21" t="inlineStr">
         <is>
-          <t>X8, B20</t>
+          <t>B13</t>
         </is>
       </c>
       <c r="E76" s="5" t="n"/>
@@ -12061,22 +12052,22 @@
     </row>
     <row r="77" ht="46" customHeight="1">
       <c r="A77" s="20" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>email = 151 ký tự
+          <t>email = 5 ký tự (a@b.c)
 (hai trường kia ở nom)</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>Từ chối — email phải ≤ 150 ký tự</t>
+          <t>Từ chối — email phải ≥ 6 ký tự</t>
         </is>
       </c>
       <c r="D77" s="21" t="inlineStr">
         <is>
-          <t>X9, B21</t>
+          <t>X8, B20</t>
         </is>
       </c>
       <c r="E77" s="5" t="n"/>
@@ -12091,22 +12082,22 @@
     </row>
     <row r="78" ht="46" customHeight="1">
       <c r="A78" s="20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>email = khong-phai-email
+          <t>email = 151 ký tự
 (hai trường kia ở nom)</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>Từ chối — email sai định dạng</t>
+          <t>Từ chối — email phải ≤ 150 ký tự</t>
         </is>
       </c>
       <c r="D78" s="21" t="inlineStr">
         <is>
-          <t>X10</t>
+          <t>X9, B21</t>
         </is>
       </c>
       <c r="E78" s="5" t="n"/>
@@ -12121,22 +12112,22 @@
     </row>
     <row r="79" ht="46" customHeight="1">
       <c r="A79" s="20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>email = null
+          <t>email = khong-phai-email
 (hai trường kia ở nom)</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>Từ chối — email bắt buộc</t>
+          <t>Từ chối — email sai định dạng</t>
         </is>
       </c>
       <c r="D79" s="21" t="inlineStr">
         <is>
-          <t>X11</t>
+          <t>X10</t>
         </is>
       </c>
       <c r="E79" s="5" t="n"/>
@@ -12150,22 +12141,23 @@
       </c>
     </row>
     <row r="80" ht="46" customHeight="1">
-      <c r="A80" s="18" t="n">
-        <v>18</v>
+      <c r="A80" s="20" t="n">
+        <v>17</v>
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>Tệp bảng điểm = 0 byte</t>
+          <t>email = null
+(hai trường kia ở nom)</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>Tải lên thành công</t>
-        </is>
-      </c>
-      <c r="D80" s="19" t="inlineStr">
-        <is>
-          <t>V5, B22</t>
+          <t>Từ chối — email bắt buộc</t>
+        </is>
+      </c>
+      <c r="D80" s="21" t="inlineStr">
+        <is>
+          <t>X11</t>
         </is>
       </c>
       <c r="E80" s="5" t="n"/>
@@ -12173,18 +12165,18 @@
       <c r="G80" s="5" t="n"/>
       <c r="H80" s="5" t="inlineStr">
         <is>
-          <t>OnboardingFileSizeBvaTest ·
-fileSize_normalBva</t>
+          <t>RegisterTagCoverageTest ·
+tagCoverage_caseKhongHopLe</t>
         </is>
       </c>
     </row>
     <row r="81" ht="46" customHeight="1">
       <c r="A81" s="18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>Tệp bảng điểm = 1 byte</t>
+          <t>Tệp bảng điểm = 0 byte</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
@@ -12194,7 +12186,7 @@
       </c>
       <c r="D81" s="19" t="inlineStr">
         <is>
-          <t>B23</t>
+          <t>V5, B22</t>
         </is>
       </c>
       <c r="E81" s="5" t="n"/>
@@ -12209,11 +12201,11 @@
     </row>
     <row r="82" ht="46" customHeight="1">
       <c r="A82" s="18" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>Tệp bảng điểm = 5 MB</t>
+          <t>Tệp bảng điểm = 1 byte</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
@@ -12223,7 +12215,7 @@
       </c>
       <c r="D82" s="19" t="inlineStr">
         <is>
-          <t>B24</t>
+          <t>B23</t>
         </is>
       </c>
       <c r="E82" s="5" t="n"/>
@@ -12238,11 +12230,11 @@
     </row>
     <row r="83" ht="46" customHeight="1">
       <c r="A83" s="18" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>Tệp bảng điểm = 10 MB − 1 byte</t>
+          <t>Tệp bảng điểm = 5 MB</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
@@ -12252,7 +12244,7 @@
       </c>
       <c r="D83" s="19" t="inlineStr">
         <is>
-          <t>B25</t>
+          <t>B24</t>
         </is>
       </c>
       <c r="E83" s="5" t="n"/>
@@ -12267,11 +12259,11 @@
     </row>
     <row r="84" ht="46" customHeight="1">
       <c r="A84" s="18" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>Tệp bảng điểm = 10 MB</t>
+          <t>Tệp bảng điểm = 10 MB − 1 byte</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
@@ -12281,7 +12273,7 @@
       </c>
       <c r="D84" s="19" t="inlineStr">
         <is>
-          <t>B26</t>
+          <t>B25</t>
         </is>
       </c>
       <c r="E84" s="5" t="n"/>
@@ -12295,22 +12287,22 @@
       </c>
     </row>
     <row r="85" ht="46" customHeight="1">
-      <c r="A85" s="20" t="n">
-        <v>23</v>
+      <c r="A85" s="18" t="n">
+        <v>22</v>
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>Tệp bảng điểm = 10 MB + 1 byte</t>
+          <t>Tệp bảng điểm = 10 MB</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>Từ chối — tệp vượt quá 10 MB</t>
-        </is>
-      </c>
-      <c r="D85" s="21" t="inlineStr">
-        <is>
-          <t>X12, B27</t>
+          <t>Tải lên thành công</t>
+        </is>
+      </c>
+      <c r="D85" s="19" t="inlineStr">
+        <is>
+          <t>B26</t>
         </is>
       </c>
       <c r="E85" s="5" t="n"/>
@@ -12319,66 +12311,96 @@
       <c r="H85" s="5" t="inlineStr">
         <is>
           <t>OnboardingFileSizeBvaTest ·
+fileSize_normalBva</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="46" customHeight="1">
+      <c r="A86" s="20" t="n">
+        <v>23</v>
+      </c>
+      <c r="B86" s="5" t="inlineStr">
+        <is>
+          <t>Tệp bảng điểm = 10 MB + 1 byte</t>
+        </is>
+      </c>
+      <c r="C86" s="5" t="inlineStr">
+        <is>
+          <t>Từ chối — tệp vượt quá 10 MB</t>
+        </is>
+      </c>
+      <c r="D86" s="21" t="inlineStr">
+        <is>
+          <t>X12, B27</t>
+        </is>
+      </c>
+      <c r="E86" s="5" t="n"/>
+      <c r="F86" s="5" t="n"/>
+      <c r="G86" s="5" t="n"/>
+      <c r="H86" s="5" t="inlineStr">
+        <is>
+          <t>OnboardingFileSizeBvaTest ·
 fileSize_maxPlusOne</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="40" customHeight="1">
-      <c r="A86" s="11" t="inlineStr">
+    <row r="87" ht="40" customHeight="1">
+      <c r="A87" s="11" t="inlineStr">
         <is>
           <t>CÁCH ĐỌC: mỗi hàng là MỘT lần điền form đầy đủ rồi bấm gửi, giống bảng Thiết kế test cases ở slide 33. Cột New Tags Covered ghi những tag mà case đó phủ LẦN ĐẦU — tag đã phủ ở case trước thì không ghi lại. Nền xanh = case hợp lệ, nền hồng = case bị từ chối.</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="54" customHeight="1">
-      <c r="A87" s="11" t="inlineStr">
+    <row r="88" ht="54" customHeight="1">
+      <c r="A88" s="11" t="inlineStr">
         <is>
           <t>VÌ SAO CHỈ CẦN 23 CASE CHO 44 TAG: case HỢP LỆ được phép gộp nhiều tag cùng lúc — TC1 vừa phủ V1 V2 V3 V4 vừa phủ ba giá trị biên B1 B8 B15, vì cả ba trường đều hợp lệ nên không trường nào che kết quả của trường nào. Ngược lại case KHÔNG hợp lệ chỉ được đặt MỘT vi phạm mỗi lần: nếu vừa để password quá ngắn vừa để email sai định dạng thì form vẫn báo lỗi, nhưng không biết nó bắt được vi phạm nào — hiện tượng che lỗi (masking). Vì vậy 12 tag X phải trải ra 12 case riêng.</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="40" customHeight="1">
-      <c r="A88" s="11" t="inlineStr">
-        <is>
-          <t>GỘP THÊM ĐỂ TỐI THIỂU HOÁ: vài case không hợp lệ phủ được hai tag cùng lúc vì giá trị biên nằm ngay trong lớp không hợp lệ. TC6 đặt password = 5 ký tự nên vừa phủ lớp X1 (&lt; 6 ký tự) vừa phủ giá trị biên B6 (min-1). TC7, TC10, TC14, TC15, TC23 cũng theo cách này.</t>
         </is>
       </c>
     </row>
     <row r="89" ht="40" customHeight="1">
       <c r="A89" s="11" t="inlineStr">
         <is>
-          <t>KIỂM CHỨNG KHÔNG CHE LỖI: mỗi case TC6-TC17 trong code khẳng định form sinh ra ĐÚNG MỘT vi phạm, và vi phạm đó nằm trên ĐÚNG trường đang bị làm sai. Nếu hai trường cùng sai thì assertion hasSize(1) sẽ đỏ — đó là cách chứng minh bằng code rằng thiết kế không bị che lỗi.</t>
+          <t>GỘP THÊM ĐỂ TỐI THIỂU HOÁ: vài case không hợp lệ phủ được hai tag cùng lúc vì giá trị biên nằm ngay trong lớp không hợp lệ. TC6 đặt password = 5 ký tự nên vừa phủ lớp X1 (&lt; 6 ký tự) vừa phủ giá trị biên B6 (min-1). TC7, TC10, TC14, TC15, TC23 cũng theo cách này.</t>
         </is>
       </c>
     </row>
     <row r="90" ht="40" customHeight="1">
       <c r="A90" s="11" t="inlineStr">
         <is>
+          <t>KIỂM CHỨNG KHÔNG CHE LỖI: mỗi case TC6-TC17 trong code khẳng định form sinh ra ĐÚNG MỘT vi phạm, và vi phạm đó nằm trên ĐÚNG trường đang bị làm sai. Nếu hai trường cùng sai thì assertion hasSize(1) sẽ đỏ — đó là cách chứng minh bằng code rằng thiết kế không bị che lỗi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="40" customHeight="1">
+      <c r="A91" s="11" t="inlineStr">
+        <is>
           <t>TC18-TC23 tách riêng vì tệp bảng điểm KHÔNG thuộc form đăng ký — nó là chức năng tải bảng điểm ở bước onboarding. Slide 33 gộp tag trong phạm vi MỘT màn hình nhập liệu, hai chức năng khác nhau thì không gộp chung một lần submit được.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="20">
     <mergeCell ref="A48:H48"/>
-    <mergeCell ref="A39:H39"/>
     <mergeCell ref="A59:H59"/>
+    <mergeCell ref="A51:H51"/>
+    <mergeCell ref="A60:H60"/>
     <mergeCell ref="A11:H11"/>
-    <mergeCell ref="A61:H61"/>
+    <mergeCell ref="A49:H49"/>
     <mergeCell ref="A88:H88"/>
     <mergeCell ref="A87:H87"/>
     <mergeCell ref="A90:H90"/>
-    <mergeCell ref="A37:H37"/>
     <mergeCell ref="A89:H89"/>
-    <mergeCell ref="A50:H50"/>
-    <mergeCell ref="A86:H86"/>
-    <mergeCell ref="A57:H57"/>
-    <mergeCell ref="A47:H47"/>
-    <mergeCell ref="A22:H22"/>
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="A21:H21"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A23:H23"/>
     <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A20:H20"/>
-    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A62:H62"/>
+    <mergeCell ref="A91:H91"/>
+    <mergeCell ref="A38:H38"/>
     <mergeCell ref="A58:H58"/>
+    <mergeCell ref="A40:H40"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14064,6 +14086,10 @@
           <t>2 giá trị</t>
         </is>
       </c>
+      <c r="K22" s="8" t="n"/>
+      <c r="L22" s="8" t="n"/>
+      <c r="M22" s="8" t="n"/>
+      <c r="N22" s="9" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="66" t="inlineStr">
@@ -14096,6 +14122,10 @@
           <t>2 giá trị — đặc tả không phân biệt bốn đuôi với nhau</t>
         </is>
       </c>
+      <c r="K23" s="8" t="n"/>
+      <c r="L23" s="8" t="n"/>
+      <c r="M23" s="8" t="n"/>
+      <c r="N23" s="9" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="66" t="inlineStr">
@@ -14128,6 +14158,10 @@
           <t>2 giá trị</t>
         </is>
       </c>
+      <c r="K24" s="8" t="n"/>
+      <c r="L24" s="8" t="n"/>
+      <c r="M24" s="8" t="n"/>
+      <c r="N24" s="9" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="70" t="inlineStr">
@@ -14241,6 +14275,10 @@
           <t>R4' gộp cả ô đã phát hiện DEF-011 — xem ghi chú bên dưới</t>
         </is>
       </c>
+      <c r="K28" s="8" t="n"/>
+      <c r="L28" s="8" t="n"/>
+      <c r="M28" s="8" t="n"/>
+      <c r="N28" s="9" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="70" t="inlineStr">
@@ -14386,6 +14424,7 @@
           <t>.pdf · .png · .jpg · .jpeg</t>
         </is>
       </c>
+      <c r="D35" s="9" t="n"/>
       <c r="E35" s="79" t="n">
         <v>4</v>
       </c>
@@ -14394,6 +14433,14 @@
           <t>Mã nguồn so sánh từng đuôi bằng một chuỗi &amp;&amp; — bốn nhánh riêng. Báo cáo bao phủ chỉ đích danh ba nhánh chưa ai chạm tới, nên phải kiểm đủ bốn.</t>
         </is>
       </c>
+      <c r="G35" s="8" t="n"/>
+      <c r="H35" s="8" t="n"/>
+      <c r="I35" s="8" t="n"/>
+      <c r="J35" s="8" t="n"/>
+      <c r="K35" s="8" t="n"/>
+      <c r="L35" s="8" t="n"/>
+      <c r="M35" s="8" t="n"/>
+      <c r="N35" s="9" t="n"/>
     </row>
     <row r="36" ht="34" customHeight="1">
       <c r="A36" s="66" t="inlineStr">
@@ -14411,6 +14458,7 @@
           <t>.exe · tên không có dấu chấm</t>
         </is>
       </c>
+      <c r="D36" s="9" t="n"/>
       <c r="E36" s="79" t="n">
         <v>2</v>
       </c>
@@ -14419,6 +14467,14 @@
           <t>Hai giá trị này TRƯỚC KHI SỬA cho hai kết quả khác nhau: .exe trả lỗi 400 đúng như đặc tả, còn tên không có dấu chấm ném StringIndexOutOfBoundsException thành lỗi 500 — chính là DEF-011. Sau khi sửa mới thật sự cùng một lớp.</t>
         </is>
       </c>
+      <c r="G36" s="8" t="n"/>
+      <c r="H36" s="8" t="n"/>
+      <c r="I36" s="8" t="n"/>
+      <c r="J36" s="8" t="n"/>
+      <c r="K36" s="8" t="n"/>
+      <c r="L36" s="8" t="n"/>
+      <c r="M36" s="8" t="n"/>
+      <c r="N36" s="9" t="n"/>
     </row>
     <row r="37" ht="34" customHeight="1">
       <c r="A37" s="66" t="inlineStr">
@@ -14436,6 +14492,7 @@
           <t>null</t>
         </is>
       </c>
+      <c r="D37" s="9" t="n"/>
       <c r="E37" s="79" t="n">
         <v>1</v>
       </c>
@@ -14444,6 +14501,14 @@
           <t>Một giá trị duy nhất, không có gì để tách.</t>
         </is>
       </c>
+      <c r="G37" s="8" t="n"/>
+      <c r="H37" s="8" t="n"/>
+      <c r="I37" s="8" t="n"/>
+      <c r="J37" s="8" t="n"/>
+      <c r="K37" s="8" t="n"/>
+      <c r="L37" s="8" t="n"/>
+      <c r="M37" s="8" t="n"/>
+      <c r="N37" s="9" t="n"/>
     </row>
     <row r="38" ht="34" customHeight="1">
       <c r="A38" s="66" t="inlineStr">
@@ -14461,6 +14526,7 @@
           <t>1 byte · 11 MB</t>
         </is>
       </c>
+      <c r="D38" s="9" t="n"/>
       <c r="E38" s="79" t="n">
         <v>1</v>
       </c>
@@ -14469,6 +14535,14 @@
           <t>Chỉ lấy giá trị nominal để phân biệt nhánh. Các giá trị sát biên 10 MB thuộc về sheet 01 — kỹ thuật giá trị biên, không phải bảng quyết định.</t>
         </is>
       </c>
+      <c r="G38" s="8" t="n"/>
+      <c r="H38" s="8" t="n"/>
+      <c r="I38" s="8" t="n"/>
+      <c r="J38" s="8" t="n"/>
+      <c r="K38" s="8" t="n"/>
+      <c r="L38" s="8" t="n"/>
+      <c r="M38" s="8" t="n"/>
+      <c r="N38" s="9" t="n"/>
     </row>
     <row r="39" ht="30" customHeight="1">
       <c r="A39" s="56" t="inlineStr">

--- a/BaoCao-KiemThu-CareerCompass.xlsx
+++ b/BaoCao-KiemThu-CareerCompass.xlsx
@@ -1713,6 +1713,7 @@
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="F21:H21"/>
     <mergeCell ref="F8:H8"/>
     <mergeCell ref="F17:H17"/>
     <mergeCell ref="F23:H23"/>
@@ -1721,7 +1722,6 @@
     <mergeCell ref="F13:H13"/>
     <mergeCell ref="F30:H30"/>
     <mergeCell ref="F9:H9"/>
-    <mergeCell ref="F15:H15"/>
     <mergeCell ref="A26:H26"/>
     <mergeCell ref="F14:H14"/>
     <mergeCell ref="A32:H32"/>
@@ -1734,7 +1734,7 @@
     <mergeCell ref="A19:H19"/>
     <mergeCell ref="F12:H12"/>
     <mergeCell ref="F7:H7"/>
-    <mergeCell ref="F21:H21"/>
+    <mergeCell ref="F15:H15"/>
     <mergeCell ref="F24:H24"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3282,7 +3282,7 @@
     <row r="3" ht="44" customHeight="1">
       <c r="A3" s="64" t="inlineStr">
         <is>
-          <t>MỐC THỜI GIAN ĐO: các chỉ số ở sheet này được đo ngày 06/09/2026, ngay sau khi bổ sung phần kiểm thử hộp trắng — giữ nguyên để phép so sánh trước/sau còn ý nghĩa. Nhóm tiếp tục bổ sung test sau mốc đó, nên số liệu HIỆN TẠI (đo 12/09/2026) cao hơn: bao phủ dòng 78,6%, bao phủ nhánh 72,5%. Xem sheet "00. Tong quan" để biết trạng thái mới nhất.</t>
+          <t>MỐC THỜI GIAN ĐO: các chỉ số ở sheet này được đo ngày 06/09/2026, ngay sau khi bổ sung phần kiểm thử hộp trắng — giữ nguyên để phép so sánh trước/sau còn ý nghĩa. Nhóm tiếp tục bổ sung test sau mốc đó, nên số liệu HIỆN TẠI (đo 16/09/2026) cao hơn: bao phủ dòng 78,6%, bao phủ nhánh 72,5%. Xem sheet "00. Tong quan" để biết trạng thái mới nhất.</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
     <row r="3" ht="44" customHeight="1">
       <c r="A3" s="64" t="inlineStr">
         <is>
-          <t>MỐC THỜI GIAN ĐO: các chỉ số ở sheet này được đo ngày 06/09/2026, ngay sau khi bổ sung phần kiểm thử hộp trắng — giữ nguyên để phép so sánh trước/sau còn ý nghĩa. Nhóm tiếp tục bổ sung test sau mốc đó, nên số liệu HIỆN TẠI (đo 12/09/2026) cao hơn: bao phủ dòng 78,6%, bao phủ nhánh 72,5%. Xem sheet "00. Tong quan" để biết trạng thái mới nhất.</t>
+          <t>MỐC THỜI GIAN ĐO: các chỉ số ở sheet này được đo ngày 06/09/2026, ngay sau khi bổ sung phần kiểm thử hộp trắng — giữ nguyên để phép so sánh trước/sau còn ý nghĩa. Nhóm tiếp tục bổ sung test sau mốc đó, nên số liệu HIỆN TẠI (đo 16/09/2026) cao hơn: bao phủ dòng 78,6%, bao phủ nhánh 72,5%. Xem sheet "00. Tong quan" để biết trạng thái mới nhất.</t>
         </is>
       </c>
     </row>
@@ -6361,6 +6361,7 @@
         <v>0</v>
       </c>
     </row>
+    <row r="73"/>
     <row r="74">
       <c r="A74" s="31" t="inlineStr">
         <is>
@@ -9344,7 +9345,7 @@
     <row r="4" ht="26" customHeight="1">
       <c r="A4" s="54" t="inlineStr">
         <is>
-          <t>KỲ BÁO CÁO — từ 22/07/2026, 74 commit của 3 thành viên, 399 trường hợp kiểm thử tự động</t>
+          <t>KỲ BÁO CÁO — từ 22/07/2026, 86 commit của 3 thành viên, 399 trường hợp kiểm thử tự động</t>
         </is>
       </c>
     </row>
@@ -9390,7 +9391,7 @@
       </c>
       <c r="C8" s="9" t="n"/>
       <c r="D8" s="6" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="E8" s="5" t="inlineStr"/>
       <c r="F8" s="5" t="inlineStr"/>
@@ -9410,7 +9411,7 @@
       </c>
       <c r="C9" s="9" t="n"/>
       <c r="D9" s="6" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E9" s="5" t="inlineStr"/>
       <c r="F9" s="5" t="inlineStr"/>
@@ -10198,7 +10199,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -10384,7 +10384,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14" ht="24" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
@@ -10549,7 +10548,6 @@
         </is>
       </c>
     </row>
-    <row r="22"/>
     <row r="23" ht="24" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
@@ -11048,7 +11046,6 @@
         </is>
       </c>
     </row>
-    <row r="39"/>
     <row r="40" ht="24" customHeight="1">
       <c r="A40" s="3" t="inlineStr">
         <is>
@@ -11316,7 +11313,6 @@
         </is>
       </c>
     </row>
-    <row r="50"/>
     <row r="51" ht="24" customHeight="1">
       <c r="A51" s="3" t="inlineStr">
         <is>
@@ -11616,7 +11612,6 @@
         </is>
       </c>
     </row>
-    <row r="61"/>
     <row r="62" ht="24" customHeight="1">
       <c r="A62" s="3" t="inlineStr">
         <is>

--- a/BaoCao-KiemThu-CareerCompass.xlsx
+++ b/BaoCao-KiemThu-CareerCompass.xlsx
@@ -389,7 +389,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -617,6 +617,12 @@
     </xf>
     <xf numFmtId="0" fontId="30" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6361,7 +6367,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73"/>
     <row r="74">
       <c r="A74" s="31" t="inlineStr">
         <is>
@@ -10172,7 +10177,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H91"/>
+  <dimension ref="A1:H103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -10199,6 +10204,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -10384,6 +10390,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14" ht="24" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
@@ -10548,6 +10555,7 @@
         </is>
       </c>
     </row>
+    <row r="22"/>
     <row r="23" ht="24" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
@@ -11046,6 +11054,7 @@
         </is>
       </c>
     </row>
+    <row r="39"/>
     <row r="40" ht="24" customHeight="1">
       <c r="A40" s="3" t="inlineStr">
         <is>
@@ -11313,73 +11322,384 @@
         </is>
       </c>
     </row>
+    <row r="50"/>
     <row r="51" ht="24" customHeight="1">
       <c r="A51" s="3" t="inlineStr">
         <is>
+          <t>BẢNG 3b — BVA DUNG LƯỢNG TỆP BẢNG ĐIỂM (n = 1 biến) · Standard 4n+1 = 5 case, cộng 1 case Robustness · 6 test</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="32" customHeight="1">
+      <c r="A52" s="55" t="inlineStr">
+        <is>
+          <t>VÌ SAO TÁCH KHỎI BẢNG 2: cột của Bảng 2 là fullName | email | password — ba biến của MỘT biểu mẫu. Dung lượng tệp thuộc chức năng khác (OnboardingService.saveTranscript), chỉ có MỘT biến, không có giá trị nào cho ba cột ấy nên phải đứng bảng riêng. Nhãn B22–B27 và các case TC18–TC23 ở Bảng 4 và Bảng 5 chính là sáu dòng dưới đây.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="65" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="B53" s="65" t="inlineStr">
+        <is>
+          <t>Nhãn</t>
+        </is>
+      </c>
+      <c r="C53" s="65" t="inlineStr">
+        <is>
+          <t>Dung lượng tệp</t>
+        </is>
+      </c>
+      <c r="D53" s="65" t="inlineStr">
+        <is>
+          <t>Giá trị biên</t>
+        </is>
+      </c>
+      <c r="E53" s="65" t="inlineStr">
+        <is>
+          <t>Expected Output</t>
+        </is>
+      </c>
+      <c r="F53" s="65" t="inlineStr">
+        <is>
+          <t>Kết quả thực tế</t>
+        </is>
+      </c>
+      <c r="G53" s="65" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="H53" s="65" t="inlineStr">
+        <is>
+          <t>Method trong code</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="67" t="n">
+        <v>20</v>
+      </c>
+      <c r="B54" s="67" t="inlineStr">
+        <is>
+          <t>B22</t>
+        </is>
+      </c>
+      <c r="C54" s="82" t="inlineStr">
+        <is>
+          <t>0 byte</t>
+        </is>
+      </c>
+      <c r="D54" s="67" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="E54" s="66" t="inlineStr">
+        <is>
+          <t>Hợp lệ — tải lên thành công</t>
+        </is>
+      </c>
+      <c r="F54" s="66" t="inlineStr">
+        <is>
+          <t>Đúng như mong đợi</t>
+        </is>
+      </c>
+      <c r="G54" s="68" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H54" s="80" t="inlineStr">
+        <is>
+          <t>fileSize_normalBva</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="67" t="n">
+        <v>21</v>
+      </c>
+      <c r="B55" s="67" t="inlineStr">
+        <is>
+          <t>B23</t>
+        </is>
+      </c>
+      <c r="C55" s="82" t="inlineStr">
+        <is>
+          <t>1 byte</t>
+        </is>
+      </c>
+      <c r="D55" s="67" t="inlineStr">
+        <is>
+          <t>min+</t>
+        </is>
+      </c>
+      <c r="E55" s="66" t="inlineStr">
+        <is>
+          <t>Hợp lệ — tải lên thành công</t>
+        </is>
+      </c>
+      <c r="F55" s="66" t="inlineStr">
+        <is>
+          <t>Đúng như mong đợi</t>
+        </is>
+      </c>
+      <c r="G55" s="68" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H55" s="80" t="inlineStr">
+        <is>
+          <t>fileSize_normalBva</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="67" t="n">
+        <v>22</v>
+      </c>
+      <c r="B56" s="67" t="inlineStr">
+        <is>
+          <t>B24</t>
+        </is>
+      </c>
+      <c r="C56" s="82" t="inlineStr">
+        <is>
+          <t>5 MB</t>
+        </is>
+      </c>
+      <c r="D56" s="67" t="inlineStr">
+        <is>
+          <t>nom</t>
+        </is>
+      </c>
+      <c r="E56" s="66" t="inlineStr">
+        <is>
+          <t>Hợp lệ — tải lên thành công</t>
+        </is>
+      </c>
+      <c r="F56" s="66" t="inlineStr">
+        <is>
+          <t>Đúng như mong đợi</t>
+        </is>
+      </c>
+      <c r="G56" s="68" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H56" s="80" t="inlineStr">
+        <is>
+          <t>fileSize_normalBva</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="67" t="n">
+        <v>23</v>
+      </c>
+      <c r="B57" s="67" t="inlineStr">
+        <is>
+          <t>B25</t>
+        </is>
+      </c>
+      <c r="C57" s="82" t="inlineStr">
+        <is>
+          <t>10 MB − 1 byte</t>
+        </is>
+      </c>
+      <c r="D57" s="67" t="inlineStr">
+        <is>
+          <t>max-</t>
+        </is>
+      </c>
+      <c r="E57" s="66" t="inlineStr">
+        <is>
+          <t>Hợp lệ — tải lên thành công</t>
+        </is>
+      </c>
+      <c r="F57" s="66" t="inlineStr">
+        <is>
+          <t>Đúng như mong đợi</t>
+        </is>
+      </c>
+      <c r="G57" s="68" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H57" s="80" t="inlineStr">
+        <is>
+          <t>fileSize_normalBva</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="67" t="n">
+        <v>24</v>
+      </c>
+      <c r="B58" s="67" t="inlineStr">
+        <is>
+          <t>B26</t>
+        </is>
+      </c>
+      <c r="C58" s="82" t="inlineStr">
+        <is>
+          <t>10 MB</t>
+        </is>
+      </c>
+      <c r="D58" s="67" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+      <c r="E58" s="66" t="inlineStr">
+        <is>
+          <t>Hợp lệ — tải lên thành công</t>
+        </is>
+      </c>
+      <c r="F58" s="66" t="inlineStr">
+        <is>
+          <t>Đúng như mong đợi</t>
+        </is>
+      </c>
+      <c r="G58" s="68" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H58" s="80" t="inlineStr">
+        <is>
+          <t>fileSize_normalBva</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="67" t="n">
+        <v>25</v>
+      </c>
+      <c r="B59" s="67" t="inlineStr">
+        <is>
+          <t>B27</t>
+        </is>
+      </c>
+      <c r="C59" s="83" t="inlineStr">
+        <is>
+          <t>10 MB + 1 byte</t>
+        </is>
+      </c>
+      <c r="D59" s="67" t="inlineStr">
+        <is>
+          <t>max+</t>
+        </is>
+      </c>
+      <c r="E59" s="66" t="inlineStr">
+        <is>
+          <t>KHÔNG hợp lệ — "File vượt quá dung lượng tối đa 10MB."</t>
+        </is>
+      </c>
+      <c r="F59" s="66" t="inlineStr">
+        <is>
+          <t>Đúng như mong đợi</t>
+        </is>
+      </c>
+      <c r="G59" s="68" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H59" s="80" t="inlineStr">
+        <is>
+          <t>fileSize_maxPlusOne_isRejected</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="42" customHeight="1">
+      <c r="A60" s="56" t="inlineStr">
+        <is>
+          <t>CÔNG THỨC GẶP GIỚI HẠN CỦA MIỀN GIÁ TRỊ THẬT — điểm chỉ trường hợp n = 1 này mới lộ ra. Robustness BVA cho 6n + 1 = 7 case, nhưng ở đây chỉ có 6. Thiếu đúng một case: min− = −1 byte. Không tồn tại tệp nào dung lượng âm, nên giá trị đó không nằm trong miền và không có gì để kiểm. Với ba biến của form đăng ký thì min− luôn tồn tại (chuỗi rỗng, chuỗi ngắn hơn giới hạn) nên Bảng 3 đủ cả 6 case bổ sung.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="26" customHeight="1">
+      <c r="A61" s="55" t="inlineStr">
+        <is>
+          <t>CÁCH ĐỌC: ô tô tím là giá trị biên trong miền hợp lệ, ô tô hồng là giá trị nằm ngoài miền (dirty case). Năm case đầu phủ đúng 4n + 1 = 5 điểm chuẩn min / min+ / nom / max− / max của một biến duy nhất.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="24" customHeight="1">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
           <t>BẢNG 4 — PHÂN HOẠCH LỚP TƯƠNG ĐƯƠNG (mẫu slide 32)</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="30" customHeight="1">
-      <c r="A52" s="4" t="inlineStr">
+    <row r="64" ht="30" customHeight="1">
+      <c r="A64" s="4" t="inlineStr">
         <is>
           <t>Conditions</t>
         </is>
       </c>
-      <c r="B52" s="4" t="inlineStr">
+      <c r="B64" s="4" t="inlineStr">
         <is>
           <t>Valid Partitions</t>
         </is>
       </c>
-      <c r="C52" s="4" t="inlineStr">
+      <c r="C64" s="4" t="inlineStr">
         <is>
           <t>Tag</t>
         </is>
       </c>
-      <c r="D52" s="4" t="inlineStr">
+      <c r="D64" s="4" t="inlineStr">
         <is>
           <t>Invalid Partitions</t>
         </is>
       </c>
-      <c r="E52" s="4" t="inlineStr">
+      <c r="E64" s="4" t="inlineStr">
         <is>
           <t>Tag</t>
         </is>
       </c>
-      <c r="F52" s="4" t="inlineStr">
+      <c r="F64" s="4" t="inlineStr">
         <is>
           <t>Valid Boundaries</t>
         </is>
       </c>
-      <c r="G52" s="4" t="inlineStr">
+      <c r="G64" s="4" t="inlineStr">
         <is>
           <t>Tag</t>
         </is>
       </c>
-      <c r="H52" s="4" t="inlineStr">
+      <c r="H64" s="4" t="inlineStr">
         <is>
           <t>Robustness</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="62" customHeight="1">
-      <c r="A53" s="5" t="inlineStr">
+    <row r="65" ht="62" customHeight="1">
+      <c r="A65" s="5" t="inlineStr">
         <is>
           <t>password</t>
         </is>
       </c>
-      <c r="B53" s="5" t="inlineStr">
+      <c r="B65" s="5" t="inlineStr">
         <is>
           <t>6–30 ký tự,
 có ít nhất 1 ký tự không trắng</t>
         </is>
       </c>
-      <c r="C53" s="5" t="inlineStr">
+      <c r="C65" s="5" t="inlineStr">
         <is>
           <t>V1</t>
         </is>
       </c>
-      <c r="D53" s="5" t="inlineStr">
+      <c r="D65" s="5" t="inlineStr">
         <is>
           <t>&lt; 6 ký tự
 &gt; 30 ký tự
@@ -11387,7 +11707,7 @@
 null</t>
         </is>
       </c>
-      <c r="E53" s="5" t="inlineStr">
+      <c r="E65" s="5" t="inlineStr">
         <is>
           <t>X1
 X2
@@ -11395,644 +11715,281 @@
 X4</t>
         </is>
       </c>
-      <c r="F53" s="5" t="inlineStr">
+      <c r="F65" s="5" t="inlineStr">
         <is>
           <t>6, 7, 18, 29, 30</t>
         </is>
       </c>
-      <c r="G53" s="5" t="inlineStr">
+      <c r="G65" s="5" t="inlineStr">
         <is>
           <t>B1–B5</t>
         </is>
       </c>
-      <c r="H53" s="5" t="inlineStr">
+      <c r="H65" s="5" t="inlineStr">
         <is>
           <t>5 và 31 (B6, B7)</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="62" customHeight="1">
-      <c r="A54" s="5" t="inlineStr">
+    <row r="66" ht="62" customHeight="1">
+      <c r="A66" s="5" t="inlineStr">
         <is>
           <t>fullName</t>
         </is>
       </c>
-      <c r="B54" s="5" t="inlineStr">
+      <c r="B66" s="5" t="inlineStr">
         <is>
           <t>1–100 ký tự,
 có ít nhất 1 ký tự không trắng</t>
         </is>
       </c>
-      <c r="C54" s="5" t="inlineStr">
+      <c r="C66" s="5" t="inlineStr">
         <is>
           <t>V2</t>
         </is>
       </c>
-      <c r="D54" s="5" t="inlineStr">
+      <c r="D66" s="5" t="inlineStr">
         <is>
           <t>&gt; 100 ký tự
 toàn khoảng trắng
 null</t>
         </is>
       </c>
-      <c r="E54" s="5" t="inlineStr">
+      <c r="E66" s="5" t="inlineStr">
         <is>
           <t>X5
 X6
 X7</t>
         </is>
       </c>
-      <c r="F54" s="5" t="inlineStr">
+      <c r="F66" s="5" t="inlineStr">
         <is>
           <t>1, 2, 50, 99, 100</t>
         </is>
       </c>
-      <c r="G54" s="5" t="inlineStr">
+      <c r="G66" s="5" t="inlineStr">
         <is>
           <t>B8–B12</t>
         </is>
       </c>
-      <c r="H54" s="5" t="inlineStr">
+      <c r="H66" s="5" t="inlineStr">
         <is>
           <t>rỗng (= min−1) và 101
 (B13, B14)</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="62" customHeight="1">
-      <c r="A55" s="5" t="inlineStr">
+    <row r="67" ht="62" customHeight="1">
+      <c r="A67" s="5" t="inlineStr">
         <is>
           <t>email — điều kiện ĐỘ DÀI</t>
         </is>
       </c>
-      <c r="B55" s="5" t="inlineStr">
+      <c r="B67" s="5" t="inlineStr">
         <is>
           <t>6–150 ký tự</t>
         </is>
       </c>
-      <c r="C55" s="5" t="inlineStr">
+      <c r="C67" s="5" t="inlineStr">
         <is>
           <t>V3</t>
         </is>
       </c>
-      <c r="D55" s="5" t="inlineStr">
+      <c r="D67" s="5" t="inlineStr">
         <is>
           <t>&lt; 6 ký tự
 &gt; 150 ký tự</t>
         </is>
       </c>
-      <c r="E55" s="5" t="inlineStr">
+      <c r="E67" s="5" t="inlineStr">
         <is>
           <t>X8
 X9</t>
         </is>
       </c>
-      <c r="F55" s="5" t="inlineStr">
+      <c r="F67" s="5" t="inlineStr">
         <is>
           <t>6, 7, 75, 149, 150</t>
         </is>
       </c>
-      <c r="G55" s="5" t="inlineStr">
+      <c r="G67" s="5" t="inlineStr">
         <is>
           <t>B15–B19</t>
         </is>
       </c>
-      <c r="H55" s="5" t="inlineStr">
+      <c r="H67" s="5" t="inlineStr">
         <is>
           <t>5 và 151 (B20, B21)</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="62" customHeight="1">
-      <c r="A56" s="5" t="inlineStr">
+    <row r="68" ht="62" customHeight="1">
+      <c r="A68" s="5" t="inlineStr">
         <is>
           <t>email — điều kiện ĐỊNH DẠNG</t>
         </is>
       </c>
-      <c r="B56" s="5" t="inlineStr">
+      <c r="B68" s="5" t="inlineStr">
         <is>
           <t>đúng định dạng email</t>
         </is>
       </c>
-      <c r="C56" s="5" t="inlineStr">
+      <c r="C68" s="5" t="inlineStr">
         <is>
           <t>V4</t>
         </is>
       </c>
-      <c r="D56" s="5" t="inlineStr">
+      <c r="D68" s="5" t="inlineStr">
         <is>
           <t>sai định dạng
 null / rỗng</t>
         </is>
       </c>
-      <c r="E56" s="5" t="inlineStr">
+      <c r="E68" s="5" t="inlineStr">
         <is>
           <t>X10
 X11</t>
         </is>
       </c>
-      <c r="F56" s="5" t="inlineStr">
+      <c r="F68" s="5" t="inlineStr">
         <is>
           <t>(không áp dụng —
 miền rời rạc)</t>
         </is>
       </c>
-      <c r="G56" s="5" t="inlineStr">
+      <c r="G68" s="5" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="H56" s="5" t="inlineStr">
+      <c r="H68" s="5" t="inlineStr">
         <is>
           <t>(không áp dụng)</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="62" customHeight="1">
-      <c r="A57" s="5" t="inlineStr">
+    <row r="69" ht="62" customHeight="1">
+      <c r="A69" s="5" t="inlineStr">
         <is>
           <t>Tệp bảng điểm — DUNG LƯỢNG</t>
         </is>
       </c>
-      <c r="B57" s="5" t="inlineStr">
+      <c r="B69" s="5" t="inlineStr">
         <is>
           <t>0 đến 10 MB</t>
         </is>
       </c>
-      <c r="C57" s="5" t="inlineStr">
+      <c r="C69" s="5" t="inlineStr">
         <is>
           <t>V5</t>
         </is>
       </c>
-      <c r="D57" s="5" t="inlineStr">
+      <c r="D69" s="5" t="inlineStr">
         <is>
           <t>&gt; 10 MB</t>
         </is>
       </c>
-      <c r="E57" s="5" t="inlineStr">
+      <c r="E69" s="5" t="inlineStr">
         <is>
           <t>X12</t>
         </is>
       </c>
-      <c r="F57" s="5" t="inlineStr">
+      <c r="F69" s="5" t="inlineStr">
         <is>
           <t>0, 1 byte, 5 MB,
 10MB−1, 10 MB</t>
         </is>
       </c>
-      <c r="G57" s="5" t="inlineStr">
+      <c r="G69" s="5" t="inlineStr">
         <is>
           <t>B22–B26</t>
         </is>
       </c>
-      <c r="H57" s="5" t="inlineStr">
+      <c r="H69" s="5" t="inlineStr">
         <is>
           <t>10MB + 1 byte (B27)</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="40" customHeight="1">
-      <c r="A58" s="11" t="inlineStr">
+    <row r="70" ht="40" customHeight="1">
+      <c r="A70" s="11" t="inlineStr">
         <is>
           <t>Slide 32 gộp phân lớp tương đương và giá trị biên vào MỘT bảng. Một trường có thể mang nhiều dòng điều kiện độc lập — trường Customer name ở slide 29 được tách thành độ dài 2-64 và ký tự hợp lệ. Email ở đây cũng vậy: điều kiện ĐỘ DÀI có thứ tự nên áp được giá trị biên, còn điều kiện ĐỊNH DẠNG là miền rời rạc nên chỉ phân lớp được — đó là ý nghĩa của dấu "-" ở cột Tag dòng thứ tư.</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="40" customHeight="1">
-      <c r="A59" s="11" t="inlineStr">
+    <row r="71" ht="40" customHeight="1">
+      <c r="A71" s="11" t="inlineStr">
         <is>
           <t>CODE KIỂM CHỨNG BẢNG NÀY: cột Valid/Invalid Partitions do RegisterEquivalencePartitionTest kiểm; cột Valid Boundaries B1–B21 do RegisterStandardBvaTest kiểm (xem Bảng 2, Bảng 3); B22–B27 của tệp bảng điểm do OnboardingFileSizeBvaTest kiểm.</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="40" customHeight="1">
-      <c r="A60" s="11" t="inlineStr">
+    <row r="72" ht="40" customHeight="1">
+      <c r="A72" s="11" t="inlineStr">
         <is>
           <t>PHÁT HIỆN — lớp X3: mật khẩu 8 dấu cách có độ dài 8, THOẢ MÃN @Size(min=6, max=30) nhưng vẫn bị @NotBlank từ chối. Lớp này không nằm ở ranh giới độ dài nào nên giá trị biên không chạm tới — chỉ phân hoạch lớp tương đương mới phát hiện được. Code: RegisterEquivalencePartitionTest · x3_toanKhoangTrang_biTuChoi.</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="24" customHeight="1">
-      <c r="A62" s="3" t="inlineStr">
+    <row r="73"/>
+    <row r="74" ht="24" customHeight="1">
+      <c r="A74" s="3" t="inlineStr">
         <is>
           <t>BẢNG 5 — THIẾT KẾ TEST CASE, GỘP TAG (mẫu slide 33) · 23 case phủ trọn 44 tag</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="30" customHeight="1">
-      <c r="A63" s="4" t="inlineStr">
+    <row r="75" ht="30" customHeight="1">
+      <c r="A75" s="4" t="inlineStr">
         <is>
           <t>Test Case</t>
         </is>
       </c>
-      <c r="B63" s="4" t="inlineStr">
+      <c r="B75" s="4" t="inlineStr">
         <is>
           <t>Input</t>
         </is>
       </c>
-      <c r="C63" s="4" t="inlineStr">
+      <c r="C75" s="4" t="inlineStr">
         <is>
           <t>Expected Outcome</t>
         </is>
       </c>
-      <c r="D63" s="4" t="inlineStr">
+      <c r="D75" s="4" t="inlineStr">
         <is>
           <t>New Tags Covered</t>
         </is>
       </c>
-      <c r="E63" s="4" t="n"/>
-      <c r="F63" s="4" t="n"/>
-      <c r="G63" s="4" t="n"/>
-      <c r="H63" s="4" t="inlineStr">
+      <c r="E75" s="4" t="n"/>
+      <c r="F75" s="4" t="n"/>
+      <c r="G75" s="4" t="n"/>
+      <c r="H75" s="4" t="inlineStr">
         <is>
           <t>Test đã thi hành</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="46" customHeight="1">
-      <c r="A64" s="18" t="n">
+    <row r="76" ht="46" customHeight="1">
+      <c r="A76" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="B64" s="5" t="inlineStr">
+      <c r="B76" s="5" t="inlineStr">
         <is>
           <t>fullName = 1 ký tự
 email = 6 ký tự
 password = 6 ký tự</t>
         </is>
       </c>
-      <c r="C64" s="5" t="inlineStr">
+      <c r="C76" s="5" t="inlineStr">
         <is>
           <t>Đăng ký thành công</t>
         </is>
       </c>
-      <c r="D64" s="19" t="inlineStr">
+      <c r="D76" s="19" t="inlineStr">
         <is>
           <t>V1, V2, V3, V4,
 B1, B8, B15</t>
-        </is>
-      </c>
-      <c r="E64" s="5" t="n"/>
-      <c r="F64" s="5" t="n"/>
-      <c r="G64" s="5" t="n"/>
-      <c r="H64" s="5" t="inlineStr">
-        <is>
-          <t>RegisterTagCoverageTest ·
-tagCoverage_caseHopLe</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="46" customHeight="1">
-      <c r="A65" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="B65" s="5" t="inlineStr">
-        <is>
-          <t>fullName = 2 ký tự
-email = 7 ký tự
-password = 7 ký tự</t>
-        </is>
-      </c>
-      <c r="C65" s="5" t="inlineStr">
-        <is>
-          <t>Đăng ký thành công</t>
-        </is>
-      </c>
-      <c r="D65" s="19" t="inlineStr">
-        <is>
-          <t>B2, B9, B16</t>
-        </is>
-      </c>
-      <c r="E65" s="5" t="n"/>
-      <c r="F65" s="5" t="n"/>
-      <c r="G65" s="5" t="n"/>
-      <c r="H65" s="5" t="inlineStr">
-        <is>
-          <t>RegisterTagCoverageTest ·
-tagCoverage_caseHopLe</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="46" customHeight="1">
-      <c r="A66" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="B66" s="5" t="inlineStr">
-        <is>
-          <t>fullName = 50 ký tự
-email = 75 ký tự
-password = 18 ký tự</t>
-        </is>
-      </c>
-      <c r="C66" s="5" t="inlineStr">
-        <is>
-          <t>Đăng ký thành công</t>
-        </is>
-      </c>
-      <c r="D66" s="19" t="inlineStr">
-        <is>
-          <t>B3, B10, B17</t>
-        </is>
-      </c>
-      <c r="E66" s="5" t="n"/>
-      <c r="F66" s="5" t="n"/>
-      <c r="G66" s="5" t="n"/>
-      <c r="H66" s="5" t="inlineStr">
-        <is>
-          <t>RegisterTagCoverageTest ·
-tagCoverage_caseHopLe</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="46" customHeight="1">
-      <c r="A67" s="18" t="n">
-        <v>4</v>
-      </c>
-      <c r="B67" s="5" t="inlineStr">
-        <is>
-          <t>fullName = 99 ký tự
-email = 149 ký tự
-password = 29 ký tự</t>
-        </is>
-      </c>
-      <c r="C67" s="5" t="inlineStr">
-        <is>
-          <t>Đăng ký thành công</t>
-        </is>
-      </c>
-      <c r="D67" s="19" t="inlineStr">
-        <is>
-          <t>B4, B11, B18</t>
-        </is>
-      </c>
-      <c r="E67" s="5" t="n"/>
-      <c r="F67" s="5" t="n"/>
-      <c r="G67" s="5" t="n"/>
-      <c r="H67" s="5" t="inlineStr">
-        <is>
-          <t>RegisterTagCoverageTest ·
-tagCoverage_caseHopLe</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="46" customHeight="1">
-      <c r="A68" s="18" t="n">
-        <v>5</v>
-      </c>
-      <c r="B68" s="5" t="inlineStr">
-        <is>
-          <t>fullName = 100 ký tự
-email = 150 ký tự
-password = 30 ký tự</t>
-        </is>
-      </c>
-      <c r="C68" s="5" t="inlineStr">
-        <is>
-          <t>Đăng ký thành công</t>
-        </is>
-      </c>
-      <c r="D68" s="19" t="inlineStr">
-        <is>
-          <t>B5, B12, B19</t>
-        </is>
-      </c>
-      <c r="E68" s="5" t="n"/>
-      <c r="F68" s="5" t="n"/>
-      <c r="G68" s="5" t="n"/>
-      <c r="H68" s="5" t="inlineStr">
-        <is>
-          <t>RegisterTagCoverageTest ·
-tagCoverage_caseHopLe</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="46" customHeight="1">
-      <c r="A69" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="B69" s="5" t="inlineStr">
-        <is>
-          <t>password = 5 ký tự
-(hai trường kia ở nom)</t>
-        </is>
-      </c>
-      <c r="C69" s="5" t="inlineStr">
-        <is>
-          <t>Từ chối — password phải ≥ 6 ký tự</t>
-        </is>
-      </c>
-      <c r="D69" s="21" t="inlineStr">
-        <is>
-          <t>X1, B6</t>
-        </is>
-      </c>
-      <c r="E69" s="5" t="n"/>
-      <c r="F69" s="5" t="n"/>
-      <c r="G69" s="5" t="n"/>
-      <c r="H69" s="5" t="inlineStr">
-        <is>
-          <t>RegisterTagCoverageTest ·
-tagCoverage_caseKhongHopLe</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="46" customHeight="1">
-      <c r="A70" s="20" t="n">
-        <v>7</v>
-      </c>
-      <c r="B70" s="5" t="inlineStr">
-        <is>
-          <t>password = 31 ký tự
-(hai trường kia ở nom)</t>
-        </is>
-      </c>
-      <c r="C70" s="5" t="inlineStr">
-        <is>
-          <t>Từ chối — password phải ≤ 30 ký tự</t>
-        </is>
-      </c>
-      <c r="D70" s="21" t="inlineStr">
-        <is>
-          <t>X2, B7</t>
-        </is>
-      </c>
-      <c r="E70" s="5" t="n"/>
-      <c r="F70" s="5" t="n"/>
-      <c r="G70" s="5" t="n"/>
-      <c r="H70" s="5" t="inlineStr">
-        <is>
-          <t>RegisterTagCoverageTest ·
-tagCoverage_caseKhongHopLe</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="46" customHeight="1">
-      <c r="A71" s="20" t="n">
-        <v>8</v>
-      </c>
-      <c r="B71" s="5" t="inlineStr">
-        <is>
-          <t>password = 8 dấu cách
-(hai trường kia ở nom)</t>
-        </is>
-      </c>
-      <c r="C71" s="5" t="inlineStr">
-        <is>
-          <t>Từ chối — password không được để trống</t>
-        </is>
-      </c>
-      <c r="D71" s="21" t="inlineStr">
-        <is>
-          <t>X3</t>
-        </is>
-      </c>
-      <c r="E71" s="5" t="n"/>
-      <c r="F71" s="5" t="n"/>
-      <c r="G71" s="5" t="n"/>
-      <c r="H71" s="5" t="inlineStr">
-        <is>
-          <t>RegisterTagCoverageTest ·
-tagCoverage_caseKhongHopLe</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="46" customHeight="1">
-      <c r="A72" s="20" t="n">
-        <v>9</v>
-      </c>
-      <c r="B72" s="5" t="inlineStr">
-        <is>
-          <t>password = null
-(hai trường kia ở nom)</t>
-        </is>
-      </c>
-      <c r="C72" s="5" t="inlineStr">
-        <is>
-          <t>Từ chối — password bắt buộc</t>
-        </is>
-      </c>
-      <c r="D72" s="21" t="inlineStr">
-        <is>
-          <t>X4</t>
-        </is>
-      </c>
-      <c r="E72" s="5" t="n"/>
-      <c r="F72" s="5" t="n"/>
-      <c r="G72" s="5" t="n"/>
-      <c r="H72" s="5" t="inlineStr">
-        <is>
-          <t>RegisterTagCoverageTest ·
-tagCoverage_caseKhongHopLe</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="46" customHeight="1">
-      <c r="A73" s="20" t="n">
-        <v>10</v>
-      </c>
-      <c r="B73" s="5" t="inlineStr">
-        <is>
-          <t>fullName = 101 ký tự
-(hai trường kia ở nom)</t>
-        </is>
-      </c>
-      <c r="C73" s="5" t="inlineStr">
-        <is>
-          <t>Từ chối — họ tên phải ≤ 100 ký tự</t>
-        </is>
-      </c>
-      <c r="D73" s="21" t="inlineStr">
-        <is>
-          <t>X5, B14</t>
-        </is>
-      </c>
-      <c r="E73" s="5" t="n"/>
-      <c r="F73" s="5" t="n"/>
-      <c r="G73" s="5" t="n"/>
-      <c r="H73" s="5" t="inlineStr">
-        <is>
-          <t>RegisterTagCoverageTest ·
-tagCoverage_caseKhongHopLe</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="46" customHeight="1">
-      <c r="A74" s="20" t="n">
-        <v>11</v>
-      </c>
-      <c r="B74" s="5" t="inlineStr">
-        <is>
-          <t>fullName = 5 dấu cách
-(hai trường kia ở nom)</t>
-        </is>
-      </c>
-      <c r="C74" s="5" t="inlineStr">
-        <is>
-          <t>Từ chối — họ tên không được để trống</t>
-        </is>
-      </c>
-      <c r="D74" s="21" t="inlineStr">
-        <is>
-          <t>X6</t>
-        </is>
-      </c>
-      <c r="E74" s="5" t="n"/>
-      <c r="F74" s="5" t="n"/>
-      <c r="G74" s="5" t="n"/>
-      <c r="H74" s="5" t="inlineStr">
-        <is>
-          <t>RegisterTagCoverageTest ·
-tagCoverage_caseKhongHopLe</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="46" customHeight="1">
-      <c r="A75" s="20" t="n">
-        <v>12</v>
-      </c>
-      <c r="B75" s="5" t="inlineStr">
-        <is>
-          <t>fullName = null
-(hai trường kia ở nom)</t>
-        </is>
-      </c>
-      <c r="C75" s="5" t="inlineStr">
-        <is>
-          <t>Từ chối — họ tên bắt buộc</t>
-        </is>
-      </c>
-      <c r="D75" s="21" t="inlineStr">
-        <is>
-          <t>X7</t>
-        </is>
-      </c>
-      <c r="E75" s="5" t="n"/>
-      <c r="F75" s="5" t="n"/>
-      <c r="G75" s="5" t="n"/>
-      <c r="H75" s="5" t="inlineStr">
-        <is>
-          <t>RegisterTagCoverageTest ·
-tagCoverage_caseKhongHopLe</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="46" customHeight="1">
-      <c r="A76" s="20" t="n">
-        <v>13</v>
-      </c>
-      <c r="B76" s="5" t="inlineStr">
-        <is>
-          <t>fullName = chuỗi rỗng
-(hai trường kia ở nom)</t>
-        </is>
-      </c>
-      <c r="C76" s="5" t="inlineStr">
-        <is>
-          <t>Từ chối — họ tên không được để trống</t>
-        </is>
-      </c>
-      <c r="D76" s="21" t="inlineStr">
-        <is>
-          <t>B13</t>
         </is>
       </c>
       <c r="E76" s="5" t="n"/>
@@ -12041,28 +11998,29 @@
       <c r="H76" s="5" t="inlineStr">
         <is>
           <t>RegisterTagCoverageTest ·
-tagCoverage_caseKhongHopLe</t>
+tagCoverage_caseHopLe</t>
         </is>
       </c>
     </row>
     <row r="77" ht="46" customHeight="1">
-      <c r="A77" s="20" t="n">
-        <v>14</v>
+      <c r="A77" s="18" t="n">
+        <v>2</v>
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>email = 5 ký tự (a@b.c)
-(hai trường kia ở nom)</t>
+          <t>fullName = 2 ký tự
+email = 7 ký tự
+password = 7 ký tự</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>Từ chối — email phải ≥ 6 ký tự</t>
-        </is>
-      </c>
-      <c r="D77" s="21" t="inlineStr">
-        <is>
-          <t>X8, B20</t>
+          <t>Đăng ký thành công</t>
+        </is>
+      </c>
+      <c r="D77" s="19" t="inlineStr">
+        <is>
+          <t>B2, B9, B16</t>
         </is>
       </c>
       <c r="E77" s="5" t="n"/>
@@ -12071,28 +12029,29 @@
       <c r="H77" s="5" t="inlineStr">
         <is>
           <t>RegisterTagCoverageTest ·
-tagCoverage_caseKhongHopLe</t>
+tagCoverage_caseHopLe</t>
         </is>
       </c>
     </row>
     <row r="78" ht="46" customHeight="1">
-      <c r="A78" s="20" t="n">
-        <v>15</v>
+      <c r="A78" s="18" t="n">
+        <v>3</v>
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>email = 151 ký tự
-(hai trường kia ở nom)</t>
+          <t>fullName = 50 ký tự
+email = 75 ký tự
+password = 18 ký tự</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>Từ chối — email phải ≤ 150 ký tự</t>
-        </is>
-      </c>
-      <c r="D78" s="21" t="inlineStr">
-        <is>
-          <t>X9, B21</t>
+          <t>Đăng ký thành công</t>
+        </is>
+      </c>
+      <c r="D78" s="19" t="inlineStr">
+        <is>
+          <t>B3, B10, B17</t>
         </is>
       </c>
       <c r="E78" s="5" t="n"/>
@@ -12101,28 +12060,29 @@
       <c r="H78" s="5" t="inlineStr">
         <is>
           <t>RegisterTagCoverageTest ·
-tagCoverage_caseKhongHopLe</t>
+tagCoverage_caseHopLe</t>
         </is>
       </c>
     </row>
     <row r="79" ht="46" customHeight="1">
-      <c r="A79" s="20" t="n">
-        <v>16</v>
+      <c r="A79" s="18" t="n">
+        <v>4</v>
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>email = khong-phai-email
-(hai trường kia ở nom)</t>
+          <t>fullName = 99 ký tự
+email = 149 ký tự
+password = 29 ký tự</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>Từ chối — email sai định dạng</t>
-        </is>
-      </c>
-      <c r="D79" s="21" t="inlineStr">
-        <is>
-          <t>X10</t>
+          <t>Đăng ký thành công</t>
+        </is>
+      </c>
+      <c r="D79" s="19" t="inlineStr">
+        <is>
+          <t>B4, B11, B18</t>
         </is>
       </c>
       <c r="E79" s="5" t="n"/>
@@ -12131,28 +12091,29 @@
       <c r="H79" s="5" t="inlineStr">
         <is>
           <t>RegisterTagCoverageTest ·
-tagCoverage_caseKhongHopLe</t>
+tagCoverage_caseHopLe</t>
         </is>
       </c>
     </row>
     <row r="80" ht="46" customHeight="1">
-      <c r="A80" s="20" t="n">
-        <v>17</v>
+      <c r="A80" s="18" t="n">
+        <v>5</v>
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>email = null
-(hai trường kia ở nom)</t>
+          <t>fullName = 100 ký tự
+email = 150 ký tự
+password = 30 ký tự</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>Từ chối — email bắt buộc</t>
-        </is>
-      </c>
-      <c r="D80" s="21" t="inlineStr">
-        <is>
-          <t>X11</t>
+          <t>Đăng ký thành công</t>
+        </is>
+      </c>
+      <c r="D80" s="19" t="inlineStr">
+        <is>
+          <t>B5, B12, B19</t>
         </is>
       </c>
       <c r="E80" s="5" t="n"/>
@@ -12161,27 +12122,28 @@
       <c r="H80" s="5" t="inlineStr">
         <is>
           <t>RegisterTagCoverageTest ·
-tagCoverage_caseKhongHopLe</t>
+tagCoverage_caseHopLe</t>
         </is>
       </c>
     </row>
     <row r="81" ht="46" customHeight="1">
-      <c r="A81" s="18" t="n">
-        <v>18</v>
+      <c r="A81" s="20" t="n">
+        <v>6</v>
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>Tệp bảng điểm = 0 byte</t>
+          <t>password = 5 ký tự
+(hai trường kia ở nom)</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>Tải lên thành công</t>
-        </is>
-      </c>
-      <c r="D81" s="19" t="inlineStr">
-        <is>
-          <t>V5, B22</t>
+          <t>Từ chối — password phải ≥ 6 ký tự</t>
+        </is>
+      </c>
+      <c r="D81" s="21" t="inlineStr">
+        <is>
+          <t>X1, B6</t>
         </is>
       </c>
       <c r="E81" s="5" t="n"/>
@@ -12189,28 +12151,29 @@
       <c r="G81" s="5" t="n"/>
       <c r="H81" s="5" t="inlineStr">
         <is>
-          <t>OnboardingFileSizeBvaTest ·
-fileSize_normalBva</t>
+          <t>RegisterTagCoverageTest ·
+tagCoverage_caseKhongHopLe</t>
         </is>
       </c>
     </row>
     <row r="82" ht="46" customHeight="1">
-      <c r="A82" s="18" t="n">
-        <v>19</v>
+      <c r="A82" s="20" t="n">
+        <v>7</v>
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>Tệp bảng điểm = 1 byte</t>
+          <t>password = 31 ký tự
+(hai trường kia ở nom)</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>Tải lên thành công</t>
-        </is>
-      </c>
-      <c r="D82" s="19" t="inlineStr">
-        <is>
-          <t>B23</t>
+          <t>Từ chối — password phải ≤ 30 ký tự</t>
+        </is>
+      </c>
+      <c r="D82" s="21" t="inlineStr">
+        <is>
+          <t>X2, B7</t>
         </is>
       </c>
       <c r="E82" s="5" t="n"/>
@@ -12218,28 +12181,29 @@
       <c r="G82" s="5" t="n"/>
       <c r="H82" s="5" t="inlineStr">
         <is>
-          <t>OnboardingFileSizeBvaTest ·
-fileSize_normalBva</t>
+          <t>RegisterTagCoverageTest ·
+tagCoverage_caseKhongHopLe</t>
         </is>
       </c>
     </row>
     <row r="83" ht="46" customHeight="1">
-      <c r="A83" s="18" t="n">
-        <v>20</v>
+      <c r="A83" s="20" t="n">
+        <v>8</v>
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>Tệp bảng điểm = 5 MB</t>
+          <t>password = 8 dấu cách
+(hai trường kia ở nom)</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>Tải lên thành công</t>
-        </is>
-      </c>
-      <c r="D83" s="19" t="inlineStr">
-        <is>
-          <t>B24</t>
+          <t>Từ chối — password không được để trống</t>
+        </is>
+      </c>
+      <c r="D83" s="21" t="inlineStr">
+        <is>
+          <t>X3</t>
         </is>
       </c>
       <c r="E83" s="5" t="n"/>
@@ -12247,28 +12211,29 @@
       <c r="G83" s="5" t="n"/>
       <c r="H83" s="5" t="inlineStr">
         <is>
-          <t>OnboardingFileSizeBvaTest ·
-fileSize_normalBva</t>
+          <t>RegisterTagCoverageTest ·
+tagCoverage_caseKhongHopLe</t>
         </is>
       </c>
     </row>
     <row r="84" ht="46" customHeight="1">
-      <c r="A84" s="18" t="n">
-        <v>21</v>
+      <c r="A84" s="20" t="n">
+        <v>9</v>
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>Tệp bảng điểm = 10 MB − 1 byte</t>
+          <t>password = null
+(hai trường kia ở nom)</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>Tải lên thành công</t>
-        </is>
-      </c>
-      <c r="D84" s="19" t="inlineStr">
-        <is>
-          <t>B25</t>
+          <t>Từ chối — password bắt buộc</t>
+        </is>
+      </c>
+      <c r="D84" s="21" t="inlineStr">
+        <is>
+          <t>X4</t>
         </is>
       </c>
       <c r="E84" s="5" t="n"/>
@@ -12276,28 +12241,29 @@
       <c r="G84" s="5" t="n"/>
       <c r="H84" s="5" t="inlineStr">
         <is>
-          <t>OnboardingFileSizeBvaTest ·
-fileSize_normalBva</t>
+          <t>RegisterTagCoverageTest ·
+tagCoverage_caseKhongHopLe</t>
         </is>
       </c>
     </row>
     <row r="85" ht="46" customHeight="1">
-      <c r="A85" s="18" t="n">
-        <v>22</v>
+      <c r="A85" s="20" t="n">
+        <v>10</v>
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>Tệp bảng điểm = 10 MB</t>
+          <t>fullName = 101 ký tự
+(hai trường kia ở nom)</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>Tải lên thành công</t>
-        </is>
-      </c>
-      <c r="D85" s="19" t="inlineStr">
-        <is>
-          <t>B26</t>
+          <t>Từ chối — họ tên phải ≤ 100 ký tự</t>
+        </is>
+      </c>
+      <c r="D85" s="21" t="inlineStr">
+        <is>
+          <t>X5, B14</t>
         </is>
       </c>
       <c r="E85" s="5" t="n"/>
@@ -12305,28 +12271,29 @@
       <c r="G85" s="5" t="n"/>
       <c r="H85" s="5" t="inlineStr">
         <is>
-          <t>OnboardingFileSizeBvaTest ·
-fileSize_normalBva</t>
+          <t>RegisterTagCoverageTest ·
+tagCoverage_caseKhongHopLe</t>
         </is>
       </c>
     </row>
     <row r="86" ht="46" customHeight="1">
       <c r="A86" s="20" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>Tệp bảng điểm = 10 MB + 1 byte</t>
+          <t>fullName = 5 dấu cách
+(hai trường kia ở nom)</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>Từ chối — tệp vượt quá 10 MB</t>
+          <t>Từ chối — họ tên không được để trống</t>
         </is>
       </c>
       <c r="D86" s="21" t="inlineStr">
         <is>
-          <t>X12, B27</t>
+          <t>X6</t>
         </is>
       </c>
       <c r="E86" s="5" t="n"/>
@@ -12334,67 +12301,425 @@
       <c r="G86" s="5" t="n"/>
       <c r="H86" s="5" t="inlineStr">
         <is>
+          <t>RegisterTagCoverageTest ·
+tagCoverage_caseKhongHopLe</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="46" customHeight="1">
+      <c r="A87" s="20" t="n">
+        <v>12</v>
+      </c>
+      <c r="B87" s="5" t="inlineStr">
+        <is>
+          <t>fullName = null
+(hai trường kia ở nom)</t>
+        </is>
+      </c>
+      <c r="C87" s="5" t="inlineStr">
+        <is>
+          <t>Từ chối — họ tên bắt buộc</t>
+        </is>
+      </c>
+      <c r="D87" s="21" t="inlineStr">
+        <is>
+          <t>X7</t>
+        </is>
+      </c>
+      <c r="E87" s="5" t="n"/>
+      <c r="F87" s="5" t="n"/>
+      <c r="G87" s="5" t="n"/>
+      <c r="H87" s="5" t="inlineStr">
+        <is>
+          <t>RegisterTagCoverageTest ·
+tagCoverage_caseKhongHopLe</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="46" customHeight="1">
+      <c r="A88" s="20" t="n">
+        <v>13</v>
+      </c>
+      <c r="B88" s="5" t="inlineStr">
+        <is>
+          <t>fullName = chuỗi rỗng
+(hai trường kia ở nom)</t>
+        </is>
+      </c>
+      <c r="C88" s="5" t="inlineStr">
+        <is>
+          <t>Từ chối — họ tên không được để trống</t>
+        </is>
+      </c>
+      <c r="D88" s="21" t="inlineStr">
+        <is>
+          <t>B13</t>
+        </is>
+      </c>
+      <c r="E88" s="5" t="n"/>
+      <c r="F88" s="5" t="n"/>
+      <c r="G88" s="5" t="n"/>
+      <c r="H88" s="5" t="inlineStr">
+        <is>
+          <t>RegisterTagCoverageTest ·
+tagCoverage_caseKhongHopLe</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="46" customHeight="1">
+      <c r="A89" s="20" t="n">
+        <v>14</v>
+      </c>
+      <c r="B89" s="5" t="inlineStr">
+        <is>
+          <t>email = 5 ký tự (a@b.c)
+(hai trường kia ở nom)</t>
+        </is>
+      </c>
+      <c r="C89" s="5" t="inlineStr">
+        <is>
+          <t>Từ chối — email phải ≥ 6 ký tự</t>
+        </is>
+      </c>
+      <c r="D89" s="21" t="inlineStr">
+        <is>
+          <t>X8, B20</t>
+        </is>
+      </c>
+      <c r="E89" s="5" t="n"/>
+      <c r="F89" s="5" t="n"/>
+      <c r="G89" s="5" t="n"/>
+      <c r="H89" s="5" t="inlineStr">
+        <is>
+          <t>RegisterTagCoverageTest ·
+tagCoverage_caseKhongHopLe</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="46" customHeight="1">
+      <c r="A90" s="20" t="n">
+        <v>15</v>
+      </c>
+      <c r="B90" s="5" t="inlineStr">
+        <is>
+          <t>email = 151 ký tự
+(hai trường kia ở nom)</t>
+        </is>
+      </c>
+      <c r="C90" s="5" t="inlineStr">
+        <is>
+          <t>Từ chối — email phải ≤ 150 ký tự</t>
+        </is>
+      </c>
+      <c r="D90" s="21" t="inlineStr">
+        <is>
+          <t>X9, B21</t>
+        </is>
+      </c>
+      <c r="E90" s="5" t="n"/>
+      <c r="F90" s="5" t="n"/>
+      <c r="G90" s="5" t="n"/>
+      <c r="H90" s="5" t="inlineStr">
+        <is>
+          <t>RegisterTagCoverageTest ·
+tagCoverage_caseKhongHopLe</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="46" customHeight="1">
+      <c r="A91" s="20" t="n">
+        <v>16</v>
+      </c>
+      <c r="B91" s="5" t="inlineStr">
+        <is>
+          <t>email = khong-phai-email
+(hai trường kia ở nom)</t>
+        </is>
+      </c>
+      <c r="C91" s="5" t="inlineStr">
+        <is>
+          <t>Từ chối — email sai định dạng</t>
+        </is>
+      </c>
+      <c r="D91" s="21" t="inlineStr">
+        <is>
+          <t>X10</t>
+        </is>
+      </c>
+      <c r="E91" s="5" t="n"/>
+      <c r="F91" s="5" t="n"/>
+      <c r="G91" s="5" t="n"/>
+      <c r="H91" s="5" t="inlineStr">
+        <is>
+          <t>RegisterTagCoverageTest ·
+tagCoverage_caseKhongHopLe</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="46" customHeight="1">
+      <c r="A92" s="20" t="n">
+        <v>17</v>
+      </c>
+      <c r="B92" s="5" t="inlineStr">
+        <is>
+          <t>email = null
+(hai trường kia ở nom)</t>
+        </is>
+      </c>
+      <c r="C92" s="5" t="inlineStr">
+        <is>
+          <t>Từ chối — email bắt buộc</t>
+        </is>
+      </c>
+      <c r="D92" s="21" t="inlineStr">
+        <is>
+          <t>X11</t>
+        </is>
+      </c>
+      <c r="E92" s="5" t="n"/>
+      <c r="F92" s="5" t="n"/>
+      <c r="G92" s="5" t="n"/>
+      <c r="H92" s="5" t="inlineStr">
+        <is>
+          <t>RegisterTagCoverageTest ·
+tagCoverage_caseKhongHopLe</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="46" customHeight="1">
+      <c r="A93" s="18" t="n">
+        <v>18</v>
+      </c>
+      <c r="B93" s="5" t="inlineStr">
+        <is>
+          <t>Tệp bảng điểm = 0 byte</t>
+        </is>
+      </c>
+      <c r="C93" s="5" t="inlineStr">
+        <is>
+          <t>Tải lên thành công</t>
+        </is>
+      </c>
+      <c r="D93" s="19" t="inlineStr">
+        <is>
+          <t>V5, B22</t>
+        </is>
+      </c>
+      <c r="E93" s="5" t="n"/>
+      <c r="F93" s="5" t="n"/>
+      <c r="G93" s="5" t="n"/>
+      <c r="H93" s="5" t="inlineStr">
+        <is>
+          <t>OnboardingFileSizeBvaTest ·
+fileSize_normalBva</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="46" customHeight="1">
+      <c r="A94" s="18" t="n">
+        <v>19</v>
+      </c>
+      <c r="B94" s="5" t="inlineStr">
+        <is>
+          <t>Tệp bảng điểm = 1 byte</t>
+        </is>
+      </c>
+      <c r="C94" s="5" t="inlineStr">
+        <is>
+          <t>Tải lên thành công</t>
+        </is>
+      </c>
+      <c r="D94" s="19" t="inlineStr">
+        <is>
+          <t>B23</t>
+        </is>
+      </c>
+      <c r="E94" s="5" t="n"/>
+      <c r="F94" s="5" t="n"/>
+      <c r="G94" s="5" t="n"/>
+      <c r="H94" s="5" t="inlineStr">
+        <is>
+          <t>OnboardingFileSizeBvaTest ·
+fileSize_normalBva</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="46" customHeight="1">
+      <c r="A95" s="18" t="n">
+        <v>20</v>
+      </c>
+      <c r="B95" s="5" t="inlineStr">
+        <is>
+          <t>Tệp bảng điểm = 5 MB</t>
+        </is>
+      </c>
+      <c r="C95" s="5" t="inlineStr">
+        <is>
+          <t>Tải lên thành công</t>
+        </is>
+      </c>
+      <c r="D95" s="19" t="inlineStr">
+        <is>
+          <t>B24</t>
+        </is>
+      </c>
+      <c r="E95" s="5" t="n"/>
+      <c r="F95" s="5" t="n"/>
+      <c r="G95" s="5" t="n"/>
+      <c r="H95" s="5" t="inlineStr">
+        <is>
+          <t>OnboardingFileSizeBvaTest ·
+fileSize_normalBva</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="46" customHeight="1">
+      <c r="A96" s="18" t="n">
+        <v>21</v>
+      </c>
+      <c r="B96" s="5" t="inlineStr">
+        <is>
+          <t>Tệp bảng điểm = 10 MB − 1 byte</t>
+        </is>
+      </c>
+      <c r="C96" s="5" t="inlineStr">
+        <is>
+          <t>Tải lên thành công</t>
+        </is>
+      </c>
+      <c r="D96" s="19" t="inlineStr">
+        <is>
+          <t>B25</t>
+        </is>
+      </c>
+      <c r="E96" s="5" t="n"/>
+      <c r="F96" s="5" t="n"/>
+      <c r="G96" s="5" t="n"/>
+      <c r="H96" s="5" t="inlineStr">
+        <is>
+          <t>OnboardingFileSizeBvaTest ·
+fileSize_normalBva</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="46" customHeight="1">
+      <c r="A97" s="18" t="n">
+        <v>22</v>
+      </c>
+      <c r="B97" s="5" t="inlineStr">
+        <is>
+          <t>Tệp bảng điểm = 10 MB</t>
+        </is>
+      </c>
+      <c r="C97" s="5" t="inlineStr">
+        <is>
+          <t>Tải lên thành công</t>
+        </is>
+      </c>
+      <c r="D97" s="19" t="inlineStr">
+        <is>
+          <t>B26</t>
+        </is>
+      </c>
+      <c r="E97" s="5" t="n"/>
+      <c r="F97" s="5" t="n"/>
+      <c r="G97" s="5" t="n"/>
+      <c r="H97" s="5" t="inlineStr">
+        <is>
+          <t>OnboardingFileSizeBvaTest ·
+fileSize_normalBva</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="46" customHeight="1">
+      <c r="A98" s="20" t="n">
+        <v>23</v>
+      </c>
+      <c r="B98" s="5" t="inlineStr">
+        <is>
+          <t>Tệp bảng điểm = 10 MB + 1 byte</t>
+        </is>
+      </c>
+      <c r="C98" s="5" t="inlineStr">
+        <is>
+          <t>Từ chối — tệp vượt quá 10 MB</t>
+        </is>
+      </c>
+      <c r="D98" s="21" t="inlineStr">
+        <is>
+          <t>X12, B27</t>
+        </is>
+      </c>
+      <c r="E98" s="5" t="n"/>
+      <c r="F98" s="5" t="n"/>
+      <c r="G98" s="5" t="n"/>
+      <c r="H98" s="5" t="inlineStr">
+        <is>
           <t>OnboardingFileSizeBvaTest ·
 fileSize_maxPlusOne</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="40" customHeight="1">
-      <c r="A87" s="11" t="inlineStr">
+    <row r="99" ht="40" customHeight="1">
+      <c r="A99" s="11" t="inlineStr">
         <is>
           <t>CÁCH ĐỌC: mỗi hàng là MỘT lần điền form đầy đủ rồi bấm gửi, giống bảng Thiết kế test cases ở slide 33. Cột New Tags Covered ghi những tag mà case đó phủ LẦN ĐẦU — tag đã phủ ở case trước thì không ghi lại. Nền xanh = case hợp lệ, nền hồng = case bị từ chối.</t>
         </is>
       </c>
     </row>
-    <row r="88" ht="54" customHeight="1">
-      <c r="A88" s="11" t="inlineStr">
+    <row r="100" ht="54" customHeight="1">
+      <c r="A100" s="11" t="inlineStr">
         <is>
           <t>VÌ SAO CHỈ CẦN 23 CASE CHO 44 TAG: case HỢP LỆ được phép gộp nhiều tag cùng lúc — TC1 vừa phủ V1 V2 V3 V4 vừa phủ ba giá trị biên B1 B8 B15, vì cả ba trường đều hợp lệ nên không trường nào che kết quả của trường nào. Ngược lại case KHÔNG hợp lệ chỉ được đặt MỘT vi phạm mỗi lần: nếu vừa để password quá ngắn vừa để email sai định dạng thì form vẫn báo lỗi, nhưng không biết nó bắt được vi phạm nào — hiện tượng che lỗi (masking). Vì vậy 12 tag X phải trải ra 12 case riêng.</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="40" customHeight="1">
-      <c r="A89" s="11" t="inlineStr">
+    <row r="101" ht="40" customHeight="1">
+      <c r="A101" s="11" t="inlineStr">
         <is>
           <t>GỘP THÊM ĐỂ TỐI THIỂU HOÁ: vài case không hợp lệ phủ được hai tag cùng lúc vì giá trị biên nằm ngay trong lớp không hợp lệ. TC6 đặt password = 5 ký tự nên vừa phủ lớp X1 (&lt; 6 ký tự) vừa phủ giá trị biên B6 (min-1). TC7, TC10, TC14, TC15, TC23 cũng theo cách này.</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="40" customHeight="1">
-      <c r="A90" s="11" t="inlineStr">
+    <row r="102" ht="40" customHeight="1">
+      <c r="A102" s="11" t="inlineStr">
         <is>
           <t>KIỂM CHỨNG KHÔNG CHE LỖI: mỗi case TC6-TC17 trong code khẳng định form sinh ra ĐÚNG MỘT vi phạm, và vi phạm đó nằm trên ĐÚNG trường đang bị làm sai. Nếu hai trường cùng sai thì assertion hasSize(1) sẽ đỏ — đó là cách chứng minh bằng code rằng thiết kế không bị che lỗi.</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="40" customHeight="1">
-      <c r="A91" s="11" t="inlineStr">
+    <row r="103" ht="40" customHeight="1">
+      <c r="A103" s="11" t="inlineStr">
         <is>
           <t>TC18-TC23 tách riêng vì tệp bảng điểm KHÔNG thuộc form đăng ký — nó là chức năng tải bảng điểm ở bước onboarding. Slide 33 gộp tag trong phạm vi MỘT màn hình nhập liệu, hai chức năng khác nhau thì không gộp chung một lần submit được.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="24">
     <mergeCell ref="A48:H48"/>
-    <mergeCell ref="A59:H59"/>
     <mergeCell ref="A51:H51"/>
     <mergeCell ref="A60:H60"/>
     <mergeCell ref="A11:H11"/>
     <mergeCell ref="A49:H49"/>
-    <mergeCell ref="A88:H88"/>
-    <mergeCell ref="A87:H87"/>
-    <mergeCell ref="A90:H90"/>
-    <mergeCell ref="A89:H89"/>
+    <mergeCell ref="A103:H103"/>
+    <mergeCell ref="A61:H61"/>
+    <mergeCell ref="A70:H70"/>
+    <mergeCell ref="A99:H99"/>
+    <mergeCell ref="A74:H74"/>
     <mergeCell ref="A12:H12"/>
+    <mergeCell ref="A101:H101"/>
     <mergeCell ref="A21:H21"/>
+    <mergeCell ref="A71:H71"/>
     <mergeCell ref="A14:H14"/>
     <mergeCell ref="A23:H23"/>
     <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A62:H62"/>
-    <mergeCell ref="A91:H91"/>
+    <mergeCell ref="A100:H100"/>
     <mergeCell ref="A38:H38"/>
-    <mergeCell ref="A58:H58"/>
+    <mergeCell ref="A72:H72"/>
+    <mergeCell ref="A63:H63"/>
+    <mergeCell ref="A52:H52"/>
+    <mergeCell ref="A102:H102"/>
     <mergeCell ref="A40:H40"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/BaoCao-KiemThu-CareerCompass.xlsx
+++ b/BaoCao-KiemThu-CareerCompass.xlsx
@@ -1723,8 +1723,8 @@
     <mergeCell ref="F8:H8"/>
     <mergeCell ref="F17:H17"/>
     <mergeCell ref="F23:H23"/>
+    <mergeCell ref="F28:H28"/>
     <mergeCell ref="F22:H22"/>
-    <mergeCell ref="F28:H28"/>
     <mergeCell ref="F13:H13"/>
     <mergeCell ref="F30:H30"/>
     <mergeCell ref="F9:H9"/>
@@ -10327,7 +10327,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="32" customHeight="1">
+    <row r="9" ht="44" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
           <t>OnboardingFileSizeBvaTest</t>
@@ -10343,7 +10343,8 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Bảng 4 · V5, X12, B22–B27
+          <t>Bảng 3b · case 20–25
+Bảng 4 · V5, X12, B22–B27
 Bảng 5 · TC18–TC23</t>
         </is>
       </c>

--- a/BaoCao-KiemThu-CareerCompass.xlsx
+++ b/BaoCao-KiemThu-CareerCompass.xlsx
@@ -1723,8 +1723,8 @@
     <mergeCell ref="F8:H8"/>
     <mergeCell ref="F17:H17"/>
     <mergeCell ref="F23:H23"/>
+    <mergeCell ref="F22:H22"/>
     <mergeCell ref="F28:H28"/>
-    <mergeCell ref="F22:H22"/>
     <mergeCell ref="F13:H13"/>
     <mergeCell ref="F30:H30"/>
     <mergeCell ref="F9:H9"/>
@@ -11634,6 +11634,7 @@
         </is>
       </c>
     </row>
+    <row r="62"/>
     <row r="63" ht="24" customHeight="1">
       <c r="A63" s="3" t="inlineStr">
         <is>
@@ -11919,10 +11920,10 @@
         </is>
       </c>
     </row>
-    <row r="71" ht="40" customHeight="1">
+    <row r="71" ht="58" customHeight="1">
       <c r="A71" s="11" t="inlineStr">
         <is>
-          <t>CODE KIỂM CHỨNG BẢNG NÀY: cột Valid/Invalid Partitions do RegisterEquivalencePartitionTest kiểm; cột Valid Boundaries B1–B21 do RegisterStandardBvaTest kiểm (xem Bảng 2, Bảng 3); B22–B27 của tệp bảng điểm do OnboardingFileSizeBvaTest kiểm.</t>
+          <t>CODE KIỂM CHỨNG BẢNG NÀY: cột Valid/Invalid Partitions do RegisterEquivalencePartitionTest kiểm; cột Valid Boundaries B1–B21 do RegisterStandardBvaTest kiểm (xem Bảng 2, Bảng 3); B22–B27 của tệp bảng điểm do OnboardingFileSizeBvaTest kiểm.  ·  VÌ SAO 15 NHÃN MÀ CHỈ 14 TEST: bảng tổng kết ghi lớp này phủ V1–V4 và X1–X11, cộng lại là 15 nhãn, nhưng lớp chỉ có 14 test. Không thiếu test nào — test của V3 dùng email "sinhvien@uth.edu.vn", vừa đúng ĐỊNH DẠNG (V4) vừa đúng ĐỘ DÀI (V3). validateProperty kiểm mọi ràng buộc trên trường email cùng lúc nên một test thoả cả hai lớp hợp lệ. Bốn lớp không hợp lệ của email (X8, X9, X10, X11) thì phải tách riêng vì mỗi lớp vi phạm một ràng buộc khác nhau.</t>
         </is>
       </c>
     </row>
@@ -11933,7 +11934,6 @@
         </is>
       </c>
     </row>
-    <row r="73"/>
     <row r="74" ht="24" customHeight="1">
       <c r="A74" s="3" t="inlineStr">
         <is>

--- a/BaoCao-KiemThu-CareerCompass.xlsx
+++ b/BaoCao-KiemThu-CareerCompass.xlsx
@@ -10204,7 +10204,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -10391,7 +10390,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14" ht="24" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
@@ -10556,7 +10554,6 @@
         </is>
       </c>
     </row>
-    <row r="22"/>
     <row r="23" ht="24" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
@@ -11055,7 +11052,6 @@
         </is>
       </c>
     </row>
-    <row r="39"/>
     <row r="40" ht="24" customHeight="1">
       <c r="A40" s="3" t="inlineStr">
         <is>
@@ -11323,7 +11319,6 @@
         </is>
       </c>
     </row>
-    <row r="50"/>
     <row r="51" ht="24" customHeight="1">
       <c r="A51" s="3" t="inlineStr">
         <is>
@@ -11634,7 +11629,6 @@
         </is>
       </c>
     </row>
-    <row r="62"/>
     <row r="63" ht="24" customHeight="1">
       <c r="A63" s="3" t="inlineStr">
         <is>
@@ -13867,10 +13861,10 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="22" customHeight="1">
+    <row r="4" ht="30" customHeight="1">
       <c r="A4" s="54" t="inlineStr">
         <is>
-          <t>TỔNG KẾT THI HÀNH — 9 test đã chạy, 9 PASS, 0 fail.</t>
+          <t>TỔNG KẾT THI HÀNH — 9 test đã chạy, 9 PASS, 0 fail.  Gồm 8 test ứng với 8 rule của bảng đầy đủ (rule1…rule8), cộng 1 test kiểm tra bổ sung NGOÀI bảng (đuôi viết hoa .PDF) — xem ghi chú cuối sheet.</t>
         </is>
       </c>
     </row>
@@ -14407,10 +14401,6 @@
           <t>2 giá trị</t>
         </is>
       </c>
-      <c r="K22" s="8" t="n"/>
-      <c r="L22" s="8" t="n"/>
-      <c r="M22" s="8" t="n"/>
-      <c r="N22" s="9" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="66" t="inlineStr">
@@ -14443,10 +14433,6 @@
           <t>2 giá trị — đặc tả không phân biệt bốn đuôi với nhau</t>
         </is>
       </c>
-      <c r="K23" s="8" t="n"/>
-      <c r="L23" s="8" t="n"/>
-      <c r="M23" s="8" t="n"/>
-      <c r="N23" s="9" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="66" t="inlineStr">
@@ -14479,10 +14465,6 @@
           <t>2 giá trị</t>
         </is>
       </c>
-      <c r="K24" s="8" t="n"/>
-      <c r="L24" s="8" t="n"/>
-      <c r="M24" s="8" t="n"/>
-      <c r="N24" s="9" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="70" t="inlineStr">
@@ -14596,10 +14578,6 @@
           <t>R4' gộp cả ô đã phát hiện DEF-011 — xem ghi chú bên dưới</t>
         </is>
       </c>
-      <c r="K28" s="8" t="n"/>
-      <c r="L28" s="8" t="n"/>
-      <c r="M28" s="8" t="n"/>
-      <c r="N28" s="9" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="70" t="inlineStr">
@@ -14745,7 +14723,6 @@
           <t>.pdf · .png · .jpg · .jpeg</t>
         </is>
       </c>
-      <c r="D35" s="9" t="n"/>
       <c r="E35" s="79" t="n">
         <v>4</v>
       </c>
@@ -14754,14 +14731,6 @@
           <t>Mã nguồn so sánh từng đuôi bằng một chuỗi &amp;&amp; — bốn nhánh riêng. Báo cáo bao phủ chỉ đích danh ba nhánh chưa ai chạm tới, nên phải kiểm đủ bốn.</t>
         </is>
       </c>
-      <c r="G35" s="8" t="n"/>
-      <c r="H35" s="8" t="n"/>
-      <c r="I35" s="8" t="n"/>
-      <c r="J35" s="8" t="n"/>
-      <c r="K35" s="8" t="n"/>
-      <c r="L35" s="8" t="n"/>
-      <c r="M35" s="8" t="n"/>
-      <c r="N35" s="9" t="n"/>
     </row>
     <row r="36" ht="34" customHeight="1">
       <c r="A36" s="66" t="inlineStr">
@@ -14779,7 +14748,6 @@
           <t>.exe · tên không có dấu chấm</t>
         </is>
       </c>
-      <c r="D36" s="9" t="n"/>
       <c r="E36" s="79" t="n">
         <v>2</v>
       </c>
@@ -14788,14 +14756,6 @@
           <t>Hai giá trị này TRƯỚC KHI SỬA cho hai kết quả khác nhau: .exe trả lỗi 400 đúng như đặc tả, còn tên không có dấu chấm ném StringIndexOutOfBoundsException thành lỗi 500 — chính là DEF-011. Sau khi sửa mới thật sự cùng một lớp.</t>
         </is>
       </c>
-      <c r="G36" s="8" t="n"/>
-      <c r="H36" s="8" t="n"/>
-      <c r="I36" s="8" t="n"/>
-      <c r="J36" s="8" t="n"/>
-      <c r="K36" s="8" t="n"/>
-      <c r="L36" s="8" t="n"/>
-      <c r="M36" s="8" t="n"/>
-      <c r="N36" s="9" t="n"/>
     </row>
     <row r="37" ht="34" customHeight="1">
       <c r="A37" s="66" t="inlineStr">
@@ -14813,7 +14773,6 @@
           <t>null</t>
         </is>
       </c>
-      <c r="D37" s="9" t="n"/>
       <c r="E37" s="79" t="n">
         <v>1</v>
       </c>
@@ -14822,14 +14781,6 @@
           <t>Một giá trị duy nhất, không có gì để tách.</t>
         </is>
       </c>
-      <c r="G37" s="8" t="n"/>
-      <c r="H37" s="8" t="n"/>
-      <c r="I37" s="8" t="n"/>
-      <c r="J37" s="8" t="n"/>
-      <c r="K37" s="8" t="n"/>
-      <c r="L37" s="8" t="n"/>
-      <c r="M37" s="8" t="n"/>
-      <c r="N37" s="9" t="n"/>
     </row>
     <row r="38" ht="34" customHeight="1">
       <c r="A38" s="66" t="inlineStr">
@@ -14847,7 +14798,6 @@
           <t>1 byte · 11 MB</t>
         </is>
       </c>
-      <c r="D38" s="9" t="n"/>
       <c r="E38" s="79" t="n">
         <v>1</v>
       </c>
@@ -14856,14 +14806,6 @@
           <t>Chỉ lấy giá trị nominal để phân biệt nhánh. Các giá trị sát biên 10 MB thuộc về sheet 01 — kỹ thuật giá trị biên, không phải bảng quyết định.</t>
         </is>
       </c>
-      <c r="G38" s="8" t="n"/>
-      <c r="H38" s="8" t="n"/>
-      <c r="I38" s="8" t="n"/>
-      <c r="J38" s="8" t="n"/>
-      <c r="K38" s="8" t="n"/>
-      <c r="L38" s="8" t="n"/>
-      <c r="M38" s="8" t="n"/>
-      <c r="N38" s="9" t="n"/>
     </row>
     <row r="39" ht="30" customHeight="1">
       <c r="A39" s="56" t="inlineStr">
@@ -16483,10 +16425,10 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="22" customHeight="1">
+    <row r="4" ht="30" customHeight="1">
       <c r="A4" s="54" t="inlineStr">
         <is>
-          <t>TỔNG KẾT THI HÀNH — 12 test đã chạy, 12 PASS, 0 fail.</t>
+          <t>TỔNG KẾT THI HÀNH — 12 test đã chạy, 12 PASS, 0 fail.  Bảng thiết kế có 8 dòng nhưng chạy ra 12 test: dòng 6 là test tham số hoá, chạy 5 lần cho 5 điểm vào khác nhau.</t>
         </is>
       </c>
     </row>

--- a/BaoCao-KiemThu-CareerCompass.xlsx
+++ b/BaoCao-KiemThu-CareerCompass.xlsx
@@ -33,7 +33,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="31">
+  <fonts count="32">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -181,6 +181,11 @@
       <i val="1"/>
       <color rgb="007F6000"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="16">
@@ -389,7 +394,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -623,6 +628,12 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1723,8 +1734,8 @@
     <mergeCell ref="F8:H8"/>
     <mergeCell ref="F17:H17"/>
     <mergeCell ref="F23:H23"/>
+    <mergeCell ref="F28:H28"/>
     <mergeCell ref="F22:H22"/>
-    <mergeCell ref="F28:H28"/>
     <mergeCell ref="F13:H13"/>
     <mergeCell ref="F30:H30"/>
     <mergeCell ref="F9:H9"/>
@@ -10204,6 +10215,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -10390,6 +10402,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14" ht="24" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
@@ -10554,6 +10567,7 @@
         </is>
       </c>
     </row>
+    <row r="22"/>
     <row r="23" ht="24" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
@@ -11052,6 +11066,7 @@
         </is>
       </c>
     </row>
+    <row r="39"/>
     <row r="40" ht="24" customHeight="1">
       <c r="A40" s="3" t="inlineStr">
         <is>
@@ -11319,6 +11334,7 @@
         </is>
       </c>
     </row>
+    <row r="50"/>
     <row r="51" ht="24" customHeight="1">
       <c r="A51" s="3" t="inlineStr">
         <is>
@@ -11629,6 +11645,7 @@
         </is>
       </c>
     </row>
+    <row r="62"/>
     <row r="63" ht="24" customHeight="1">
       <c r="A63" s="3" t="inlineStr">
         <is>
@@ -11928,6 +11945,7 @@
         </is>
       </c>
     </row>
+    <row r="73"/>
     <row r="74" ht="24" customHeight="1">
       <c r="A74" s="3" t="inlineStr">
         <is>
@@ -11958,7 +11976,11 @@
       </c>
       <c r="E75" s="4" t="n"/>
       <c r="F75" s="4" t="n"/>
-      <c r="G75" s="4" t="n"/>
+      <c r="G75" s="84" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
           <t>Test đã thi hành</t>
@@ -11989,7 +12011,11 @@
       </c>
       <c r="E76" s="5" t="n"/>
       <c r="F76" s="5" t="n"/>
-      <c r="G76" s="5" t="n"/>
+      <c r="G76" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="H76" s="5" t="inlineStr">
         <is>
           <t>RegisterTagCoverageTest ·
@@ -12020,7 +12046,11 @@
       </c>
       <c r="E77" s="5" t="n"/>
       <c r="F77" s="5" t="n"/>
-      <c r="G77" s="5" t="n"/>
+      <c r="G77" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="H77" s="5" t="inlineStr">
         <is>
           <t>RegisterTagCoverageTest ·
@@ -12051,7 +12081,11 @@
       </c>
       <c r="E78" s="5" t="n"/>
       <c r="F78" s="5" t="n"/>
-      <c r="G78" s="5" t="n"/>
+      <c r="G78" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="H78" s="5" t="inlineStr">
         <is>
           <t>RegisterTagCoverageTest ·
@@ -12082,7 +12116,11 @@
       </c>
       <c r="E79" s="5" t="n"/>
       <c r="F79" s="5" t="n"/>
-      <c r="G79" s="5" t="n"/>
+      <c r="G79" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="H79" s="5" t="inlineStr">
         <is>
           <t>RegisterTagCoverageTest ·
@@ -12113,7 +12151,11 @@
       </c>
       <c r="E80" s="5" t="n"/>
       <c r="F80" s="5" t="n"/>
-      <c r="G80" s="5" t="n"/>
+      <c r="G80" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="H80" s="5" t="inlineStr">
         <is>
           <t>RegisterTagCoverageTest ·
@@ -12143,7 +12185,11 @@
       </c>
       <c r="E81" s="5" t="n"/>
       <c r="F81" s="5" t="n"/>
-      <c r="G81" s="5" t="n"/>
+      <c r="G81" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="H81" s="5" t="inlineStr">
         <is>
           <t>RegisterTagCoverageTest ·
@@ -12173,7 +12219,11 @@
       </c>
       <c r="E82" s="5" t="n"/>
       <c r="F82" s="5" t="n"/>
-      <c r="G82" s="5" t="n"/>
+      <c r="G82" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="H82" s="5" t="inlineStr">
         <is>
           <t>RegisterTagCoverageTest ·
@@ -12203,7 +12253,11 @@
       </c>
       <c r="E83" s="5" t="n"/>
       <c r="F83" s="5" t="n"/>
-      <c r="G83" s="5" t="n"/>
+      <c r="G83" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="H83" s="5" t="inlineStr">
         <is>
           <t>RegisterTagCoverageTest ·
@@ -12233,7 +12287,11 @@
       </c>
       <c r="E84" s="5" t="n"/>
       <c r="F84" s="5" t="n"/>
-      <c r="G84" s="5" t="n"/>
+      <c r="G84" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="H84" s="5" t="inlineStr">
         <is>
           <t>RegisterTagCoverageTest ·
@@ -12263,7 +12321,11 @@
       </c>
       <c r="E85" s="5" t="n"/>
       <c r="F85" s="5" t="n"/>
-      <c r="G85" s="5" t="n"/>
+      <c r="G85" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="H85" s="5" t="inlineStr">
         <is>
           <t>RegisterTagCoverageTest ·
@@ -12293,7 +12355,11 @@
       </c>
       <c r="E86" s="5" t="n"/>
       <c r="F86" s="5" t="n"/>
-      <c r="G86" s="5" t="n"/>
+      <c r="G86" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="H86" s="5" t="inlineStr">
         <is>
           <t>RegisterTagCoverageTest ·
@@ -12323,7 +12389,11 @@
       </c>
       <c r="E87" s="5" t="n"/>
       <c r="F87" s="5" t="n"/>
-      <c r="G87" s="5" t="n"/>
+      <c r="G87" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="H87" s="5" t="inlineStr">
         <is>
           <t>RegisterTagCoverageTest ·
@@ -12353,7 +12423,11 @@
       </c>
       <c r="E88" s="5" t="n"/>
       <c r="F88" s="5" t="n"/>
-      <c r="G88" s="5" t="n"/>
+      <c r="G88" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="H88" s="5" t="inlineStr">
         <is>
           <t>RegisterTagCoverageTest ·
@@ -12383,7 +12457,11 @@
       </c>
       <c r="E89" s="5" t="n"/>
       <c r="F89" s="5" t="n"/>
-      <c r="G89" s="5" t="n"/>
+      <c r="G89" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="H89" s="5" t="inlineStr">
         <is>
           <t>RegisterTagCoverageTest ·
@@ -12413,7 +12491,11 @@
       </c>
       <c r="E90" s="5" t="n"/>
       <c r="F90" s="5" t="n"/>
-      <c r="G90" s="5" t="n"/>
+      <c r="G90" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="H90" s="5" t="inlineStr">
         <is>
           <t>RegisterTagCoverageTest ·
@@ -12443,7 +12525,11 @@
       </c>
       <c r="E91" s="5" t="n"/>
       <c r="F91" s="5" t="n"/>
-      <c r="G91" s="5" t="n"/>
+      <c r="G91" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="H91" s="5" t="inlineStr">
         <is>
           <t>RegisterTagCoverageTest ·
@@ -12473,7 +12559,11 @@
       </c>
       <c r="E92" s="5" t="n"/>
       <c r="F92" s="5" t="n"/>
-      <c r="G92" s="5" t="n"/>
+      <c r="G92" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="H92" s="5" t="inlineStr">
         <is>
           <t>RegisterTagCoverageTest ·
@@ -12502,7 +12592,11 @@
       </c>
       <c r="E93" s="5" t="n"/>
       <c r="F93" s="5" t="n"/>
-      <c r="G93" s="5" t="n"/>
+      <c r="G93" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="H93" s="5" t="inlineStr">
         <is>
           <t>OnboardingFileSizeBvaTest ·
@@ -12531,7 +12625,11 @@
       </c>
       <c r="E94" s="5" t="n"/>
       <c r="F94" s="5" t="n"/>
-      <c r="G94" s="5" t="n"/>
+      <c r="G94" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="H94" s="5" t="inlineStr">
         <is>
           <t>OnboardingFileSizeBvaTest ·
@@ -12560,7 +12658,11 @@
       </c>
       <c r="E95" s="5" t="n"/>
       <c r="F95" s="5" t="n"/>
-      <c r="G95" s="5" t="n"/>
+      <c r="G95" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="H95" s="5" t="inlineStr">
         <is>
           <t>OnboardingFileSizeBvaTest ·
@@ -12589,7 +12691,11 @@
       </c>
       <c r="E96" s="5" t="n"/>
       <c r="F96" s="5" t="n"/>
-      <c r="G96" s="5" t="n"/>
+      <c r="G96" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="H96" s="5" t="inlineStr">
         <is>
           <t>OnboardingFileSizeBvaTest ·
@@ -12618,7 +12724,11 @@
       </c>
       <c r="E97" s="5" t="n"/>
       <c r="F97" s="5" t="n"/>
-      <c r="G97" s="5" t="n"/>
+      <c r="G97" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="H97" s="5" t="inlineStr">
         <is>
           <t>OnboardingFileSizeBvaTest ·
@@ -12647,7 +12757,11 @@
       </c>
       <c r="E98" s="5" t="n"/>
       <c r="F98" s="5" t="n"/>
-      <c r="G98" s="5" t="n"/>
+      <c r="G98" s="13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="H98" s="5" t="inlineStr">
         <is>
           <t>OnboardingFileSizeBvaTest ·
@@ -13828,7 +13942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N48"/>
+  <dimension ref="A1:N50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -14327,203 +14441,260 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="70" t="inlineStr">
+        <is>
+          <t>Kết quả chạy test</t>
+        </is>
+      </c>
+      <c r="B19" s="68" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C19" s="68" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="D19" s="68" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="E19" s="68" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F19" s="68" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G19" s="68" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H19" s="68" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I19" s="68" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="46" customHeight="1">
+      <c r="A20" s="70" t="inlineStr">
+        <is>
+          <t>Test thi hành rule này</t>
+        </is>
+      </c>
+      <c r="B20" s="85" t="inlineStr">
+        <is>
+          <t>rule1</t>
+        </is>
+      </c>
+      <c r="C20" s="85" t="inlineStr">
+        <is>
+          <t>rule1</t>
+        </is>
+      </c>
+      <c r="D20" s="85" t="inlineStr">
+        <is>
+          <t>rule1</t>
+        </is>
+      </c>
+      <c r="E20" s="85" t="inlineStr">
+        <is>
+          <t>rule1</t>
+        </is>
+      </c>
+      <c r="F20" s="85" t="inlineStr">
+        <is>
+          <t>rule2
+rule3
+rule4
+rule5</t>
+        </is>
+      </c>
+      <c r="G20" s="85" t="inlineStr">
+        <is>
+          <t>rule6</t>
+        </is>
+      </c>
+      <c r="H20" s="85" t="inlineStr">
+        <is>
+          <t>rule7
+rule8</t>
+        </is>
+      </c>
+      <c r="I20" s="85" t="inlineStr">
+        <is>
+          <t>rule7
+rule8</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="24" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>BẢNG SAU KHI RÚT GỌN — bước 6 slide 42 · 8 rule → 4 rule</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="65" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="65" t="inlineStr">
         <is>
           <t>Condition / Action</t>
         </is>
       </c>
-      <c r="B21" s="65" t="inlineStr">
+      <c r="B23" s="65" t="inlineStr">
         <is>
           <t>R1'</t>
         </is>
       </c>
-      <c r="C21" s="65" t="inlineStr">
+      <c r="C23" s="65" t="inlineStr">
         <is>
           <t>R2'</t>
         </is>
       </c>
-      <c r="D21" s="65" t="inlineStr">
+      <c r="D23" s="65" t="inlineStr">
         <is>
           <t>R3'</t>
         </is>
       </c>
-      <c r="E21" s="65" t="inlineStr">
+      <c r="E23" s="65" t="inlineStr">
         <is>
           <t>R4'</t>
         </is>
       </c>
-      <c r="J21" s="65" t="inlineStr">
+      <c r="J23" s="65" t="inlineStr">
         <is>
           <t>Ghi chú</t>
         </is>
       </c>
-      <c r="K21" s="8" t="n"/>
-      <c r="L21" s="8" t="n"/>
-      <c r="M21" s="8" t="n"/>
-      <c r="N21" s="9" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="66" t="inlineStr">
-        <is>
-          <t>C1 · Tên tệp = null</t>
-        </is>
-      </c>
-      <c r="B22" s="69" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="C22" s="69" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="D22" s="69" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E22" s="69" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="J22" s="77" t="inlineStr">
-        <is>
-          <t>2 giá trị</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="66" t="inlineStr">
-        <is>
-          <t>C2 · Đuôi tệp thuộc {.pdf, .png, .jpg, .jpeg}</t>
-        </is>
-      </c>
-      <c r="B23" s="72" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C23" s="69" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D23" s="69" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E23" s="69" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="J23" s="77" t="inlineStr">
-        <is>
-          <t>2 giá trị — đặc tả không phân biệt bốn đuôi với nhau</t>
-        </is>
-      </c>
+      <c r="K23" s="8" t="n"/>
+      <c r="L23" s="8" t="n"/>
+      <c r="M23" s="8" t="n"/>
+      <c r="N23" s="9" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="66" t="inlineStr">
         <is>
+          <t>C1 · Tên tệp = null</t>
+        </is>
+      </c>
+      <c r="B24" s="69" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="C24" s="69" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D24" s="69" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E24" s="69" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J24" s="77" t="inlineStr">
+        <is>
+          <t>2 giá trị</t>
+        </is>
+      </c>
+      <c r="K24" s="8" t="n"/>
+      <c r="L24" s="8" t="n"/>
+      <c r="M24" s="8" t="n"/>
+      <c r="N24" s="9" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="66" t="inlineStr">
+        <is>
+          <t>C2 · Đuôi tệp thuộc {.pdf, .png, .jpg, .jpeg}</t>
+        </is>
+      </c>
+      <c r="B25" s="72" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C25" s="69" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D25" s="69" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E25" s="69" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="J25" s="77" t="inlineStr">
+        <is>
+          <t>2 giá trị — đặc tả không phân biệt bốn đuôi với nhau</t>
+        </is>
+      </c>
+      <c r="K25" s="8" t="n"/>
+      <c r="L25" s="8" t="n"/>
+      <c r="M25" s="8" t="n"/>
+      <c r="N25" s="9" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="66" t="inlineStr">
+        <is>
           <t>C3 · Dung lượng ≤ 10MB</t>
         </is>
       </c>
-      <c r="B24" s="72" t="inlineStr">
+      <c r="B26" s="72" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="C24" s="69" t="inlineStr">
+      <c r="C26" s="69" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="D24" s="69" t="inlineStr">
+      <c r="D26" s="69" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="E24" s="72" t="inlineStr">
+      <c r="E26" s="72" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="J24" s="77" t="inlineStr">
+      <c r="J26" s="77" t="inlineStr">
         <is>
           <t>2 giá trị</t>
         </is>
       </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="70" t="inlineStr">
-        <is>
-          <t>A1 · Lưu tệp, trả đường dẫn</t>
-        </is>
-      </c>
-      <c r="B25" s="67" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="C25" s="71" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D25" s="67" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="E25" s="67" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="70" t="inlineStr">
-        <is>
-          <t>A2 · Lỗi "Tên file không hợp lệ"</t>
-        </is>
-      </c>
-      <c r="B26" s="71" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C26" s="67" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="D26" s="67" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="E26" s="67" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
+      <c r="K26" s="8" t="n"/>
+      <c r="L26" s="8" t="n"/>
+      <c r="M26" s="8" t="n"/>
+      <c r="N26" s="9" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="70" t="inlineStr">
         <is>
-          <t>A3 · Lỗi "Vượt quá dung lượng 10MB"</t>
+          <t>A1 · Lưu tệp, trả đường dẫn</t>
         </is>
       </c>
       <c r="B27" s="67" t="inlineStr">
@@ -14531,14 +14702,14 @@
           <t>–</t>
         </is>
       </c>
-      <c r="C27" s="67" t="inlineStr">
+      <c r="C27" s="71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D27" s="67" t="inlineStr">
         <is>
           <t>–</t>
-        </is>
-      </c>
-      <c r="D27" s="71" t="inlineStr">
-        <is>
-          <t>X</t>
         </is>
       </c>
       <c r="E27" s="67" t="inlineStr">
@@ -14550,74 +14721,132 @@
     <row r="28">
       <c r="A28" s="70" t="inlineStr">
         <is>
-          <t>A4 · Lỗi "Chỉ chấp nhận PDF, PNG hoặc JPG"</t>
-        </is>
-      </c>
-      <c r="B28" s="67" t="inlineStr">
+          <t>A2 · Lỗi "Tên file không hợp lệ"</t>
+        </is>
+      </c>
+      <c r="B28" s="71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C28" s="67" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="C28" s="67" t="inlineStr">
+      <c r="D28" s="67" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="D28" s="67" t="inlineStr">
+      <c r="E28" s="67" t="inlineStr">
         <is>
           <t>–</t>
-        </is>
-      </c>
-      <c r="E28" s="71" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J28" s="77" t="inlineStr">
-        <is>
-          <t>R4' gộp cả ô đã phát hiện DEF-011 — xem ghi chú bên dưới</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="70" t="inlineStr">
         <is>
+          <t>A3 · Lỗi "Vượt quá dung lượng 10MB"</t>
+        </is>
+      </c>
+      <c r="B29" s="67" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C29" s="67" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="D29" s="71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E29" s="67" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="70" t="inlineStr">
+        <is>
+          <t>A4 · Lỗi "Chỉ chấp nhận PDF, PNG hoặc JPG"</t>
+        </is>
+      </c>
+      <c r="B30" s="67" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="C30" s="67" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="D30" s="67" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E30" s="71" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J30" s="77" t="inlineStr">
+        <is>
+          <t>R4' gộp cả ô đã phát hiện DEF-011 — xem ghi chú bên dưới</t>
+        </is>
+      </c>
+      <c r="K30" s="8" t="n"/>
+      <c r="L30" s="8" t="n"/>
+      <c r="M30" s="8" t="n"/>
+      <c r="N30" s="9" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="70" t="inlineStr">
+        <is>
           <t>Kết quả chạy test</t>
         </is>
       </c>
-      <c r="B29" s="68" t="inlineStr">
+      <c r="B31" s="68" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="C29" s="68" t="inlineStr">
+      <c r="C31" s="68" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="D29" s="68" t="inlineStr">
+      <c r="D31" s="68" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="E29" s="68" t="inlineStr">
+      <c r="E31" s="68" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="56" customHeight="1">
-      <c r="A30" s="70" t="inlineStr">
+    <row r="32" ht="56" customHeight="1">
+      <c r="A32" s="70" t="inlineStr">
         <is>
           <t>Test thi hành rule này</t>
         </is>
       </c>
-      <c r="B30" s="73" t="inlineStr">
+      <c r="B32" s="73" t="inlineStr">
         <is>
           <t>rule1_tenTepNull_tuChoi</t>
         </is>
       </c>
-      <c r="C30" s="73" t="inlineStr">
+      <c r="C32" s="73" t="inlineStr">
         <is>
           <t>rule2_duoiPdf_luuThanhCong
 rule3_duoiPng_luuThanhCong
@@ -14625,246 +14854,282 @@
 rule5_duoiJpeg_luuThanhCong</t>
         </is>
       </c>
-      <c r="D30" s="73" t="inlineStr">
+      <c r="D32" s="73" t="inlineStr">
         <is>
           <t>rule6_duoiHopLe_dungLuongQuaLon_tuChoi</t>
         </is>
       </c>
-      <c r="E30" s="73" t="inlineStr">
+      <c r="E32" s="73" t="inlineStr">
         <is>
           <t>rule7_duoiKhongHopLe_tuChoi
 rule8_tenTepKhongCoDuoi_tuChoi</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="70" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="70" t="inlineStr">
         <is>
           <t>Gộp từ rule nào</t>
         </is>
       </c>
-      <c r="B31" s="78" t="inlineStr">
+      <c r="B33" s="78" t="inlineStr">
         <is>
           <t>gộp R1–R4</t>
         </is>
       </c>
-      <c r="C31" s="78" t="inlineStr">
+      <c r="C33" s="78" t="inlineStr">
         <is>
           <t>chính là R5</t>
         </is>
       </c>
-      <c r="D31" s="78" t="inlineStr">
+      <c r="D33" s="78" t="inlineStr">
         <is>
           <t>chính là R6</t>
         </is>
       </c>
-      <c r="E31" s="78" t="inlineStr">
+      <c r="E33" s="78" t="inlineStr">
         <is>
           <t>gộp R7 + R8</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="24" customHeight="1">
-      <c r="A33" s="3" t="inlineStr">
+    <row r="35" ht="24" customHeight="1">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>GIÁ TRỊ ĐẠI DIỆN CHO TỪNG LỚP — vì sao 4 rule mà có 8 test</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="65" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="65" t="inlineStr">
         <is>
           <t>Điều kiện</t>
         </is>
       </c>
-      <c r="B34" s="65" t="inlineStr">
+      <c r="B36" s="65" t="inlineStr">
         <is>
           <t>Lớp</t>
         </is>
       </c>
-      <c r="C34" s="65" t="inlineStr">
+      <c r="C36" s="65" t="inlineStr">
         <is>
           <t>Giá trị đại diện được kiểm</t>
         </is>
       </c>
-      <c r="D34" s="9" t="n"/>
-      <c r="E34" s="65" t="inlineStr">
+      <c r="D36" s="9" t="n"/>
+      <c r="E36" s="65" t="inlineStr">
         <is>
           <t>Số test</t>
         </is>
       </c>
-      <c r="F34" s="65" t="inlineStr">
+      <c r="F36" s="65" t="inlineStr">
         <is>
           <t>Lý do tách riêng</t>
         </is>
       </c>
-      <c r="G34" s="8" t="n"/>
-      <c r="H34" s="8" t="n"/>
-      <c r="I34" s="8" t="n"/>
-      <c r="J34" s="8" t="n"/>
-      <c r="K34" s="8" t="n"/>
-      <c r="L34" s="8" t="n"/>
-      <c r="M34" s="8" t="n"/>
-      <c r="N34" s="9" t="n"/>
-    </row>
-    <row r="35" ht="34" customHeight="1">
-      <c r="A35" s="66" t="inlineStr">
-        <is>
-          <t>C2 · Đuôi tệp</t>
-        </is>
-      </c>
-      <c r="B35" s="67" t="inlineStr">
-        <is>
-          <t>Hợp lệ (Y)</t>
-        </is>
-      </c>
-      <c r="C35" s="67" t="inlineStr">
-        <is>
-          <t>.pdf · .png · .jpg · .jpeg</t>
-        </is>
-      </c>
-      <c r="E35" s="79" t="n">
-        <v>4</v>
-      </c>
-      <c r="F35" s="80" t="inlineStr">
-        <is>
-          <t>Mã nguồn so sánh từng đuôi bằng một chuỗi &amp;&amp; — bốn nhánh riêng. Báo cáo bao phủ chỉ đích danh ba nhánh chưa ai chạm tới, nên phải kiểm đủ bốn.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="34" customHeight="1">
-      <c r="A36" s="66" t="inlineStr">
-        <is>
-          <t>C2 · Đuôi tệp</t>
-        </is>
-      </c>
-      <c r="B36" s="67" t="inlineStr">
-        <is>
-          <t>Không hợp lệ (N)</t>
-        </is>
-      </c>
-      <c r="C36" s="67" t="inlineStr">
-        <is>
-          <t>.exe · tên không có dấu chấm</t>
-        </is>
-      </c>
-      <c r="E36" s="79" t="n">
-        <v>2</v>
-      </c>
-      <c r="F36" s="80" t="inlineStr">
-        <is>
-          <t>Hai giá trị này TRƯỚC KHI SỬA cho hai kết quả khác nhau: .exe trả lỗi 400 đúng như đặc tả, còn tên không có dấu chấm ném StringIndexOutOfBoundsException thành lỗi 500 — chính là DEF-011. Sau khi sửa mới thật sự cùng một lớp.</t>
-        </is>
-      </c>
+      <c r="G36" s="8" t="n"/>
+      <c r="H36" s="8" t="n"/>
+      <c r="I36" s="8" t="n"/>
+      <c r="J36" s="8" t="n"/>
+      <c r="K36" s="8" t="n"/>
+      <c r="L36" s="8" t="n"/>
+      <c r="M36" s="8" t="n"/>
+      <c r="N36" s="9" t="n"/>
     </row>
     <row r="37" ht="34" customHeight="1">
       <c r="A37" s="66" t="inlineStr">
         <is>
-          <t>C1 · Tên tệp null</t>
+          <t>C2 · Đuôi tệp</t>
         </is>
       </c>
       <c r="B37" s="67" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>Hợp lệ (Y)</t>
         </is>
       </c>
       <c r="C37" s="67" t="inlineStr">
         <is>
-          <t>null</t>
-        </is>
-      </c>
+          <t>.pdf · .png · .jpg · .jpeg</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="n"/>
       <c r="E37" s="79" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F37" s="80" t="inlineStr">
         <is>
-          <t>Một giá trị duy nhất, không có gì để tách.</t>
-        </is>
-      </c>
+          <t>Mã nguồn so sánh từng đuôi bằng một chuỗi &amp;&amp; — bốn nhánh riêng. Báo cáo bao phủ chỉ đích danh ba nhánh chưa ai chạm tới, nên phải kiểm đủ bốn.</t>
+        </is>
+      </c>
+      <c r="G37" s="8" t="n"/>
+      <c r="H37" s="8" t="n"/>
+      <c r="I37" s="8" t="n"/>
+      <c r="J37" s="8" t="n"/>
+      <c r="K37" s="8" t="n"/>
+      <c r="L37" s="8" t="n"/>
+      <c r="M37" s="8" t="n"/>
+      <c r="N37" s="9" t="n"/>
     </row>
     <row r="38" ht="34" customHeight="1">
       <c r="A38" s="66" t="inlineStr">
         <is>
+          <t>C2 · Đuôi tệp</t>
+        </is>
+      </c>
+      <c r="B38" s="67" t="inlineStr">
+        <is>
+          <t>Không hợp lệ (N)</t>
+        </is>
+      </c>
+      <c r="C38" s="67" t="inlineStr">
+        <is>
+          <t>.exe · tên không có dấu chấm</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="n"/>
+      <c r="E38" s="79" t="n">
+        <v>2</v>
+      </c>
+      <c r="F38" s="80" t="inlineStr">
+        <is>
+          <t>Hai giá trị này TRƯỚC KHI SỬA cho hai kết quả khác nhau: .exe trả lỗi 400 đúng như đặc tả, còn tên không có dấu chấm ném StringIndexOutOfBoundsException thành lỗi 500 — chính là DEF-011. Sau khi sửa mới thật sự cùng một lớp.</t>
+        </is>
+      </c>
+      <c r="G38" s="8" t="n"/>
+      <c r="H38" s="8" t="n"/>
+      <c r="I38" s="8" t="n"/>
+      <c r="J38" s="8" t="n"/>
+      <c r="K38" s="8" t="n"/>
+      <c r="L38" s="8" t="n"/>
+      <c r="M38" s="8" t="n"/>
+      <c r="N38" s="9" t="n"/>
+    </row>
+    <row r="39" ht="34" customHeight="1">
+      <c r="A39" s="66" t="inlineStr">
+        <is>
+          <t>C1 · Tên tệp null</t>
+        </is>
+      </c>
+      <c r="B39" s="67" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="C39" s="67" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="n"/>
+      <c r="E39" s="79" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" s="80" t="inlineStr">
+        <is>
+          <t>Một giá trị duy nhất, không có gì để tách.</t>
+        </is>
+      </c>
+      <c r="G39" s="8" t="n"/>
+      <c r="H39" s="8" t="n"/>
+      <c r="I39" s="8" t="n"/>
+      <c r="J39" s="8" t="n"/>
+      <c r="K39" s="8" t="n"/>
+      <c r="L39" s="8" t="n"/>
+      <c r="M39" s="8" t="n"/>
+      <c r="N39" s="9" t="n"/>
+    </row>
+    <row r="40" ht="34" customHeight="1">
+      <c r="A40" s="66" t="inlineStr">
+        <is>
           <t>C3 · Dung lượng</t>
         </is>
       </c>
-      <c r="B38" s="67" t="inlineStr">
+      <c r="B40" s="67" t="inlineStr">
         <is>
           <t>Y và N</t>
         </is>
       </c>
-      <c r="C38" s="67" t="inlineStr">
+      <c r="C40" s="67" t="inlineStr">
         <is>
           <t>1 byte · 11 MB</t>
         </is>
       </c>
-      <c r="E38" s="79" t="n">
+      <c r="D40" s="9" t="n"/>
+      <c r="E40" s="79" t="n">
         <v>1</v>
       </c>
-      <c r="F38" s="80" t="inlineStr">
+      <c r="F40" s="80" t="inlineStr">
         <is>
           <t>Chỉ lấy giá trị nominal để phân biệt nhánh. Các giá trị sát biên 10 MB thuộc về sheet 01 — kỹ thuật giá trị biên, không phải bảng quyết định.</t>
         </is>
       </c>
-    </row>
-    <row r="39" ht="30" customHeight="1">
-      <c r="A39" s="56" t="inlineStr">
+      <c r="G40" s="8" t="n"/>
+      <c r="H40" s="8" t="n"/>
+      <c r="I40" s="8" t="n"/>
+      <c r="J40" s="8" t="n"/>
+      <c r="K40" s="8" t="n"/>
+      <c r="L40" s="8" t="n"/>
+      <c r="M40" s="8" t="n"/>
+      <c r="N40" s="9" t="n"/>
+    </row>
+    <row r="41" ht="30" customHeight="1">
+      <c r="A41" s="56" t="inlineStr">
         <is>
           <t>Bảng quyết định trả lời "tổ hợp điều kiện nào dẫn tới hành động nào" — nó dừng ở mức LỚP. Việc chọn giá trị nào làm đại diện cho mỗi lớp là việc của phân hoạch lớp tương đương và bao phủ nhánh. Đó là lý do 4 rule sinh ra 8 test chứ không phải 4.</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="20" customHeight="1">
-      <c r="A41" s="55" t="inlineStr">
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="55" t="inlineStr">
         <is>
           <t>Ô tô vàng là ô "không quan tâm" (–) sinh ra khi gộp rule.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="44" customHeight="1">
-      <c r="A42" s="56" t="inlineStr">
-        <is>
-          <t>BẢNG RÚT GỌN NÓI ÍT HƠN BẢNG ĐẦY ĐỦ — và đó là lý do vẫn phải giữ cả hai. Rút gọn xong chỉ còn 4 rule, nhưng bộ kiểm thử có 8 test. Chênh lệch nằm ở chỗ: xét theo ĐẶC TẢ thì bốn đuôi .pdf, .png, .jpg, .jpeg là MỘT lớp tương đương (cùng được chấp nhận), nên rút gọn gộp chúng làm một ô "hợp lệ". Nhưng xét theo MÃ NGUỒN thì mỗi đuôi là một nhánh riêng của chuỗi &amp;&amp; , và báo cáo bao phủ đã chỉ đích danh ba nhánh chưa ai chạm tới. Nếu chỉ nhìn bảng rút gọn mà viết test thì ba nhánh đó vẫn nằm im.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="44" customHeight="1">
-      <c r="A43" s="56" t="inlineStr">
-        <is>
-          <t>RÚT GỌN CÒN CHE MẤT TRƯỜNG HỢP ĐÃ TÌM RA LỖI: "không có dấu chấm" bị gộp vào R4' cùng với "đuôi khác" vì hai bên cho cùng hành động A4. Nhưng chính ô đó mới là ô làm lộ DEF-011 — trước khi sửa, nó không trả lỗi 400 mà ném StringIndexOutOfBoundsException thành lỗi 500. Bảng đầy đủ giữ nó ở cột R23–R24 nên còn nhìn thấy; bảng rút gọn thì không.</t>
         </is>
       </c>
     </row>
     <row r="44" ht="44" customHeight="1">
       <c r="A44" s="56" t="inlineStr">
         <is>
-          <t>VÌ SAO GỘP ĐƯỢC: mã nguồn kiểm ba điều kiện TUẦN TỰ và thoát ngay khi gặp lỗi. Khi một điều kiện phía trước đã quyết định kết quả thì điều kiện phía sau không còn ảnh hưởng, đánh dấu "–". R1' gộp 12 rule (tên tệp null thì đuôi và dung lượng vô nghĩa); R7' và R8' mỗi cột gộp 2 rule (đuôi sai thì chặn trước khi xét dung lượng).</t>
+          <t>BẢNG RÚT GỌN NÓI ÍT HƠN BẢNG ĐẦY ĐỦ — và đó là lý do vẫn phải giữ cả hai. Rút gọn xong chỉ còn 4 rule, nhưng bộ kiểm thử có 8 test. Chênh lệch nằm ở chỗ: xét theo ĐẶC TẢ thì bốn đuôi .pdf, .png, .jpg, .jpeg là MỘT lớp tương đương (cùng được chấp nhận), nên rút gọn gộp chúng làm một ô "hợp lệ". Nhưng xét theo MÃ NGUỒN thì mỗi đuôi là một nhánh riêng của chuỗi &amp;&amp; , và báo cáo bao phủ đã chỉ đích danh ba nhánh chưa ai chạm tới. Nếu chỉ nhìn bảng rút gọn mà viết test thì ba nhánh đó vẫn nằm im.</t>
         </is>
       </c>
     </row>
     <row r="45" ht="44" customHeight="1">
       <c r="A45" s="56" t="inlineStr">
         <is>
-          <t>KHIẾM KHUYẾT DEF-011 — nằm trong lớp C2 = N. Tệp không có dấu chấm làm lastIndexOf(".") trả -1, kéo theo substring(-1) ném StringIndexOutOfBoundsException, người dùng nhận lỗi 500 thay vì thông báo 400. Nói rõ để không nhận công sai: test hộp trắng đã ghi đúng nguyên nhân từ trước nhưng lại CHỐT hành vi lỗi bằng một khẳng định, nên bộ test vẫn xanh. Đóng góp của kỹ thuật này là BUỘC PHẢI SỬA — mỗi cột của bảng phải ứng với một hành động xác định trong nhóm A1–A4, không thể để một ô là "sập 500".</t>
+          <t>RÚT GỌN CÒN CHE MẤT TRƯỜNG HỢP ĐÃ TÌM RA LỖI: "không có dấu chấm" bị gộp vào R4' cùng với "đuôi khác" vì hai bên cho cùng hành động A4. Nhưng chính ô đó mới là ô làm lộ DEF-011 — trước khi sửa, nó không trả lỗi 400 mà ném StringIndexOutOfBoundsException thành lỗi 500. Bảng đầy đủ giữ nó ở cột R23–R24 nên còn nhìn thấy; bảng rút gọn thì không.</t>
         </is>
       </c>
     </row>
     <row r="46" ht="44" customHeight="1">
       <c r="A46" s="56" t="inlineStr">
         <is>
-          <t>CON SỐ ĐO ĐƯỢC: nhánh OnboardingService 75,0% (9/12) → 100,0% (14/14); dòng 94,7% (18/19) → 100,0% (19/19). Nguồn: target/site/jacoco/jacoco.csv.</t>
+          <t>VÌ SAO GỘP ĐƯỢC: mã nguồn kiểm ba điều kiện TUẦN TỰ và thoát ngay khi gặp lỗi. Khi một điều kiện phía trước đã quyết định kết quả thì điều kiện phía sau không còn ảnh hưởng, đánh dấu "–". R1' gộp 12 rule (tên tệp null thì đuôi và dung lượng vô nghĩa); R7' và R8' mỗi cột gộp 2 rule (đuôi sai thì chặn trước khi xét dung lượng).</t>
         </is>
       </c>
     </row>
     <row r="47" ht="44" customHeight="1">
       <c r="A47" s="56" t="inlineStr">
         <is>
-          <t>QUAN HỆ VỚI SHEET GIÁ TRỊ BIÊN: điều kiện C3 ở bảng này chỉ lấy giá trị NOMINAL (1 byte và 11 MB) để phân biệt nhánh. Các giá trị sát biên 10 MB thuộc về sheet 01.</t>
+          <t>KHIẾM KHUYẾT DEF-011 — nằm trong lớp C2 = N. Tệp không có dấu chấm làm lastIndexOf(".") trả -1, kéo theo substring(-1) ném StringIndexOutOfBoundsException, người dùng nhận lỗi 500 thay vì thông báo 400. Nói rõ để không nhận công sai: test hộp trắng đã ghi đúng nguyên nhân từ trước nhưng lại CHỐT hành vi lỗi bằng một khẳng định, nên bộ test vẫn xanh. Đóng góp của kỹ thuật này là BUỘC PHẢI SỬA — mỗi cột của bảng phải ứng với một hành động xác định trong nhóm A1–A4, không thể để một ô là "sập 500".</t>
         </is>
       </c>
     </row>
     <row r="48" ht="44" customHeight="1">
       <c r="A48" s="56" t="inlineStr">
+        <is>
+          <t>CON SỐ ĐO ĐƯỢC: nhánh OnboardingService 75,0% (9/12) → 100,0% (14/14); dòng 94,7% (18/19) → 100,0% (19/19). Nguồn: target/site/jacoco/jacoco.csv.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="44" customHeight="1">
+      <c r="A49" s="56" t="inlineStr">
+        <is>
+          <t>QUAN HỆ VỚI SHEET GIÁ TRỊ BIÊN: điều kiện C3 ở bảng này chỉ lấy giá trị NOMINAL (1 byte và 11 MB) để phân biệt nhánh. Các giá trị sát biên 10 MB thuộc về sheet 01.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="44" customHeight="1">
+      <c r="A50" s="56" t="inlineStr">
         <is>
           <t>KIỂM TRA BỔ SUNG ngoài bảng: đuôi viết HOA "BANGDIEM.PDF" được chấp nhận vì mã gọi toLowerCase — method boSung_duoiVietHoa_duocChapNhan, PASS. Không đưa vào bảng vì đây là biến thể trình bày của C2, không sinh thêm hành động mới.</t>
         </is>
@@ -14873,32 +15138,32 @@
   </sheetData>
   <mergeCells count="30">
     <mergeCell ref="A9:N9"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="A39:N39"/>
     <mergeCell ref="A48:N48"/>
     <mergeCell ref="F36:N36"/>
-    <mergeCell ref="J28:N28"/>
-    <mergeCell ref="F35:N35"/>
+    <mergeCell ref="A49:N49"/>
     <mergeCell ref="A45:N45"/>
-    <mergeCell ref="C35:D35"/>
     <mergeCell ref="F38:N38"/>
+    <mergeCell ref="J30:N30"/>
     <mergeCell ref="J24:N24"/>
     <mergeCell ref="A7:N7"/>
     <mergeCell ref="A41:N41"/>
+    <mergeCell ref="C40:D40"/>
     <mergeCell ref="A46:N46"/>
+    <mergeCell ref="F39:N39"/>
+    <mergeCell ref="J26:N26"/>
     <mergeCell ref="F37:N37"/>
+    <mergeCell ref="A50:N50"/>
+    <mergeCell ref="J25:N25"/>
     <mergeCell ref="C36:D36"/>
-    <mergeCell ref="A33:N33"/>
     <mergeCell ref="A47:N47"/>
-    <mergeCell ref="A42:N42"/>
-    <mergeCell ref="J22:N22"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="A22:N22"/>
     <mergeCell ref="C38:D38"/>
-    <mergeCell ref="J21:N21"/>
-    <mergeCell ref="F34:N34"/>
+    <mergeCell ref="A35:N35"/>
     <mergeCell ref="A4:N4"/>
-    <mergeCell ref="A20:N20"/>
     <mergeCell ref="C37:D37"/>
     <mergeCell ref="A43:N43"/>
+    <mergeCell ref="F40:N40"/>
     <mergeCell ref="A10:N10"/>
     <mergeCell ref="J23:N23"/>
     <mergeCell ref="A44:N44"/>

--- a/BaoCao-KiemThu-CareerCompass.xlsx
+++ b/BaoCao-KiemThu-CareerCompass.xlsx
@@ -1403,7 +1403,7 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>92 case</t>
+          <t>94 case</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>358 phép kiểm</t>
+          <t>376 phép kiểm</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="C29" s="6" t="n">
-        <v>358</v>
+        <v>376</v>
       </c>
       <c r="D29" s="7" t="n">
         <v>0</v>
@@ -1734,8 +1734,8 @@
     <mergeCell ref="F8:H8"/>
     <mergeCell ref="F17:H17"/>
     <mergeCell ref="F23:H23"/>
+    <mergeCell ref="F22:H22"/>
     <mergeCell ref="F28:H28"/>
-    <mergeCell ref="F22:H22"/>
     <mergeCell ref="F13:H13"/>
     <mergeCell ref="F30:H30"/>
     <mergeCell ref="F9:H9"/>
@@ -7365,7 +7365,7 @@
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>TỔNG KẾT THI HÀNH — 112 request, 358 phép kiểm, 0 lỗi</t>
+          <t>TỔNG KẾT THI HÀNH — 111 request, 376 phép kiểm, 0 lỗi</t>
         </is>
       </c>
     </row>
@@ -7394,11 +7394,16 @@
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>Test case gốc</t>
+          <t>Test case chính</t>
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>92</v>
+        <v>94</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Mã TC-xxx-nn không có hậu tố — trường hợp kiểm thử do nhóm thiết kế</t>
+        </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
@@ -7412,11 +7417,16 @@
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>Bước chuẩn bị</t>
+          <t>Request phụ trợ</t>
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>20</v>
+        <v>17</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Mã có hậu tố a/b/c: làm mới CSRF, đăng nhập lại, đọc id thật, dọn dẹp</t>
+        </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
@@ -7434,7 +7444,12 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>112</v>
+        <v>111</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Số item trong bộ sưu tập. Newman báo 112 lượt gửi vì một request bị gửi lại theo chuyển hướng</t>
+        </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
@@ -7452,7 +7467,12 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>358</v>
+        <v>376</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Postman gọi là All tests; mỗi request có nhiều phép kiểm</t>
+        </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
@@ -7472,6 +7492,11 @@
       <c r="B10" s="13" t="n">
         <v>0</v>
       </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Chạy trên CSDL sạch</t>
+        </is>
+      </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
           <t>Chạy trên CSDL sạch</t>
@@ -7624,7 +7649,7 @@
         <v>10</v>
       </c>
       <c r="C18" s="6" t="n">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="D18" s="13" t="n">
         <v>0</v>
@@ -7648,7 +7673,7 @@
         <v>10</v>
       </c>
       <c r="C19" s="6" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="D19" s="13" t="n">
         <v>0</v>
@@ -7693,10 +7718,10 @@
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C21" s="6" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D21" s="13" t="n">
         <v>0</v>
@@ -7813,10 +7838,10 @@
         </is>
       </c>
       <c r="B26" s="15" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C26" s="15" t="n">
-        <v>358</v>
+        <v>376</v>
       </c>
       <c r="D26" s="15" t="n">
         <v>0</v>
@@ -7982,7 +8007,7 @@
     <row r="35" ht="54" customHeight="1">
       <c r="A35" s="11" t="inlineStr">
         <is>
-          <t>Vì sao có 92 test case nhưng Postman hiện 358: Postman đếm PHÉP KIỂM chứ không đếm test case. Một test case có nhiều phép kiểm, cộng thêm 2 phép kiểm phi chức năng mà nhóm áp cho MỌI request (một ngưỡng hiệu năng và một kiểm tra rò rỉ thông tin). Cụ thể: 151 phép kiểm riêng + 112 × 2 = 375, trừ đi các nhánh if/else không chạy còn 358.</t>
+          <t>Vì sao có 94 test case nhưng Postman hiện 376: Postman đếm PHÉP KIỂM chứ không đếm test case. Một test case có nhiều phép kiểm, cộng thêm 2 phép kiểm phi chức năng mà script cấp collection áp cho MỌI request (một ngưỡng hiệu năng và một kiểm tra rò rỉ thông tin). Cộng chính xác: 154 phép kiểm viết riêng trong từng request + 111 × 2 = 222 phép kiểm phi chức năng, tổng 376.</t>
         </is>
       </c>
     </row>
@@ -10215,7 +10240,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -10402,7 +10426,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14" ht="24" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
@@ -10567,7 +10590,6 @@
         </is>
       </c>
     </row>
-    <row r="22"/>
     <row r="23" ht="24" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
@@ -11066,7 +11088,6 @@
         </is>
       </c>
     </row>
-    <row r="39"/>
     <row r="40" ht="24" customHeight="1">
       <c r="A40" s="3" t="inlineStr">
         <is>
@@ -11334,7 +11355,6 @@
         </is>
       </c>
     </row>
-    <row r="50"/>
     <row r="51" ht="24" customHeight="1">
       <c r="A51" s="3" t="inlineStr">
         <is>
@@ -11645,7 +11665,6 @@
         </is>
       </c>
     </row>
-    <row r="62"/>
     <row r="63" ht="24" customHeight="1">
       <c r="A63" s="3" t="inlineStr">
         <is>
@@ -11945,7 +11964,6 @@
         </is>
       </c>
     </row>
-    <row r="73"/>
     <row r="74" ht="24" customHeight="1">
       <c r="A74" s="3" t="inlineStr">
         <is>

--- a/BaoCao-KiemThu-CareerCompass.xlsx
+++ b/BaoCao-KiemThu-CareerCompass.xlsx
@@ -24,6 +24,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05. API - Postman" sheetId="15" state="visible" r:id="rId15"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06. E2E - CodeceptJS" sheetId="16" state="visible" r:id="rId16"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07. Khiem khuyet" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08. Truy vet SRS" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -394,7 +395,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -634,6 +635,30 @@
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1506,12 +1531,12 @@
       </c>
       <c r="C21" s="63" t="inlineStr">
         <is>
-          <t>78,6%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>+18,5 điểm</t>
+          <t>+30,8 điểm</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
@@ -1535,12 +1560,12 @@
       </c>
       <c r="C22" s="63" t="inlineStr">
         <is>
-          <t>72,5%</t>
+          <t>85,5%</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>+24,3 điểm</t>
+          <t>+37,3 điểm</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
@@ -1564,12 +1589,12 @@
       </c>
       <c r="C23" s="63" t="inlineStr">
         <is>
-          <t>71,0%</t>
+          <t>84,9%</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>+17,6 điểm</t>
+          <t>+31,5 điểm</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -1593,12 +1618,12 @@
       </c>
       <c r="C24" s="63" t="inlineStr">
         <is>
-          <t>81,2%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>+16,1 điểm</t>
+          <t>+27,2 điểm</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
@@ -1658,7 +1683,7 @@
         </is>
       </c>
       <c r="C28" s="6" t="n">
-        <v>399</v>
+        <v>510</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>0</v>
@@ -1730,7 +1755,6 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="F21:H21"/>
     <mergeCell ref="F8:H8"/>
     <mergeCell ref="F17:H17"/>
     <mergeCell ref="F23:H23"/>
@@ -1739,6 +1763,7 @@
     <mergeCell ref="F13:H13"/>
     <mergeCell ref="F30:H30"/>
     <mergeCell ref="F9:H9"/>
+    <mergeCell ref="F15:H15"/>
     <mergeCell ref="A26:H26"/>
     <mergeCell ref="F14:H14"/>
     <mergeCell ref="A32:H32"/>
@@ -1751,7 +1776,7 @@
     <mergeCell ref="A19:H19"/>
     <mergeCell ref="F12:H12"/>
     <mergeCell ref="F7:H7"/>
-    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="F21:H21"/>
     <mergeCell ref="F24:H24"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9345,6 +9370,1973 @@
     <mergeCell ref="G13:H13"/>
     <mergeCell ref="G8:H8"/>
     <mergeCell ref="G9:H9"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="86" t="inlineStr">
+        <is>
+          <t>MA TRẬN TRUY VẾT — YÊU CẦU TRONG SRS ↔ KIỂM THỬ</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="36" customHeight="1">
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>Trả lời câu hỏi mà bảng độ bao phủ không trả lời được: yêu cầu nào trong đặc tả đã có test chạm tới, và chạm tới ở mức nào. Cột bao phủ là của các LỚP MÃ NGUỒN hiện thực yêu cầu đó, đo bằng bộ kiểm thử hộp trắng (target/site/jacoco-whitebox).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="87" t="inlineStr">
+        <is>
+          <t>BẢNG 1 — 26 YÊU CẦU CHỨC NĂNG</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Mã</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Yêu cầu</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Lớp mã nguồn hiện thực</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Lớp kiểm thử chạm tới</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Số test</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Bao phủ dòng</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="61" t="inlineStr">
+        <is>
+          <t>FR1.1</t>
+        </is>
+      </c>
+      <c r="B6" s="88" t="inlineStr">
+        <is>
+          <t>Hỏi đáp nghề nghiệp bằng ngôn ngữ tự nhiên
+(4 tiêu chí chấp nhận)</t>
+        </is>
+      </c>
+      <c r="C6" s="89" t="inlineStr">
+        <is>
+          <t>MentorService
+MentorController</t>
+        </is>
+      </c>
+      <c r="D6" s="89" t="inlineStr">
+        <is>
+          <t>MentorServiceTest
+MentorControllerTest</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>90,5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="61" t="inlineStr">
+        <is>
+          <t>FR1.2</t>
+        </is>
+      </c>
+      <c r="B7" s="88" t="inlineStr">
+        <is>
+          <t>Tích hợp mô hình ngôn ngữ lớn (retry + backoff)
+(2 tiêu chí chấp nhận)</t>
+        </is>
+      </c>
+      <c r="C7" s="89" t="inlineStr">
+        <is>
+          <t>LlmClient</t>
+        </is>
+      </c>
+      <c r="D7" s="89" t="inlineStr">
+        <is>
+          <t>LlmClientTest</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>93,5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" s="61" t="inlineStr">
+        <is>
+          <t>FR1.3</t>
+        </is>
+      </c>
+      <c r="B8" s="88" t="inlineStr">
+        <is>
+          <t>Cá nhân hoá theo bảng điểm và GitHub
+(3 tiêu chí chấp nhận)</t>
+        </is>
+      </c>
+      <c r="C8" s="89" t="inlineStr">
+        <is>
+          <t>TranscriptAnalysisService
+OnboardingService
+OnboardingController</t>
+        </is>
+      </c>
+      <c r="D8" s="89" t="inlineStr">
+        <is>
+          <t>TranscriptAnalysisServiceTest
+OnboardingServiceTest
+OnboardingControllerTest
+TranscriptFileDecisionTableTest
+OnboardingFileSizeBvaTest</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="61" t="inlineStr">
+        <is>
+          <t>FR2.1</t>
+        </is>
+      </c>
+      <c r="B9" s="88" t="inlineStr">
+        <is>
+          <t>Chọn vai trò nghề nghiệp mục tiêu
+(3 tiêu chí chấp nhận)</t>
+        </is>
+      </c>
+      <c r="C9" s="89" t="inlineStr">
+        <is>
+          <t>OnboardingController
+UserProfileService</t>
+        </is>
+      </c>
+      <c r="D9" s="89" t="inlineStr">
+        <is>
+          <t>OnboardingControllerTest
+UserProfileServiceTest
+OnboardingStateTransitionTest</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="61" t="inlineStr">
+        <is>
+          <t>FR2.2</t>
+        </is>
+      </c>
+      <c r="B10" s="88" t="inlineStr">
+        <is>
+          <t>Sinh Skill Tree phân cấp theo mức ưu tiên
+(4 tiêu chí chấp nhận)</t>
+        </is>
+      </c>
+      <c r="C10" s="89" t="inlineStr">
+        <is>
+          <t>RoadmapService
+RoadmapController
+RoadmapPageController</t>
+        </is>
+      </c>
+      <c r="D10" s="89" t="inlineStr">
+        <is>
+          <t>RoadmapServiceTest
+RoadmapControllerTest
+RoadmapPageControllerTest</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>41</v>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>98,7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="61" t="inlineStr">
+        <is>
+          <t>FR2.3</t>
+        </is>
+      </c>
+      <c r="B11" s="88" t="inlineStr">
+        <is>
+          <t>Mỗi node có tối thiểu 2 tài nguyên học
+(3 tiêu chí chấp nhận)</t>
+        </is>
+      </c>
+      <c r="C11" s="89" t="inlineStr">
+        <is>
+          <t>RoadmapService</t>
+        </is>
+      </c>
+      <c r="D11" s="89" t="inlineStr">
+        <is>
+          <t>RoadmapServiceTest</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="48" customHeight="1">
+      <c r="A12" s="61" t="inlineStr">
+        <is>
+          <t>FR2.4</t>
+        </is>
+      </c>
+      <c r="B12" s="88" t="inlineStr">
+        <is>
+          <t>Đánh dấu hoàn thành và cập nhật tiến độ
+(7 tiêu chí chấp nhận)</t>
+        </is>
+      </c>
+      <c r="C12" s="89" t="inlineStr">
+        <is>
+          <t>ProgressService
+RoadmapController</t>
+        </is>
+      </c>
+      <c r="D12" s="89" t="inlineStr">
+        <is>
+          <t>ProgressServiceTest
+RoadmapControllerTest
+ProgressDecisionTableTest
+ProgressStateTransitionTest</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>29</v>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="61" t="inlineStr">
+        <is>
+          <t>FR3.1</t>
+        </is>
+      </c>
+      <c r="B13" s="88" t="inlineStr">
+        <is>
+          <t>Nhập/chọn kỹ năng hiện có
+(3 tiêu chí chấp nhận)</t>
+        </is>
+      </c>
+      <c r="C13" s="89" t="inlineStr">
+        <is>
+          <t>OnboardingController
+UserProfileService</t>
+        </is>
+      </c>
+      <c r="D13" s="89" t="inlineStr">
+        <is>
+          <t>OnboardingControllerTest
+UserProfileServiceTest</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="61" t="inlineStr">
+        <is>
+          <t>FR3.2</t>
+        </is>
+      </c>
+      <c r="B14" s="88" t="inlineStr">
+        <is>
+          <t>So khớp kỹ năng với yêu cầu vai trò
+(6 tiêu chí chấp nhận)</t>
+        </is>
+      </c>
+      <c r="C14" s="89" t="inlineStr">
+        <is>
+          <t>SkillGapService
+SkillGapController</t>
+        </is>
+      </c>
+      <c r="D14" s="89" t="inlineStr">
+        <is>
+          <t>SkillGapServiceTest
+SkillGapControllerTest</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="36" customHeight="1">
+      <c r="A15" s="61" t="inlineStr">
+        <is>
+          <t>FR3.3</t>
+        </is>
+      </c>
+      <c r="B15" s="88" t="inlineStr">
+        <is>
+          <t>Báo cáo trực quan, xuất PDF, ưu tiên học gấp
+(5 tiêu chí chấp nhận)</t>
+        </is>
+      </c>
+      <c r="C15" s="89" t="inlineStr">
+        <is>
+          <t>PdfService
+SkillGapController
+SkillGapPageController</t>
+        </is>
+      </c>
+      <c r="D15" s="89" t="inlineStr">
+        <is>
+          <t>PdfServiceTest
+SkillGapControllerTest
+SkillGapPageControllerTest</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>95,0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="61" t="inlineStr">
+        <is>
+          <t>FR4.1</t>
+        </is>
+      </c>
+      <c r="B16" s="88" t="inlineStr">
+        <is>
+          <t>Thu thập tin tuyển dụng định kỳ
+(4 tiêu chí chấp nhận)</t>
+        </is>
+      </c>
+      <c r="C16" s="89" t="inlineStr">
+        <is>
+          <t>ScraperService</t>
+        </is>
+      </c>
+      <c r="D16" s="89" t="inlineStr">
+        <is>
+          <t>ScraperServiceTest</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>92,6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="61" t="inlineStr">
+        <is>
+          <t>FR4.2</t>
+        </is>
+      </c>
+      <c r="B17" s="88" t="inlineStr">
+        <is>
+          <t>Phân tích tần suất từ khoá
+(3 tiêu chí chấp nhận)</t>
+        </is>
+      </c>
+      <c r="C17" s="89" t="inlineStr">
+        <is>
+          <t>KeywordAnalysisService</t>
+        </is>
+      </c>
+      <c r="D17" s="89" t="inlineStr">
+        <is>
+          <t>KeywordAnalysisServiceTest</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="61" t="inlineStr">
+        <is>
+          <t>FR4.3</t>
+        </is>
+      </c>
+      <c r="B18" s="88" t="inlineStr">
+        <is>
+          <t>Biểu đồ xu hướng tương tác
+(2 tiêu chí chấp nhận)</t>
+        </is>
+      </c>
+      <c r="C18" s="89" t="inlineStr">
+        <is>
+          <t>MarketPulseService
+MarketPulseController</t>
+        </is>
+      </c>
+      <c r="D18" s="89" t="inlineStr">
+        <is>
+          <t>MarketPulseServiceTest
+MarketPulseControllerTest</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="61" t="inlineStr">
+        <is>
+          <t>FR5.1</t>
+        </is>
+      </c>
+      <c r="B19" s="88" t="inlineStr">
+        <is>
+          <t>Liên kết GitHub và đồng bộ repository
+(4 tiêu chí chấp nhận)</t>
+        </is>
+      </c>
+      <c r="C19" s="89" t="inlineStr">
+        <is>
+          <t>PortfolioService
+PortfolioController</t>
+        </is>
+      </c>
+      <c r="D19" s="89" t="inlineStr">
+        <is>
+          <t>PortfolioServiceTest
+PortfolioControllerTest</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>98,4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="61" t="inlineStr">
+        <is>
+          <t>FR5.2</t>
+        </is>
+      </c>
+      <c r="B20" s="88" t="inlineStr">
+        <is>
+          <t>Tóm tắt README bằng AI
+(3 tiêu chí chấp nhận)</t>
+        </is>
+      </c>
+      <c r="C20" s="89" t="inlineStr">
+        <is>
+          <t>PortfolioService</t>
+        </is>
+      </c>
+      <c r="D20" s="89" t="inlineStr">
+        <is>
+          <t>PortfolioServiceTest</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>98,0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="61" t="inlineStr">
+        <is>
+          <t>FR5.3</t>
+        </is>
+      </c>
+      <c r="B21" s="88" t="inlineStr">
+        <is>
+          <t>Chia sẻ hồ sơ qua URL công khai
+(5 tiêu chí chấp nhận)</t>
+        </is>
+      </c>
+      <c r="C21" s="89" t="inlineStr">
+        <is>
+          <t>PublicPortfolioController
+PortfolioController</t>
+        </is>
+      </c>
+      <c r="D21" s="89" t="inlineStr">
+        <is>
+          <t>PortfolioControllerTest</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="156" customHeight="1">
+      <c r="A22" s="61" t="inlineStr">
+        <is>
+          <t>FR6.1</t>
+        </is>
+      </c>
+      <c r="B22" s="88" t="inlineStr">
+        <is>
+          <t>Đăng ký, đăng nhập, khôi phục mật khẩu
+(9 tiêu chí chấp nhận)</t>
+        </is>
+      </c>
+      <c r="C22" s="89" t="inlineStr">
+        <is>
+          <t>AuthService
+AuthController
+PasswordResetService
+ProfileService
+ProfileController
+CustomUserDetailsService
+HomeController</t>
+        </is>
+      </c>
+      <c r="D22" s="89" t="inlineStr">
+        <is>
+          <t>AuthServiceTest
+AuthControllerTest
+PasswordResetServiceTest
+ProfileServiceTest
+ProfileControllerTest
+CustomUserDetailsServiceTest
+HomeControllerTest
+RegisterStandardBvaTest
+RegisterFormDTOBvaTest
+RegisterEquivalencePartitionTest
+RegisterTagCoverageTest
+TokenValidityDecisionTableTest
+TokenStateTransitionTest</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>143</v>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="61" t="inlineStr">
+        <is>
+          <t>FR6.2</t>
+        </is>
+      </c>
+      <c r="B23" s="88" t="inlineStr">
+        <is>
+          <t>Lưu lịch sử chat, đánh giá và tiến độ
+(3 tiêu chí chấp nhận)</t>
+        </is>
+      </c>
+      <c r="C23" s="89" t="inlineStr">
+        <is>
+          <t>DashboardService
+DashboardController
+ActivityLogService</t>
+        </is>
+      </c>
+      <c r="D23" s="89" t="inlineStr">
+        <is>
+          <t>DashboardServiceTest
+DashboardControllerTest
+ActivityLogServiceTest</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="61" t="inlineStr">
+        <is>
+          <t>FR6.3</t>
+        </is>
+      </c>
+      <c r="B24" s="88" t="inlineStr">
+        <is>
+          <t>Ép hoàn tất onboarding (quy tắc dẫn xuất)
+(3 tiêu chí chấp nhận)</t>
+        </is>
+      </c>
+      <c r="C24" s="89" t="inlineStr">
+        <is>
+          <t>OnboardingInterceptor</t>
+        </is>
+      </c>
+      <c r="D24" s="89" t="inlineStr">
+        <is>
+          <t>OnboardingInterceptorTest
+OnboardingControllerTest</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>49</v>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="61" t="inlineStr">
+        <is>
+          <t>FR7.1</t>
+        </is>
+      </c>
+      <c r="B25" s="88" t="inlineStr">
+        <is>
+          <t>Bảng điều khiển thống kê quản trị
+(1 tiêu chí chấp nhận)</t>
+        </is>
+      </c>
+      <c r="C25" s="89" t="inlineStr">
+        <is>
+          <t>AdminDashboardService
+AdminDashboardController</t>
+        </is>
+      </c>
+      <c r="D25" s="89" t="inlineStr">
+        <is>
+          <t>AdminDashboardServiceTest
+AdminDashboardControllerTest</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="36" customHeight="1">
+      <c r="A26" s="61" t="inlineStr">
+        <is>
+          <t>FR7.2</t>
+        </is>
+      </c>
+      <c r="B26" s="88" t="inlineStr">
+        <is>
+          <t>Danh sách và tìm kiếm người dùng
+(1 tiêu chí chấp nhận)</t>
+        </is>
+      </c>
+      <c r="C26" s="89" t="inlineStr">
+        <is>
+          <t>AdminUserService
+AdminUserController
+UserAdminMapper</t>
+        </is>
+      </c>
+      <c r="D26" s="89" t="inlineStr">
+        <is>
+          <t>AdminUserServiceTest
+AdminUserControllerTest
+UserAdminMapperTest</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>98,3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="61" t="inlineStr">
+        <is>
+          <t>FR7.3</t>
+        </is>
+      </c>
+      <c r="B27" s="88" t="inlineStr">
+        <is>
+          <t>Khoá/mở khoá, đổi vai trò, xoá người dùng
+(3 tiêu chí chấp nhận)</t>
+        </is>
+      </c>
+      <c r="C27" s="89" t="inlineStr">
+        <is>
+          <t>AdminUserService
+AdminUserController</t>
+        </is>
+      </c>
+      <c r="D27" s="89" t="inlineStr">
+        <is>
+          <t>AdminUserServiceTest
+AdminUserControllerTest</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="61" t="inlineStr">
+        <is>
+          <t>FR8.1</t>
+        </is>
+      </c>
+      <c r="B28" s="88" t="inlineStr">
+        <is>
+          <t>Tạo, sửa, xoá template lộ trình
+(1 tiêu chí chấp nhận)</t>
+        </is>
+      </c>
+      <c r="C28" s="89" t="inlineStr">
+        <is>
+          <t>CounselorTemplateService
+CounselorTemplateController</t>
+        </is>
+      </c>
+      <c r="D28" s="89" t="inlineStr">
+        <is>
+          <t>CounselorTemplateServiceTest
+CounselorTemplateControllerTest</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>56</v>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="61" t="inlineStr">
+        <is>
+          <t>FR8.2</t>
+        </is>
+      </c>
+      <c r="B29" s="88" t="inlineStr">
+        <is>
+          <t>Thêm/xoá node kỹ năng, đặt tầng và node cha
+(2 tiêu chí chấp nhận)</t>
+        </is>
+      </c>
+      <c r="C29" s="89" t="inlineStr">
+        <is>
+          <t>CounselorTemplateService
+CounselorTemplateController</t>
+        </is>
+      </c>
+      <c r="D29" s="89" t="inlineStr">
+        <is>
+          <t>CounselorTemplateServiceTest
+CounselorTemplateControllerTest</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="n">
+        <v>56</v>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="61" t="inlineStr">
+        <is>
+          <t>FR8.3</t>
+        </is>
+      </c>
+      <c r="B30" s="88" t="inlineStr">
+        <is>
+          <t>Gắn ≥ 2 tài liệu học cho mỗi node
+(1 tiêu chí chấp nhận)</t>
+        </is>
+      </c>
+      <c r="C30" s="89" t="inlineStr">
+        <is>
+          <t>CounselorTemplateService
+CounselorTemplateController</t>
+        </is>
+      </c>
+      <c r="D30" s="89" t="inlineStr">
+        <is>
+          <t>CounselorTemplateServiceTest
+CounselorTemplateControllerTest</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="n">
+        <v>56</v>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="61" t="inlineStr">
+        <is>
+          <t>FR8.4</t>
+        </is>
+      </c>
+      <c r="B31" s="88" t="inlineStr">
+        <is>
+          <t>Sắp xếp thứ tự ưu tiên node trong cùng tầng
+(1 tiêu chí chấp nhận)</t>
+        </is>
+      </c>
+      <c r="C31" s="89" t="inlineStr">
+        <is>
+          <t>CounselorTemplateService
+CounselorTemplateController</t>
+        </is>
+      </c>
+      <c r="D31" s="89" t="inlineStr">
+        <is>
+          <t>CounselorTemplateServiceTest
+CounselorTemplateControllerTest</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>56</v>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="90" t="inlineStr">
+        <is>
+          <t>TỔNG</t>
+        </is>
+      </c>
+      <c r="B32" s="90" t="inlineStr">
+        <is>
+          <t>26 yêu cầu chức năng · 86 tiêu chí chấp nhận</t>
+        </is>
+      </c>
+      <c r="C32" s="91" t="inlineStr"/>
+      <c r="D32" s="91" t="inlineStr"/>
+      <c r="E32" s="15" t="n">
+        <v>510</v>
+      </c>
+      <c r="F32" s="15" t="inlineStr">
+        <is>
+          <t>90,9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="34" customHeight="1">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t>CÁCH ĐỌC CỘT BAO PHỦ: xanh ≥ 90%, vàng 75–90%, đỏ &lt; 75%. Đây là bao phủ của các lớp hiện thực yêu cầu, KHÔNG phải tỉ lệ tiêu chí chấp nhận đã kiểm — một lớp phủ 100% dòng vẫn có thể bỏ sót một AC. Hai thước đo bổ sung cho nhau chứ không thay được nhau.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="24" customHeight="1">
+      <c r="A36" s="87" t="inlineStr">
+        <is>
+          <t>BẢNG 2 — 36 YÊU CẦU PHI CHỨC NĂNG</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="24" customHeight="1">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Mã</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>Yêu cầu</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>Cách kiểm chứng</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="n"/>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>Tầng kiểm thử</t>
+        </is>
+      </c>
+      <c r="F37" s="9" t="n"/>
+    </row>
+    <row r="38" ht="26" customHeight="1">
+      <c r="A38" s="61" t="inlineStr">
+        <is>
+          <t>NFR-P01</t>
+        </is>
+      </c>
+      <c r="B38" s="88" t="inlineStr">
+        <is>
+          <t>Trang nội bộ phản hồi &lt; 2 giây</t>
+        </is>
+      </c>
+      <c r="C38" s="89" t="inlineStr">
+        <is>
+          <t>Phép kiểm responseTime cấp collection</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="n"/>
+      <c r="E38" s="92" t="inlineStr">
+        <is>
+          <t>Postman</t>
+        </is>
+      </c>
+      <c r="F38" s="9" t="n"/>
+    </row>
+    <row r="39" ht="26" customHeight="1">
+      <c r="A39" s="61" t="inlineStr">
+        <is>
+          <t>NFR-P02</t>
+        </is>
+      </c>
+      <c r="B39" s="88" t="inlineStr">
+        <is>
+          <t>Endpoint gọi LLM &lt; 15 giây</t>
+        </is>
+      </c>
+      <c r="C39" s="89" t="inlineStr">
+        <is>
+          <t>TC-MEN-04</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="n"/>
+      <c r="E39" s="92" t="inlineStr">
+        <is>
+          <t>Postman</t>
+        </is>
+      </c>
+      <c r="F39" s="9" t="n"/>
+    </row>
+    <row r="40" ht="26" customHeight="1">
+      <c r="A40" s="61" t="inlineStr">
+        <is>
+          <t>NFR-P03</t>
+        </is>
+      </c>
+      <c r="B40" s="88" t="inlineStr">
+        <is>
+          <t>Đồng bộ GitHub &lt; 30 giây</t>
+        </is>
+      </c>
+      <c r="C40" s="89" t="inlineStr">
+        <is>
+          <t>TC-PF-02</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="n"/>
+      <c r="E40" s="92" t="inlineStr">
+        <is>
+          <t>Postman</t>
+        </is>
+      </c>
+      <c r="F40" s="9" t="n"/>
+    </row>
+    <row r="41" ht="26" customHeight="1">
+      <c r="A41" s="61" t="inlineStr">
+        <is>
+          <t>NFR-P04</t>
+        </is>
+      </c>
+      <c r="B41" s="88" t="inlineStr">
+        <is>
+          <t>Sinh và tải PDF &lt; 5 giây</t>
+        </is>
+      </c>
+      <c r="C41" s="89" t="inlineStr">
+        <is>
+          <t>TC-SG-09</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="n"/>
+      <c r="E41" s="92" t="inlineStr">
+        <is>
+          <t>Postman</t>
+        </is>
+      </c>
+      <c r="F41" s="9" t="n"/>
+    </row>
+    <row r="42" ht="26" customHeight="1">
+      <c r="A42" s="61" t="inlineStr">
+        <is>
+          <t>NFR-P05</t>
+        </is>
+      </c>
+      <c r="B42" s="88" t="inlineStr">
+        <is>
+          <t>Truy vấn roadmap không phát sinh N+1</t>
+        </is>
+      </c>
+      <c r="C42" s="89" t="inlineStr">
+        <is>
+          <t>Bật show-sql, đếm câu truy vấn</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="n"/>
+      <c r="E42" s="93" t="inlineStr">
+        <is>
+          <t>Thủ công</t>
+        </is>
+      </c>
+      <c r="F42" s="9" t="n"/>
+    </row>
+    <row r="43" ht="26" customHeight="1">
+      <c r="A43" s="61" t="inlineStr">
+        <is>
+          <t>NFR-P06</t>
+        </is>
+      </c>
+      <c r="B43" s="88" t="inlineStr">
+        <is>
+          <t>Cào dữ liệu nền không làm chậm request</t>
+        </is>
+      </c>
+      <c r="C43" s="89" t="inlineStr">
+        <is>
+          <t>Giám sát log khung 02:00</t>
+        </is>
+      </c>
+      <c r="D43" s="9" t="n"/>
+      <c r="E43" s="93" t="inlineStr">
+        <is>
+          <t>Thủ công</t>
+        </is>
+      </c>
+      <c r="F43" s="9" t="n"/>
+    </row>
+    <row r="44" ht="26" customHeight="1">
+      <c r="A44" s="61" t="inlineStr">
+        <is>
+          <t>NFR-S01</t>
+        </is>
+      </c>
+      <c r="B44" s="88" t="inlineStr">
+        <is>
+          <t>Tài nguyên ngoài danh sách công khai phải xác thực</t>
+        </is>
+      </c>
+      <c r="C44" s="89" t="inlineStr">
+        <is>
+          <t>TC-SEC-01, TC-SEC-02</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="n"/>
+      <c r="E44" s="92" t="inlineStr">
+        <is>
+          <t>Postman</t>
+        </is>
+      </c>
+      <c r="F44" s="9" t="n"/>
+    </row>
+    <row r="45" ht="26" customHeight="1">
+      <c r="A45" s="61" t="inlineStr">
+        <is>
+          <t>NFR-S02</t>
+        </is>
+      </c>
+      <c r="B45" s="88" t="inlineStr">
+        <is>
+          <t>Chống CSRF trên mọi request đổi trạng thái</t>
+        </is>
+      </c>
+      <c r="C45" s="89" t="inlineStr">
+        <is>
+          <t>TC-RM-07, TC-SEC-05</t>
+        </is>
+      </c>
+      <c r="D45" s="9" t="n"/>
+      <c r="E45" s="92" t="inlineStr">
+        <is>
+          <t>Postman</t>
+        </is>
+      </c>
+      <c r="F45" s="9" t="n"/>
+    </row>
+    <row r="46" ht="26" customHeight="1">
+      <c r="A46" s="61" t="inlineStr">
+        <is>
+          <t>NFR-S03</t>
+        </is>
+      </c>
+      <c r="B46" s="88" t="inlineStr">
+        <is>
+          <t>Phân quyền theo vai trò</t>
+        </is>
+      </c>
+      <c r="C46" s="89" t="inlineStr">
+        <is>
+          <t>TC-SEC-03, TC-SEC-04 · OnboardingInterceptorTest</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="n"/>
+      <c r="E46" s="92" t="inlineStr">
+        <is>
+          <t>Postman + JUnit</t>
+        </is>
+      </c>
+      <c r="F46" s="9" t="n"/>
+    </row>
+    <row r="47" ht="26" customHeight="1">
+      <c r="A47" s="61" t="inlineStr">
+        <is>
+          <t>NFR-S04</t>
+        </is>
+      </c>
+      <c r="B47" s="88" t="inlineStr">
+        <is>
+          <t>Chống SQL Injection nhờ JPA tham số hoá</t>
+        </is>
+      </c>
+      <c r="C47" s="89" t="inlineStr">
+        <is>
+          <t>TC-SEC-07</t>
+        </is>
+      </c>
+      <c r="D47" s="9" t="n"/>
+      <c r="E47" s="92" t="inlineStr">
+        <is>
+          <t>Postman</t>
+        </is>
+      </c>
+      <c r="F47" s="9" t="n"/>
+    </row>
+    <row r="48" ht="26" customHeight="1">
+      <c r="A48" s="61" t="inlineStr">
+        <is>
+          <t>NFR-S05</t>
+        </is>
+      </c>
+      <c r="B48" s="88" t="inlineStr">
+        <is>
+          <t>Không lộ stack trace / SQL trong phản hồi lỗi</t>
+        </is>
+      </c>
+      <c r="C48" s="89" t="inlineStr">
+        <is>
+          <t>Phép kiểm cấp collection cho mọi request · GlobalExceptionHandlerTest · PortfolioControllerTest (ràng buộc CSDL)</t>
+        </is>
+      </c>
+      <c r="D48" s="9" t="n"/>
+      <c r="E48" s="92" t="inlineStr">
+        <is>
+          <t>Postman + JUnit</t>
+        </is>
+      </c>
+      <c r="F48" s="9" t="n"/>
+    </row>
+    <row r="49" ht="26" customHeight="1">
+      <c r="A49" s="61" t="inlineStr">
+        <is>
+          <t>NFR-S06</t>
+        </is>
+      </c>
+      <c r="B49" s="88" t="inlineStr">
+        <is>
+          <t>Mật khẩu băm BCrypt, không lưu bản rõ</t>
+        </is>
+      </c>
+      <c r="C49" s="89" t="inlineStr">
+        <is>
+          <t>AuthServiceTest · kiểm tra trực tiếp CSDL</t>
+        </is>
+      </c>
+      <c r="D49" s="9" t="n"/>
+      <c r="E49" s="92" t="inlineStr">
+        <is>
+          <t>JUnit + Thủ công</t>
+        </is>
+      </c>
+      <c r="F49" s="9" t="n"/>
+    </row>
+    <row r="50" ht="26" customHeight="1">
+      <c r="A50" s="61" t="inlineStr">
+        <is>
+          <t>NFR-S07</t>
+        </is>
+      </c>
+      <c r="B50" s="88" t="inlineStr">
+        <is>
+          <t>Chống dò tài khoản qua quên mật khẩu</t>
+        </is>
+      </c>
+      <c r="C50" s="89" t="inlineStr">
+        <is>
+          <t>TC-AUTH-11, TC-AUTH-12 · PasswordResetServiceTest</t>
+        </is>
+      </c>
+      <c r="D50" s="9" t="n"/>
+      <c r="E50" s="92" t="inlineStr">
+        <is>
+          <t>Postman + JUnit</t>
+        </is>
+      </c>
+      <c r="F50" s="9" t="n"/>
+    </row>
+    <row r="51" ht="26" customHeight="1">
+      <c r="A51" s="61" t="inlineStr">
+        <is>
+          <t>NFR-S08</t>
+        </is>
+      </c>
+      <c r="B51" s="88" t="inlineStr">
+        <is>
+          <t>Cấp session mới sau đăng nhập</t>
+        </is>
+      </c>
+      <c r="C51" s="89" t="inlineStr">
+        <is>
+          <t>TC-AUTH-02</t>
+        </is>
+      </c>
+      <c r="D51" s="9" t="n"/>
+      <c r="E51" s="92" t="inlineStr">
+        <is>
+          <t>Postman</t>
+        </is>
+      </c>
+      <c r="F51" s="9" t="n"/>
+    </row>
+    <row r="52" ht="26" customHeight="1">
+      <c r="A52" s="61" t="inlineStr">
+        <is>
+          <t>NFR-S09</t>
+        </is>
+      </c>
+      <c r="B52" s="88" t="inlineStr">
+        <is>
+          <t>Bí mật nạp từ biến môi trường</t>
+        </is>
+      </c>
+      <c r="C52" s="89" t="inlineStr">
+        <is>
+          <t>Rà soát mã nguồn</t>
+        </is>
+      </c>
+      <c r="D52" s="9" t="n"/>
+      <c r="E52" s="93" t="inlineStr">
+        <is>
+          <t>Thủ công</t>
+        </is>
+      </c>
+      <c r="F52" s="9" t="n"/>
+    </row>
+    <row r="53" ht="26" customHeight="1">
+      <c r="A53" s="61" t="inlineStr">
+        <is>
+          <t>NFR-S10</t>
+        </is>
+      </c>
+      <c r="B53" s="88" t="inlineStr">
+        <is>
+          <t>Giới hạn dung lượng tệp, lưu ngoài thư mục tĩnh</t>
+        </is>
+      </c>
+      <c r="C53" s="89" t="inlineStr">
+        <is>
+          <t>OnboardingFileSizeBvaTest · TranscriptFileDecisionTableTest · OnboardingServiceTest</t>
+        </is>
+      </c>
+      <c r="D53" s="9" t="n"/>
+      <c r="E53" s="92" t="inlineStr">
+        <is>
+          <t>JUnit</t>
+        </is>
+      </c>
+      <c r="F53" s="9" t="n"/>
+    </row>
+    <row r="54" ht="26" customHeight="1">
+      <c r="A54" s="61" t="inlineStr">
+        <is>
+          <t>NFR-S11</t>
+        </is>
+      </c>
+      <c r="B54" s="88" t="inlineStr">
+        <is>
+          <t>Trang công khai không lộ dữ liệu nhạy cảm</t>
+        </is>
+      </c>
+      <c r="C54" s="89" t="inlineStr">
+        <is>
+          <t>AC-5.3.4 · PortfolioControllerTest</t>
+        </is>
+      </c>
+      <c r="D54" s="9" t="n"/>
+      <c r="E54" s="92" t="inlineStr">
+        <is>
+          <t>JUnit + Thủ công</t>
+        </is>
+      </c>
+      <c r="F54" s="9" t="n"/>
+    </row>
+    <row r="55" ht="26" customHeight="1">
+      <c r="A55" s="61" t="inlineStr">
+        <is>
+          <t>NFR-U01</t>
+        </is>
+      </c>
+      <c r="B55" s="88" t="inlineStr">
+        <is>
+          <t>Toàn bộ thông báo bằng tiếng Việt</t>
+        </is>
+      </c>
+      <c r="C55" s="89" t="inlineStr">
+        <is>
+          <t>Rà soát giao diện</t>
+        </is>
+      </c>
+      <c r="D55" s="9" t="n"/>
+      <c r="E55" s="93" t="inlineStr">
+        <is>
+          <t>Thủ công</t>
+        </is>
+      </c>
+      <c r="F55" s="9" t="n"/>
+    </row>
+    <row r="56" ht="26" customHeight="1">
+      <c r="A56" s="61" t="inlineStr">
+        <is>
+          <t>NFR-U02</t>
+        </is>
+      </c>
+      <c r="B56" s="88" t="inlineStr">
+        <is>
+          <t>Hoàn tất onboarding trong ≤ 3 phút</t>
+        </is>
+      </c>
+      <c r="C56" s="89" t="inlineStr">
+        <is>
+          <t>Đo trên CodeceptJS</t>
+        </is>
+      </c>
+      <c r="D56" s="9" t="n"/>
+      <c r="E56" s="92" t="inlineStr">
+        <is>
+          <t>CodeceptJS</t>
+        </is>
+      </c>
+      <c r="F56" s="9" t="n"/>
+    </row>
+    <row r="57" ht="26" customHeight="1">
+      <c r="A57" s="61" t="inlineStr">
+        <is>
+          <t>NFR-U03</t>
+        </is>
+      </c>
+      <c r="B57" s="88" t="inlineStr">
+        <is>
+          <t>Mọi trang chính ≤ 2 lần nhấp từ Dashboard</t>
+        </is>
+      </c>
+      <c r="C57" s="89" t="inlineStr">
+        <is>
+          <t>Rà soát điều hướng</t>
+        </is>
+      </c>
+      <c r="D57" s="9" t="n"/>
+      <c r="E57" s="93" t="inlineStr">
+        <is>
+          <t>Thủ công</t>
+        </is>
+      </c>
+      <c r="F57" s="9" t="n"/>
+    </row>
+    <row r="58" ht="26" customHeight="1">
+      <c r="A58" s="61" t="inlineStr">
+        <is>
+          <t>NFR-U04</t>
+        </is>
+      </c>
+      <c r="B58" s="88" t="inlineStr">
+        <is>
+          <t>Thao tác mất dữ liệu phải có xác nhận</t>
+        </is>
+      </c>
+      <c r="C58" s="89" t="inlineStr">
+        <is>
+          <t>TC-ADM-003 (CodeceptJS)</t>
+        </is>
+      </c>
+      <c r="D58" s="9" t="n"/>
+      <c r="E58" s="92" t="inlineStr">
+        <is>
+          <t>CodeceptJS</t>
+        </is>
+      </c>
+      <c r="F58" s="9" t="n"/>
+    </row>
+    <row r="59" ht="26" customHeight="1">
+      <c r="A59" s="61" t="inlineStr">
+        <is>
+          <t>NFR-U05</t>
+        </is>
+      </c>
+      <c r="B59" s="88" t="inlineStr">
+        <is>
+          <t>Hiển thị chỉ báo đang xử lý</t>
+        </is>
+      </c>
+      <c r="C59" s="89" t="inlineStr">
+        <is>
+          <t>Rà soát giao diện</t>
+        </is>
+      </c>
+      <c r="D59" s="9" t="n"/>
+      <c r="E59" s="93" t="inlineStr">
+        <is>
+          <t>Thủ công</t>
+        </is>
+      </c>
+      <c r="F59" s="9" t="n"/>
+    </row>
+    <row r="60" ht="26" customHeight="1">
+      <c r="A60" s="61" t="inlineStr">
+        <is>
+          <t>NFR-R01</t>
+        </is>
+      </c>
+      <c r="B60" s="88" t="inlineStr">
+        <is>
+          <t>Lỗi dịch vụ ngoài không làm hỏng nghiệp vụ chính</t>
+        </is>
+      </c>
+      <c r="C60" s="89" t="inlineStr">
+        <is>
+          <t>LlmClientTest · MentorServiceTest · PortfolioControllerTest</t>
+        </is>
+      </c>
+      <c r="D60" s="9" t="n"/>
+      <c r="E60" s="92" t="inlineStr">
+        <is>
+          <t>JUnit</t>
+        </is>
+      </c>
+      <c r="F60" s="9" t="n"/>
+    </row>
+    <row r="61" ht="26" customHeight="1">
+      <c r="A61" s="61" t="inlineStr">
+        <is>
+          <t>NFR-R02</t>
+        </is>
+      </c>
+      <c r="B61" s="88" t="inlineStr">
+        <is>
+          <t>Cào dữ liệu thất bại thì giữ dữ liệu cũ</t>
+        </is>
+      </c>
+      <c r="C61" s="89" t="inlineStr">
+        <is>
+          <t>ScraperServiceTest</t>
+        </is>
+      </c>
+      <c r="D61" s="9" t="n"/>
+      <c r="E61" s="92" t="inlineStr">
+        <is>
+          <t>JUnit</t>
+        </is>
+      </c>
+      <c r="F61" s="9" t="n"/>
+    </row>
+    <row r="62" ht="26" customHeight="1">
+      <c r="A62" s="61" t="inlineStr">
+        <is>
+          <t>NFR-R03</t>
+        </is>
+      </c>
+      <c r="B62" s="88" t="inlineStr">
+        <is>
+          <t>Không endpoint nào trả 500 với đầu vào sai</t>
+        </is>
+      </c>
+      <c r="C62" s="89" t="inlineStr">
+        <is>
+          <t>GlobalExceptionHandlerTest · bộ kiểm thử tiêu cực Postman</t>
+        </is>
+      </c>
+      <c r="D62" s="9" t="n"/>
+      <c r="E62" s="92" t="inlineStr">
+        <is>
+          <t>JUnit + Postman</t>
+        </is>
+      </c>
+      <c r="F62" s="9" t="n"/>
+    </row>
+    <row r="63" ht="26" customHeight="1">
+      <c r="A63" s="61" t="inlineStr">
+        <is>
+          <t>NFR-R04</t>
+        </is>
+      </c>
+      <c r="B63" s="88" t="inlineStr">
+        <is>
+          <t>Giao dịch ghi dữ liệu là nguyên tử</t>
+        </is>
+      </c>
+      <c r="C63" s="89" t="inlineStr">
+        <is>
+          <t>Kiểm thử tích hợp</t>
+        </is>
+      </c>
+      <c r="D63" s="9" t="n"/>
+      <c r="E63" s="93" t="inlineStr">
+        <is>
+          <t>Thủ công</t>
+        </is>
+      </c>
+      <c r="F63" s="9" t="n"/>
+    </row>
+    <row r="64" ht="26" customHeight="1">
+      <c r="A64" s="61" t="inlineStr">
+        <is>
+          <t>NFR-R05</t>
+        </is>
+      </c>
+      <c r="B64" s="88" t="inlineStr">
+        <is>
+          <t>Tỉ lệ sẵn sàng ≥ 99%</t>
+        </is>
+      </c>
+      <c r="C64" s="89" t="inlineStr">
+        <is>
+          <t>Nhật ký giám sát</t>
+        </is>
+      </c>
+      <c r="D64" s="9" t="n"/>
+      <c r="E64" s="93" t="inlineStr">
+        <is>
+          <t>Thủ công</t>
+        </is>
+      </c>
+      <c r="F64" s="9" t="n"/>
+    </row>
+    <row r="65" ht="26" customHeight="1">
+      <c r="A65" s="61" t="inlineStr">
+        <is>
+          <t>NFR-C01</t>
+        </is>
+      </c>
+      <c r="B65" s="88" t="inlineStr">
+        <is>
+          <t>Chạy đúng trên Chrome, Edge, Firefox</t>
+        </is>
+      </c>
+      <c r="C65" s="89" t="inlineStr">
+        <is>
+          <t>CodeceptJS chạy Chromium; còn lại thủ công</t>
+        </is>
+      </c>
+      <c r="D65" s="9" t="n"/>
+      <c r="E65" s="92" t="inlineStr">
+        <is>
+          <t>CodeceptJS + Thủ công</t>
+        </is>
+      </c>
+      <c r="F65" s="9" t="n"/>
+    </row>
+    <row r="66" ht="26" customHeight="1">
+      <c r="A66" s="61" t="inlineStr">
+        <is>
+          <t>NFR-C02</t>
+        </is>
+      </c>
+      <c r="B66" s="88" t="inlineStr">
+        <is>
+          <t>Bố cục đúng ở ≥ 1366×768</t>
+        </is>
+      </c>
+      <c r="C66" s="89" t="inlineStr">
+        <is>
+          <t>Rà soát giao diện</t>
+        </is>
+      </c>
+      <c r="D66" s="9" t="n"/>
+      <c r="E66" s="93" t="inlineStr">
+        <is>
+          <t>Thủ công</t>
+        </is>
+      </c>
+      <c r="F66" s="9" t="n"/>
+    </row>
+    <row r="67" ht="26" customHeight="1">
+      <c r="A67" s="61" t="inlineStr">
+        <is>
+          <t>NFR-C03</t>
+        </is>
+      </c>
+      <c r="B67" s="88" t="inlineStr">
+        <is>
+          <t>Tương thích MySQL 8.x</t>
+        </is>
+      </c>
+      <c r="C67" s="89" t="inlineStr">
+        <is>
+          <t>Chạy thật trên MySQL 8</t>
+        </is>
+      </c>
+      <c r="D67" s="9" t="n"/>
+      <c r="E67" s="93" t="inlineStr">
+        <is>
+          <t>Thủ công</t>
+        </is>
+      </c>
+      <c r="F67" s="9" t="n"/>
+    </row>
+    <row r="68" ht="26" customHeight="1">
+      <c r="A68" s="61" t="inlineStr">
+        <is>
+          <t>NFR-C04</t>
+        </is>
+      </c>
+      <c r="B68" s="88" t="inlineStr">
+        <is>
+          <t>API JSON dùng UTF-8, đủ tiếng Việt có dấu</t>
+        </is>
+      </c>
+      <c r="C68" s="89" t="inlineStr">
+        <is>
+          <t>Phép kiểm nội dung trong Postman</t>
+        </is>
+      </c>
+      <c r="D68" s="9" t="n"/>
+      <c r="E68" s="92" t="inlineStr">
+        <is>
+          <t>Postman</t>
+        </is>
+      </c>
+      <c r="F68" s="9" t="n"/>
+    </row>
+    <row r="69" ht="26" customHeight="1">
+      <c r="A69" s="61" t="inlineStr">
+        <is>
+          <t>NFR-M01</t>
+        </is>
+      </c>
+      <c r="B69" s="88" t="inlineStr">
+        <is>
+          <t>Mã nguồn tổ chức theo module nghiệp vụ</t>
+        </is>
+      </c>
+      <c r="C69" s="89" t="inlineStr">
+        <is>
+          <t>Rà soát cấu trúc thư mục</t>
+        </is>
+      </c>
+      <c r="D69" s="9" t="n"/>
+      <c r="E69" s="93" t="inlineStr">
+        <is>
+          <t>Thủ công</t>
+        </is>
+      </c>
+      <c r="F69" s="9" t="n"/>
+    </row>
+    <row r="70" ht="26" customHeight="1">
+      <c r="A70" s="61" t="inlineStr">
+        <is>
+          <t>NFR-M02</t>
+        </is>
+      </c>
+      <c r="B70" s="88" t="inlineStr">
+        <is>
+          <t>Tách bạch controller - service - repository</t>
+        </is>
+      </c>
+      <c r="C70" s="89" t="inlineStr">
+        <is>
+          <t>Rà soát mã nguồn</t>
+        </is>
+      </c>
+      <c r="D70" s="9" t="n"/>
+      <c r="E70" s="93" t="inlineStr">
+        <is>
+          <t>Thủ công</t>
+        </is>
+      </c>
+      <c r="F70" s="9" t="n"/>
+    </row>
+    <row r="71" ht="26" customHeight="1">
+      <c r="A71" s="61" t="inlineStr">
+        <is>
+          <t>NFR-M03</t>
+        </is>
+      </c>
+      <c r="B71" s="88" t="inlineStr">
+        <is>
+          <t>Tầng web dùng DTO, không phơi entity</t>
+        </is>
+      </c>
+      <c r="C71" s="89" t="inlineStr">
+        <is>
+          <t>UserAdminMapperTest · rà soát mã nguồn</t>
+        </is>
+      </c>
+      <c r="D71" s="9" t="n"/>
+      <c r="E71" s="92" t="inlineStr">
+        <is>
+          <t>JUnit + Thủ công</t>
+        </is>
+      </c>
+      <c r="F71" s="9" t="n"/>
+    </row>
+    <row r="72" ht="26" customHeight="1">
+      <c r="A72" s="61" t="inlineStr">
+        <is>
+          <t>NFR-M04</t>
+        </is>
+      </c>
+      <c r="B72" s="88" t="inlineStr">
+        <is>
+          <t>Cấu hình tập trung ở application.yml + biến môi trường</t>
+        </is>
+      </c>
+      <c r="C72" s="89" t="inlineStr">
+        <is>
+          <t>Rà soát mã nguồn</t>
+        </is>
+      </c>
+      <c r="D72" s="9" t="n"/>
+      <c r="E72" s="93" t="inlineStr">
+        <is>
+          <t>Thủ công</t>
+        </is>
+      </c>
+      <c r="F72" s="9" t="n"/>
+    </row>
+    <row r="73" ht="26" customHeight="1">
+      <c r="A73" s="61" t="inlineStr">
+        <is>
+          <t>NFR-M05</t>
+        </is>
+      </c>
+      <c r="B73" s="88" t="inlineStr">
+        <is>
+          <t>Bộ kiểm thử chạy được bằng Newman</t>
+        </is>
+      </c>
+      <c r="C73" s="89" t="inlineStr">
+        <is>
+          <t>newman run — 376 phép kiểm, 0 lỗi</t>
+        </is>
+      </c>
+      <c r="D73" s="9" t="n"/>
+      <c r="E73" s="92" t="inlineStr">
+        <is>
+          <t>Postman</t>
+        </is>
+      </c>
+      <c r="F73" s="9" t="n"/>
+    </row>
+    <row r="75" ht="44" customHeight="1">
+      <c r="A75" s="11" t="inlineStr">
+        <is>
+          <t>23/36 yêu cầu phi chức năng được kiểm bằng công cụ tự động (ô xanh); 13 còn lại phải rà soát thủ công (ô vàng) vì chúng nói về cấu trúc mã nguồn, giao diện hoặc vận hành — không có phép kiểm tự động nào khẳng định thay được. Ghi rõ ra đây để người chấm biết chỗ nào là bằng chứng máy đo và chỗ nào là cam kết của nhóm.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="80">
+    <mergeCell ref="C62:D62"/>
+    <mergeCell ref="E62:F62"/>
+    <mergeCell ref="E71:F71"/>
+    <mergeCell ref="A75:F75"/>
+    <mergeCell ref="C64:D64"/>
+    <mergeCell ref="E64:F64"/>
+    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="E73:F73"/>
+    <mergeCell ref="E51:F51"/>
+    <mergeCell ref="C54:D54"/>
+    <mergeCell ref="C63:D63"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="E63:F63"/>
+    <mergeCell ref="C50:D50"/>
+    <mergeCell ref="C56:D56"/>
+    <mergeCell ref="E65:F65"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="C67:D67"/>
+    <mergeCell ref="E53:F53"/>
+    <mergeCell ref="C69:D69"/>
+    <mergeCell ref="E55:F55"/>
+    <mergeCell ref="E67:F67"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="E48:F48"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="E38:F38"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="E40:F40"/>
+    <mergeCell ref="C60:D60"/>
+    <mergeCell ref="C71:D71"/>
+    <mergeCell ref="C57:D57"/>
+    <mergeCell ref="C66:D66"/>
+    <mergeCell ref="E66:F66"/>
+    <mergeCell ref="C53:D53"/>
+    <mergeCell ref="E58:F58"/>
+    <mergeCell ref="E50:F50"/>
+    <mergeCell ref="C68:D68"/>
+    <mergeCell ref="E68:F68"/>
+    <mergeCell ref="C58:D58"/>
+    <mergeCell ref="E52:F52"/>
+    <mergeCell ref="E39:F39"/>
+    <mergeCell ref="E44:F44"/>
+    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="E69:F69"/>
+    <mergeCell ref="C59:D59"/>
+    <mergeCell ref="E59:F59"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="E46:F46"/>
+    <mergeCell ref="C51:D51"/>
+    <mergeCell ref="C61:D61"/>
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="C70:D70"/>
+    <mergeCell ref="C48:D48"/>
+    <mergeCell ref="E70:F70"/>
+    <mergeCell ref="E57:F57"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="E54:F54"/>
+    <mergeCell ref="A36:F36"/>
+    <mergeCell ref="E72:F72"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="E41:F41"/>
+    <mergeCell ref="E56:F56"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="E43:F43"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="E42:F42"/>
+    <mergeCell ref="C55:D55"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="E60:F60"/>
+    <mergeCell ref="E45:F45"/>
+    <mergeCell ref="C52:D52"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="C72:D72"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="E37:F37"/>
+    <mergeCell ref="E47:F47"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BaoCao-KiemThu-CareerCompass.xlsx
+++ b/BaoCao-KiemThu-CareerCompass.xlsx
@@ -25,6 +25,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06. E2E - CodeceptJS" sheetId="16" state="visible" r:id="rId16"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07. Khiem khuyet" sheetId="17" state="visible" r:id="rId17"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08. Truy vet SRS" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09. Vi tri file test" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10. Ra soat BVA" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -34,7 +36,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="32">
+  <fonts count="34">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -188,8 +190,18 @@
       <color rgb="FFFFFFFF"/>
       <sz val="12"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00375623"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="16">
+  <fills count="18">
     <fill>
       <patternFill/>
     </fill>
@@ -266,8 +278,18 @@
         <fgColor rgb="00FFD7D7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE699"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="11">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -391,11 +413,44 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="111">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -659,6 +714,51 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1560,12 +1660,12 @@
       </c>
       <c r="C22" s="63" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>85,9%</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>+37,3 điểm</t>
+          <t>+37,7 điểm</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
@@ -1589,12 +1689,12 @@
       </c>
       <c r="C23" s="63" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>85,2%</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>+31,5 điểm</t>
+          <t>+31,8 điểm</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -1618,12 +1718,12 @@
       </c>
       <c r="C24" s="63" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>+27,2 điểm</t>
+          <t>+27,3 điểm</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
@@ -1683,7 +1783,7 @@
         </is>
       </c>
       <c r="C28" s="6" t="n">
-        <v>510</v>
+        <v>536</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>0</v>
@@ -1749,7 +1849,7 @@
     <row r="32" ht="24" customHeight="1">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t>Mười một khiếm khuyết được phát hiện và đều đã khắc phục kèm test hồi quy. Chi tiết ở sheet 07. Khiem khuyet.</t>
+          <t>Mười hai khiếm khuyết được phát hiện và đều đã khắc phục kèm test hồi quy. Chi tiết ở sheet 07. Khiem khuyet.</t>
         </is>
       </c>
     </row>
@@ -1758,8 +1858,8 @@
     <mergeCell ref="F8:H8"/>
     <mergeCell ref="F17:H17"/>
     <mergeCell ref="F23:H23"/>
+    <mergeCell ref="F28:H28"/>
     <mergeCell ref="F22:H22"/>
-    <mergeCell ref="F28:H28"/>
     <mergeCell ref="F13:H13"/>
     <mergeCell ref="F30:H30"/>
     <mergeCell ref="F9:H9"/>
@@ -8866,7 +8966,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -8929,7 +9029,7 @@
           <t>Cách khắc phục</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr"/>
+      <c r="H4" s="4" t="n"/>
     </row>
     <row r="5" ht="78" customHeight="1">
       <c r="A5" s="10" t="inlineStr">
@@ -9349,27 +9449,66 @@
       </c>
       <c r="H15" s="9" t="n"/>
     </row>
-    <row r="16" ht="44" customHeight="1">
-      <c r="A16" s="11" t="inlineStr">
-        <is>
-          <t>Cả mười một khiếm khuyết đã được khắc phục và có test hồi quy đi kèm. Ba khiếm khuyết DEF-001, DEF-009 và DEF-010 đều do KIỂM THỬ GIAO DIỆN tìm ra — đây là tầng duy nhất chạm tới HTML nên là tầng duy nhất thấy được chúng; suốt thời gian đó test đơn vị và test API vẫn xanh. DEF-011 đáng chú ý theo cách ngược lại: test hộp trắng đã GHI ĐÚNG nguyên nhân từ trước nhưng lại chốt luôn hành vi lỗi bằng một khẳng định, nên bộ test vẫn xanh và khiếm khuyết nằm im. Phải tới khi dựng bảng quyết định — nơi mỗi cột buộc phải có một hành động xác định — nó mới bị buộc phải sửa.</t>
+    <row r="16" ht="78" customHeight="1">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>DEF-013</t>
+        </is>
+      </c>
+      <c r="B16" s="17" t="inlineStr">
+        <is>
+          <t>Trung bình</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Biên độ dài mật khẩu không nhất quán giữa ba đường đặt mật khẩu, và đo sai đơn vị. Đăng ký dựa vào @Size(min = 6, max = 30) đếm KÝ TỰ; đặt lại và đổi mật khẩu chỉ kiểm length() &lt; 6, KHÔNG có giới hạn trên. Trong khi đó BCrypt giới hạn 72 BYTE và ném IllegalArgumentException khi vượt — mật khẩu 25 ký tự tiếng Việt có dấu là 75 byte, lọt qua kiểm tra hợp lệ rồi vỡ ở tầng mã hoá.</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Giá trị biên — rà soát toàn hệ thống (sheet 10)</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>Ba hậu quả tái hiện được: đăng ký trả 400 kèm nguyên văn tiếng Anh "password cannot be more than 72 bytes" (vi phạm NFR-U01); đặt lại mật khẩu báo SAI rằng "link đã hết hạn" nên người dùng xin link mới mãi không xong; đổi mật khẩu cũng lộ thông điệp tiếng Anh. NFR-R03 vẫn đạt vì GlobalExceptionHandler đổi thành 400 chứ không phải 500.</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>ĐÃ SỬA</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>Gom cả hai biên vào PasswordPolicy dùng chung cho ba đường, trả thông điệp tiếng Việt. PasswordPolicyBvaTest phủ 5 điểm chuẩn theo ký tự, 2 điểm Robustness, và biên 72 byte — biên mà mọi mật khẩu ASCII đều không bao giờ chạm tới nên ẩn rất lâu.</t>
+        </is>
+      </c>
+      <c r="H16" s="9" t="n"/>
+    </row>
+    <row r="17" ht="44" customHeight="1">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>Cả 12 khiếm khuyết đã được khắc phục và có test hồi quy đi kèm. Ba khiếm khuyết DEF-001, DEF-009 và DEF-010 đều do KIỂM THỬ GIAO DIỆN tìm ra — đây là tầng duy nhất chạm tới HTML nên là tầng duy nhất thấy được chúng; suốt thời gian đó test đơn vị và test API vẫn xanh. DEF-011 đáng chú ý theo cách ngược lại: test hộp trắng đã GHI ĐÚNG nguyên nhân từ trước nhưng lại chốt luôn hành vi lỗi bằng một khẳng định, nên bộ test vẫn xanh và khiếm khuyết nằm im. Phải tới khi dựng bảng quyết định — nơi mỗi cột buộc phải có một hành động xác định — nó mới bị buộc phải sửa. DEF-013 thì cho thấy giới hạn của chính phép phân tích biên: nhóm đã áp BVA cho mật khẩu từ đầu, nhưng đo bằng KÝ TỰ trong khi biên thật của BCrypt tính bằng BYTE. Áp đúng kỹ thuật mà sai đơn vị đo thì vẫn lọt. VỀ SỐ HIỆU BỊ NHẢY: DEF-012 có thật và không bị bỏ quên — AdminUserService.deleteUser chỉ dọn 2 trong 6 bảng đang tham chiếu tới người dùng, thiếu skill_gap_reports, user_node_progress, mentor_sessions và password_reset_tokens, nên việc xoá thất bại TRONG IM LẶNG. Nhóm quyết định chưa sửa trong kỳ này vì phải đụng tới thứ tự xoá của bốn bảng, và bảng này theo quy ước chỉ liệt kê khiếm khuyết ĐÃ khắc phục kèm test hồi quy.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="13">
     <mergeCell ref="G12:H12"/>
     <mergeCell ref="G7:H7"/>
+    <mergeCell ref="G16:H16"/>
     <mergeCell ref="G15:H15"/>
-    <mergeCell ref="A16:H16"/>
+    <mergeCell ref="G10:H10"/>
     <mergeCell ref="G11:H11"/>
-    <mergeCell ref="G10:H10"/>
     <mergeCell ref="G5:H5"/>
     <mergeCell ref="G14:H14"/>
     <mergeCell ref="G6:H6"/>
     <mergeCell ref="G13:H13"/>
     <mergeCell ref="G8:H8"/>
     <mergeCell ref="G9:H9"/>
+    <mergeCell ref="A17:H17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9807,7 +9946,7 @@
         </is>
       </c>
       <c r="E16" s="6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
@@ -10020,7 +10159,7 @@
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>98,8%</t>
         </is>
       </c>
     </row>
@@ -10338,11 +10477,11 @@
       <c r="C32" s="91" t="inlineStr"/>
       <c r="D32" s="91" t="inlineStr"/>
       <c r="E32" s="15" t="n">
-        <v>510</v>
+        <v>536</v>
       </c>
       <c r="F32" s="15" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>90,7%</t>
         </is>
       </c>
     </row>
@@ -11342,6 +11481,1730 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F77"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="86" t="inlineStr">
+        <is>
+          <t>VỊ TRÍ TỆP KIỂM THỬ THEO TỪNG YÊU CẦU CHỨC NĂNG</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="38" customHeight="1">
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>Mỗi dòng là một lớp kiểm thử: mở đúng đường dẫn ở cột 3 là thấy mã nguồn. Cột phương pháp ghi kỹ thuật thiết kế test case đã dùng — ô vàng là kỹ thuật hộp đen (suy từ đặc tả), ô xanh là kỹ thuật hộp trắng (nhắm vào mã nguồn). Cột cuối dẫn sang mã ca kiểm thử tương ứng trong bộ Postman.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="65" t="inlineStr">
+        <is>
+          <t>Mã FR</t>
+        </is>
+      </c>
+      <c r="B4" s="65" t="inlineStr">
+        <is>
+          <t>Yêu cầu</t>
+        </is>
+      </c>
+      <c r="C4" s="65" t="inlineStr">
+        <is>
+          <t>Đường dẫn tệp kiểm thử</t>
+        </is>
+      </c>
+      <c r="D4" s="65" t="inlineStr">
+        <is>
+          <t>Phương pháp</t>
+        </is>
+      </c>
+      <c r="E4" s="65" t="inlineStr">
+        <is>
+          <t>Số test</t>
+        </is>
+      </c>
+      <c r="F4" s="65" t="inlineStr">
+        <is>
+          <t>Ca kiểm thử API</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="79" t="inlineStr">
+        <is>
+          <t>FR1.1</t>
+        </is>
+      </c>
+      <c r="B5" s="66" t="inlineStr">
+        <is>
+          <t>Hỏi đáp nghề nghiệp bằng ngôn ngữ tự nhiên</t>
+        </is>
+      </c>
+      <c r="C5" s="80" t="inlineStr">
+        <is>
+          <t>src/test/java/vn/uth/careercompass/mentor/service/MentorServiceTest.java</t>
+        </is>
+      </c>
+      <c r="D5" s="94" t="inlineStr">
+        <is>
+          <t>Kiểm thử đơn vị (mock)</t>
+        </is>
+      </c>
+      <c r="E5" s="67" t="n">
+        <v>10</v>
+      </c>
+      <c r="F5" s="80" t="inlineStr">
+        <is>
+          <t>TC-MEN-01 → TC-MEN-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="100" t="n"/>
+      <c r="B6" s="100" t="n"/>
+      <c r="C6" s="80" t="inlineStr">
+        <is>
+          <t>src/test/java/vn/uth/careercompass/mentor/controller/MentorControllerTest.java</t>
+        </is>
+      </c>
+      <c r="D6" s="94" t="inlineStr">
+        <is>
+          <t>Lát cắt web (@WebMvcTest)</t>
+        </is>
+      </c>
+      <c r="E6" s="67" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" s="100" t="n"/>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="79" t="inlineStr">
+        <is>
+          <t>FR1.2</t>
+        </is>
+      </c>
+      <c r="B7" s="66" t="inlineStr">
+        <is>
+          <t>Tích hợp mô hình ngôn ngữ lớn (thử lại + backoff)</t>
+        </is>
+      </c>
+      <c r="C7" s="80" t="inlineStr">
+        <is>
+          <t>src/test/java/vn/uth/careercompass/mentor/service/LlmClientTest.java</t>
+        </is>
+      </c>
+      <c r="D7" s="94" t="inlineStr">
+        <is>
+          <t>Kiểm thử đơn vị (mock)</t>
+        </is>
+      </c>
+      <c r="E7" s="67" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" s="80" t="inlineStr">
+        <is>
+          <t>TC-MEN-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="79" t="inlineStr">
+        <is>
+          <t>FR1.3</t>
+        </is>
+      </c>
+      <c r="B8" s="66" t="inlineStr">
+        <is>
+          <t>Cá nhân hoá theo bảng điểm và GitHub</t>
+        </is>
+      </c>
+      <c r="C8" s="80" t="inlineStr">
+        <is>
+          <t>src/test/java/vn/uth/careercompass/bva/OnboardingFileSizeBvaTest.java</t>
+        </is>
+      </c>
+      <c r="D8" s="72" t="inlineStr">
+        <is>
+          <t>Giá trị biên (BVA)</t>
+        </is>
+      </c>
+      <c r="E8" s="67" t="n">
+        <v>6</v>
+      </c>
+      <c r="F8" s="80" t="inlineStr">
+        <is>
+          <t>TC-ONB-05, TC-PR-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="101" t="n"/>
+      <c r="B9" s="101" t="n"/>
+      <c r="C9" s="80" t="inlineStr">
+        <is>
+          <t>src/test/java/vn/uth/careercompass/blackbox/TranscriptFileDecisionTableTest.java</t>
+        </is>
+      </c>
+      <c r="D9" s="72" t="inlineStr">
+        <is>
+          <t>Bảng quyết định</t>
+        </is>
+      </c>
+      <c r="E9" s="67" t="n">
+        <v>9</v>
+      </c>
+      <c r="F9" s="101" t="n"/>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="101" t="n"/>
+      <c r="B10" s="101" t="n"/>
+      <c r="C10" s="80" t="inlineStr">
+        <is>
+          <t>src/test/java/vn/uth/careercompass/onboarding/service/OnboardingServiceTest.java</t>
+        </is>
+      </c>
+      <c r="D10" s="94" t="inlineStr">
+        <is>
+          <t>Kiểm thử đơn vị (mock)</t>
+        </is>
+      </c>
+      <c r="E10" s="67" t="n">
+        <v>7</v>
+      </c>
+      <c r="F10" s="101" t="n"/>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="101" t="n"/>
+      <c r="B11" s="101" t="n"/>
+      <c r="C11" s="80" t="inlineStr">
+        <is>
+          <t>src/test/java/vn/uth/careercompass/onboarding/service/TranscriptAnalysisServiceTest.java</t>
+        </is>
+      </c>
+      <c r="D11" s="94" t="inlineStr">
+        <is>
+          <t>Kiểm thử đơn vị (mock)</t>
+        </is>
+      </c>
+      <c r="E11" s="67" t="n">
+        <v>5</v>
+      </c>
+      <c r="F11" s="101" t="n"/>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="100" t="n"/>
+      <c r="B12" s="100" t="n"/>
+      <c r="C12" s="80" t="inlineStr">
+        <is>
+          <t>src/test/java/vn/uth/careercompass/onboarding/controller/OnboardingControllerTest.java</t>
+        </is>
+      </c>
+      <c r="D12" s="94" t="inlineStr">
+        <is>
+          <t>Lát cắt web (@WebMvcTest)</t>
+        </is>
+      </c>
+      <c r="E12" s="67" t="n">
+        <v>23</v>
+      </c>
+      <c r="F12" s="100" t="n"/>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="79" t="inlineStr">
+        <is>
+          <t>FR2.1</t>
+        </is>
+      </c>
+      <c r="B13" s="66" t="inlineStr">
+        <is>
+          <t>Chọn vai trò nghề nghiệp mục tiêu</t>
+        </is>
+      </c>
+      <c r="C13" s="80" t="inlineStr">
+        <is>
+          <t>src/test/java/vn/uth/careercompass/blackbox/OnboardingStateTransitionTest.java</t>
+        </is>
+      </c>
+      <c r="D13" s="72" t="inlineStr">
+        <is>
+          <t>Chuyển đổi trạng thái</t>
+        </is>
+      </c>
+      <c r="E13" s="67" t="n">
+        <v>12</v>
+      </c>
+      <c r="F13" s="80" t="inlineStr">
+        <is>
+          <t>TC-ONB-01 → TC-ONB-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="101" t="n"/>
+      <c r="B14" s="101" t="n"/>
+      <c r="C14" s="80" t="inlineStr">
+        <is>
+          <t>src/test/java/vn/uth/careercompass/onboarding/controller/OnboardingControllerTest.java</t>
+        </is>
+      </c>
+      <c r="D14" s="94" t="inlineStr">
+        <is>
+          <t>Lát cắt web (@WebMvcTest)</t>
+        </is>
+      </c>
+      <c r="E14" s="67" t="n">
+        <v>23</v>
+      </c>
+      <c r="F14" s="101" t="n"/>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="100" t="n"/>
+      <c r="B15" s="100" t="n"/>
+      <c r="C15" s="80" t="inlineStr">
+        <is>
+          <t>src/test/java/vn/uth/careercompass/kernel/service/UserProfileServiceTest.java</t>
+        </is>
+      </c>
+      <c r="D15" s="94" t="inlineStr">
+        <is>
+          <t>Kiểm thử đơn vị (mock)</t>
+        </is>
+      </c>
+      <c r="E15" s="67" t="n">
+        <v>7</v>
+      </c>
+      <c r="F15" s="100" t="n"/>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="79" t="inlineStr">
+        <is>
+          <t>FR2.2</t>
+        </is>
+      </c>
+      <c r="B16" s="66" t="inlineStr">
+        <is>
+          <t>Sinh Skill Tree phân cấp theo mức ưu tiên</t>
+        </is>
+      </c>
+      <c r="C16" s="80" t="inlineStr">
+        <is>
+          <t>src/test/java/vn/uth/careercompass/roadmap/service/RoadmapServiceTest.java</t>
+        </is>
+      </c>
+      <c r="D16" s="94" t="inlineStr">
+        <is>
+          <t>Kiểm thử đơn vị (mock)</t>
+        </is>
+      </c>
+      <c r="E16" s="67" t="n">
+        <v>28</v>
+      </c>
+      <c r="F16" s="80" t="inlineStr">
+        <is>
+          <t>TC-RM-01, TC-RM-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="101" t="n"/>
+      <c r="B17" s="101" t="n"/>
+      <c r="C17" s="80" t="inlineStr">
+        <is>
+          <t>src/test/java/vn/uth/careercompass/roadmap/controller/RoadmapControllerTest.java</t>
+        </is>
+      </c>
+      <c r="D17" s="94" t="inlineStr">
+        <is>
+          <t>Lát cắt web (@WebMvcTest)</t>
+        </is>
+      </c>
+      <c r="E17" s="67" t="n">
+        <v>7</v>
+      </c>
+      <c r="F17" s="101" t="n"/>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="100" t="n"/>
+      <c r="B18" s="100" t="n"/>
+      <c r="C18" s="80" t="inlineStr">
+        <is>
+          <t>src/test/java/vn/uth/careercompass/roadmap/controller/RoadmapPageControllerTest.java</t>
+        </is>
+      </c>
+      <c r="D18" s="94" t="inlineStr">
+        <is>
+          <t>Lát cắt web (@WebMvcTest)</t>
+        </is>
+      </c>
+      <c r="E18" s="67" t="n">
+        <v>6</v>
+      </c>
+      <c r="F18" s="100" t="n"/>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="79" t="inlineStr">
+        <is>
+          <t>FR2.3</t>
+        </is>
+      </c>
+      <c r="B19" s="66" t="inlineStr">
+        <is>
+          <t>Mỗi node có tối thiểu 2 tài nguyên học</t>
+        </is>
+      </c>
+      <c r="C19" s="80" t="inlineStr">
+        <is>
+          <t>src/test/java/vn/uth/careercompass/roadmap/service/RoadmapServiceTest.java</t>
+        </is>
+      </c>
+      <c r="D19" s="94" t="inlineStr">
+        <is>
+          <t>Kiểm thử đơn vị (mock)</t>
+        </is>
+      </c>
+      <c r="E19" s="67" t="n">
+        <v>28</v>
+      </c>
+      <c r="F19" s="80" t="inlineStr">
+        <is>
+          <t>TC-RM-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="79" t="inlineStr">
+        <is>
+          <t>FR2.4</t>
+        </is>
+      </c>
+      <c r="B20" s="66" t="inlineStr">
+        <is>
+          <t>Đánh dấu hoàn thành và cập nhật tiến độ</t>
+        </is>
+      </c>
+      <c r="C20" s="80" t="inlineStr">
+        <is>
+          <t>src/test/java/vn/uth/careercompass/blackbox/ProgressDecisionTableTest.java</t>
+        </is>
+      </c>
+      <c r="D20" s="72" t="inlineStr">
+        <is>
+          <t>Bảng quyết định</t>
+        </is>
+      </c>
+      <c r="E20" s="67" t="n">
+        <v>6</v>
+      </c>
+      <c r="F20" s="80" t="inlineStr">
+        <is>
+          <t>TC-RM-03 → TC-RM-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="101" t="n"/>
+      <c r="B21" s="101" t="n"/>
+      <c r="C21" s="80" t="inlineStr">
+        <is>
+          <t>src/test/java/vn/uth/careercompass/blackbox/ProgressStateTransitionTest.java</t>
+        </is>
+      </c>
+      <c r="D21" s="72" t="inlineStr">
+        <is>
+          <t>Chuyển đổi trạng thái</t>
+        </is>
+      </c>
+      <c r="E21" s="67" t="n">
+        <v>9</v>
+      </c>
+      <c r="F21" s="101" t="n"/>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="101" t="n"/>
+      <c r="B22" s="101" t="n"/>
+      <c r="C22" s="80" t="inlineStr">
+        <is>
+          <t>src/test/java/vn/uth/careercompass/roadmap/service/ProgressServiceTest.java</t>
+        </is>
+      </c>
+      <c r="D22" s="94" t="inlineStr">
+        <is>
+          <t>Kiểm thử đơn vị (mock)</t>
+        </is>
+      </c>
+      <c r="E22" s="67" t="n">
+        <v>7</v>
+      </c>
+      <c r="F22" s="101" t="n"/>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="100" t="n"/>
+      <c r="B23" s="100" t="n"/>
+      <c r="C23" s="80" t="inlineStr">
+        <is>
+          <t>src/test/java/vn/uth/careercompass/roadmap/controller/RoadmapControllerTest.java</t>
+        </is>
+      </c>
+      <c r="D23" s="94" t="inlineStr">
+        <is>
+          <t>Lát cắt web (@WebMvcTest)</t>
+        </is>
+      </c>
+      <c r="E23" s="67" t="n">
+        <v>7</v>
+      </c>
+      <c r="F23" s="100" t="n"/>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="79" t="inlineStr">
+        <is>
+          <t>FR3.1</t>
+        </is>
+      </c>
+      <c r="B24" s="66" t="inlineStr">
+        <is>
+          <t>Nhập/chọn kỹ năng hiện có</t>
+        </is>
+      </c>
+      <c r="C24" s="80" t="inlineStr">
+        <is>
+          <t>src/test/java/vn/uth/careercompass/onboarding/controller/OnboardingControllerTest.java</t>
+        </is>
+      </c>
+      <c r="D24" s="94" t="inlineStr">
+        <is>
+          <t>Lát cắt web (@WebMvcTest)</t>
+        </is>
+      </c>
+      <c r="E24" s="67" t="n">
+        <v>23</v>
+      </c>
+      <c r="F24" s="80" t="inlineStr">
+        <is>
+          <t>TC-ONB-06, TC-SG-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="100" t="n"/>
+      <c r="B25" s="100" t="n"/>
+      <c r="C25" s="80" t="inlineStr">
+        <is>
+          <t>src/test/java/vn/uth/careercompass/kernel/service/UserProfileServiceTest.java</t>
+        </is>
+      </c>
+      <c r="D25" s="94" t="inlineStr">
+        <is>
+          <t>Kiểm thử đơn vị (mock)</t>
+        </is>
+      </c>
+      <c r="E25" s="67" t="n">
+        <v>7</v>
+      </c>
+      <c r="F25" s="100" t="n"/>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="79" t="inlineStr">
+        <is>
+          <t>FR3.2</t>
+        </is>
+      </c>
+      <c r="B26" s="66" t="inlineStr">
+        <is>
+          <t>So khớp kỹ năng với yêu cầu vai trò</t>
+        </is>
+      </c>
+      <c r="C26" s="80" t="inlineStr">
+        <is>
+          <t>src/test/java/vn/uth/careercompass/roadmap/service/SkillGapServiceTest.java</t>
+        </is>
+      </c>
+      <c r="D26" s="94" t="inlineStr">
+        <is>
+          <t>Kiểm thử đơn vị (mock)</t>
+        </is>
+      </c>
+      <c r="E26" s="67" t="n">
+        <v>11</v>
+      </c>
+      <c r="F26" s="80" t="inlineStr">
+        <is>
+          <t>TC-SG-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="100" t="n"/>
+      <c r="B27" s="100" t="n"/>
+      <c r="C27" s="80" t="inlineStr">
+        <is>
+          <t>src/test/java/vn/uth/careercompass/roadmap/controller/SkillGapControllerTest.java</t>
+        </is>
+      </c>
+      <c r="D27" s="94" t="inlineStr">
+        <is>
+          <t>Lát cắt web (@WebMvcTest)</t>
+        </is>
+      </c>
+      <c r="E27" s="67" t="n">
+        <v>8</v>
+      </c>
+      <c r="F27" s="100" t="n"/>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="79" t="inlineStr">
+        <is>
+          <t>FR3.3</t>
+        </is>
+      </c>
+      <c r="B28" s="66" t="inlineStr">
+        <is>
+          <t>Báo cáo trực quan, xuất PDF, ưu tiên học gấp</t>
+        </is>
+      </c>
+      <c r="C28" s="80" t="inlineStr">
+        <is>
+          <t>src/test/java/vn/uth/careercompass/roadmap/service/PdfServiceTest.java</t>
+        </is>
+      </c>
+      <c r="D28" s="94" t="inlineStr">
+        <is>
+          <t>Kiểm thử đơn vị (mock)</t>
+        </is>
+      </c>
+      <c r="E28" s="67" t="n">
+        <v>5</v>
+      </c>
+      <c r="F28" s="80" t="inlineStr">
+        <is>
+          <t>TC-SG-03 → TC-SG-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="101" t="n"/>
+      <c r="B29" s="101" t="n"/>
+      <c r="C29" s="80" t="inlineStr">
+        <is>
+          <t>src/test/java/vn/uth/careercompass/roadmap/controller/SkillGapControllerTest.java</t>
+        </is>
+      </c>
+      <c r="D29" s="94" t="inlineStr">
+        <is>
+          <t>Lát cắt web (@WebMvcTest)</t>
+        </is>
+      </c>
+      <c r="E29" s="67" t="n">
+        <v>8</v>
+      </c>
+      <c r="F29" s="101" t="n"/>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="100" t="n"/>
+      <c r="B30" s="100" t="n"/>
+      <c r="C30" s="80" t="inlineStr">
+        <is>
+          <t>src/test/java/vn/uth/careercompass/roadmap/controller/SkillGapPageControllerTest.java</t>
+        </is>
+      </c>
+      <c r="D30" s="94" t="inlineStr">
+        <is>
+          <t>Lát cắt web (@WebMvcTest)</t>
+        </is>
+      </c>
+      <c r="E30" s="67" t="n">
+        <v>7</v>
+      </c>
+      <c r="F30" s="100" t="n"/>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="79" t="inlineStr">
+        <is>
+          <t>FR4.1</t>
+        </is>
+      </c>
+      <c r="B31" s="66" t="inlineStr">
+        <is>
+          <t>Thu thập tin tuyển dụng định kỳ</t>
+        </is>
+      </c>
+      <c r="C31" s="80" t="inlineStr">
+        <is>
+          <t>src/test/java/vn/uth/careercompass/marketpulse/service/ScraperServiceTest.java</t>
+        </is>
+      </c>
+      <c r="D31" s="96" t="inlineStr">
+        <is>
+          <t>Giá trị biên (BVA) + Kiểm thử đơn vị (mock)</t>
+        </is>
+      </c>
+      <c r="E31" s="67" t="n">
+        <v>8</v>
+      </c>
+      <c r="F31" s="80" t="inlineStr">
+        <is>
+          <t>TC-MP-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="79" t="inlineStr">
+        <is>
+          <t>FR4.2</t>
+        </is>
+      </c>
+      <c r="B32" s="66" t="inlineStr">
+        <is>
+          <t>Phân tích tần suất từ khoá</t>
+        </is>
+      </c>
+      <c r="C32" s="80" t="inlineStr">
+        <is>
+          <t>src/test/java/vn/uth/careercompass/marketpulse/service/KeywordAnalysisServiceTest.java</t>
+        </is>
+      </c>
+      <c r="D32" s="94" t="inlineStr">
+        <is>
+          <t>Kiểm thử đơn vị (mock)</t>
+        </is>
+      </c>
+      <c r="E32" s="67" t="n">
+        <v>7</v>
+      </c>
+      <c r="F32" s="80" t="inlineStr">
+        <is>
+          <t>TC-MP-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="79" t="inlineStr">
+        <is>
+          <t>FR4.3</t>
+        </is>
+      </c>
+      <c r="B33" s="66" t="inlineStr">
+        <is>
+          <t>Biểu đồ xu hướng tương tác</t>
+        </is>
+      </c>
+      <c r="C33" s="80" t="inlineStr">
+        <is>
+          <t>src/test/java/vn/uth/careercompass/marketpulse/service/MarketPulseServiceTest.java</t>
+        </is>
+      </c>
+      <c r="D33" s="94" t="inlineStr">
+        <is>
+          <t>Kiểm thử đơn vị (mock)</t>
+        </is>
+      </c>
+      <c r="E33" s="67" t="n">
+        <v>3</v>
+      </c>
+      <c r="F33" s="80" t="inlineStr">
+        <is>
+          <t>TC-MP-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="100" t="n"/>
+      <c r="B34" s="100" t="n"/>
+      <c r="C34" s="80" t="inlineStr">
+        <is>
+          <t>src/test/java/vn/uth/careercompass/marketpulse/controller/MarketPulseControllerTest.java</t>
+        </is>
+      </c>
+      <c r="D34" s="94" t="inlineStr">
+        <is>
+          <t>Lát cắt web (@WebMvcTest)</t>
+        </is>
+      </c>
+      <c r="E34" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" s="100" t="n"/>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="79" t="inlineStr">
+        <is>
+          <t>FR5.1</t>
+        </is>
+      </c>
+      <c r="B35" s="66" t="inlineStr">
+        <is>
+          <t>Liên kết GitHub và đồng bộ repository</t>
+        </is>
+      </c>
+      <c r="C35" s="80" t="inlineStr">
+        <is>
+          <t>src/test/java/vn/uth/careercompass/portfolio/service/PortfolioServiceTest.java</t>
+        </is>
+      </c>
+      <c r="D35" s="94" t="inlineStr">
+        <is>
+          <t>Kiểm thử đơn vị (mock)</t>
+        </is>
+      </c>
+      <c r="E35" s="67" t="n">
+        <v>22</v>
+      </c>
+      <c r="F35" s="80" t="inlineStr">
+        <is>
+          <t>TC-PF-01, TC-PF-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="100" t="n"/>
+      <c r="B36" s="100" t="n"/>
+      <c r="C36" s="80" t="inlineStr">
+        <is>
+          <t>src/test/java/vn/uth/careercompass/portfolio/controller/PortfolioControllerTest.java</t>
+        </is>
+      </c>
+      <c r="D36" s="94" t="inlineStr">
+        <is>
+          <t>Lát cắt web (@WebMvcTest)</t>
+        </is>
+      </c>
+      <c r="E36" s="67" t="n">
+        <v>8</v>
+      </c>
+      <c r="F36" s="100" t="n"/>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="79" t="inlineStr">
+        <is>
+          <t>FR5.2</t>
+        </is>
+      </c>
+      <c r="B37" s="66" t="inlineStr">
+        <is>
+          <t>Tóm tắt README bằng AI</t>
+        </is>
+      </c>
+      <c r="C37" s="80" t="inlineStr">
+        <is>
+          <t>src/test/java/vn/uth/careercompass/portfolio/service/PortfolioServiceTest.java</t>
+        </is>
+      </c>
+      <c r="D37" s="94" t="inlineStr">
+        <is>
+          <t>Kiểm thử đơn vị (mock)</t>
+        </is>
+      </c>
+      <c r="E37" s="67" t="n">
+        <v>22</v>
+      </c>
+      <c r="F37" s="80" t="inlineStr">
+        <is>
+          <t>TC-PF-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="79" t="inlineStr">
+        <is>
+          <t>FR5.3</t>
+        </is>
+      </c>
+      <c r="B38" s="66" t="inlineStr">
+        <is>
+          <t>Chia sẻ hồ sơ qua URL công khai</t>
+        </is>
+      </c>
+      <c r="C38" s="80" t="inlineStr">
+        <is>
+          <t>src/test/java/vn/uth/careercompass/portfolio/controller/PortfolioControllerTest.java</t>
+        </is>
+      </c>
+      <c r="D38" s="94" t="inlineStr">
+        <is>
+          <t>Lát cắt web (@WebMvcTest)</t>
+        </is>
+      </c>
+      <c r="E38" s="67" t="n">
+        <v>8</v>
+      </c>
+      <c r="F38" s="80" t="inlineStr">
+        <is>
+          <t>TC-PF-04, TC-SEC-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="79" t="inlineStr">
+        <is>
+          <t>FR6.1</t>
+        </is>
+      </c>
+      <c r="B39" s="66" t="inlineStr">
+        <is>
+          <t>Đăng ký, đăng nhập, khôi phục mật khẩu</t>
+        </is>
+      </c>
+      <c r="C39" s="80" t="inlineStr">
+        <is>
+          <t>src/test/java/vn/uth/careercompass/blackbox/RegisterStandardBvaTest.java</t>
+        </is>
+      </c>
+      <c r="D39" s="72" t="inlineStr">
+        <is>
+          <t>Giá trị biên (BVA)</t>
+        </is>
+      </c>
+      <c r="E39" s="67" t="n">
+        <v>19</v>
+      </c>
+      <c r="F39" s="80" t="inlineStr">
+        <is>
+          <t>TC-AUTH-01 → TC-AUTH-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="101" t="n"/>
+      <c r="B40" s="101" t="n"/>
+      <c r="C40" s="80" t="inlineStr">
+        <is>
+          <t>src/test/java/vn/uth/careercompass/bva/RegisterFormDTOBvaTest.java</t>
+        </is>
+      </c>
+      <c r="D40" s="72" t="inlineStr">
+        <is>
+          <t>Giá trị biên (BVA)</t>
+        </is>
+      </c>
+      <c r="E40" s="67" t="n">
+        <v>27</v>
+      </c>
+      <c r="F40" s="101" t="n"/>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="101" t="n"/>
+      <c r="B41" s="101" t="n"/>
+      <c r="C41" s="80" t="inlineStr">
+        <is>
+          <t>src/test/java/vn/uth/careercompass/bva/PasswordPolicyBvaTest.java</t>
+        </is>
+      </c>
+      <c r="D41" s="72" t="inlineStr">
+        <is>
+          <t>Giá trị biên (BVA)</t>
+        </is>
+      </c>
+      <c r="E41" s="67" t="n">
+        <v>15</v>
+      </c>
+      <c r="F41" s="101" t="n"/>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="101" t="n"/>
+      <c r="B42" s="101" t="n"/>
+      <c r="C42" s="80" t="inlineStr">
+        <is>
+          <t>src/test/java/vn/uth/careercompass/bva/TokenExpiryBvaTest.java</t>
+        </is>
+      </c>
+      <c r="D42" s="72" t="inlineStr">
+        <is>
+          <t>Giá trị biên (BVA)</t>
+        </is>
+      </c>
+      <c r="E42" s="67" t="n">
+        <v>8</v>
+      </c>
+      <c r="F42" s="101" t="n"/>
+    </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="101" t="n"/>
+      <c r="B43" s="101" t="n"/>
+      <c r="C43" s="80" t="inlineStr">
+        <is>
+          <t>src/test/java/vn/uth/careercompass/blackbox/RegisterEquivalencePartitionTest.java</t>
+        </is>
+      </c>
+      <c r="D43" s="72" t="inlineStr">
+        <is>
+          <t>Phân hoạch lớp tương đương</t>
+        </is>
+      </c>
+      <c r="E43" s="67" t="n">
+        <v>14</v>
+      </c>
+      <c r="F43" s="101" t="n"/>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="A44" s="101" t="n"/>
+      <c r="B44" s="101" t="n"/>
+      <c r="C44" s="80" t="inlineStr">
+        <is>
+          <t>src/test/java/vn/uth/careercompass/blackbox/RegisterTagCoverageTest.java</t>
+        </is>
+      </c>
+      <c r="D44" s="72" t="inlineStr">
+        <is>
+          <t>Gộp tag thành test case</t>
+        </is>
+      </c>
+      <c r="E44" s="67" t="n">
+        <v>17</v>
+      </c>
+      <c r="F44" s="101" t="n"/>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="A45" s="101" t="n"/>
+      <c r="B45" s="101" t="n"/>
+      <c r="C45" s="80" t="inlineStr">
+        <is>
+          <t>src/test/java/vn/uth/careercompass/blackbox/TokenValidityDecisionTableTest.java</t>
+        </is>
+      </c>
+      <c r="D45" s="72" t="inlineStr">
+        <is>
+          <t>Bảng quyết định</t>
+        </is>
+      </c>
+      <c r="E45" s="67" t="n">
+        <v>4</v>
+      </c>
+      <c r="F45" s="101" t="n"/>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="A46" s="101" t="n"/>
+      <c r="B46" s="101" t="n"/>
+      <c r="C46" s="80" t="inlineStr">
+        <is>
+          <t>src/test/java/vn/uth/careercompass/blackbox/TokenStateTransitionTest.java</t>
+        </is>
+      </c>
+      <c r="D46" s="72" t="inlineStr">
+        <is>
+          <t>Chuyển đổi trạng thái</t>
+        </is>
+      </c>
+      <c r="E46" s="67" t="n">
+        <v>7</v>
+      </c>
+      <c r="F46" s="101" t="n"/>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="A47" s="101" t="n"/>
+      <c r="B47" s="101" t="n"/>
+      <c r="C47" s="80" t="inlineStr">
+        <is>
+          <t>src/test/java/vn/uth/careercompass/kernel/service/AuthServiceTest.java</t>
+        </is>
+      </c>
+      <c r="D47" s="94" t="inlineStr">
+        <is>
+          <t>Kiểm thử đơn vị (mock)</t>
+        </is>
+      </c>
+      <c r="E47" s="67" t="n">
+        <v>3</v>
+      </c>
+      <c r="F47" s="101" t="n"/>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="A48" s="101" t="n"/>
+      <c r="B48" s="101" t="n"/>
+      <c r="C48" s="80" t="inlineStr">
+        <is>
+          <t>src/test/java/vn/uth/careercompass/kernel/service/PasswordResetServiceTest.java</t>
+        </is>
+      </c>
+      <c r="D48" s="94" t="inlineStr">
+        <is>
+          <t>Kiểm thử đơn vị (mock)</t>
+        </is>
+      </c>
+      <c r="E48" s="67" t="n">
+        <v>8</v>
+      </c>
+      <c r="F48" s="101" t="n"/>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="A49" s="101" t="n"/>
+      <c r="B49" s="101" t="n"/>
+      <c r="C49" s="80" t="inlineStr">
+        <is>
+          <t>src/test/java/vn/uth/careercompass/profile/service/ProfileServiceTest.java</t>
+        </is>
+      </c>
+      <c r="D49" s="94" t="inlineStr">
+        <is>
+          <t>Kiểm thử đơn vị (mock)</t>
+        </is>
+      </c>
+      <c r="E49" s="67" t="n">
+        <v>14</v>
+      </c>
+      <c r="F49" s="101" t="n"/>
+    </row>
+    <row r="50" ht="18" customHeight="1">
+      <c r="A50" s="101" t="n"/>
+      <c r="B50" s="101" t="n"/>
+      <c r="C50" s="80" t="inlineStr">
+        <is>
+          <t>src/test/java/vn/uth/careercompass/kernel/service/CustomUserDetailsServiceTest.java</t>
+        </is>
+      </c>
+      <c r="D50" s="94" t="inlineStr">
+        <is>
+          <t>Kiểm thử đơn vị (mock)</t>
+        </is>
+      </c>
+      <c r="E50" s="67" t="n">
+        <v>2</v>
+      </c>
+      <c r="F50" s="101" t="n"/>
+    </row>
+    <row r="51" ht="18" customHeight="1">
+      <c r="A51" s="101" t="n"/>
+      <c r="B51" s="101" t="n"/>
+      <c r="C51" s="80" t="inlineStr">
+        <is>
+          <t>src/test/java/vn/uth/careercompass/kernel/web/controller/AuthControllerTest.java</t>
+        </is>
+      </c>
+      <c r="D51" s="94" t="inlineStr">
+        <is>
+          <t>Lát cắt web (@WebMvcTest)</t>
+        </is>
+      </c>
+      <c r="E51" s="67" t="n">
+        <v>13</v>
+      </c>
+      <c r="F51" s="101" t="n"/>
+    </row>
+    <row r="52" ht="18" customHeight="1">
+      <c r="A52" s="101" t="n"/>
+      <c r="B52" s="101" t="n"/>
+      <c r="C52" s="80" t="inlineStr">
+        <is>
+          <t>src/test/java/vn/uth/careercompass/kernel/web/controller/HomeControllerTest.java</t>
+        </is>
+      </c>
+      <c r="D52" s="94" t="inlineStr">
+        <is>
+          <t>Lát cắt web (@WebMvcTest)</t>
+        </is>
+      </c>
+      <c r="E52" s="67" t="n">
+        <v>5</v>
+      </c>
+      <c r="F52" s="101" t="n"/>
+    </row>
+    <row r="53" ht="18" customHeight="1">
+      <c r="A53" s="100" t="n"/>
+      <c r="B53" s="100" t="n"/>
+      <c r="C53" s="80" t="inlineStr">
+        <is>
+          <t>src/test/java/vn/uth/careercompass/profile/controller/ProfileControllerTest.java</t>
+        </is>
+      </c>
+      <c r="D53" s="94" t="inlineStr">
+        <is>
+          <t>Lát cắt web (@WebMvcTest)</t>
+        </is>
+      </c>
+      <c r="E53" s="67" t="n">
+        <v>10</v>
+      </c>
+      <c r="F53" s="100" t="n"/>
+    </row>
+    <row r="54" ht="18" customHeight="1">
+      <c r="A54" s="79" t="inlineStr">
+        <is>
+          <t>FR6.2</t>
+        </is>
+      </c>
+      <c r="B54" s="66" t="inlineStr">
+        <is>
+          <t>Lưu lịch sử chat, đánh giá và tiến độ</t>
+        </is>
+      </c>
+      <c r="C54" s="80" t="inlineStr">
+        <is>
+          <t>src/test/java/vn/uth/careercompass/dashboard/service/DashboardServiceTest.java</t>
+        </is>
+      </c>
+      <c r="D54" s="94" t="inlineStr">
+        <is>
+          <t>Kiểm thử đơn vị (mock)</t>
+        </is>
+      </c>
+      <c r="E54" s="67" t="n">
+        <v>2</v>
+      </c>
+      <c r="F54" s="80" t="inlineStr">
+        <is>
+          <t>TC-DASH-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="18" customHeight="1">
+      <c r="A55" s="101" t="n"/>
+      <c r="B55" s="101" t="n"/>
+      <c r="C55" s="80" t="inlineStr">
+        <is>
+          <t>src/test/java/vn/uth/careercompass/dashboard/controller/DashboardControllerTest.java</t>
+        </is>
+      </c>
+      <c r="D55" s="94" t="inlineStr">
+        <is>
+          <t>Lát cắt web (@WebMvcTest)</t>
+        </is>
+      </c>
+      <c r="E55" s="67" t="n">
+        <v>2</v>
+      </c>
+      <c r="F55" s="101" t="n"/>
+    </row>
+    <row r="56" ht="18" customHeight="1">
+      <c r="A56" s="100" t="n"/>
+      <c r="B56" s="100" t="n"/>
+      <c r="C56" s="80" t="inlineStr">
+        <is>
+          <t>src/test/java/vn/uth/careercompass/kernel/service/ActivityLogServiceTest.java</t>
+        </is>
+      </c>
+      <c r="D56" s="94" t="inlineStr">
+        <is>
+          <t>Kiểm thử đơn vị (mock)</t>
+        </is>
+      </c>
+      <c r="E56" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="F56" s="100" t="n"/>
+    </row>
+    <row r="57" ht="18" customHeight="1">
+      <c r="A57" s="79" t="inlineStr">
+        <is>
+          <t>FR6.3</t>
+        </is>
+      </c>
+      <c r="B57" s="66" t="inlineStr">
+        <is>
+          <t>Ép hoàn tất onboarding (quy tắc dẫn xuất)</t>
+        </is>
+      </c>
+      <c r="C57" s="80" t="inlineStr">
+        <is>
+          <t>src/test/java/vn/uth/careercompass/config/OnboardingInterceptorTest.java</t>
+        </is>
+      </c>
+      <c r="D57" s="94" t="inlineStr">
+        <is>
+          <t>Kiểm thử đơn vị (mock)</t>
+        </is>
+      </c>
+      <c r="E57" s="67" t="n">
+        <v>26</v>
+      </c>
+      <c r="F57" s="80" t="inlineStr">
+        <is>
+          <t>TC-ONB-01, TC-SEC-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="18" customHeight="1">
+      <c r="A58" s="100" t="n"/>
+      <c r="B58" s="100" t="n"/>
+      <c r="C58" s="80" t="inlineStr">
+        <is>
+          <t>src/test/java/vn/uth/careercompass/onboarding/controller/OnboardingControllerTest.java</t>
+        </is>
+      </c>
+      <c r="D58" s="94" t="inlineStr">
+        <is>
+          <t>Lát cắt web (@WebMvcTest)</t>
+        </is>
+      </c>
+      <c r="E58" s="67" t="n">
+        <v>23</v>
+      </c>
+      <c r="F58" s="100" t="n"/>
+    </row>
+    <row r="59" ht="18" customHeight="1">
+      <c r="A59" s="79" t="inlineStr">
+        <is>
+          <t>FR7.1</t>
+        </is>
+      </c>
+      <c r="B59" s="66" t="inlineStr">
+        <is>
+          <t>Bảng điều khiển thống kê quản trị</t>
+        </is>
+      </c>
+      <c r="C59" s="80" t="inlineStr">
+        <is>
+          <t>src/test/java/vn/uth/careercompass/admin/service/AdminDashboardServiceTest.java</t>
+        </is>
+      </c>
+      <c r="D59" s="94" t="inlineStr">
+        <is>
+          <t>Kiểm thử đơn vị (mock)</t>
+        </is>
+      </c>
+      <c r="E59" s="67" t="n">
+        <v>3</v>
+      </c>
+      <c r="F59" s="80" t="inlineStr">
+        <is>
+          <t>TC-AD-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="18" customHeight="1">
+      <c r="A60" s="100" t="n"/>
+      <c r="B60" s="100" t="n"/>
+      <c r="C60" s="80" t="inlineStr">
+        <is>
+          <t>src/test/java/vn/uth/careercompass/admin/web/AdminDashboardControllerTest.java</t>
+        </is>
+      </c>
+      <c r="D60" s="94" t="inlineStr">
+        <is>
+          <t>Lát cắt web (@WebMvcTest)</t>
+        </is>
+      </c>
+      <c r="E60" s="67" t="n">
+        <v>3</v>
+      </c>
+      <c r="F60" s="100" t="n"/>
+    </row>
+    <row r="61" ht="18" customHeight="1">
+      <c r="A61" s="79" t="inlineStr">
+        <is>
+          <t>FR7.2</t>
+        </is>
+      </c>
+      <c r="B61" s="66" t="inlineStr">
+        <is>
+          <t>Danh sách và tìm kiếm người dùng</t>
+        </is>
+      </c>
+      <c r="C61" s="80" t="inlineStr">
+        <is>
+          <t>src/test/java/vn/uth/careercompass/admin/service/AdminUserServiceTest.java</t>
+        </is>
+      </c>
+      <c r="D61" s="94" t="inlineStr">
+        <is>
+          <t>Kiểm thử đơn vị (mock)</t>
+        </is>
+      </c>
+      <c r="E61" s="67" t="n">
+        <v>14</v>
+      </c>
+      <c r="F61" s="80" t="inlineStr">
+        <is>
+          <t>TC-AD-02, TC-AD-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="18" customHeight="1">
+      <c r="A62" s="101" t="n"/>
+      <c r="B62" s="101" t="n"/>
+      <c r="C62" s="80" t="inlineStr">
+        <is>
+          <t>src/test/java/vn/uth/careercompass/admin/web/AdminUserControllerTest.java</t>
+        </is>
+      </c>
+      <c r="D62" s="94" t="inlineStr">
+        <is>
+          <t>Lát cắt web (@WebMvcTest)</t>
+        </is>
+      </c>
+      <c r="E62" s="67" t="n">
+        <v>8</v>
+      </c>
+      <c r="F62" s="101" t="n"/>
+    </row>
+    <row r="63" ht="18" customHeight="1">
+      <c r="A63" s="100" t="n"/>
+      <c r="B63" s="100" t="n"/>
+      <c r="C63" s="80" t="inlineStr">
+        <is>
+          <t>src/test/java/vn/uth/careercompass/admin/mapper/UserAdminMapperTest.java</t>
+        </is>
+      </c>
+      <c r="D63" s="94" t="inlineStr">
+        <is>
+          <t>Kiểm thử đơn vị (mock)</t>
+        </is>
+      </c>
+      <c r="E63" s="67" t="n">
+        <v>5</v>
+      </c>
+      <c r="F63" s="100" t="n"/>
+    </row>
+    <row r="64" ht="18" customHeight="1">
+      <c r="A64" s="79" t="inlineStr">
+        <is>
+          <t>FR7.3</t>
+        </is>
+      </c>
+      <c r="B64" s="66" t="inlineStr">
+        <is>
+          <t>Khoá/mở khoá, đổi vai trò, xoá người dùng</t>
+        </is>
+      </c>
+      <c r="C64" s="80" t="inlineStr">
+        <is>
+          <t>src/test/java/vn/uth/careercompass/admin/service/AdminUserServiceTest.java</t>
+        </is>
+      </c>
+      <c r="D64" s="94" t="inlineStr">
+        <is>
+          <t>Kiểm thử đơn vị (mock)</t>
+        </is>
+      </c>
+      <c r="E64" s="67" t="n">
+        <v>14</v>
+      </c>
+      <c r="F64" s="80" t="inlineStr">
+        <is>
+          <t>TC-AD-04 → TC-AD-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="18" customHeight="1">
+      <c r="A65" s="100" t="n"/>
+      <c r="B65" s="100" t="n"/>
+      <c r="C65" s="80" t="inlineStr">
+        <is>
+          <t>src/test/java/vn/uth/careercompass/admin/web/AdminUserControllerTest.java</t>
+        </is>
+      </c>
+      <c r="D65" s="94" t="inlineStr">
+        <is>
+          <t>Lát cắt web (@WebMvcTest)</t>
+        </is>
+      </c>
+      <c r="E65" s="67" t="n">
+        <v>8</v>
+      </c>
+      <c r="F65" s="100" t="n"/>
+    </row>
+    <row r="66" ht="18" customHeight="1">
+      <c r="A66" s="79" t="inlineStr">
+        <is>
+          <t>FR8.1</t>
+        </is>
+      </c>
+      <c r="B66" s="66" t="inlineStr">
+        <is>
+          <t>Tạo, sửa, xoá template lộ trình</t>
+        </is>
+      </c>
+      <c r="C66" s="80" t="inlineStr">
+        <is>
+          <t>src/test/java/vn/uth/careercompass/admin/service/CounselorTemplateServiceTest.java</t>
+        </is>
+      </c>
+      <c r="D66" s="94" t="inlineStr">
+        <is>
+          <t>Kiểm thử đơn vị (mock)</t>
+        </is>
+      </c>
+      <c r="E66" s="67" t="n">
+        <v>37</v>
+      </c>
+      <c r="F66" s="80" t="inlineStr">
+        <is>
+          <t>TC-CS-01 → TC-CS-03, TC-CS-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="18" customHeight="1">
+      <c r="A67" s="100" t="n"/>
+      <c r="B67" s="100" t="n"/>
+      <c r="C67" s="80" t="inlineStr">
+        <is>
+          <t>src/test/java/vn/uth/careercompass/admin/web/CounselorTemplateControllerTest.java</t>
+        </is>
+      </c>
+      <c r="D67" s="94" t="inlineStr">
+        <is>
+          <t>Lát cắt web (@WebMvcTest)</t>
+        </is>
+      </c>
+      <c r="E67" s="67" t="n">
+        <v>19</v>
+      </c>
+      <c r="F67" s="100" t="n"/>
+    </row>
+    <row r="68" ht="18" customHeight="1">
+      <c r="A68" s="79" t="inlineStr">
+        <is>
+          <t>FR8.2</t>
+        </is>
+      </c>
+      <c r="B68" s="66" t="inlineStr">
+        <is>
+          <t>Thêm/xoá node kỹ năng, đặt tầng và node cha</t>
+        </is>
+      </c>
+      <c r="C68" s="80" t="inlineStr">
+        <is>
+          <t>src/test/java/vn/uth/careercompass/admin/service/CounselorTemplateServiceTest.java</t>
+        </is>
+      </c>
+      <c r="D68" s="94" t="inlineStr">
+        <is>
+          <t>Kiểm thử đơn vị (mock)</t>
+        </is>
+      </c>
+      <c r="E68" s="67" t="n">
+        <v>37</v>
+      </c>
+      <c r="F68" s="80" t="inlineStr">
+        <is>
+          <t>TC-CS-05, TC-CS-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="18" customHeight="1">
+      <c r="A69" s="100" t="n"/>
+      <c r="B69" s="100" t="n"/>
+      <c r="C69" s="80" t="inlineStr">
+        <is>
+          <t>src/test/java/vn/uth/careercompass/admin/web/CounselorTemplateControllerTest.java</t>
+        </is>
+      </c>
+      <c r="D69" s="94" t="inlineStr">
+        <is>
+          <t>Lát cắt web (@WebMvcTest)</t>
+        </is>
+      </c>
+      <c r="E69" s="67" t="n">
+        <v>19</v>
+      </c>
+      <c r="F69" s="100" t="n"/>
+    </row>
+    <row r="70" ht="18" customHeight="1">
+      <c r="A70" s="79" t="inlineStr">
+        <is>
+          <t>FR8.3</t>
+        </is>
+      </c>
+      <c r="B70" s="66" t="inlineStr">
+        <is>
+          <t>Gắn ≥ 2 tài liệu học cho mỗi node</t>
+        </is>
+      </c>
+      <c r="C70" s="80" t="inlineStr">
+        <is>
+          <t>src/test/java/vn/uth/careercompass/admin/service/CounselorTemplateServiceTest.java</t>
+        </is>
+      </c>
+      <c r="D70" s="94" t="inlineStr">
+        <is>
+          <t>Kiểm thử đơn vị (mock)</t>
+        </is>
+      </c>
+      <c r="E70" s="67" t="n">
+        <v>37</v>
+      </c>
+      <c r="F70" s="80" t="inlineStr">
+        <is>
+          <t>TC-CS-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="18" customHeight="1">
+      <c r="A71" s="100" t="n"/>
+      <c r="B71" s="100" t="n"/>
+      <c r="C71" s="80" t="inlineStr">
+        <is>
+          <t>src/test/java/vn/uth/careercompass/admin/web/CounselorTemplateControllerTest.java</t>
+        </is>
+      </c>
+      <c r="D71" s="94" t="inlineStr">
+        <is>
+          <t>Lát cắt web (@WebMvcTest)</t>
+        </is>
+      </c>
+      <c r="E71" s="67" t="n">
+        <v>19</v>
+      </c>
+      <c r="F71" s="100" t="n"/>
+    </row>
+    <row r="72" ht="18" customHeight="1">
+      <c r="A72" s="79" t="inlineStr">
+        <is>
+          <t>FR8.4</t>
+        </is>
+      </c>
+      <c r="B72" s="66" t="inlineStr">
+        <is>
+          <t>Sắp xếp thứ tự ưu tiên node trong cùng tầng</t>
+        </is>
+      </c>
+      <c r="C72" s="80" t="inlineStr">
+        <is>
+          <t>src/test/java/vn/uth/careercompass/admin/service/CounselorTemplateServiceTest.java</t>
+        </is>
+      </c>
+      <c r="D72" s="94" t="inlineStr">
+        <is>
+          <t>Kiểm thử đơn vị (mock)</t>
+        </is>
+      </c>
+      <c r="E72" s="67" t="n">
+        <v>37</v>
+      </c>
+      <c r="F72" s="80" t="inlineStr">
+        <is>
+          <t>TC-CS-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="18" customHeight="1">
+      <c r="A73" s="100" t="n"/>
+      <c r="B73" s="100" t="n"/>
+      <c r="C73" s="80" t="inlineStr">
+        <is>
+          <t>src/test/java/vn/uth/careercompass/admin/web/CounselorTemplateControllerTest.java</t>
+        </is>
+      </c>
+      <c r="D73" s="94" t="inlineStr">
+        <is>
+          <t>Lát cắt web (@WebMvcTest)</t>
+        </is>
+      </c>
+      <c r="E73" s="67" t="n">
+        <v>19</v>
+      </c>
+      <c r="F73" s="100" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="97" t="inlineStr">
+        <is>
+          <t>TỔNG</t>
+        </is>
+      </c>
+      <c r="B74" s="97" t="inlineStr">
+        <is>
+          <t>26 yêu cầu chức năng</t>
+        </is>
+      </c>
+      <c r="C74" s="97" t="inlineStr">
+        <is>
+          <t>56 tệp kiểm thử trong src/test/java</t>
+        </is>
+      </c>
+      <c r="D74" s="98" t="inlineStr"/>
+      <c r="E74" s="99" t="n">
+        <v>536</v>
+      </c>
+      <c r="F74" s="98" t="inlineStr"/>
+    </row>
+    <row r="76" ht="28" customHeight="1">
+      <c r="A76" s="11" t="inlineStr">
+        <is>
+          <t>LƯU Ý KHI ĐỌC CỘT SỐ TEST: một lớp phục vụ nhiều yêu cầu sẽ xuất hiện ở nhiều dòng, nên cộng dồn cột này sẽ LỚN HƠN tổng thật. Dòng TỔNG lấy từ surefire-reports: 536 test trên 57 lớp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="26" customHeight="1">
+      <c r="A77" s="11" t="inlineStr">
+        <is>
+          <t>CÁCH CHẠY MỘT LỚP BẤT KỲ:   ./mvnw test -Dtest=TênLớpTest     Chạy nhiều lớp:   ./mvnw test -Dtest='LớpA,LớpB'     Chạy một phương thức:   ./mvnw test -Dtest='LớpA#tênPhươngThức'</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="64">
+    <mergeCell ref="F13:F15"/>
+    <mergeCell ref="A39:A53"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="A70:A71"/>
+    <mergeCell ref="A8:A12"/>
+    <mergeCell ref="B70:B71"/>
+    <mergeCell ref="F28:F30"/>
+    <mergeCell ref="F59:F60"/>
+    <mergeCell ref="F70:F71"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="A66:A67"/>
+    <mergeCell ref="A13:A15"/>
+    <mergeCell ref="B54:B56"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="B57:B58"/>
+    <mergeCell ref="F61:F63"/>
+    <mergeCell ref="F35:F36"/>
+    <mergeCell ref="A76:F76"/>
+    <mergeCell ref="B39:B53"/>
+    <mergeCell ref="F26:F27"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="F66:F67"/>
+    <mergeCell ref="F20:F23"/>
+    <mergeCell ref="F33:F34"/>
+    <mergeCell ref="F72:F73"/>
+    <mergeCell ref="B16:B18"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="A57:A58"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="F16:F18"/>
+    <mergeCell ref="F54:F56"/>
+    <mergeCell ref="B33:B34"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="B64:B65"/>
+    <mergeCell ref="A72:A73"/>
+    <mergeCell ref="F64:F65"/>
+    <mergeCell ref="F68:F69"/>
+    <mergeCell ref="A54:A56"/>
+    <mergeCell ref="A61:A63"/>
+    <mergeCell ref="A77:F77"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="A68:A69"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="B61:B63"/>
+    <mergeCell ref="F57:F58"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="F39:F53"/>
+    <mergeCell ref="B66:B67"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B8:B12"/>
+    <mergeCell ref="B13:B15"/>
+    <mergeCell ref="B20:B23"/>
+    <mergeCell ref="A64:A65"/>
+    <mergeCell ref="F8:F12"/>
+    <mergeCell ref="A59:A60"/>
+    <mergeCell ref="B59:B60"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="B28:B30"/>
+    <mergeCell ref="F24:F25"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -12199,6 +14062,807 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="62" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="86" t="inlineStr">
+        <is>
+          <t>RÀ SOÁT GIÁ TRỊ BIÊN TOÀN HỆ THỐNG — CÒN SÓT CHỖ NÀO KHÔNG?</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="40" customHeight="1">
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>Sheet 01 trình bày các bảng BVA đã làm. Sheet này trả lời câu khác: đã quét hết hệ thống chưa. Danh sách dựng bằng cách grep mọi ngưỡng số học trong src/main/java rồi đối chiếu với mọi ràng buộc có biên trong SRS. Mỗi dòng nói rõ đã áp BVA chưa, và nếu không áp thì vì sao — nói thẳng vẫn hơn im lặng.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Biến có biên</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Biên</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Vị trí trong mã nguồn</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Ràng buộc trong SRS</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Trạng thái</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Lớp kiểm thử</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Nhận định</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="34" customHeight="1">
+      <c r="A5" s="102" t="inlineStr">
+        <is>
+          <t>Họ tên khi đăng ký</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>1 → 100 ký tự</t>
+        </is>
+      </c>
+      <c r="C5" s="89" t="inlineStr">
+        <is>
+          <t>RegisterFormDTO @Size(max = 100)</t>
+        </is>
+      </c>
+      <c r="D5" s="103" t="inlineStr">
+        <is>
+          <t>AC-6.1.x, bảng trường mục 4.6</t>
+        </is>
+      </c>
+      <c r="E5" s="104" t="inlineStr">
+        <is>
+          <t>Đã áp dụng</t>
+        </is>
+      </c>
+      <c r="F5" s="89" t="inlineStr">
+        <is>
+          <t>RegisterStandardBvaTest, RegisterFormDTOBvaTest</t>
+        </is>
+      </c>
+      <c r="G5" s="89" t="inlineStr">
+        <is>
+          <t>Bảng 1, 2, 3 của sheet 01 — Standard 4n+1 và Robustness 6n+1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="34" customHeight="1">
+      <c r="A6" s="102" t="inlineStr">
+        <is>
+          <t>Email khi đăng ký</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>6 → 150 ký tự</t>
+        </is>
+      </c>
+      <c r="C6" s="89" t="inlineStr">
+        <is>
+          <t>RegisterFormDTO @Size(min = 6, max = 150)</t>
+        </is>
+      </c>
+      <c r="D6" s="103" t="inlineStr">
+        <is>
+          <t>AC-6.1.x</t>
+        </is>
+      </c>
+      <c r="E6" s="104" t="inlineStr">
+        <is>
+          <t>Đã áp dụng</t>
+        </is>
+      </c>
+      <c r="F6" s="89" t="inlineStr">
+        <is>
+          <t>RegisterStandardBvaTest, RegisterFormDTOBvaTest</t>
+        </is>
+      </c>
+      <c r="G6" s="89" t="inlineStr">
+        <is>
+          <t>Cùng ba bảng trên. min = 6 là email ngắn nhất có thật: a@b.co.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="34" customHeight="1">
+      <c r="A7" s="102" t="inlineStr">
+        <is>
+          <t>Mật khẩu khi đăng ký</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>6 → 30 ký tự</t>
+        </is>
+      </c>
+      <c r="C7" s="89" t="inlineStr">
+        <is>
+          <t>RegisterFormDTO @Size(min = 6, max = 30)</t>
+        </is>
+      </c>
+      <c r="D7" s="103" t="inlineStr">
+        <is>
+          <t>AC-6.1.3 (nêu đích danh 5/6/30/31)</t>
+        </is>
+      </c>
+      <c r="E7" s="104" t="inlineStr">
+        <is>
+          <t>Đã áp dụng</t>
+        </is>
+      </c>
+      <c r="F7" s="89" t="inlineStr">
+        <is>
+          <t>RegisterStandardBvaTest, RegisterFormDTOBvaTest</t>
+        </is>
+      </c>
+      <c r="G7" s="89" t="inlineStr">
+        <is>
+          <t>AC-6.1.3 yêu cầu đúng bốn điểm 5/6/30/31 — đã phủ đủ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="34" customHeight="1">
+      <c r="A8" s="102" t="inlineStr">
+        <is>
+          <t>Dung lượng tệp bảng điểm</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>0 → 10 MB</t>
+        </is>
+      </c>
+      <c r="C8" s="89" t="inlineStr">
+        <is>
+          <t>OnboardingService:48  file.getSize() &gt; 10*1024*1024</t>
+        </is>
+      </c>
+      <c r="D8" s="103" t="inlineStr">
+        <is>
+          <t>AC-1.3.3</t>
+        </is>
+      </c>
+      <c r="E8" s="104" t="inlineStr">
+        <is>
+          <t>Đã áp dụng</t>
+        </is>
+      </c>
+      <c r="F8" s="89" t="inlineStr">
+        <is>
+          <t>OnboardingFileSizeBvaTest</t>
+        </is>
+      </c>
+      <c r="G8" s="89" t="inlineStr">
+        <is>
+          <t>Bảng 3b sheet 01. Trường hợp n = 1 biến, và là chỗ duy nhất lộ ra giới hạn của công thức: Robustness cho 6n+1 = 7 case nhưng min− = −1 byte không tồn tại.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="44" customHeight="1">
+      <c r="A9" s="102" t="inlineStr">
+        <is>
+          <t>Mật khẩu ở BA đường đặt</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>6 → 30 ký tự VÀ ≤ 72 byte</t>
+        </is>
+      </c>
+      <c r="C9" s="89" t="inlineStr">
+        <is>
+          <t>PasswordPolicy  ·  AuthController:register/resetPassword  ·  ProfileController:changePassword</t>
+        </is>
+      </c>
+      <c r="D9" s="103" t="inlineStr">
+        <is>
+          <t>AC-6.1.3 (mới chỉ nói ký tự)</t>
+        </is>
+      </c>
+      <c r="E9" s="105" t="inlineStr">
+        <is>
+          <t>Mới bổ sung</t>
+        </is>
+      </c>
+      <c r="F9" s="89" t="inlineStr">
+        <is>
+          <t>PasswordPolicyBvaTest</t>
+        </is>
+      </c>
+      <c r="G9" s="89" t="inlineStr">
+        <is>
+          <t>DEF-013. Trước đây chỉ đường ĐĂNG KÝ có biên trên; đặt lại và đổi mật khẩu chỉ kiểm &lt; 6, không có max. Nặng hơn: @Size đếm KÝ TỰ còn BCrypt giới hạn 72 BYTE — 25 ký tự tiếng Việt có dấu là 75 byte, lọt validation rồi vỡ ở tầng mã hoá.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="44" customHeight="1">
+      <c r="A10" s="102" t="inlineStr">
+        <is>
+          <t>Hạn dùng token đặt lại mật khẩu</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>30 phút</t>
+        </is>
+      </c>
+      <c r="C10" s="89" t="inlineStr">
+        <is>
+          <t>PasswordResetService:40 plusMinutes(30)  ·  PasswordResetToken:34 isAfter</t>
+        </is>
+      </c>
+      <c r="D10" s="103" t="inlineStr">
+        <is>
+          <t>FR6.1, NFR-S07</t>
+        </is>
+      </c>
+      <c r="E10" s="105" t="inlineStr">
+        <is>
+          <t>Mới bổ sung</t>
+        </is>
+      </c>
+      <c r="F10" s="89" t="inlineStr">
+        <is>
+          <t>TokenExpiryBvaTest</t>
+        </is>
+      </c>
+      <c r="G10" s="89" t="inlineStr">
+        <is>
+          <t>Sheet 03b và 04b đã có bảng quyết định và chuyển trạng thái cho token, nhưng chỉ dùng hai mốc cách biên rất xa (±1 phút, +30 phút). Biên thật nằm ở phép so sánh isAfter — nghiêm ngặt, nên đúng thời điểm hết hạn vẫn còn hiệu lực.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="34" customHeight="1">
+      <c r="A11" s="102" t="inlineStr">
+        <is>
+          <t>Độ dài mô tả tin tuyển dụng</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>3.900 ký tự (cột VARCHAR(4000))</t>
+        </is>
+      </c>
+      <c r="C11" s="89" t="inlineStr">
+        <is>
+          <t>ScraperService:38 MAX_DESC  ·  :107 cap(raw, MAX_DESC)</t>
+        </is>
+      </c>
+      <c r="D11" s="103" t="inlineStr">
+        <is>
+          <t>AC-4.1.4</t>
+        </is>
+      </c>
+      <c r="E11" s="105" t="inlineStr">
+        <is>
+          <t>Mới bổ sung</t>
+        </is>
+      </c>
+      <c r="F11" s="89" t="inlineStr">
+        <is>
+          <t>ScraperServiceTest</t>
+        </is>
+      </c>
+      <c r="G11" s="89" t="inlineStr">
+        <is>
+          <t>Có AC riêng trong SRS và đụng trần cột CSDL. Tác vụ cào chạy nền lúc 02:00 nên nếu tràn thì lỗi chỉ nằm trong log, không ai thấy cho tới khi trang trống.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="34" customHeight="1">
+      <c r="A12" s="102" t="inlineStr">
+        <is>
+          <t>Độ dài tiêu đề tin tuyển dụng</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>255 ký tự</t>
+        </is>
+      </c>
+      <c r="C12" s="89" t="inlineStr">
+        <is>
+          <t>ScraperService:107 cap(title, 255)</t>
+        </is>
+      </c>
+      <c r="D12" s="103" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E12" s="104" t="inlineStr">
+        <is>
+          <t>Đã áp dụng</t>
+        </is>
+      </c>
+      <c r="F12" s="89" t="inlineStr">
+        <is>
+          <t>ScraperServiceTest</t>
+        </is>
+      </c>
+      <c r="G12" s="89" t="inlineStr">
+        <is>
+          <t>Đã có sẵn một phép kiểm biên trước đợt rà soát này.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="34" customHeight="1">
+      <c r="A13" s="102" t="inlineStr">
+        <is>
+          <t>Số lần thử lại khi gọi LLM</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>4 lần</t>
+        </is>
+      </c>
+      <c r="C13" s="89" t="inlineStr">
+        <is>
+          <t>LlmClient:41  for (attempt = 1; attempt &lt;= 4)</t>
+        </is>
+      </c>
+      <c r="D13" s="103" t="inlineStr">
+        <is>
+          <t>FR1.2, NFR-P02</t>
+        </is>
+      </c>
+      <c r="E13" s="104" t="inlineStr">
+        <is>
+          <t>Đã áp dụng</t>
+        </is>
+      </c>
+      <c r="F13" s="89" t="inlineStr">
+        <is>
+          <t>LlmClientTest</t>
+        </is>
+      </c>
+      <c r="G13" s="89" t="inlineStr">
+        <is>
+          <t>Miền rời rạc rất nhỏ nên phủ được TOÀN BỘ: 1 lần (thành công ngay), 2 lần (lỗi rồi thành công), 4 lần (hỏng suốt), và 1 lần với lỗi 400 không được thử lại.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="34" customHeight="1">
+      <c r="A14" s="102" t="inlineStr">
+        <is>
+          <t>Tầng của node kỹ năng</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>tier ≤ 1, = 2, ≥ 3</t>
+        </is>
+      </c>
+      <c r="C14" s="89" t="inlineStr">
+        <is>
+          <t>RoadmapService:87, :131</t>
+        </is>
+      </c>
+      <c r="D14" s="103" t="inlineStr">
+        <is>
+          <t>FR2.2, AC-2.2.x</t>
+        </is>
+      </c>
+      <c r="E14" s="106" t="inlineStr">
+        <is>
+          <t>Không áp dụng</t>
+        </is>
+      </c>
+      <c r="F14" s="89" t="inlineStr">
+        <is>
+          <t>RoadmapServiceTest + sheet B2 (MC/DC)</t>
+        </is>
+      </c>
+      <c r="G14" s="89" t="inlineStr">
+        <is>
+          <t>Miền chỉ có ba lớp hành vi và chúng khác nhau về LOGIC chứ không về độ lớn, nên bảng tổ hợp điều kiện MC/DC ở sheet B2 mô tả đúng bản chất hơn BVA. Vẫn phủ 100% nhánh.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="44" customHeight="1">
+      <c r="A15" s="102" t="inlineStr">
+        <is>
+          <t>Độ dài tiêu đề phiên chat</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>cắt ở 60 ký tự</t>
+        </is>
+      </c>
+      <c r="C15" s="89" t="inlineStr">
+        <is>
+          <t>MentorService:52</t>
+        </is>
+      </c>
+      <c r="D15" s="103" t="inlineStr">
+        <is>
+          <t>AC-1.1.4</t>
+        </is>
+      </c>
+      <c r="E15" s="106" t="inlineStr">
+        <is>
+          <t>Không áp dụng</t>
+        </is>
+      </c>
+      <c r="F15" s="89" t="inlineStr">
+        <is>
+          <t>MentorServiceTest</t>
+        </is>
+      </c>
+      <c r="G15" s="89" t="inlineStr">
+        <is>
+          <t>Biên CẮT chứ không phải biên CHẤP NHẬN/TỪ CHỐI: qua 60 ký tự không bị từ chối mà chỉ bị rút gọn để hiển thị. Sai một ký tự ở đây không gây hỏng nghiệp vụ nào. AC-1.1.4 chỉ yêu cầu tiêu đề khác 'Cuộc trò chuyện mới', đã có phép kiểm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="34" customHeight="1">
+      <c r="A16" s="102" t="inlineStr">
+        <is>
+          <t>Độ dài văn bản bảng điểm gửi AI</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>cắt ở 6.000 ký tự</t>
+        </is>
+      </c>
+      <c r="C16" s="89" t="inlineStr">
+        <is>
+          <t>TranscriptAnalysisService:32</t>
+        </is>
+      </c>
+      <c r="D16" s="103" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E16" s="106" t="inlineStr">
+        <is>
+          <t>Không áp dụng</t>
+        </is>
+      </c>
+      <c r="F16" s="89" t="inlineStr">
+        <is>
+          <t>TranscriptAnalysisServiceTest</t>
+        </is>
+      </c>
+      <c r="G16" s="89" t="inlineStr">
+        <is>
+          <t>Biên cắt nội bộ để tiết kiệm token của mô hình, không có yêu cầu nào trong SRS ràng buộc con số này và không đụng trần cột CSDL.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="34" customHeight="1">
+      <c r="A17" s="102" t="inlineStr">
+        <is>
+          <t>Độ dài ngữ cảnh README gửi AI</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>cắt ở 3.000 / trích 200 ký tự</t>
+        </is>
+      </c>
+      <c r="C17" s="89" t="inlineStr">
+        <is>
+          <t>PortfolioService:243, :249</t>
+        </is>
+      </c>
+      <c r="D17" s="103" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E17" s="106" t="inlineStr">
+        <is>
+          <t>Không áp dụng</t>
+        </is>
+      </c>
+      <c r="F17" s="89" t="inlineStr">
+        <is>
+          <t>PortfolioServiceTest</t>
+        </is>
+      </c>
+      <c r="G17" s="89" t="inlineStr">
+        <is>
+          <t>Cùng lý do trên: biên cắt nội bộ, không phải ràng buộc nghiệp vụ.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="44" customHeight="1">
+      <c r="A18" s="102" t="inlineStr">
+        <is>
+          <t>Số tài liệu học mỗi node</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>≥ 2</t>
+        </is>
+      </c>
+      <c r="C18" s="89" t="inlineStr">
+        <is>
+          <t>(không cưỡng chế trong mã nguồn)</t>
+        </is>
+      </c>
+      <c r="D18" s="103" t="inlineStr">
+        <is>
+          <t>AC-2.3.1, AC-2.3.3, BR-61</t>
+        </is>
+      </c>
+      <c r="E18" s="106" t="inlineStr">
+        <is>
+          <t>Không áp dụng</t>
+        </is>
+      </c>
+      <c r="F18" s="89" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G18" s="89" t="inlineStr">
+        <is>
+          <t>KHÔNG kiểm được bằng BVA vì mã nguồn KHÔNG cưỡng chế quy tắc này — hệ thống cho lưu node có 0 hoặc 1 tài liệu. Đây là khoảng trống HIỆN THỰC chứ không phải khoảng trống kiểm thử; ghi nhận để nhóm xử lý sau.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="34" customHeight="1">
+      <c r="A19" s="102" t="inlineStr">
+        <is>
+          <t>Độ dài URL tài nguyên học</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>≤ 500 ký tự</t>
+        </is>
+      </c>
+      <c r="C19" s="89" t="inlineStr">
+        <is>
+          <t>(không cưỡng chế trong mã nguồn)</t>
+        </is>
+      </c>
+      <c r="D19" s="103" t="inlineStr">
+        <is>
+          <t>AC-2.3.2</t>
+        </is>
+      </c>
+      <c r="E19" s="106" t="inlineStr">
+        <is>
+          <t>Không áp dụng</t>
+        </is>
+      </c>
+      <c r="F19" s="89" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="89" t="inlineStr">
+        <is>
+          <t>Cùng tình trạng: SRS nêu giới hạn nhưng mã nguồn chưa kiểm, nên chưa có biên để kiểm thử. Ghi nhận cùng nhóm với dòng trên.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="34" customHeight="1">
+      <c r="A20" s="102" t="inlineStr">
+        <is>
+          <t>Độ dài slug hồ sơ công khai</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>≤ 120 ký tự</t>
+        </is>
+      </c>
+      <c r="C20" s="89" t="inlineStr">
+        <is>
+          <t>PortfolioService:256 (base + 6 ký tự UUID)</t>
+        </is>
+      </c>
+      <c r="D20" s="103" t="inlineStr">
+        <is>
+          <t>Bảng CSDL mục 8</t>
+        </is>
+      </c>
+      <c r="E20" s="106" t="inlineStr">
+        <is>
+          <t>Không áp dụng</t>
+        </is>
+      </c>
+      <c r="F20" s="89" t="inlineStr">
+        <is>
+          <t>PortfolioServiceTest</t>
+        </is>
+      </c>
+      <c r="G20" s="89" t="inlineStr">
+        <is>
+          <t>Slug do hệ thống sinh chứ người dùng không nhập, và độ dài bị chặn bởi tên repository của GitHub (tối đa 100). Không có đầu vào nào đẩy tới biên.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="34" customHeight="1">
+      <c r="A21" s="102" t="inlineStr">
+        <is>
+          <t>Ngưỡng thời gian phản hồi</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>2s / 15s / 30s / 5s</t>
+        </is>
+      </c>
+      <c r="C21" s="89" t="inlineStr">
+        <is>
+          <t>(không có trong mã nguồn)</t>
+        </is>
+      </c>
+      <c r="D21" s="103" t="inlineStr">
+        <is>
+          <t>NFR-P01 → NFR-P04</t>
+        </is>
+      </c>
+      <c r="E21" s="106" t="inlineStr">
+        <is>
+          <t>Không áp dụng</t>
+        </is>
+      </c>
+      <c r="F21" s="89" t="inlineStr">
+        <is>
+          <t>Postman — phép kiểm responseTime</t>
+        </is>
+      </c>
+      <c r="G21" s="89" t="inlineStr">
+        <is>
+          <t>Là ngưỡng HIỆU NĂNG đo trên hệ thống đang chạy, không phải biên của một tham số đầu vào. Kiểm ở tầng Postman đúng chỗ hơn; BVA đơn vị không nói được gì.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="90" t="inlineStr">
+        <is>
+          <t>TỔNG</t>
+        </is>
+      </c>
+      <c r="B22" s="15" t="inlineStr">
+        <is>
+          <t>17 biên</t>
+        </is>
+      </c>
+      <c r="C22" s="91" t="inlineStr"/>
+      <c r="D22" s="91" t="inlineStr"/>
+      <c r="E22" s="107" t="inlineStr">
+        <is>
+          <t>6 đã áp · 3 mới · 8 không áp</t>
+        </is>
+      </c>
+      <c r="F22" s="91" t="inlineStr"/>
+      <c r="G22" s="91" t="inlineStr"/>
+    </row>
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="108" t="inlineStr">
+        <is>
+          <t>KẾT LUẬN: quét được 17 biên trong toàn hệ thống. 6 biên đã có BVA từ trước, 3 biên vừa bổ sung sau đợt rà soát này, 8 biên cố ý không áp và đã ghi rõ lý do ở cột cuối.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="109" t="inlineStr">
+        <is>
+          <t>BA LÝ DO KHIẾN MỘT BIÊN KHÔNG ĐÁNG ÁP BVA — dùng để trả lời khi bị hỏi:</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="40" customHeight="1">
+      <c r="A26" s="110" t="inlineStr">
+        <is>
+          <t>1. Biên CẮT chứ không phải biên CHẤP NHẬN</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="n"/>
+      <c r="C26" s="89" t="inlineStr">
+        <is>
+          <t>Vượt biên không bị từ chối mà chỉ bị rút gọn (tiêu đề chat 60 ký tự, ngữ cảnh README 3.000 ký tự). Không có hành vi nào lật ở biên nên không có lỗi lệch một đơn vị để bắt. Ngoại lệ là mô tả tin tuyển dụng: nó đụng trần cột CSDL nên vượt biên là hỏng thật — vì vậy dòng đó VẪN được áp BVA.</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="n"/>
+      <c r="E26" s="8" t="n"/>
+      <c r="F26" s="8" t="n"/>
+      <c r="G26" s="9" t="n"/>
+    </row>
+    <row r="27" ht="40" customHeight="1">
+      <c r="A27" s="110" t="inlineStr">
+        <is>
+          <t>2. Miền phân biệt bằng LOGIC chứ không bằng độ lớn</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="n"/>
+      <c r="C27" s="89" t="inlineStr">
+        <is>
+          <t>Tầng node chỉ có ba lớp hành vi (≤1, =2, ≥3) và khác nhau ở điều kiện mở khoá chứ không ở chỗ 'gần biên'. Bảng tổ hợp điều kiện MC/DC mô tả đúng bản chất hơn.</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="n"/>
+      <c r="E27" s="8" t="n"/>
+      <c r="F27" s="8" t="n"/>
+      <c r="G27" s="9" t="n"/>
+    </row>
+    <row r="28" ht="40" customHeight="1">
+      <c r="A28" s="110" t="inlineStr">
+        <is>
+          <t>3. Mã nguồn chưa cưỡng chế ràng buộc</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="n"/>
+      <c r="C28" s="89" t="inlineStr">
+        <is>
+          <t>SRS nêu 'mỗi node ≥ 2 tài liệu' và 'URL ≤ 500 ký tự' nhưng mã nguồn không kiểm, nên chưa tồn tại biên để kiểm thử. Đây là khoảng trống HIỆN THỰC, không phải khoảng trống kiểm thử — đã ghi nhận để xử lý sau.</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="n"/>
+      <c r="E28" s="8" t="n"/>
+      <c r="F28" s="8" t="n"/>
+      <c r="G28" s="9" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="A24:G24"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C26:G26"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/BaoCao-KiemThu-CareerCompass.xlsx
+++ b/BaoCao-KiemThu-CareerCompass.xlsx
@@ -1152,6 +1152,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1581,6 +1582,7 @@
       <c r="G17" s="8" t="n"/>
       <c r="H17" s="9" t="n"/>
     </row>
+    <row r="18"/>
     <row r="19" ht="24" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
@@ -1631,12 +1633,12 @@
       </c>
       <c r="C21" s="63" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>+30,8 điểm</t>
+          <t>+36,8 điểm</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
@@ -1660,12 +1662,12 @@
       </c>
       <c r="C22" s="63" t="inlineStr">
         <is>
-          <t>85,9%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>+37,7 điểm</t>
+          <t>+42,2 điểm</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
@@ -1689,12 +1691,12 @@
       </c>
       <c r="C23" s="63" t="inlineStr">
         <is>
-          <t>85,2%</t>
+          <t>88,5%</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>+31,8 điểm</t>
+          <t>+35,1 điểm</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -1718,12 +1720,12 @@
       </c>
       <c r="C24" s="63" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>+27,3 điểm</t>
+          <t>+28,6 điểm</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
@@ -1734,6 +1736,7 @@
       <c r="G24" s="8" t="n"/>
       <c r="H24" s="9" t="n"/>
     </row>
+    <row r="25"/>
     <row r="26" ht="24" customHeight="1">
       <c r="A26" s="3" t="inlineStr">
         <is>
@@ -1783,7 +1786,7 @@
         </is>
       </c>
       <c r="C28" s="6" t="n">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>0</v>
@@ -1846,24 +1849,25 @@
       <c r="G30" s="8" t="n"/>
       <c r="H30" s="9" t="n"/>
     </row>
+    <row r="31"/>
     <row r="32" ht="24" customHeight="1">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t>Mười hai khiếm khuyết được phát hiện và đều đã khắc phục kèm test hồi quy. Chi tiết ở sheet 07. Khiem khuyet.</t>
+          <t>Mười ba khiếm khuyết được phát hiện và đều đã khắc phục kèm test hồi quy. Chi tiết ở sheet 07. Khiem khuyet.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="F21:H21"/>
     <mergeCell ref="F8:H8"/>
     <mergeCell ref="F17:H17"/>
     <mergeCell ref="F23:H23"/>
+    <mergeCell ref="F22:H22"/>
     <mergeCell ref="F28:H28"/>
-    <mergeCell ref="F22:H22"/>
     <mergeCell ref="F13:H13"/>
     <mergeCell ref="F30:H30"/>
     <mergeCell ref="F9:H9"/>
-    <mergeCell ref="F15:H15"/>
     <mergeCell ref="A26:H26"/>
     <mergeCell ref="F14:H14"/>
     <mergeCell ref="A32:H32"/>
@@ -1876,7 +1880,7 @@
     <mergeCell ref="A19:H19"/>
     <mergeCell ref="F12:H12"/>
     <mergeCell ref="F7:H7"/>
-    <mergeCell ref="F21:H21"/>
+    <mergeCell ref="F15:H15"/>
     <mergeCell ref="F24:H24"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3424,7 +3428,7 @@
     <row r="3" ht="44" customHeight="1">
       <c r="A3" s="64" t="inlineStr">
         <is>
-          <t>MỐC THỜI GIAN ĐO: các chỉ số ở sheet này được đo ngày 06/09/2026, ngay sau khi bổ sung phần kiểm thử hộp trắng — giữ nguyên để phép so sánh trước/sau còn ý nghĩa. Nhóm tiếp tục bổ sung test sau mốc đó, nên số liệu HIỆN TẠI (đo 16/09/2026) cao hơn: bao phủ dòng 78,6%, bao phủ nhánh 72,5%. Xem sheet "00. Tong quan" để biết trạng thái mới nhất.</t>
+          <t>MỐC THỜI GIAN ĐO: các chỉ số ở sheet này được đo ngày 06/09/2026, ngay sau khi bổ sung phần kiểm thử hộp trắng — giữ nguyên để phép so sánh trước/sau còn ý nghĩa. Nhóm tiếp tục bổ sung test sau mốc đó, nên số liệu HIỆN TẠI (đo 23/09/2026) cao hơn: bao phủ dòng 96,9%, bao phủ nhánh 90,4%. Xem sheet "00. Tong quan" để biết trạng thái mới nhất.</t>
         </is>
       </c>
     </row>
@@ -3994,7 +3998,7 @@
     <row r="3" ht="44" customHeight="1">
       <c r="A3" s="64" t="inlineStr">
         <is>
-          <t>MỐC THỜI GIAN ĐO: các chỉ số ở sheet này được đo ngày 06/09/2026, ngay sau khi bổ sung phần kiểm thử hộp trắng — giữ nguyên để phép so sánh trước/sau còn ý nghĩa. Nhóm tiếp tục bổ sung test sau mốc đó, nên số liệu HIỆN TẠI (đo 16/09/2026) cao hơn: bao phủ dòng 78,6%, bao phủ nhánh 72,5%. Xem sheet "00. Tong quan" để biết trạng thái mới nhất.</t>
+          <t>MỐC THỜI GIAN ĐO: các chỉ số ở sheet này được đo ngày 06/09/2026, ngay sau khi bổ sung phần kiểm thử hộp trắng — giữ nguyên để phép so sánh trước/sau còn ý nghĩa. Nhóm tiếp tục bổ sung test sau mốc đó, nên số liệu HIỆN TẠI (đo 23/09/2026) cao hơn: bao phủ dòng 96,9%, bao phủ nhánh 90,4%. Xem sheet "00. Tong quan" để biết trạng thái mới nhất.</t>
         </is>
       </c>
     </row>
@@ -8966,7 +8970,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -8993,6 +8997,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -9452,50 +9457,89 @@
     <row r="16" ht="78" customHeight="1">
       <c r="A16" s="10" t="inlineStr">
         <is>
+          <t>DEF-012</t>
+        </is>
+      </c>
+      <c r="B16" s="17" t="inlineStr">
+        <is>
+          <t>Cao</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Xoá người dùng chỉ dọn 2 trong 6 bảng có khoá ngoại tới users (users_skills và activity_logs), bỏ sót password_reset_tokens, mentor_sessions, skill_gap_reports và user_node_progress. Lệnh xoá vi phạm ràng buộc khoá ngoại và THẤT BẠI TRONG IM LẶNG: quản trị viên bấm xoá, trang tải lại, người dùng vẫn nguyên trong danh sách. Nặng hơn nữa, github_profiles trỏ tới người dùng bằng cột user_id kiểu Long chứ không phải quan hệ @ManyToOne nên KHÔNG có khoá ngoại — hồ sơ E-Portfolio trở thành mồ côi và trang chia sẻ công khai /p/{slug} vẫn trả HTTP 200, phơi tên tài khoản GitHub, danh sách repository, mô tả và phần tóm tắt do AI sinh của người đã bị xoá.</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Rà soát mã nguồn khi dọn tài khoản rác trên môi trường thật</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>Đối chiếu sáu thực thể khai @ManyToOne tới User với thân hàm deleteUser: chỉ khớp hai. Đọc PublicPortfolioController xác nhận trang công khai vẫn dựng được khi owner đã bị xoá — biến owner nhận null nhưng profile và repositories vẫn hiển thị.</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>ĐÃ SỬA</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>Dọn đủ tám bảng theo thứ tự đi từ bảng con lên bảng cha, kèm hồ sơ GitHub và danh sách repository của nó. Phiên chat dùng derived delete của Spring Data — nó NẠP thực thể rồi gọi em.remove() từng cái nên cascade khai trên chatMessages mới chạy; đổi sang @Query xoá hàng loạt là để lại tin nhắn mồ côi. Bốn phép kiểm mới trong AdminUserServiceTest khoá cả danh sách bảng lẫn THỨ TỰ gọi.</t>
+        </is>
+      </c>
+      <c r="H16" s="9" t="n"/>
+    </row>
+    <row r="17" ht="78" customHeight="1">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
           <t>DEF-013</t>
         </is>
       </c>
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B17" s="17" t="inlineStr">
         <is>
           <t>Trung bình</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>Biên độ dài mật khẩu không nhất quán giữa ba đường đặt mật khẩu, và đo sai đơn vị. Đăng ký dựa vào @Size(min = 6, max = 30) đếm KÝ TỰ; đặt lại và đổi mật khẩu chỉ kiểm length() &lt; 6, KHÔNG có giới hạn trên. Trong khi đó BCrypt giới hạn 72 BYTE và ném IllegalArgumentException khi vượt — mật khẩu 25 ký tự tiếng Việt có dấu là 75 byte, lọt qua kiểm tra hợp lệ rồi vỡ ở tầng mã hoá.</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>Giá trị biên — rà soát toàn hệ thống (sheet 10)</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>Ba hậu quả tái hiện được: đăng ký trả 400 kèm nguyên văn tiếng Anh "password cannot be more than 72 bytes" (vi phạm NFR-U01); đặt lại mật khẩu báo SAI rằng "link đã hết hạn" nên người dùng xin link mới mãi không xong; đổi mật khẩu cũng lộ thông điệp tiếng Anh. NFR-R03 vẫn đạt vì GlobalExceptionHandler đổi thành 400 chứ không phải 500.</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr">
+      <c r="F17" s="7" t="inlineStr">
         <is>
           <t>ĐÃ SỬA</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>Gom cả hai biên vào PasswordPolicy dùng chung cho ba đường, trả thông điệp tiếng Việt. PasswordPolicyBvaTest phủ 5 điểm chuẩn theo ký tự, 2 điểm Robustness, và biên 72 byte — biên mà mọi mật khẩu ASCII đều không bao giờ chạm tới nên ẩn rất lâu.</t>
         </is>
       </c>
-      <c r="H16" s="9" t="n"/>
-    </row>
-    <row r="17" ht="44" customHeight="1">
-      <c r="A17" s="11" t="inlineStr">
-        <is>
-          <t>Cả 12 khiếm khuyết đã được khắc phục và có test hồi quy đi kèm. Ba khiếm khuyết DEF-001, DEF-009 và DEF-010 đều do KIỂM THỬ GIAO DIỆN tìm ra — đây là tầng duy nhất chạm tới HTML nên là tầng duy nhất thấy được chúng; suốt thời gian đó test đơn vị và test API vẫn xanh. DEF-011 đáng chú ý theo cách ngược lại: test hộp trắng đã GHI ĐÚNG nguyên nhân từ trước nhưng lại chốt luôn hành vi lỗi bằng một khẳng định, nên bộ test vẫn xanh và khiếm khuyết nằm im. Phải tới khi dựng bảng quyết định — nơi mỗi cột buộc phải có một hành động xác định — nó mới bị buộc phải sửa. DEF-013 thì cho thấy giới hạn của chính phép phân tích biên: nhóm đã áp BVA cho mật khẩu từ đầu, nhưng đo bằng KÝ TỰ trong khi biên thật của BCrypt tính bằng BYTE. Áp đúng kỹ thuật mà sai đơn vị đo thì vẫn lọt. VỀ SỐ HIỆU BỊ NHẢY: DEF-012 có thật và không bị bỏ quên — AdminUserService.deleteUser chỉ dọn 2 trong 6 bảng đang tham chiếu tới người dùng, thiếu skill_gap_reports, user_node_progress, mentor_sessions và password_reset_tokens, nên việc xoá thất bại TRONG IM LẶNG. Nhóm quyết định chưa sửa trong kỳ này vì phải đụng tới thứ tự xoá của bốn bảng, và bảng này theo quy ước chỉ liệt kê khiếm khuyết ĐÃ khắc phục kèm test hồi quy.</t>
+      <c r="H17" s="9" t="n"/>
+    </row>
+    <row r="18" ht="44" customHeight="1">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>Cả 13 khiếm khuyết đã được khắc phục và có test hồi quy đi kèm. Ba khiếm khuyết DEF-001, DEF-009 và DEF-010 đều do KIỂM THỬ GIAO DIỆN tìm ra — đây là tầng duy nhất chạm tới HTML nên là tầng duy nhất thấy được chúng; suốt thời gian đó test đơn vị và test API vẫn xanh. DEF-011 đáng chú ý theo cách ngược lại: test hộp trắng đã GHI ĐÚNG nguyên nhân từ trước nhưng lại chốt luôn hành vi lỗi bằng một khẳng định, nên bộ test vẫn xanh và khiếm khuyết nằm im. Phải tới khi dựng bảng quyết định — nơi mỗi cột buộc phải có một hành động xác định — nó mới bị buộc phải sửa. DEF-013 thì cho thấy giới hạn của chính phép phân tích biên: nhóm đã áp BVA cho mật khẩu từ đầu, nhưng đo bằng KÝ TỰ trong khi biên thật của BCrypt tính bằng BYTE. Áp đúng kỹ thuật mà sai đơn vị đo thì vẫn lọt. DEF-012 là khiếm khuyết duy nhất KHÔNG do một kỹ thuật kiểm thử nào tìm ra, mà lộ ra trong lúc dọn tài khoản rác trên môi trường thật. Đáng suy nghĩ ở chỗ: bảng users_skills và activity_logs đều đã có phép kiểm xác nhận được dọn, và phép kiểm đó vẫn xanh suốt thời gian bốn bảng còn lại bị bỏ sót — vì nó chỉ khẳng định những gì hàm CÓ làm, không khẳng định những gì hàm PHẢI làm. Bản sửa đối chiếu ngược từ danh sách thực thể tham chiếu tới User thay vì từ thân hàm.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="14">
+    <mergeCell ref="A18:H18"/>
     <mergeCell ref="G12:H12"/>
     <mergeCell ref="G7:H7"/>
     <mergeCell ref="G16:H16"/>
@@ -9508,7 +9552,7 @@
     <mergeCell ref="G13:H13"/>
     <mergeCell ref="G8:H8"/>
     <mergeCell ref="G9:H9"/>
-    <mergeCell ref="A17:H17"/>
+    <mergeCell ref="G17:H17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10290,11 +10334,11 @@
         </is>
       </c>
       <c r="E26" s="6" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,5%</t>
         </is>
       </c>
     </row>
@@ -10323,7 +10367,7 @@
         </is>
       </c>
       <c r="E27" s="6" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
@@ -10477,11 +10521,11 @@
       <c r="C32" s="91" t="inlineStr"/>
       <c r="D32" s="91" t="inlineStr"/>
       <c r="E32" s="15" t="n">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="F32" s="15" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>96,7%</t>
         </is>
       </c>
     </row>
@@ -12814,7 +12858,7 @@
         </is>
       </c>
       <c r="E61" s="67" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F61" s="80" t="inlineStr">
         <is>
@@ -12880,7 +12924,7 @@
         </is>
       </c>
       <c r="E64" s="67" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F64" s="80" t="inlineStr">
         <is>
@@ -13116,14 +13160,14 @@
       </c>
       <c r="D74" s="98" t="inlineStr"/>
       <c r="E74" s="99" t="n">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="F74" s="98" t="inlineStr"/>
     </row>
     <row r="76" ht="28" customHeight="1">
       <c r="A76" s="11" t="inlineStr">
         <is>
-          <t>LƯU Ý KHI ĐỌC CỘT SỐ TEST: một lớp phục vụ nhiều yêu cầu sẽ xuất hiện ở nhiều dòng, nên cộng dồn cột này sẽ LỚN HƠN tổng thật. Dòng TỔNG lấy từ surefire-reports: 536 test trên 57 lớp.</t>
+          <t>LƯU Ý KHI ĐỌC CỘT SỐ TEST: một lớp phục vụ nhiều yêu cầu sẽ xuất hiện ở nhiều dòng, nên cộng dồn cột này sẽ LỚN HƠN tổng thật. Dòng TỔNG lấy từ surefire-reports: 539 test trên 57 lớp.</t>
         </is>
       </c>
     </row>

--- a/BaoCao-KiemThu-CareerCompass.xlsx
+++ b/BaoCao-KiemThu-CareerCompass.xlsx
@@ -1152,7 +1152,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1582,7 +1581,6 @@
       <c r="G17" s="8" t="n"/>
       <c r="H17" s="9" t="n"/>
     </row>
-    <row r="18"/>
     <row r="19" ht="24" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
@@ -1633,12 +1631,12 @@
       </c>
       <c r="C21" s="63" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>+36,8 điểm</t>
+          <t>+38,6 điểm</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
@@ -1662,12 +1660,12 @@
       </c>
       <c r="C22" s="63" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>+42,2 điểm</t>
+          <t>+46,6 điểm</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
@@ -1691,12 +1689,12 @@
       </c>
       <c r="C23" s="63" t="inlineStr">
         <is>
-          <t>88,5%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>+35,1 điểm</t>
+          <t>+40,4 điểm</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -1720,12 +1718,12 @@
       </c>
       <c r="C24" s="63" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>+28,6 điểm</t>
+          <t>+31,8 điểm</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
@@ -1736,7 +1734,6 @@
       <c r="G24" s="8" t="n"/>
       <c r="H24" s="9" t="n"/>
     </row>
-    <row r="25"/>
     <row r="26" ht="24" customHeight="1">
       <c r="A26" s="3" t="inlineStr">
         <is>
@@ -1786,7 +1783,7 @@
         </is>
       </c>
       <c r="C28" s="6" t="n">
-        <v>539</v>
+        <v>572</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>0</v>
@@ -1849,7 +1846,6 @@
       <c r="G30" s="8" t="n"/>
       <c r="H30" s="9" t="n"/>
     </row>
-    <row r="31"/>
     <row r="32" ht="24" customHeight="1">
       <c r="A32" s="11" t="inlineStr">
         <is>
@@ -1859,15 +1855,15 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="F21:H21"/>
     <mergeCell ref="F8:H8"/>
     <mergeCell ref="F17:H17"/>
     <mergeCell ref="F23:H23"/>
+    <mergeCell ref="F28:H28"/>
     <mergeCell ref="F22:H22"/>
-    <mergeCell ref="F28:H28"/>
     <mergeCell ref="F13:H13"/>
     <mergeCell ref="F30:H30"/>
     <mergeCell ref="F9:H9"/>
+    <mergeCell ref="F15:H15"/>
     <mergeCell ref="A26:H26"/>
     <mergeCell ref="F14:H14"/>
     <mergeCell ref="A32:H32"/>
@@ -1880,7 +1876,7 @@
     <mergeCell ref="A19:H19"/>
     <mergeCell ref="F12:H12"/>
     <mergeCell ref="F7:H7"/>
-    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="F21:H21"/>
     <mergeCell ref="F24:H24"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3428,7 +3424,7 @@
     <row r="3" ht="44" customHeight="1">
       <c r="A3" s="64" t="inlineStr">
         <is>
-          <t>MỐC THỜI GIAN ĐO: các chỉ số ở sheet này được đo ngày 06/09/2026, ngay sau khi bổ sung phần kiểm thử hộp trắng — giữ nguyên để phép so sánh trước/sau còn ý nghĩa. Nhóm tiếp tục bổ sung test sau mốc đó, nên số liệu HIỆN TẠI (đo 23/09/2026) cao hơn: bao phủ dòng 96,9%, bao phủ nhánh 90,4%. Xem sheet "00. Tong quan" để biết trạng thái mới nhất.</t>
+          <t>MỐC THỜI GIAN ĐO: các chỉ số ở sheet này được đo ngày 06/09/2026, ngay sau khi bổ sung phần kiểm thử hộp trắng — giữ nguyên để phép so sánh trước/sau còn ý nghĩa. Nhóm tiếp tục bổ sung test sau mốc đó, nên số liệu HIỆN TẠI (đo 23/09/2026) cao hơn: bao phủ dòng 98,7%, bao phủ nhánh 94,8%. Xem sheet "00. Tong quan" để biết trạng thái mới nhất.</t>
         </is>
       </c>
     </row>
@@ -3998,7 +3994,7 @@
     <row r="3" ht="44" customHeight="1">
       <c r="A3" s="64" t="inlineStr">
         <is>
-          <t>MỐC THỜI GIAN ĐO: các chỉ số ở sheet này được đo ngày 06/09/2026, ngay sau khi bổ sung phần kiểm thử hộp trắng — giữ nguyên để phép so sánh trước/sau còn ý nghĩa. Nhóm tiếp tục bổ sung test sau mốc đó, nên số liệu HIỆN TẠI (đo 23/09/2026) cao hơn: bao phủ dòng 96,9%, bao phủ nhánh 90,4%. Xem sheet "00. Tong quan" để biết trạng thái mới nhất.</t>
+          <t>MỐC THỜI GIAN ĐO: các chỉ số ở sheet này được đo ngày 06/09/2026, ngay sau khi bổ sung phần kiểm thử hộp trắng — giữ nguyên để phép so sánh trước/sau còn ý nghĩa. Nhóm tiếp tục bổ sung test sau mốc đó, nên số liệu HIỆN TẠI (đo 23/09/2026) cao hơn: bao phủ dòng 98,7%, bao phủ nhánh 94,8%. Xem sheet "00. Tong quan" để biết trạng thái mới nhất.</t>
         </is>
       </c>
     </row>
@@ -8997,7 +8993,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -9655,11 +9650,11 @@
         </is>
       </c>
       <c r="E6" s="6" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>100,0%</t>
         </is>
       </c>
     </row>
@@ -9686,11 +9681,11 @@
         </is>
       </c>
       <c r="E7" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>100,0%</t>
         </is>
       </c>
     </row>
@@ -9792,11 +9787,11 @@
         </is>
       </c>
       <c r="E10" s="6" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>100,0%</t>
         </is>
       </c>
     </row>
@@ -9959,11 +9954,11 @@
         </is>
       </c>
       <c r="E15" s="6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>97,4%</t>
         </is>
       </c>
     </row>
@@ -9990,11 +9985,11 @@
         </is>
       </c>
       <c r="E16" s="6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>98,1%</t>
         </is>
       </c>
     </row>
@@ -10087,11 +10082,11 @@
         </is>
       </c>
       <c r="E19" s="6" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>100,0%</t>
         </is>
       </c>
     </row>
@@ -10118,11 +10113,11 @@
         </is>
       </c>
       <c r="E20" s="6" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
     </row>
@@ -10199,11 +10194,11 @@
         </is>
       </c>
       <c r="E22" s="6" t="n">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>100,0%</t>
         </is>
       </c>
     </row>
@@ -10521,11 +10516,11 @@
       <c r="C32" s="91" t="inlineStr"/>
       <c r="D32" s="91" t="inlineStr"/>
       <c r="E32" s="15" t="n">
-        <v>539</v>
+        <v>572</v>
       </c>
       <c r="F32" s="15" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>98,7%</t>
         </is>
       </c>
     </row>
@@ -11632,7 +11627,7 @@
         </is>
       </c>
       <c r="E6" s="67" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F6" s="100" t="n"/>
     </row>
@@ -11658,7 +11653,7 @@
         </is>
       </c>
       <c r="E7" s="67" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F7" s="80" t="inlineStr">
         <is>
@@ -11896,7 +11891,7 @@
         </is>
       </c>
       <c r="E18" s="67" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F18" s="100" t="n"/>
     </row>
@@ -12132,7 +12127,7 @@
         </is>
       </c>
       <c r="E28" s="67" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F28" s="80" t="inlineStr">
         <is>
@@ -12198,7 +12193,7 @@
         </is>
       </c>
       <c r="E31" s="67" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F31" s="80" t="inlineStr">
         <is>
@@ -12306,7 +12301,7 @@
         </is>
       </c>
       <c r="E35" s="67" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="F35" s="80" t="inlineStr">
         <is>
@@ -12354,7 +12349,7 @@
         </is>
       </c>
       <c r="E37" s="67" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="F37" s="80" t="inlineStr">
         <is>
@@ -12634,7 +12629,7 @@
         </is>
       </c>
       <c r="E51" s="67" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F51" s="101" t="n"/>
     </row>
@@ -13155,19 +13150,19 @@
       </c>
       <c r="C74" s="97" t="inlineStr">
         <is>
-          <t>56 tệp kiểm thử trong src/test/java</t>
+          <t>57 tệp kiểm thử trong src/test/java</t>
         </is>
       </c>
       <c r="D74" s="98" t="inlineStr"/>
       <c r="E74" s="99" t="n">
-        <v>539</v>
+        <v>572</v>
       </c>
       <c r="F74" s="98" t="inlineStr"/>
     </row>
     <row r="76" ht="28" customHeight="1">
       <c r="A76" s="11" t="inlineStr">
         <is>
-          <t>LƯU Ý KHI ĐỌC CỘT SỐ TEST: một lớp phục vụ nhiều yêu cầu sẽ xuất hiện ở nhiều dòng, nên cộng dồn cột này sẽ LỚN HƠN tổng thật. Dòng TỔNG lấy từ surefire-reports: 539 test trên 57 lớp.</t>
+          <t>LƯU Ý KHI ĐỌC CỘT SỐ TEST: một lớp phục vụ nhiều yêu cầu sẽ xuất hiện ở nhiều dòng, nên cộng dồn cột này sẽ LỚN HƠN tổng thật. Dòng TỔNG lấy từ surefire-reports: 572 test trên 58 lớp.</t>
         </is>
       </c>
     </row>
